--- a/static/templates/tec02-A_template.xlsx
+++ b/static/templates/tec02-A_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\diseño-afk\static\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{994F8249-5572-444B-B461-380E4E2477DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A600D408-5D33-4F97-9C4D-AE3485880350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>CORPORACION NACIONAL DEL COBRE DE CHILE</t>
   </si>
@@ -133,13 +133,16 @@
     <t>ANTECEDENTES ACADEMICOS</t>
   </si>
   <si>
-    <t>Nombre, Fecha y Firma del Profesional</t>
-  </si>
-  <si>
     <t>NOTAS:</t>
   </si>
   <si>
     <t>1) El CV debe señalar en forma ordenada y cronológica, los proyectos en que ha participado, su cargo en éstos, y las características relevantes del proyecto: Plazo, Monto, Cantidades de obra, fechas, mandante, descripción general.</t>
+  </si>
+  <si>
+    <t>Nombre y Apellido</t>
+  </si>
+  <si>
+    <t>Firma</t>
   </si>
 </sst>
 </file>
@@ -149,7 +152,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,6 +214,17 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -238,7 +252,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="54">
+  <borders count="49">
     <border>
       <left/>
       <right/>
@@ -665,53 +679,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -740,14 +707,16 @@
       <left/>
       <right/>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -851,11 +820,69 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -865,74 +892,21 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1257,125 +1231,125 @@
     </row>
     <row r="3" spans="1:27" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
-      <c r="O3" s="36"/>
-      <c r="P3" s="36"/>
-      <c r="Q3" s="36"/>
-      <c r="R3" s="36"/>
-      <c r="S3" s="36"/>
-      <c r="T3" s="36"/>
-      <c r="U3" s="36"/>
-      <c r="V3" s="36"/>
-      <c r="W3" s="36"/>
-      <c r="X3" s="36"/>
-      <c r="Y3" s="36"/>
-      <c r="Z3" s="36"/>
-      <c r="AA3" s="37"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="62"/>
+      <c r="N3" s="62"/>
+      <c r="O3" s="62"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="62"/>
+      <c r="Y3" s="62"/>
+      <c r="Z3" s="62"/>
+      <c r="AA3" s="63"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
-      <c r="B4" s="38"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="36"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
-      <c r="S4" s="36"/>
-      <c r="T4" s="36"/>
-      <c r="U4" s="36"/>
-      <c r="V4" s="36"/>
-      <c r="W4" s="36"/>
-      <c r="X4" s="36"/>
-      <c r="Y4" s="36"/>
-      <c r="Z4" s="36"/>
-      <c r="AA4" s="37"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="62"/>
+      <c r="O4" s="62"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="62"/>
+      <c r="Y4" s="62"/>
+      <c r="Z4" s="62"/>
+      <c r="AA4" s="63"/>
     </row>
     <row r="5" spans="1:27" ht="20" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
-      <c r="S5" s="36"/>
-      <c r="T5" s="36"/>
-      <c r="U5" s="36"/>
-      <c r="V5" s="36"/>
-      <c r="W5" s="36"/>
-      <c r="X5" s="36"/>
-      <c r="Y5" s="36"/>
-      <c r="Z5" s="36"/>
-      <c r="AA5" s="37"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="62"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="62"/>
+      <c r="N5" s="62"/>
+      <c r="O5" s="62"/>
+      <c r="P5" s="62"/>
+      <c r="Q5" s="62"/>
+      <c r="R5" s="62"/>
+      <c r="S5" s="62"/>
+      <c r="T5" s="62"/>
+      <c r="U5" s="62"/>
+      <c r="V5" s="62"/>
+      <c r="W5" s="62"/>
+      <c r="X5" s="62"/>
+      <c r="Y5" s="62"/>
+      <c r="Z5" s="62"/>
+      <c r="AA5" s="63"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
-      <c r="S6" s="36"/>
-      <c r="T6" s="36"/>
-      <c r="U6" s="36"/>
-      <c r="V6" s="36"/>
-      <c r="W6" s="36"/>
-      <c r="X6" s="36"/>
-      <c r="Y6" s="36"/>
-      <c r="Z6" s="36"/>
-      <c r="AA6" s="37"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="62"/>
+      <c r="O6" s="62"/>
+      <c r="P6" s="62"/>
+      <c r="Q6" s="62"/>
+      <c r="R6" s="62"/>
+      <c r="S6" s="62"/>
+      <c r="T6" s="62"/>
+      <c r="U6" s="62"/>
+      <c r="V6" s="62"/>
+      <c r="W6" s="62"/>
+      <c r="X6" s="62"/>
+      <c r="Y6" s="62"/>
+      <c r="Z6" s="62"/>
+      <c r="AA6" s="63"/>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2"/>
@@ -1474,25 +1448,25 @@
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="42"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="42"/>
-      <c r="O10" s="42"/>
-      <c r="P10" s="42"/>
-      <c r="Q10" s="42"/>
-      <c r="R10" s="42"/>
-      <c r="S10" s="42"/>
-      <c r="T10" s="42"/>
-      <c r="U10" s="42"/>
-      <c r="V10" s="42"/>
-      <c r="W10" s="42"/>
-      <c r="X10" s="42"/>
-      <c r="Y10" s="42"/>
-      <c r="Z10" s="43"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="65"/>
+      <c r="J10" s="65"/>
+      <c r="K10" s="65"/>
+      <c r="L10" s="65"/>
+      <c r="M10" s="65"/>
+      <c r="N10" s="65"/>
+      <c r="O10" s="65"/>
+      <c r="P10" s="65"/>
+      <c r="Q10" s="65"/>
+      <c r="R10" s="65"/>
+      <c r="S10" s="65"/>
+      <c r="T10" s="65"/>
+      <c r="U10" s="65"/>
+      <c r="V10" s="65"/>
+      <c r="W10" s="65"/>
+      <c r="X10" s="65"/>
+      <c r="Y10" s="65"/>
+      <c r="Z10" s="66"/>
       <c r="AA10" s="11"/>
     </row>
     <row r="11" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1534,27 +1508,27 @@
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
-      <c r="K12" s="42"/>
-      <c r="L12" s="42"/>
-      <c r="M12" s="42"/>
-      <c r="N12" s="42"/>
-      <c r="O12" s="42"/>
-      <c r="P12" s="42"/>
-      <c r="Q12" s="42"/>
-      <c r="R12" s="42"/>
-      <c r="S12" s="42"/>
-      <c r="T12" s="43"/>
+      <c r="H12" s="70"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="65"/>
+      <c r="M12" s="65"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="65"/>
+      <c r="P12" s="65"/>
+      <c r="Q12" s="65"/>
+      <c r="R12" s="65"/>
+      <c r="S12" s="65"/>
+      <c r="T12" s="66"/>
       <c r="U12" s="13"/>
       <c r="V12" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="W12" s="44"/>
-      <c r="X12" s="42"/>
-      <c r="Y12" s="42"/>
-      <c r="Z12" s="43"/>
+      <c r="W12" s="71"/>
+      <c r="X12" s="65"/>
+      <c r="Y12" s="65"/>
+      <c r="Z12" s="66"/>
       <c r="AA12" s="15"/>
     </row>
     <row r="13" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1588,63 +1562,63 @@
     </row>
     <row r="14" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46"/>
-      <c r="N14" s="46"/>
-      <c r="O14" s="46"/>
-      <c r="P14" s="46"/>
-      <c r="Q14" s="46"/>
-      <c r="R14" s="46"/>
-      <c r="S14" s="46"/>
-      <c r="T14" s="46"/>
-      <c r="U14" s="46"/>
-      <c r="V14" s="46"/>
-      <c r="W14" s="46"/>
-      <c r="X14" s="46"/>
-      <c r="Y14" s="46"/>
-      <c r="Z14" s="46"/>
-      <c r="AA14" s="47"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="59"/>
+      <c r="J14" s="59"/>
+      <c r="K14" s="59"/>
+      <c r="L14" s="59"/>
+      <c r="M14" s="59"/>
+      <c r="N14" s="59"/>
+      <c r="O14" s="59"/>
+      <c r="P14" s="59"/>
+      <c r="Q14" s="59"/>
+      <c r="R14" s="59"/>
+      <c r="S14" s="59"/>
+      <c r="T14" s="59"/>
+      <c r="U14" s="59"/>
+      <c r="V14" s="59"/>
+      <c r="W14" s="59"/>
+      <c r="X14" s="59"/>
+      <c r="Y14" s="59"/>
+      <c r="Z14" s="59"/>
+      <c r="AA14" s="60"/>
     </row>
     <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
-      <c r="B15" s="48"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="49"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="49"/>
-      <c r="L15" s="49"/>
-      <c r="M15" s="49"/>
-      <c r="N15" s="49"/>
-      <c r="O15" s="49"/>
-      <c r="P15" s="49"/>
-      <c r="Q15" s="49"/>
-      <c r="R15" s="49"/>
-      <c r="S15" s="49"/>
-      <c r="T15" s="49"/>
-      <c r="U15" s="49"/>
-      <c r="V15" s="49"/>
-      <c r="W15" s="49"/>
-      <c r="X15" s="49"/>
-      <c r="Y15" s="49"/>
-      <c r="Z15" s="49"/>
-      <c r="AA15" s="50"/>
+      <c r="B15" s="67"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="68"/>
+      <c r="G15" s="68"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="68"/>
+      <c r="L15" s="68"/>
+      <c r="M15" s="68"/>
+      <c r="N15" s="68"/>
+      <c r="O15" s="68"/>
+      <c r="P15" s="68"/>
+      <c r="Q15" s="68"/>
+      <c r="R15" s="68"/>
+      <c r="S15" s="68"/>
+      <c r="T15" s="68"/>
+      <c r="U15" s="68"/>
+      <c r="V15" s="68"/>
+      <c r="W15" s="68"/>
+      <c r="X15" s="68"/>
+      <c r="Y15" s="68"/>
+      <c r="Z15" s="68"/>
+      <c r="AA15" s="69"/>
     </row>
     <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
@@ -1677,33 +1651,33 @@
     </row>
     <row r="17" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
-      <c r="B17" s="51" t="s">
+      <c r="B17" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="52"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="42"/>
-      <c r="K17" s="42"/>
-      <c r="L17" s="42"/>
-      <c r="M17" s="42"/>
-      <c r="N17" s="42"/>
-      <c r="O17" s="42"/>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="42"/>
-      <c r="R17" s="42"/>
-      <c r="S17" s="42"/>
-      <c r="T17" s="42"/>
-      <c r="U17" s="42"/>
-      <c r="V17" s="42"/>
-      <c r="W17" s="42"/>
-      <c r="X17" s="42"/>
-      <c r="Y17" s="42"/>
-      <c r="Z17" s="43"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="62"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="65"/>
+      <c r="K17" s="65"/>
+      <c r="L17" s="65"/>
+      <c r="M17" s="65"/>
+      <c r="N17" s="65"/>
+      <c r="O17" s="65"/>
+      <c r="P17" s="65"/>
+      <c r="Q17" s="65"/>
+      <c r="R17" s="65"/>
+      <c r="S17" s="65"/>
+      <c r="T17" s="65"/>
+      <c r="U17" s="65"/>
+      <c r="V17" s="65"/>
+      <c r="W17" s="65"/>
+      <c r="X17" s="65"/>
+      <c r="Y17" s="65"/>
+      <c r="Z17" s="66"/>
       <c r="AA17" s="24"/>
     </row>
     <row r="18" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1737,33 +1711,33 @@
     </row>
     <row r="19" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
-      <c r="B19" s="51" t="s">
+      <c r="B19" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="52"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="42"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="42"/>
-      <c r="O19" s="42"/>
-      <c r="P19" s="42"/>
-      <c r="Q19" s="42"/>
-      <c r="R19" s="42"/>
-      <c r="S19" s="42"/>
-      <c r="T19" s="42"/>
-      <c r="U19" s="42"/>
-      <c r="V19" s="42"/>
-      <c r="W19" s="42"/>
-      <c r="X19" s="42"/>
-      <c r="Y19" s="42"/>
-      <c r="Z19" s="43"/>
+      <c r="C19" s="62"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="65"/>
+      <c r="K19" s="65"/>
+      <c r="L19" s="65"/>
+      <c r="M19" s="65"/>
+      <c r="N19" s="65"/>
+      <c r="O19" s="65"/>
+      <c r="P19" s="65"/>
+      <c r="Q19" s="65"/>
+      <c r="R19" s="65"/>
+      <c r="S19" s="65"/>
+      <c r="T19" s="65"/>
+      <c r="U19" s="65"/>
+      <c r="V19" s="65"/>
+      <c r="W19" s="65"/>
+      <c r="X19" s="65"/>
+      <c r="Y19" s="65"/>
+      <c r="Z19" s="66"/>
       <c r="AA19" s="24"/>
     </row>
     <row r="20" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1797,33 +1771,33 @@
     </row>
     <row r="21" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
-      <c r="B21" s="51" t="s">
+      <c r="B21" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="42"/>
-      <c r="K21" s="42"/>
-      <c r="L21" s="42"/>
-      <c r="M21" s="42"/>
-      <c r="N21" s="42"/>
-      <c r="O21" s="42"/>
-      <c r="P21" s="42"/>
-      <c r="Q21" s="42"/>
-      <c r="R21" s="42"/>
-      <c r="S21" s="42"/>
-      <c r="T21" s="42"/>
-      <c r="U21" s="42"/>
-      <c r="V21" s="42"/>
-      <c r="W21" s="42"/>
-      <c r="X21" s="42"/>
-      <c r="Y21" s="42"/>
-      <c r="Z21" s="43"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="63"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="65"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="65"/>
+      <c r="M21" s="65"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="65"/>
+      <c r="P21" s="65"/>
+      <c r="Q21" s="65"/>
+      <c r="R21" s="65"/>
+      <c r="S21" s="65"/>
+      <c r="T21" s="65"/>
+      <c r="U21" s="65"/>
+      <c r="V21" s="65"/>
+      <c r="W21" s="65"/>
+      <c r="X21" s="65"/>
+      <c r="Y21" s="65"/>
+      <c r="Z21" s="66"/>
       <c r="AA21" s="24"/>
     </row>
     <row r="22" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1857,968 +1831,968 @@
     </row>
     <row r="23" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
-      <c r="B23" s="70" t="s">
+      <c r="B23" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="71"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="71"/>
-      <c r="H23" s="71"/>
-      <c r="I23" s="71"/>
-      <c r="J23" s="71"/>
-      <c r="K23" s="71"/>
-      <c r="L23" s="71"/>
-      <c r="M23" s="71"/>
-      <c r="N23" s="71"/>
-      <c r="O23" s="71"/>
-      <c r="P23" s="71"/>
-      <c r="Q23" s="71"/>
-      <c r="R23" s="71"/>
-      <c r="S23" s="71"/>
-      <c r="T23" s="71"/>
-      <c r="U23" s="71"/>
-      <c r="V23" s="71"/>
-      <c r="W23" s="71"/>
-      <c r="X23" s="71"/>
-      <c r="Y23" s="71"/>
-      <c r="Z23" s="71"/>
-      <c r="AA23" s="72"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="42"/>
+      <c r="L23" s="42"/>
+      <c r="M23" s="42"/>
+      <c r="N23" s="42"/>
+      <c r="O23" s="42"/>
+      <c r="P23" s="42"/>
+      <c r="Q23" s="42"/>
+      <c r="R23" s="42"/>
+      <c r="S23" s="42"/>
+      <c r="T23" s="42"/>
+      <c r="U23" s="42"/>
+      <c r="V23" s="42"/>
+      <c r="W23" s="42"/>
+      <c r="X23" s="42"/>
+      <c r="Y23" s="42"/>
+      <c r="Z23" s="42"/>
+      <c r="AA23" s="43"/>
     </row>
     <row r="24" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
-      <c r="B24" s="73"/>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="54"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="54"/>
-      <c r="J24" s="54"/>
-      <c r="K24" s="54"/>
-      <c r="L24" s="54"/>
-      <c r="M24" s="54"/>
-      <c r="N24" s="54"/>
-      <c r="O24" s="54"/>
-      <c r="P24" s="54"/>
-      <c r="Q24" s="54"/>
-      <c r="R24" s="54"/>
-      <c r="S24" s="54"/>
-      <c r="T24" s="54"/>
-      <c r="U24" s="54"/>
-      <c r="V24" s="54"/>
-      <c r="W24" s="54"/>
-      <c r="X24" s="54"/>
-      <c r="Y24" s="54"/>
-      <c r="Z24" s="54"/>
-      <c r="AA24" s="55"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="36"/>
+      <c r="J24" s="36"/>
+      <c r="K24" s="36"/>
+      <c r="L24" s="36"/>
+      <c r="M24" s="36"/>
+      <c r="N24" s="36"/>
+      <c r="O24" s="36"/>
+      <c r="P24" s="36"/>
+      <c r="Q24" s="36"/>
+      <c r="R24" s="36"/>
+      <c r="S24" s="36"/>
+      <c r="T24" s="36"/>
+      <c r="U24" s="36"/>
+      <c r="V24" s="36"/>
+      <c r="W24" s="36"/>
+      <c r="X24" s="36"/>
+      <c r="Y24" s="36"/>
+      <c r="Z24" s="36"/>
+      <c r="AA24" s="45"/>
     </row>
     <row r="25" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
-      <c r="B25" s="56"/>
-      <c r="C25" s="57"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="57"/>
-      <c r="K25" s="57"/>
-      <c r="L25" s="57"/>
-      <c r="M25" s="57"/>
-      <c r="N25" s="57"/>
-      <c r="O25" s="57"/>
-      <c r="P25" s="57"/>
-      <c r="Q25" s="57"/>
-      <c r="R25" s="57"/>
-      <c r="S25" s="57"/>
-      <c r="T25" s="57"/>
-      <c r="U25" s="57"/>
-      <c r="V25" s="57"/>
-      <c r="W25" s="57"/>
-      <c r="X25" s="57"/>
-      <c r="Y25" s="57"/>
-      <c r="Z25" s="57"/>
-      <c r="AA25" s="58"/>
+      <c r="B25" s="46"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="47"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="47"/>
+      <c r="K25" s="47"/>
+      <c r="L25" s="47"/>
+      <c r="M25" s="47"/>
+      <c r="N25" s="47"/>
+      <c r="O25" s="47"/>
+      <c r="P25" s="47"/>
+      <c r="Q25" s="47"/>
+      <c r="R25" s="47"/>
+      <c r="S25" s="47"/>
+      <c r="T25" s="47"/>
+      <c r="U25" s="47"/>
+      <c r="V25" s="47"/>
+      <c r="W25" s="47"/>
+      <c r="X25" s="47"/>
+      <c r="Y25" s="47"/>
+      <c r="Z25" s="47"/>
+      <c r="AA25" s="48"/>
     </row>
     <row r="26" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
-      <c r="B26" s="56"/>
-      <c r="C26" s="57"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="57"/>
-      <c r="K26" s="57"/>
-      <c r="L26" s="57"/>
-      <c r="M26" s="57"/>
-      <c r="N26" s="57"/>
-      <c r="O26" s="57"/>
-      <c r="P26" s="57"/>
-      <c r="Q26" s="57"/>
-      <c r="R26" s="57"/>
-      <c r="S26" s="57"/>
-      <c r="T26" s="57"/>
-      <c r="U26" s="57"/>
-      <c r="V26" s="57"/>
-      <c r="W26" s="57"/>
-      <c r="X26" s="57"/>
-      <c r="Y26" s="57"/>
-      <c r="Z26" s="57"/>
-      <c r="AA26" s="58"/>
+      <c r="B26" s="46"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="47"/>
+      <c r="J26" s="47"/>
+      <c r="K26" s="47"/>
+      <c r="L26" s="47"/>
+      <c r="M26" s="47"/>
+      <c r="N26" s="47"/>
+      <c r="O26" s="47"/>
+      <c r="P26" s="47"/>
+      <c r="Q26" s="47"/>
+      <c r="R26" s="47"/>
+      <c r="S26" s="47"/>
+      <c r="T26" s="47"/>
+      <c r="U26" s="47"/>
+      <c r="V26" s="47"/>
+      <c r="W26" s="47"/>
+      <c r="X26" s="47"/>
+      <c r="Y26" s="47"/>
+      <c r="Z26" s="47"/>
+      <c r="AA26" s="48"/>
     </row>
     <row r="27" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="57"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="57"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="57"/>
-      <c r="K27" s="57"/>
-      <c r="L27" s="57"/>
-      <c r="M27" s="57"/>
-      <c r="N27" s="57"/>
-      <c r="O27" s="57"/>
-      <c r="P27" s="57"/>
-      <c r="Q27" s="57"/>
-      <c r="R27" s="57"/>
-      <c r="S27" s="57"/>
-      <c r="T27" s="57"/>
-      <c r="U27" s="57"/>
-      <c r="V27" s="57"/>
-      <c r="W27" s="57"/>
-      <c r="X27" s="57"/>
-      <c r="Y27" s="57"/>
-      <c r="Z27" s="57"/>
-      <c r="AA27" s="58"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="47"/>
+      <c r="K27" s="47"/>
+      <c r="L27" s="47"/>
+      <c r="M27" s="47"/>
+      <c r="N27" s="47"/>
+      <c r="O27" s="47"/>
+      <c r="P27" s="47"/>
+      <c r="Q27" s="47"/>
+      <c r="R27" s="47"/>
+      <c r="S27" s="47"/>
+      <c r="T27" s="47"/>
+      <c r="U27" s="47"/>
+      <c r="V27" s="47"/>
+      <c r="W27" s="47"/>
+      <c r="X27" s="47"/>
+      <c r="Y27" s="47"/>
+      <c r="Z27" s="47"/>
+      <c r="AA27" s="48"/>
     </row>
     <row r="28" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
-      <c r="B28" s="56"/>
-      <c r="C28" s="57"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="57"/>
-      <c r="K28" s="57"/>
-      <c r="L28" s="57"/>
-      <c r="M28" s="57"/>
-      <c r="N28" s="57"/>
-      <c r="O28" s="57"/>
-      <c r="P28" s="57"/>
-      <c r="Q28" s="57"/>
-      <c r="R28" s="57"/>
-      <c r="S28" s="57"/>
-      <c r="T28" s="57"/>
-      <c r="U28" s="57"/>
-      <c r="V28" s="57"/>
-      <c r="W28" s="57"/>
-      <c r="X28" s="57"/>
-      <c r="Y28" s="57"/>
-      <c r="Z28" s="57"/>
-      <c r="AA28" s="58"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="47"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="47"/>
+      <c r="K28" s="47"/>
+      <c r="L28" s="47"/>
+      <c r="M28" s="47"/>
+      <c r="N28" s="47"/>
+      <c r="O28" s="47"/>
+      <c r="P28" s="47"/>
+      <c r="Q28" s="47"/>
+      <c r="R28" s="47"/>
+      <c r="S28" s="47"/>
+      <c r="T28" s="47"/>
+      <c r="U28" s="47"/>
+      <c r="V28" s="47"/>
+      <c r="W28" s="47"/>
+      <c r="X28" s="47"/>
+      <c r="Y28" s="47"/>
+      <c r="Z28" s="47"/>
+      <c r="AA28" s="48"/>
     </row>
     <row r="29" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
-      <c r="B29" s="56"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="57"/>
-      <c r="J29" s="57"/>
-      <c r="K29" s="57"/>
-      <c r="L29" s="57"/>
-      <c r="M29" s="57"/>
-      <c r="N29" s="57"/>
-      <c r="O29" s="57"/>
-      <c r="P29" s="57"/>
-      <c r="Q29" s="57"/>
-      <c r="R29" s="57"/>
-      <c r="S29" s="57"/>
-      <c r="T29" s="57"/>
-      <c r="U29" s="57"/>
-      <c r="V29" s="57"/>
-      <c r="W29" s="57"/>
-      <c r="X29" s="57"/>
-      <c r="Y29" s="57"/>
-      <c r="Z29" s="57"/>
-      <c r="AA29" s="58"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="47"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="47"/>
+      <c r="H29" s="47"/>
+      <c r="I29" s="47"/>
+      <c r="J29" s="47"/>
+      <c r="K29" s="47"/>
+      <c r="L29" s="47"/>
+      <c r="M29" s="47"/>
+      <c r="N29" s="47"/>
+      <c r="O29" s="47"/>
+      <c r="P29" s="47"/>
+      <c r="Q29" s="47"/>
+      <c r="R29" s="47"/>
+      <c r="S29" s="47"/>
+      <c r="T29" s="47"/>
+      <c r="U29" s="47"/>
+      <c r="V29" s="47"/>
+      <c r="W29" s="47"/>
+      <c r="X29" s="47"/>
+      <c r="Y29" s="47"/>
+      <c r="Z29" s="47"/>
+      <c r="AA29" s="48"/>
     </row>
     <row r="30" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
-      <c r="B30" s="56"/>
-      <c r="C30" s="57"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="57"/>
-      <c r="J30" s="57"/>
-      <c r="K30" s="57"/>
-      <c r="L30" s="57"/>
-      <c r="M30" s="57"/>
-      <c r="N30" s="57"/>
-      <c r="O30" s="57"/>
-      <c r="P30" s="57"/>
-      <c r="Q30" s="57"/>
-      <c r="R30" s="57"/>
-      <c r="S30" s="57"/>
-      <c r="T30" s="57"/>
-      <c r="U30" s="57"/>
-      <c r="V30" s="57"/>
-      <c r="W30" s="57"/>
-      <c r="X30" s="57"/>
-      <c r="Y30" s="57"/>
-      <c r="Z30" s="57"/>
-      <c r="AA30" s="58"/>
+      <c r="B30" s="46"/>
+      <c r="C30" s="47"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="47"/>
+      <c r="G30" s="47"/>
+      <c r="H30" s="47"/>
+      <c r="I30" s="47"/>
+      <c r="J30" s="47"/>
+      <c r="K30" s="47"/>
+      <c r="L30" s="47"/>
+      <c r="M30" s="47"/>
+      <c r="N30" s="47"/>
+      <c r="O30" s="47"/>
+      <c r="P30" s="47"/>
+      <c r="Q30" s="47"/>
+      <c r="R30" s="47"/>
+      <c r="S30" s="47"/>
+      <c r="T30" s="47"/>
+      <c r="U30" s="47"/>
+      <c r="V30" s="47"/>
+      <c r="W30" s="47"/>
+      <c r="X30" s="47"/>
+      <c r="Y30" s="47"/>
+      <c r="Z30" s="47"/>
+      <c r="AA30" s="48"/>
     </row>
     <row r="31" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
-      <c r="B31" s="74"/>
-      <c r="C31" s="68"/>
-      <c r="D31" s="68"/>
-      <c r="E31" s="68"/>
-      <c r="F31" s="68"/>
-      <c r="G31" s="68"/>
-      <c r="H31" s="68"/>
-      <c r="I31" s="68"/>
-      <c r="J31" s="68"/>
-      <c r="K31" s="68"/>
-      <c r="L31" s="68"/>
-      <c r="M31" s="68"/>
-      <c r="N31" s="68"/>
-      <c r="O31" s="68"/>
-      <c r="P31" s="68"/>
-      <c r="Q31" s="68"/>
-      <c r="R31" s="68"/>
-      <c r="S31" s="68"/>
-      <c r="T31" s="68"/>
-      <c r="U31" s="68"/>
-      <c r="V31" s="68"/>
-      <c r="W31" s="68"/>
-      <c r="X31" s="68"/>
-      <c r="Y31" s="68"/>
-      <c r="Z31" s="68"/>
-      <c r="AA31" s="75"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="39"/>
+      <c r="K31" s="39"/>
+      <c r="L31" s="39"/>
+      <c r="M31" s="39"/>
+      <c r="N31" s="39"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="39"/>
+      <c r="Q31" s="39"/>
+      <c r="R31" s="39"/>
+      <c r="S31" s="39"/>
+      <c r="T31" s="39"/>
+      <c r="U31" s="39"/>
+      <c r="V31" s="39"/>
+      <c r="W31" s="39"/>
+      <c r="X31" s="39"/>
+      <c r="Y31" s="39"/>
+      <c r="Z31" s="39"/>
+      <c r="AA31" s="50"/>
     </row>
     <row r="32" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
-      <c r="B32" s="76" t="s">
+      <c r="B32" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="77"/>
-      <c r="D32" s="77"/>
-      <c r="E32" s="77"/>
-      <c r="F32" s="77"/>
-      <c r="G32" s="77"/>
-      <c r="H32" s="77"/>
-      <c r="I32" s="77"/>
-      <c r="J32" s="77"/>
-      <c r="K32" s="77"/>
-      <c r="L32" s="77"/>
-      <c r="M32" s="77"/>
-      <c r="N32" s="77"/>
-      <c r="O32" s="77"/>
-      <c r="P32" s="77"/>
-      <c r="Q32" s="77"/>
-      <c r="R32" s="77"/>
-      <c r="S32" s="77"/>
-      <c r="T32" s="77"/>
-      <c r="U32" s="77"/>
-      <c r="V32" s="77"/>
-      <c r="W32" s="77"/>
-      <c r="X32" s="77"/>
-      <c r="Y32" s="77"/>
-      <c r="Z32" s="77"/>
-      <c r="AA32" s="78"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="52"/>
+      <c r="K32" s="52"/>
+      <c r="L32" s="52"/>
+      <c r="M32" s="52"/>
+      <c r="N32" s="52"/>
+      <c r="O32" s="52"/>
+      <c r="P32" s="52"/>
+      <c r="Q32" s="52"/>
+      <c r="R32" s="52"/>
+      <c r="S32" s="52"/>
+      <c r="T32" s="52"/>
+      <c r="U32" s="52"/>
+      <c r="V32" s="52"/>
+      <c r="W32" s="52"/>
+      <c r="X32" s="52"/>
+      <c r="Y32" s="52"/>
+      <c r="Z32" s="52"/>
+      <c r="AA32" s="53"/>
     </row>
     <row r="33" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
-      <c r="B33" s="53"/>
-      <c r="C33" s="54"/>
-      <c r="D33" s="54"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="54"/>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="54"/>
-      <c r="J33" s="54"/>
-      <c r="K33" s="54"/>
-      <c r="L33" s="54"/>
-      <c r="M33" s="54"/>
-      <c r="N33" s="54"/>
-      <c r="O33" s="54"/>
-      <c r="P33" s="54"/>
-      <c r="Q33" s="54"/>
-      <c r="R33" s="54"/>
-      <c r="S33" s="54"/>
-      <c r="T33" s="54"/>
-      <c r="U33" s="54"/>
-      <c r="V33" s="54"/>
-      <c r="W33" s="54"/>
-      <c r="X33" s="54"/>
-      <c r="Y33" s="54"/>
-      <c r="Z33" s="54"/>
-      <c r="AA33" s="55"/>
+      <c r="B33" s="54"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="36"/>
+      <c r="J33" s="36"/>
+      <c r="K33" s="36"/>
+      <c r="L33" s="36"/>
+      <c r="M33" s="36"/>
+      <c r="N33" s="36"/>
+      <c r="O33" s="36"/>
+      <c r="P33" s="36"/>
+      <c r="Q33" s="36"/>
+      <c r="R33" s="36"/>
+      <c r="S33" s="36"/>
+      <c r="T33" s="36"/>
+      <c r="U33" s="36"/>
+      <c r="V33" s="36"/>
+      <c r="W33" s="36"/>
+      <c r="X33" s="36"/>
+      <c r="Y33" s="36"/>
+      <c r="Z33" s="36"/>
+      <c r="AA33" s="45"/>
     </row>
     <row r="34" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
-      <c r="B34" s="56"/>
-      <c r="C34" s="57"/>
-      <c r="D34" s="57"/>
-      <c r="E34" s="57"/>
-      <c r="F34" s="57"/>
-      <c r="G34" s="57"/>
-      <c r="H34" s="57"/>
-      <c r="I34" s="57"/>
-      <c r="J34" s="57"/>
-      <c r="K34" s="57"/>
-      <c r="L34" s="57"/>
-      <c r="M34" s="57"/>
-      <c r="N34" s="57"/>
-      <c r="O34" s="57"/>
-      <c r="P34" s="57"/>
-      <c r="Q34" s="57"/>
-      <c r="R34" s="57"/>
-      <c r="S34" s="57"/>
-      <c r="T34" s="57"/>
-      <c r="U34" s="57"/>
-      <c r="V34" s="57"/>
-      <c r="W34" s="57"/>
-      <c r="X34" s="57"/>
-      <c r="Y34" s="57"/>
-      <c r="Z34" s="57"/>
-      <c r="AA34" s="58"/>
+      <c r="B34" s="46"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="47"/>
+      <c r="H34" s="47"/>
+      <c r="I34" s="47"/>
+      <c r="J34" s="47"/>
+      <c r="K34" s="47"/>
+      <c r="L34" s="47"/>
+      <c r="M34" s="47"/>
+      <c r="N34" s="47"/>
+      <c r="O34" s="47"/>
+      <c r="P34" s="47"/>
+      <c r="Q34" s="47"/>
+      <c r="R34" s="47"/>
+      <c r="S34" s="47"/>
+      <c r="T34" s="47"/>
+      <c r="U34" s="47"/>
+      <c r="V34" s="47"/>
+      <c r="W34" s="47"/>
+      <c r="X34" s="47"/>
+      <c r="Y34" s="47"/>
+      <c r="Z34" s="47"/>
+      <c r="AA34" s="48"/>
     </row>
     <row r="35" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
-      <c r="B35" s="56"/>
-      <c r="C35" s="57"/>
-      <c r="D35" s="57"/>
-      <c r="E35" s="57"/>
-      <c r="F35" s="57"/>
-      <c r="G35" s="57"/>
-      <c r="H35" s="57"/>
-      <c r="I35" s="57"/>
-      <c r="J35" s="57"/>
-      <c r="K35" s="57"/>
-      <c r="L35" s="57"/>
-      <c r="M35" s="57"/>
-      <c r="N35" s="57"/>
-      <c r="O35" s="57"/>
-      <c r="P35" s="57"/>
-      <c r="Q35" s="57"/>
-      <c r="R35" s="57"/>
-      <c r="S35" s="57"/>
-      <c r="T35" s="57"/>
-      <c r="U35" s="57"/>
-      <c r="V35" s="57"/>
-      <c r="W35" s="57"/>
-      <c r="X35" s="57"/>
-      <c r="Y35" s="57"/>
-      <c r="Z35" s="57"/>
-      <c r="AA35" s="58"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="47"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="47"/>
+      <c r="J35" s="47"/>
+      <c r="K35" s="47"/>
+      <c r="L35" s="47"/>
+      <c r="M35" s="47"/>
+      <c r="N35" s="47"/>
+      <c r="O35" s="47"/>
+      <c r="P35" s="47"/>
+      <c r="Q35" s="47"/>
+      <c r="R35" s="47"/>
+      <c r="S35" s="47"/>
+      <c r="T35" s="47"/>
+      <c r="U35" s="47"/>
+      <c r="V35" s="47"/>
+      <c r="W35" s="47"/>
+      <c r="X35" s="47"/>
+      <c r="Y35" s="47"/>
+      <c r="Z35" s="47"/>
+      <c r="AA35" s="48"/>
     </row>
     <row r="36" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
-      <c r="B36" s="56"/>
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="57"/>
-      <c r="K36" s="57"/>
-      <c r="L36" s="57"/>
-      <c r="M36" s="57"/>
-      <c r="N36" s="57"/>
-      <c r="O36" s="57"/>
-      <c r="P36" s="57"/>
-      <c r="Q36" s="57"/>
-      <c r="R36" s="57"/>
-      <c r="S36" s="57"/>
-      <c r="T36" s="57"/>
-      <c r="U36" s="57"/>
-      <c r="V36" s="57"/>
-      <c r="W36" s="57"/>
-      <c r="X36" s="57"/>
-      <c r="Y36" s="57"/>
-      <c r="Z36" s="57"/>
-      <c r="AA36" s="58"/>
+      <c r="B36" s="46"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="47"/>
+      <c r="J36" s="47"/>
+      <c r="K36" s="47"/>
+      <c r="L36" s="47"/>
+      <c r="M36" s="47"/>
+      <c r="N36" s="47"/>
+      <c r="O36" s="47"/>
+      <c r="P36" s="47"/>
+      <c r="Q36" s="47"/>
+      <c r="R36" s="47"/>
+      <c r="S36" s="47"/>
+      <c r="T36" s="47"/>
+      <c r="U36" s="47"/>
+      <c r="V36" s="47"/>
+      <c r="W36" s="47"/>
+      <c r="X36" s="47"/>
+      <c r="Y36" s="47"/>
+      <c r="Z36" s="47"/>
+      <c r="AA36" s="48"/>
     </row>
     <row r="37" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
-      <c r="B37" s="56"/>
-      <c r="C37" s="57"/>
-      <c r="D37" s="57"/>
-      <c r="E37" s="57"/>
-      <c r="F37" s="57"/>
-      <c r="G37" s="57"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="57"/>
-      <c r="J37" s="57"/>
-      <c r="K37" s="57"/>
-      <c r="L37" s="57"/>
-      <c r="M37" s="57"/>
-      <c r="N37" s="57"/>
-      <c r="O37" s="57"/>
-      <c r="P37" s="57"/>
-      <c r="Q37" s="57"/>
-      <c r="R37" s="57"/>
-      <c r="S37" s="57"/>
-      <c r="T37" s="57"/>
-      <c r="U37" s="57"/>
-      <c r="V37" s="57"/>
-      <c r="W37" s="57"/>
-      <c r="X37" s="57"/>
-      <c r="Y37" s="57"/>
-      <c r="Z37" s="57"/>
-      <c r="AA37" s="58"/>
+      <c r="B37" s="46"/>
+      <c r="C37" s="47"/>
+      <c r="D37" s="47"/>
+      <c r="E37" s="47"/>
+      <c r="F37" s="47"/>
+      <c r="G37" s="47"/>
+      <c r="H37" s="47"/>
+      <c r="I37" s="47"/>
+      <c r="J37" s="47"/>
+      <c r="K37" s="47"/>
+      <c r="L37" s="47"/>
+      <c r="M37" s="47"/>
+      <c r="N37" s="47"/>
+      <c r="O37" s="47"/>
+      <c r="P37" s="47"/>
+      <c r="Q37" s="47"/>
+      <c r="R37" s="47"/>
+      <c r="S37" s="47"/>
+      <c r="T37" s="47"/>
+      <c r="U37" s="47"/>
+      <c r="V37" s="47"/>
+      <c r="W37" s="47"/>
+      <c r="X37" s="47"/>
+      <c r="Y37" s="47"/>
+      <c r="Z37" s="47"/>
+      <c r="AA37" s="48"/>
     </row>
     <row r="38" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
-      <c r="B38" s="56"/>
-      <c r="C38" s="57"/>
-      <c r="D38" s="57"/>
-      <c r="E38" s="57"/>
-      <c r="F38" s="57"/>
-      <c r="G38" s="57"/>
-      <c r="H38" s="57"/>
-      <c r="I38" s="57"/>
-      <c r="J38" s="57"/>
-      <c r="K38" s="57"/>
-      <c r="L38" s="57"/>
-      <c r="M38" s="57"/>
-      <c r="N38" s="57"/>
-      <c r="O38" s="57"/>
-      <c r="P38" s="57"/>
-      <c r="Q38" s="57"/>
-      <c r="R38" s="57"/>
-      <c r="S38" s="57"/>
-      <c r="T38" s="57"/>
-      <c r="U38" s="57"/>
-      <c r="V38" s="57"/>
-      <c r="W38" s="57"/>
-      <c r="X38" s="57"/>
-      <c r="Y38" s="57"/>
-      <c r="Z38" s="57"/>
-      <c r="AA38" s="58"/>
+      <c r="B38" s="46"/>
+      <c r="C38" s="47"/>
+      <c r="D38" s="47"/>
+      <c r="E38" s="47"/>
+      <c r="F38" s="47"/>
+      <c r="G38" s="47"/>
+      <c r="H38" s="47"/>
+      <c r="I38" s="47"/>
+      <c r="J38" s="47"/>
+      <c r="K38" s="47"/>
+      <c r="L38" s="47"/>
+      <c r="M38" s="47"/>
+      <c r="N38" s="47"/>
+      <c r="O38" s="47"/>
+      <c r="P38" s="47"/>
+      <c r="Q38" s="47"/>
+      <c r="R38" s="47"/>
+      <c r="S38" s="47"/>
+      <c r="T38" s="47"/>
+      <c r="U38" s="47"/>
+      <c r="V38" s="47"/>
+      <c r="W38" s="47"/>
+      <c r="X38" s="47"/>
+      <c r="Y38" s="47"/>
+      <c r="Z38" s="47"/>
+      <c r="AA38" s="48"/>
     </row>
     <row r="39" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
-      <c r="B39" s="74"/>
-      <c r="C39" s="68"/>
-      <c r="D39" s="68"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="68"/>
-      <c r="G39" s="68"/>
-      <c r="H39" s="68"/>
-      <c r="I39" s="68"/>
-      <c r="J39" s="68"/>
-      <c r="K39" s="68"/>
-      <c r="L39" s="68"/>
-      <c r="M39" s="68"/>
-      <c r="N39" s="68"/>
-      <c r="O39" s="68"/>
-      <c r="P39" s="68"/>
-      <c r="Q39" s="68"/>
-      <c r="R39" s="68"/>
-      <c r="S39" s="68"/>
-      <c r="T39" s="68"/>
-      <c r="U39" s="68"/>
-      <c r="V39" s="68"/>
-      <c r="W39" s="68"/>
-      <c r="X39" s="68"/>
-      <c r="Y39" s="68"/>
-      <c r="Z39" s="68"/>
-      <c r="AA39" s="75"/>
+      <c r="B39" s="49"/>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="39"/>
+      <c r="H39" s="39"/>
+      <c r="I39" s="39"/>
+      <c r="J39" s="39"/>
+      <c r="K39" s="39"/>
+      <c r="L39" s="39"/>
+      <c r="M39" s="39"/>
+      <c r="N39" s="39"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="39"/>
+      <c r="Q39" s="39"/>
+      <c r="R39" s="39"/>
+      <c r="S39" s="39"/>
+      <c r="T39" s="39"/>
+      <c r="U39" s="39"/>
+      <c r="V39" s="39"/>
+      <c r="W39" s="39"/>
+      <c r="X39" s="39"/>
+      <c r="Y39" s="39"/>
+      <c r="Z39" s="39"/>
+      <c r="AA39" s="50"/>
     </row>
     <row r="40" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
-      <c r="B40" s="76" t="s">
+      <c r="B40" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="77"/>
-      <c r="D40" s="77"/>
-      <c r="E40" s="77"/>
-      <c r="F40" s="77"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="77"/>
-      <c r="I40" s="77"/>
-      <c r="J40" s="77"/>
-      <c r="K40" s="77"/>
-      <c r="L40" s="77"/>
-      <c r="M40" s="77"/>
-      <c r="N40" s="77"/>
-      <c r="O40" s="77"/>
-      <c r="P40" s="77"/>
-      <c r="Q40" s="77"/>
-      <c r="R40" s="77"/>
-      <c r="S40" s="77"/>
-      <c r="T40" s="77"/>
-      <c r="U40" s="77"/>
-      <c r="V40" s="77"/>
-      <c r="W40" s="77"/>
-      <c r="X40" s="77"/>
-      <c r="Y40" s="77"/>
-      <c r="Z40" s="77"/>
-      <c r="AA40" s="78"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="52"/>
+      <c r="I40" s="52"/>
+      <c r="J40" s="52"/>
+      <c r="K40" s="52"/>
+      <c r="L40" s="52"/>
+      <c r="M40" s="52"/>
+      <c r="N40" s="52"/>
+      <c r="O40" s="52"/>
+      <c r="P40" s="52"/>
+      <c r="Q40" s="52"/>
+      <c r="R40" s="52"/>
+      <c r="S40" s="52"/>
+      <c r="T40" s="52"/>
+      <c r="U40" s="52"/>
+      <c r="V40" s="52"/>
+      <c r="W40" s="52"/>
+      <c r="X40" s="52"/>
+      <c r="Y40" s="52"/>
+      <c r="Z40" s="52"/>
+      <c r="AA40" s="53"/>
     </row>
     <row r="41" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
-      <c r="B41" s="53"/>
-      <c r="C41" s="54"/>
-      <c r="D41" s="54"/>
-      <c r="E41" s="54"/>
-      <c r="F41" s="54"/>
-      <c r="G41" s="54"/>
-      <c r="H41" s="54"/>
-      <c r="I41" s="54"/>
-      <c r="J41" s="54"/>
-      <c r="K41" s="54"/>
-      <c r="L41" s="54"/>
-      <c r="M41" s="54"/>
-      <c r="N41" s="54"/>
-      <c r="O41" s="54"/>
-      <c r="P41" s="54"/>
-      <c r="Q41" s="54"/>
-      <c r="R41" s="54"/>
-      <c r="S41" s="54"/>
-      <c r="T41" s="54"/>
-      <c r="U41" s="54"/>
-      <c r="V41" s="54"/>
-      <c r="W41" s="54"/>
-      <c r="X41" s="54"/>
-      <c r="Y41" s="54"/>
-      <c r="Z41" s="54"/>
-      <c r="AA41" s="55"/>
+      <c r="B41" s="54"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="36"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="36"/>
+      <c r="H41" s="36"/>
+      <c r="I41" s="36"/>
+      <c r="J41" s="36"/>
+      <c r="K41" s="36"/>
+      <c r="L41" s="36"/>
+      <c r="M41" s="36"/>
+      <c r="N41" s="36"/>
+      <c r="O41" s="36"/>
+      <c r="P41" s="36"/>
+      <c r="Q41" s="36"/>
+      <c r="R41" s="36"/>
+      <c r="S41" s="36"/>
+      <c r="T41" s="36"/>
+      <c r="U41" s="36"/>
+      <c r="V41" s="36"/>
+      <c r="W41" s="36"/>
+      <c r="X41" s="36"/>
+      <c r="Y41" s="36"/>
+      <c r="Z41" s="36"/>
+      <c r="AA41" s="45"/>
     </row>
     <row r="42" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
-      <c r="B42" s="56"/>
-      <c r="C42" s="57"/>
-      <c r="D42" s="57"/>
-      <c r="E42" s="57"/>
-      <c r="F42" s="57"/>
-      <c r="G42" s="57"/>
-      <c r="H42" s="57"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="57"/>
-      <c r="K42" s="57"/>
-      <c r="L42" s="57"/>
-      <c r="M42" s="57"/>
-      <c r="N42" s="57"/>
-      <c r="O42" s="57"/>
-      <c r="P42" s="57"/>
-      <c r="Q42" s="57"/>
-      <c r="R42" s="57"/>
-      <c r="S42" s="57"/>
-      <c r="T42" s="57"/>
-      <c r="U42" s="57"/>
-      <c r="V42" s="57"/>
-      <c r="W42" s="57"/>
-      <c r="X42" s="57"/>
-      <c r="Y42" s="57"/>
-      <c r="Z42" s="57"/>
-      <c r="AA42" s="58"/>
+      <c r="B42" s="46"/>
+      <c r="C42" s="47"/>
+      <c r="D42" s="47"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="47"/>
+      <c r="G42" s="47"/>
+      <c r="H42" s="47"/>
+      <c r="I42" s="47"/>
+      <c r="J42" s="47"/>
+      <c r="K42" s="47"/>
+      <c r="L42" s="47"/>
+      <c r="M42" s="47"/>
+      <c r="N42" s="47"/>
+      <c r="O42" s="47"/>
+      <c r="P42" s="47"/>
+      <c r="Q42" s="47"/>
+      <c r="R42" s="47"/>
+      <c r="S42" s="47"/>
+      <c r="T42" s="47"/>
+      <c r="U42" s="47"/>
+      <c r="V42" s="47"/>
+      <c r="W42" s="47"/>
+      <c r="X42" s="47"/>
+      <c r="Y42" s="47"/>
+      <c r="Z42" s="47"/>
+      <c r="AA42" s="48"/>
     </row>
     <row r="43" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
-      <c r="B43" s="56"/>
-      <c r="C43" s="57"/>
-      <c r="D43" s="57"/>
-      <c r="E43" s="57"/>
-      <c r="F43" s="57"/>
-      <c r="G43" s="57"/>
-      <c r="H43" s="57"/>
-      <c r="I43" s="57"/>
-      <c r="J43" s="57"/>
-      <c r="K43" s="57"/>
-      <c r="L43" s="57"/>
-      <c r="M43" s="57"/>
-      <c r="N43" s="57"/>
-      <c r="O43" s="57"/>
-      <c r="P43" s="57"/>
-      <c r="Q43" s="57"/>
-      <c r="R43" s="57"/>
-      <c r="S43" s="57"/>
-      <c r="T43" s="57"/>
-      <c r="U43" s="57"/>
-      <c r="V43" s="57"/>
-      <c r="W43" s="57"/>
-      <c r="X43" s="57"/>
-      <c r="Y43" s="57"/>
-      <c r="Z43" s="57"/>
-      <c r="AA43" s="58"/>
+      <c r="B43" s="46"/>
+      <c r="C43" s="47"/>
+      <c r="D43" s="47"/>
+      <c r="E43" s="47"/>
+      <c r="F43" s="47"/>
+      <c r="G43" s="47"/>
+      <c r="H43" s="47"/>
+      <c r="I43" s="47"/>
+      <c r="J43" s="47"/>
+      <c r="K43" s="47"/>
+      <c r="L43" s="47"/>
+      <c r="M43" s="47"/>
+      <c r="N43" s="47"/>
+      <c r="O43" s="47"/>
+      <c r="P43" s="47"/>
+      <c r="Q43" s="47"/>
+      <c r="R43" s="47"/>
+      <c r="S43" s="47"/>
+      <c r="T43" s="47"/>
+      <c r="U43" s="47"/>
+      <c r="V43" s="47"/>
+      <c r="W43" s="47"/>
+      <c r="X43" s="47"/>
+      <c r="Y43" s="47"/>
+      <c r="Z43" s="47"/>
+      <c r="AA43" s="48"/>
     </row>
     <row r="44" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
-      <c r="B44" s="56"/>
-      <c r="C44" s="57"/>
-      <c r="D44" s="57"/>
-      <c r="E44" s="57"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="57"/>
-      <c r="H44" s="57"/>
-      <c r="I44" s="57"/>
-      <c r="J44" s="57"/>
-      <c r="K44" s="57"/>
-      <c r="L44" s="57"/>
-      <c r="M44" s="57"/>
-      <c r="N44" s="57"/>
-      <c r="O44" s="57"/>
-      <c r="P44" s="57"/>
-      <c r="Q44" s="57"/>
-      <c r="R44" s="57"/>
-      <c r="S44" s="57"/>
-      <c r="T44" s="57"/>
-      <c r="U44" s="57"/>
-      <c r="V44" s="57"/>
-      <c r="W44" s="57"/>
-      <c r="X44" s="57"/>
-      <c r="Y44" s="57"/>
-      <c r="Z44" s="57"/>
-      <c r="AA44" s="58"/>
+      <c r="B44" s="46"/>
+      <c r="C44" s="47"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="47"/>
+      <c r="G44" s="47"/>
+      <c r="H44" s="47"/>
+      <c r="I44" s="47"/>
+      <c r="J44" s="47"/>
+      <c r="K44" s="47"/>
+      <c r="L44" s="47"/>
+      <c r="M44" s="47"/>
+      <c r="N44" s="47"/>
+      <c r="O44" s="47"/>
+      <c r="P44" s="47"/>
+      <c r="Q44" s="47"/>
+      <c r="R44" s="47"/>
+      <c r="S44" s="47"/>
+      <c r="T44" s="47"/>
+      <c r="U44" s="47"/>
+      <c r="V44" s="47"/>
+      <c r="W44" s="47"/>
+      <c r="X44" s="47"/>
+      <c r="Y44" s="47"/>
+      <c r="Z44" s="47"/>
+      <c r="AA44" s="48"/>
     </row>
     <row r="45" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
-      <c r="B45" s="56"/>
-      <c r="C45" s="57"/>
-      <c r="D45" s="57"/>
-      <c r="E45" s="57"/>
-      <c r="F45" s="57"/>
-      <c r="G45" s="57"/>
-      <c r="H45" s="57"/>
-      <c r="I45" s="57"/>
-      <c r="J45" s="57"/>
-      <c r="K45" s="57"/>
-      <c r="L45" s="57"/>
-      <c r="M45" s="57"/>
-      <c r="N45" s="57"/>
-      <c r="O45" s="57"/>
-      <c r="P45" s="57"/>
-      <c r="Q45" s="57"/>
-      <c r="R45" s="57"/>
-      <c r="S45" s="57"/>
-      <c r="T45" s="57"/>
-      <c r="U45" s="57"/>
-      <c r="V45" s="57"/>
-      <c r="W45" s="57"/>
-      <c r="X45" s="57"/>
-      <c r="Y45" s="57"/>
-      <c r="Z45" s="57"/>
-      <c r="AA45" s="58"/>
+      <c r="B45" s="46"/>
+      <c r="C45" s="47"/>
+      <c r="D45" s="47"/>
+      <c r="E45" s="47"/>
+      <c r="F45" s="47"/>
+      <c r="G45" s="47"/>
+      <c r="H45" s="47"/>
+      <c r="I45" s="47"/>
+      <c r="J45" s="47"/>
+      <c r="K45" s="47"/>
+      <c r="L45" s="47"/>
+      <c r="M45" s="47"/>
+      <c r="N45" s="47"/>
+      <c r="O45" s="47"/>
+      <c r="P45" s="47"/>
+      <c r="Q45" s="47"/>
+      <c r="R45" s="47"/>
+      <c r="S45" s="47"/>
+      <c r="T45" s="47"/>
+      <c r="U45" s="47"/>
+      <c r="V45" s="47"/>
+      <c r="W45" s="47"/>
+      <c r="X45" s="47"/>
+      <c r="Y45" s="47"/>
+      <c r="Z45" s="47"/>
+      <c r="AA45" s="48"/>
     </row>
     <row r="46" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
-      <c r="B46" s="56"/>
-      <c r="C46" s="57"/>
-      <c r="D46" s="57"/>
-      <c r="E46" s="57"/>
-      <c r="F46" s="57"/>
-      <c r="G46" s="57"/>
-      <c r="H46" s="57"/>
-      <c r="I46" s="57"/>
-      <c r="J46" s="57"/>
-      <c r="K46" s="57"/>
-      <c r="L46" s="57"/>
-      <c r="M46" s="57"/>
-      <c r="N46" s="57"/>
-      <c r="O46" s="57"/>
-      <c r="P46" s="57"/>
-      <c r="Q46" s="57"/>
-      <c r="R46" s="57"/>
-      <c r="S46" s="57"/>
-      <c r="T46" s="57"/>
-      <c r="U46" s="57"/>
-      <c r="V46" s="57"/>
-      <c r="W46" s="57"/>
-      <c r="X46" s="57"/>
-      <c r="Y46" s="57"/>
-      <c r="Z46" s="57"/>
-      <c r="AA46" s="58"/>
+      <c r="B46" s="46"/>
+      <c r="C46" s="47"/>
+      <c r="D46" s="47"/>
+      <c r="E46" s="47"/>
+      <c r="F46" s="47"/>
+      <c r="G46" s="47"/>
+      <c r="H46" s="47"/>
+      <c r="I46" s="47"/>
+      <c r="J46" s="47"/>
+      <c r="K46" s="47"/>
+      <c r="L46" s="47"/>
+      <c r="M46" s="47"/>
+      <c r="N46" s="47"/>
+      <c r="O46" s="47"/>
+      <c r="P46" s="47"/>
+      <c r="Q46" s="47"/>
+      <c r="R46" s="47"/>
+      <c r="S46" s="47"/>
+      <c r="T46" s="47"/>
+      <c r="U46" s="47"/>
+      <c r="V46" s="47"/>
+      <c r="W46" s="47"/>
+      <c r="X46" s="47"/>
+      <c r="Y46" s="47"/>
+      <c r="Z46" s="47"/>
+      <c r="AA46" s="48"/>
     </row>
     <row r="47" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
-      <c r="B47" s="79"/>
-      <c r="C47" s="80"/>
-      <c r="D47" s="80"/>
-      <c r="E47" s="80"/>
-      <c r="F47" s="80"/>
-      <c r="G47" s="80"/>
-      <c r="H47" s="80"/>
-      <c r="I47" s="80"/>
-      <c r="J47" s="80"/>
-      <c r="K47" s="80"/>
-      <c r="L47" s="80"/>
-      <c r="M47" s="80"/>
-      <c r="N47" s="80"/>
-      <c r="O47" s="80"/>
-      <c r="P47" s="80"/>
-      <c r="Q47" s="80"/>
-      <c r="R47" s="80"/>
-      <c r="S47" s="80"/>
-      <c r="T47" s="80"/>
-      <c r="U47" s="80"/>
-      <c r="V47" s="80"/>
-      <c r="W47" s="80"/>
-      <c r="X47" s="80"/>
-      <c r="Y47" s="80"/>
-      <c r="Z47" s="80"/>
-      <c r="AA47" s="81"/>
+      <c r="B47" s="55"/>
+      <c r="C47" s="56"/>
+      <c r="D47" s="56"/>
+      <c r="E47" s="56"/>
+      <c r="F47" s="56"/>
+      <c r="G47" s="56"/>
+      <c r="H47" s="56"/>
+      <c r="I47" s="56"/>
+      <c r="J47" s="56"/>
+      <c r="K47" s="56"/>
+      <c r="L47" s="56"/>
+      <c r="M47" s="56"/>
+      <c r="N47" s="56"/>
+      <c r="O47" s="56"/>
+      <c r="P47" s="56"/>
+      <c r="Q47" s="56"/>
+      <c r="R47" s="56"/>
+      <c r="S47" s="56"/>
+      <c r="T47" s="56"/>
+      <c r="U47" s="56"/>
+      <c r="V47" s="56"/>
+      <c r="W47" s="56"/>
+      <c r="X47" s="56"/>
+      <c r="Y47" s="56"/>
+      <c r="Z47" s="56"/>
+      <c r="AA47" s="57"/>
     </row>
     <row r="48" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
-      <c r="B48" s="82" t="s">
+      <c r="B48" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="46"/>
-      <c r="D48" s="46"/>
-      <c r="E48" s="46"/>
-      <c r="F48" s="46"/>
-      <c r="G48" s="46"/>
-      <c r="H48" s="46"/>
-      <c r="I48" s="46"/>
-      <c r="J48" s="46"/>
-      <c r="K48" s="46"/>
-      <c r="L48" s="46"/>
-      <c r="M48" s="46"/>
-      <c r="N48" s="46"/>
-      <c r="O48" s="46"/>
-      <c r="P48" s="46"/>
-      <c r="Q48" s="46"/>
-      <c r="R48" s="46"/>
-      <c r="S48" s="46"/>
-      <c r="T48" s="46"/>
-      <c r="U48" s="46"/>
-      <c r="V48" s="46"/>
-      <c r="W48" s="46"/>
-      <c r="X48" s="46"/>
-      <c r="Y48" s="46"/>
-      <c r="Z48" s="46"/>
-      <c r="AA48" s="47"/>
+      <c r="C48" s="59"/>
+      <c r="D48" s="59"/>
+      <c r="E48" s="59"/>
+      <c r="F48" s="59"/>
+      <c r="G48" s="59"/>
+      <c r="H48" s="59"/>
+      <c r="I48" s="59"/>
+      <c r="J48" s="59"/>
+      <c r="K48" s="59"/>
+      <c r="L48" s="59"/>
+      <c r="M48" s="59"/>
+      <c r="N48" s="59"/>
+      <c r="O48" s="59"/>
+      <c r="P48" s="59"/>
+      <c r="Q48" s="59"/>
+      <c r="R48" s="59"/>
+      <c r="S48" s="59"/>
+      <c r="T48" s="59"/>
+      <c r="U48" s="59"/>
+      <c r="V48" s="59"/>
+      <c r="W48" s="59"/>
+      <c r="X48" s="59"/>
+      <c r="Y48" s="59"/>
+      <c r="Z48" s="59"/>
+      <c r="AA48" s="60"/>
     </row>
     <row r="49" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="30"/>
-      <c r="B49" s="53"/>
-      <c r="C49" s="54"/>
-      <c r="D49" s="54"/>
-      <c r="E49" s="54"/>
-      <c r="F49" s="54"/>
-      <c r="G49" s="54"/>
-      <c r="H49" s="54"/>
-      <c r="I49" s="54"/>
-      <c r="J49" s="54"/>
-      <c r="K49" s="54"/>
-      <c r="L49" s="54"/>
-      <c r="M49" s="54"/>
-      <c r="N49" s="54"/>
-      <c r="O49" s="54"/>
-      <c r="P49" s="54"/>
-      <c r="Q49" s="54"/>
-      <c r="R49" s="54"/>
-      <c r="S49" s="54"/>
-      <c r="T49" s="54"/>
-      <c r="U49" s="54"/>
-      <c r="V49" s="54"/>
-      <c r="W49" s="54"/>
-      <c r="X49" s="54"/>
-      <c r="Y49" s="54"/>
-      <c r="Z49" s="54"/>
-      <c r="AA49" s="55"/>
+      <c r="B49" s="54"/>
+      <c r="C49" s="36"/>
+      <c r="D49" s="36"/>
+      <c r="E49" s="36"/>
+      <c r="F49" s="36"/>
+      <c r="G49" s="36"/>
+      <c r="H49" s="36"/>
+      <c r="I49" s="36"/>
+      <c r="J49" s="36"/>
+      <c r="K49" s="36"/>
+      <c r="L49" s="36"/>
+      <c r="M49" s="36"/>
+      <c r="N49" s="36"/>
+      <c r="O49" s="36"/>
+      <c r="P49" s="36"/>
+      <c r="Q49" s="36"/>
+      <c r="R49" s="36"/>
+      <c r="S49" s="36"/>
+      <c r="T49" s="36"/>
+      <c r="U49" s="36"/>
+      <c r="V49" s="36"/>
+      <c r="W49" s="36"/>
+      <c r="X49" s="36"/>
+      <c r="Y49" s="36"/>
+      <c r="Z49" s="36"/>
+      <c r="AA49" s="45"/>
     </row>
     <row r="50" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="30"/>
-      <c r="B50" s="56"/>
-      <c r="C50" s="57"/>
-      <c r="D50" s="57"/>
-      <c r="E50" s="57"/>
-      <c r="F50" s="57"/>
-      <c r="G50" s="57"/>
-      <c r="H50" s="57"/>
-      <c r="I50" s="57"/>
-      <c r="J50" s="57"/>
-      <c r="K50" s="57"/>
-      <c r="L50" s="57"/>
-      <c r="M50" s="57"/>
-      <c r="N50" s="57"/>
-      <c r="O50" s="57"/>
-      <c r="P50" s="57"/>
-      <c r="Q50" s="57"/>
-      <c r="R50" s="57"/>
-      <c r="S50" s="57"/>
-      <c r="T50" s="57"/>
-      <c r="U50" s="57"/>
-      <c r="V50" s="57"/>
-      <c r="W50" s="57"/>
-      <c r="X50" s="57"/>
-      <c r="Y50" s="57"/>
-      <c r="Z50" s="57"/>
-      <c r="AA50" s="58"/>
+      <c r="B50" s="46"/>
+      <c r="C50" s="47"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="47"/>
+      <c r="G50" s="47"/>
+      <c r="H50" s="47"/>
+      <c r="I50" s="47"/>
+      <c r="J50" s="47"/>
+      <c r="K50" s="47"/>
+      <c r="L50" s="47"/>
+      <c r="M50" s="47"/>
+      <c r="N50" s="47"/>
+      <c r="O50" s="47"/>
+      <c r="P50" s="47"/>
+      <c r="Q50" s="47"/>
+      <c r="R50" s="47"/>
+      <c r="S50" s="47"/>
+      <c r="T50" s="47"/>
+      <c r="U50" s="47"/>
+      <c r="V50" s="47"/>
+      <c r="W50" s="47"/>
+      <c r="X50" s="47"/>
+      <c r="Y50" s="47"/>
+      <c r="Z50" s="47"/>
+      <c r="AA50" s="48"/>
     </row>
     <row r="51" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="30"/>
-      <c r="B51" s="56"/>
-      <c r="C51" s="57"/>
-      <c r="D51" s="57"/>
-      <c r="E51" s="57"/>
-      <c r="F51" s="57"/>
-      <c r="G51" s="57"/>
-      <c r="H51" s="57"/>
-      <c r="I51" s="57"/>
-      <c r="J51" s="57"/>
-      <c r="K51" s="57"/>
-      <c r="L51" s="57"/>
-      <c r="M51" s="57"/>
-      <c r="N51" s="57"/>
-      <c r="O51" s="57"/>
-      <c r="P51" s="57"/>
-      <c r="Q51" s="57"/>
-      <c r="R51" s="57"/>
-      <c r="S51" s="57"/>
-      <c r="T51" s="57"/>
-      <c r="U51" s="57"/>
-      <c r="V51" s="57"/>
-      <c r="W51" s="57"/>
-      <c r="X51" s="57"/>
-      <c r="Y51" s="57"/>
-      <c r="Z51" s="57"/>
-      <c r="AA51" s="58"/>
+      <c r="B51" s="46"/>
+      <c r="C51" s="47"/>
+      <c r="D51" s="47"/>
+      <c r="E51" s="47"/>
+      <c r="F51" s="47"/>
+      <c r="G51" s="47"/>
+      <c r="H51" s="47"/>
+      <c r="I51" s="47"/>
+      <c r="J51" s="47"/>
+      <c r="K51" s="47"/>
+      <c r="L51" s="47"/>
+      <c r="M51" s="47"/>
+      <c r="N51" s="47"/>
+      <c r="O51" s="47"/>
+      <c r="P51" s="47"/>
+      <c r="Q51" s="47"/>
+      <c r="R51" s="47"/>
+      <c r="S51" s="47"/>
+      <c r="T51" s="47"/>
+      <c r="U51" s="47"/>
+      <c r="V51" s="47"/>
+      <c r="W51" s="47"/>
+      <c r="X51" s="47"/>
+      <c r="Y51" s="47"/>
+      <c r="Z51" s="47"/>
+      <c r="AA51" s="48"/>
     </row>
     <row r="52" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="30"/>
-      <c r="B52" s="56"/>
-      <c r="C52" s="57"/>
-      <c r="D52" s="57"/>
-      <c r="E52" s="57"/>
-      <c r="F52" s="57"/>
-      <c r="G52" s="57"/>
-      <c r="H52" s="57"/>
-      <c r="I52" s="57"/>
-      <c r="J52" s="57"/>
-      <c r="K52" s="57"/>
-      <c r="L52" s="57"/>
-      <c r="M52" s="57"/>
-      <c r="N52" s="57"/>
-      <c r="O52" s="57"/>
-      <c r="P52" s="57"/>
-      <c r="Q52" s="57"/>
-      <c r="R52" s="57"/>
-      <c r="S52" s="57"/>
-      <c r="T52" s="57"/>
-      <c r="U52" s="57"/>
-      <c r="V52" s="57"/>
-      <c r="W52" s="57"/>
-      <c r="X52" s="57"/>
-      <c r="Y52" s="57"/>
-      <c r="Z52" s="57"/>
-      <c r="AA52" s="58"/>
+      <c r="B52" s="46"/>
+      <c r="C52" s="47"/>
+      <c r="D52" s="47"/>
+      <c r="E52" s="47"/>
+      <c r="F52" s="47"/>
+      <c r="G52" s="47"/>
+      <c r="H52" s="47"/>
+      <c r="I52" s="47"/>
+      <c r="J52" s="47"/>
+      <c r="K52" s="47"/>
+      <c r="L52" s="47"/>
+      <c r="M52" s="47"/>
+      <c r="N52" s="47"/>
+      <c r="O52" s="47"/>
+      <c r="P52" s="47"/>
+      <c r="Q52" s="47"/>
+      <c r="R52" s="47"/>
+      <c r="S52" s="47"/>
+      <c r="T52" s="47"/>
+      <c r="U52" s="47"/>
+      <c r="V52" s="47"/>
+      <c r="W52" s="47"/>
+      <c r="X52" s="47"/>
+      <c r="Y52" s="47"/>
+      <c r="Z52" s="47"/>
+      <c r="AA52" s="48"/>
     </row>
     <row r="53" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="30"/>
-      <c r="B53" s="56"/>
-      <c r="C53" s="57"/>
-      <c r="D53" s="57"/>
-      <c r="E53" s="57"/>
-      <c r="F53" s="57"/>
-      <c r="G53" s="57"/>
-      <c r="H53" s="57"/>
-      <c r="I53" s="57"/>
-      <c r="J53" s="57"/>
-      <c r="K53" s="57"/>
-      <c r="L53" s="57"/>
-      <c r="M53" s="57"/>
-      <c r="N53" s="57"/>
-      <c r="O53" s="57"/>
-      <c r="P53" s="57"/>
-      <c r="Q53" s="57"/>
-      <c r="R53" s="57"/>
-      <c r="S53" s="57"/>
-      <c r="T53" s="57"/>
-      <c r="U53" s="57"/>
-      <c r="V53" s="57"/>
-      <c r="W53" s="57"/>
-      <c r="X53" s="57"/>
-      <c r="Y53" s="57"/>
-      <c r="Z53" s="57"/>
-      <c r="AA53" s="58"/>
+      <c r="B53" s="46"/>
+      <c r="C53" s="47"/>
+      <c r="D53" s="47"/>
+      <c r="E53" s="47"/>
+      <c r="F53" s="47"/>
+      <c r="G53" s="47"/>
+      <c r="H53" s="47"/>
+      <c r="I53" s="47"/>
+      <c r="J53" s="47"/>
+      <c r="K53" s="47"/>
+      <c r="L53" s="47"/>
+      <c r="M53" s="47"/>
+      <c r="N53" s="47"/>
+      <c r="O53" s="47"/>
+      <c r="P53" s="47"/>
+      <c r="Q53" s="47"/>
+      <c r="R53" s="47"/>
+      <c r="S53" s="47"/>
+      <c r="T53" s="47"/>
+      <c r="U53" s="47"/>
+      <c r="V53" s="47"/>
+      <c r="W53" s="47"/>
+      <c r="X53" s="47"/>
+      <c r="Y53" s="47"/>
+      <c r="Z53" s="47"/>
+      <c r="AA53" s="48"/>
     </row>
     <row r="54" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="30"/>
-      <c r="B54" s="56"/>
-      <c r="C54" s="57"/>
-      <c r="D54" s="57"/>
-      <c r="E54" s="57"/>
-      <c r="F54" s="57"/>
-      <c r="G54" s="57"/>
-      <c r="H54" s="57"/>
-      <c r="I54" s="57"/>
-      <c r="J54" s="57"/>
-      <c r="K54" s="57"/>
-      <c r="L54" s="57"/>
-      <c r="M54" s="57"/>
-      <c r="N54" s="57"/>
-      <c r="O54" s="57"/>
-      <c r="P54" s="57"/>
-      <c r="Q54" s="57"/>
-      <c r="R54" s="57"/>
-      <c r="S54" s="57"/>
-      <c r="T54" s="57"/>
-      <c r="U54" s="57"/>
-      <c r="V54" s="57"/>
-      <c r="W54" s="57"/>
-      <c r="X54" s="57"/>
-      <c r="Y54" s="57"/>
-      <c r="Z54" s="57"/>
-      <c r="AA54" s="58"/>
+      <c r="B54" s="46"/>
+      <c r="C54" s="47"/>
+      <c r="D54" s="47"/>
+      <c r="E54" s="47"/>
+      <c r="F54" s="47"/>
+      <c r="G54" s="47"/>
+      <c r="H54" s="47"/>
+      <c r="I54" s="47"/>
+      <c r="J54" s="47"/>
+      <c r="K54" s="47"/>
+      <c r="L54" s="47"/>
+      <c r="M54" s="47"/>
+      <c r="N54" s="47"/>
+      <c r="O54" s="47"/>
+      <c r="P54" s="47"/>
+      <c r="Q54" s="47"/>
+      <c r="R54" s="47"/>
+      <c r="S54" s="47"/>
+      <c r="T54" s="47"/>
+      <c r="U54" s="47"/>
+      <c r="V54" s="47"/>
+      <c r="W54" s="47"/>
+      <c r="X54" s="47"/>
+      <c r="Y54" s="47"/>
+      <c r="Z54" s="47"/>
+      <c r="AA54" s="48"/>
     </row>
     <row r="55" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A55" s="30"/>
-      <c r="B55" s="48"/>
-      <c r="C55" s="49"/>
-      <c r="D55" s="49"/>
-      <c r="E55" s="49"/>
-      <c r="F55" s="49"/>
-      <c r="G55" s="49"/>
-      <c r="H55" s="49"/>
-      <c r="I55" s="49"/>
-      <c r="J55" s="49"/>
-      <c r="K55" s="49"/>
-      <c r="L55" s="49"/>
-      <c r="M55" s="49"/>
-      <c r="N55" s="49"/>
-      <c r="O55" s="49"/>
-      <c r="P55" s="49"/>
-      <c r="Q55" s="49"/>
-      <c r="R55" s="49"/>
-      <c r="S55" s="49"/>
-      <c r="T55" s="49"/>
-      <c r="U55" s="49"/>
-      <c r="V55" s="49"/>
-      <c r="W55" s="49"/>
-      <c r="X55" s="49"/>
-      <c r="Y55" s="49"/>
-      <c r="Z55" s="49"/>
-      <c r="AA55" s="50"/>
+      <c r="B55" s="67"/>
+      <c r="C55" s="68"/>
+      <c r="D55" s="68"/>
+      <c r="E55" s="68"/>
+      <c r="F55" s="68"/>
+      <c r="G55" s="68"/>
+      <c r="H55" s="68"/>
+      <c r="I55" s="68"/>
+      <c r="J55" s="68"/>
+      <c r="K55" s="68"/>
+      <c r="L55" s="68"/>
+      <c r="M55" s="68"/>
+      <c r="N55" s="68"/>
+      <c r="O55" s="68"/>
+      <c r="P55" s="68"/>
+      <c r="Q55" s="68"/>
+      <c r="R55" s="68"/>
+      <c r="S55" s="68"/>
+      <c r="T55" s="68"/>
+      <c r="U55" s="68"/>
+      <c r="V55" s="68"/>
+      <c r="W55" s="68"/>
+      <c r="X55" s="68"/>
+      <c r="Y55" s="68"/>
+      <c r="Z55" s="68"/>
+      <c r="AA55" s="69"/>
     </row>
     <row r="56" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
@@ -2882,88 +2856,91 @@
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
-      <c r="M58" s="1"/>
-      <c r="N58" s="1"/>
-      <c r="O58" s="1"/>
-      <c r="P58" s="1"/>
-      <c r="Q58" s="1"/>
-      <c r="R58" s="1"/>
-      <c r="S58" s="1"/>
-      <c r="T58" s="1"/>
-      <c r="U58" s="1"/>
-      <c r="V58" s="1"/>
-      <c r="W58" s="1"/>
-      <c r="X58" s="1"/>
-      <c r="Y58" s="1"/>
+      <c r="D58" s="77"/>
+      <c r="E58" s="77"/>
+      <c r="F58" s="77"/>
+      <c r="G58" s="77"/>
+      <c r="H58" s="77"/>
+      <c r="I58" s="77"/>
+      <c r="J58" s="77"/>
+      <c r="K58" s="77"/>
+      <c r="L58" s="77"/>
+      <c r="M58" s="77"/>
+      <c r="N58" s="77"/>
+      <c r="O58" s="77"/>
+      <c r="P58" s="77"/>
+      <c r="Q58" s="77"/>
+      <c r="R58" s="77"/>
+      <c r="S58" s="77"/>
+      <c r="T58" s="77"/>
+      <c r="U58" s="77"/>
+      <c r="V58" s="77"/>
+      <c r="W58" s="77"/>
+      <c r="X58" s="77"/>
+      <c r="Y58" s="77"/>
       <c r="Z58" s="1"/>
       <c r="AA58" s="1"/>
     </row>
     <row r="59" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
-      <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
-      <c r="E59" s="59"/>
-      <c r="F59" s="60"/>
-      <c r="G59" s="60"/>
-      <c r="H59" s="60"/>
-      <c r="I59" s="60"/>
-      <c r="J59" s="60"/>
-      <c r="K59" s="60"/>
-      <c r="L59" s="60"/>
-      <c r="M59" s="60"/>
-      <c r="N59" s="60"/>
-      <c r="O59" s="60"/>
-      <c r="P59" s="60"/>
-      <c r="Q59" s="60"/>
-      <c r="R59" s="60"/>
-      <c r="S59" s="60"/>
-      <c r="T59" s="60"/>
-      <c r="U59" s="60"/>
-      <c r="V59" s="60"/>
-      <c r="W59" s="60"/>
-      <c r="X59" s="61"/>
-      <c r="Y59" s="1"/>
-      <c r="Z59" s="1"/>
+      <c r="B59" s="78"/>
+      <c r="C59" s="78"/>
+      <c r="D59" s="78"/>
+      <c r="E59" s="78"/>
+      <c r="F59" s="82"/>
+      <c r="G59" s="82"/>
+      <c r="H59" s="82"/>
+      <c r="I59" s="79"/>
+      <c r="J59" s="79"/>
+      <c r="K59" s="82"/>
+      <c r="L59" s="82"/>
+      <c r="M59" s="82"/>
+      <c r="N59" s="82"/>
+      <c r="O59" s="82"/>
+      <c r="P59" s="82"/>
+      <c r="Q59" s="82"/>
+      <c r="R59" s="79"/>
+      <c r="S59" s="82"/>
+      <c r="T59" s="82"/>
+      <c r="U59" s="82"/>
+      <c r="V59" s="82"/>
+      <c r="W59" s="82"/>
+      <c r="X59" s="82"/>
+      <c r="Y59" s="78"/>
+      <c r="Z59" s="78"/>
       <c r="AA59" s="1"/>
     </row>
     <row r="60" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="62" t="s">
-        <v>13</v>
+      <c r="D60" s="81" t="s">
+        <v>15</v>
       </c>
-      <c r="F60" s="63"/>
-      <c r="G60" s="63"/>
-      <c r="H60" s="63"/>
-      <c r="I60" s="63"/>
-      <c r="J60" s="63"/>
-      <c r="K60" s="63"/>
-      <c r="L60" s="63"/>
-      <c r="M60" s="63"/>
-      <c r="N60" s="63"/>
-      <c r="O60" s="63"/>
-      <c r="P60" s="63"/>
-      <c r="Q60" s="63"/>
-      <c r="R60" s="63"/>
-      <c r="S60" s="63"/>
-      <c r="T60" s="63"/>
-      <c r="U60" s="63"/>
-      <c r="V60" s="63"/>
-      <c r="W60" s="63"/>
-      <c r="X60" s="64"/>
-      <c r="Y60" s="1"/>
+      <c r="E60" s="80"/>
+      <c r="F60" s="79"/>
+      <c r="G60" s="79"/>
+      <c r="H60" s="79"/>
+      <c r="I60" s="79"/>
+      <c r="J60" s="79"/>
+      <c r="K60" s="79"/>
+      <c r="L60" s="79"/>
+      <c r="M60" s="79"/>
+      <c r="N60" s="83" t="s">
+        <v>5</v>
+      </c>
+      <c r="O60" s="79"/>
+      <c r="P60" s="79"/>
+      <c r="Q60" s="79"/>
+      <c r="R60" s="79"/>
+      <c r="S60" s="79"/>
+      <c r="T60" s="79"/>
+      <c r="V60" s="79"/>
+      <c r="W60" s="83" t="s">
+        <v>16</v>
+      </c>
+      <c r="X60" s="79"/>
+      <c r="Y60" s="77"/>
       <c r="Z60" s="1"/>
       <c r="AA60" s="1"/>
     </row>
@@ -3058,7 +3035,7 @@
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D64" s="33"/>
       <c r="E64" s="33"/>
@@ -3088,61 +3065,61 @@
     <row r="65" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
       <c r="B65" s="34"/>
-      <c r="C65" s="65" t="s">
-        <v>15</v>
+      <c r="C65" s="35" t="s">
+        <v>14</v>
       </c>
-      <c r="D65" s="54"/>
-      <c r="E65" s="54"/>
-      <c r="F65" s="54"/>
-      <c r="G65" s="54"/>
-      <c r="H65" s="54"/>
-      <c r="I65" s="54"/>
-      <c r="J65" s="54"/>
-      <c r="K65" s="54"/>
-      <c r="L65" s="54"/>
-      <c r="M65" s="54"/>
-      <c r="N65" s="54"/>
-      <c r="O65" s="54"/>
-      <c r="P65" s="54"/>
-      <c r="Q65" s="54"/>
-      <c r="R65" s="54"/>
-      <c r="S65" s="54"/>
-      <c r="T65" s="54"/>
-      <c r="U65" s="54"/>
-      <c r="V65" s="54"/>
-      <c r="W65" s="54"/>
-      <c r="X65" s="54"/>
-      <c r="Y65" s="54"/>
-      <c r="Z65" s="66"/>
+      <c r="D65" s="36"/>
+      <c r="E65" s="36"/>
+      <c r="F65" s="36"/>
+      <c r="G65" s="36"/>
+      <c r="H65" s="36"/>
+      <c r="I65" s="36"/>
+      <c r="J65" s="36"/>
+      <c r="K65" s="36"/>
+      <c r="L65" s="36"/>
+      <c r="M65" s="36"/>
+      <c r="N65" s="36"/>
+      <c r="O65" s="36"/>
+      <c r="P65" s="36"/>
+      <c r="Q65" s="36"/>
+      <c r="R65" s="36"/>
+      <c r="S65" s="36"/>
+      <c r="T65" s="36"/>
+      <c r="U65" s="36"/>
+      <c r="V65" s="36"/>
+      <c r="W65" s="36"/>
+      <c r="X65" s="36"/>
+      <c r="Y65" s="36"/>
+      <c r="Z65" s="37"/>
       <c r="AA65" s="34"/>
     </row>
     <row r="66" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
       <c r="B66" s="34"/>
-      <c r="C66" s="67"/>
-      <c r="D66" s="68"/>
-      <c r="E66" s="68"/>
-      <c r="F66" s="68"/>
-      <c r="G66" s="68"/>
-      <c r="H66" s="68"/>
-      <c r="I66" s="68"/>
-      <c r="J66" s="68"/>
-      <c r="K66" s="68"/>
-      <c r="L66" s="68"/>
-      <c r="M66" s="68"/>
-      <c r="N66" s="68"/>
-      <c r="O66" s="68"/>
-      <c r="P66" s="68"/>
-      <c r="Q66" s="68"/>
-      <c r="R66" s="68"/>
-      <c r="S66" s="68"/>
-      <c r="T66" s="68"/>
-      <c r="U66" s="68"/>
-      <c r="V66" s="68"/>
-      <c r="W66" s="68"/>
-      <c r="X66" s="68"/>
-      <c r="Y66" s="68"/>
-      <c r="Z66" s="69"/>
+      <c r="C66" s="38"/>
+      <c r="D66" s="39"/>
+      <c r="E66" s="39"/>
+      <c r="F66" s="39"/>
+      <c r="G66" s="39"/>
+      <c r="H66" s="39"/>
+      <c r="I66" s="39"/>
+      <c r="J66" s="39"/>
+      <c r="K66" s="39"/>
+      <c r="L66" s="39"/>
+      <c r="M66" s="39"/>
+      <c r="N66" s="39"/>
+      <c r="O66" s="39"/>
+      <c r="P66" s="39"/>
+      <c r="Q66" s="39"/>
+      <c r="R66" s="39"/>
+      <c r="S66" s="39"/>
+      <c r="T66" s="39"/>
+      <c r="U66" s="39"/>
+      <c r="V66" s="39"/>
+      <c r="W66" s="39"/>
+      <c r="X66" s="39"/>
+      <c r="Y66" s="39"/>
+      <c r="Z66" s="40"/>
       <c r="AA66" s="34"/>
     </row>
     <row r="67" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30232,9 +30209,22 @@
       <c r="AA1000" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="E59:X59"/>
-    <mergeCell ref="E60:X60"/>
+  <mergeCells count="23">
+    <mergeCell ref="B3:AA3"/>
+    <mergeCell ref="B4:AA4"/>
+    <mergeCell ref="B5:AA5"/>
+    <mergeCell ref="B6:AA6"/>
+    <mergeCell ref="H10:Z10"/>
+    <mergeCell ref="H12:T12"/>
+    <mergeCell ref="W12:Z12"/>
+    <mergeCell ref="B14:AA15"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="H17:Z17"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="H19:Z19"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="H21:Z21"/>
+    <mergeCell ref="B49:AA55"/>
     <mergeCell ref="C65:Z66"/>
     <mergeCell ref="B23:AA23"/>
     <mergeCell ref="B24:AA31"/>
@@ -30243,28 +30233,13 @@
     <mergeCell ref="B40:AA40"/>
     <mergeCell ref="B41:AA47"/>
     <mergeCell ref="B48:AA48"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="H19:Z19"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="H21:Z21"/>
-    <mergeCell ref="B49:AA55"/>
-    <mergeCell ref="H12:T12"/>
-    <mergeCell ref="W12:Z12"/>
-    <mergeCell ref="B14:AA15"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="H17:Z17"/>
-    <mergeCell ref="B3:AA3"/>
-    <mergeCell ref="B4:AA4"/>
-    <mergeCell ref="B5:AA5"/>
-    <mergeCell ref="B6:AA6"/>
-    <mergeCell ref="H10:Z10"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.98425196850393704" header="0" footer="0"/>
-  <pageSetup scale="62" orientation="portrait"/>
+  <pageSetup scale="62" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;A&amp;R&amp;P de</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/static/templates/tec02-A_template.xlsx
+++ b/static/templates/tec02-A_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\diseño-afk\static\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A600D408-5D33-4F97-9C4D-AE3485880350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4715DAA5-2055-4E49-8F4A-752C0D578400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -716,7 +716,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -820,10 +820,68 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
@@ -833,13 +891,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -847,66 +898,36 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1231,125 +1252,125 @@
     </row>
     <row r="3" spans="1:27" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
-      <c r="M3" s="62"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="62"/>
-      <c r="Q3" s="62"/>
-      <c r="R3" s="62"/>
-      <c r="S3" s="62"/>
-      <c r="T3" s="62"/>
-      <c r="U3" s="62"/>
-      <c r="V3" s="62"/>
-      <c r="W3" s="62"/>
-      <c r="X3" s="62"/>
-      <c r="Y3" s="62"/>
-      <c r="Z3" s="62"/>
-      <c r="AA3" s="63"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="43"/>
+      <c r="V3" s="43"/>
+      <c r="W3" s="43"/>
+      <c r="X3" s="43"/>
+      <c r="Y3" s="43"/>
+      <c r="Z3" s="43"/>
+      <c r="AA3" s="44"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
-      <c r="B4" s="74"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
-      <c r="L4" s="62"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="62"/>
-      <c r="Q4" s="62"/>
-      <c r="R4" s="62"/>
-      <c r="S4" s="62"/>
-      <c r="T4" s="62"/>
-      <c r="U4" s="62"/>
-      <c r="V4" s="62"/>
-      <c r="W4" s="62"/>
-      <c r="X4" s="62"/>
-      <c r="Y4" s="62"/>
-      <c r="Z4" s="62"/>
-      <c r="AA4" s="63"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="43"/>
+      <c r="T4" s="43"/>
+      <c r="U4" s="43"/>
+      <c r="V4" s="43"/>
+      <c r="W4" s="43"/>
+      <c r="X4" s="43"/>
+      <c r="Y4" s="43"/>
+      <c r="Z4" s="43"/>
+      <c r="AA4" s="44"/>
     </row>
     <row r="5" spans="1:27" ht="20" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
-      <c r="B5" s="75" t="s">
+      <c r="B5" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="62"/>
-      <c r="L5" s="62"/>
-      <c r="M5" s="62"/>
-      <c r="N5" s="62"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="62"/>
-      <c r="Q5" s="62"/>
-      <c r="R5" s="62"/>
-      <c r="S5" s="62"/>
-      <c r="T5" s="62"/>
-      <c r="U5" s="62"/>
-      <c r="V5" s="62"/>
-      <c r="W5" s="62"/>
-      <c r="X5" s="62"/>
-      <c r="Y5" s="62"/>
-      <c r="Z5" s="62"/>
-      <c r="AA5" s="63"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="43"/>
+      <c r="P5" s="43"/>
+      <c r="Q5" s="43"/>
+      <c r="R5" s="43"/>
+      <c r="S5" s="43"/>
+      <c r="T5" s="43"/>
+      <c r="U5" s="43"/>
+      <c r="V5" s="43"/>
+      <c r="W5" s="43"/>
+      <c r="X5" s="43"/>
+      <c r="Y5" s="43"/>
+      <c r="Z5" s="43"/>
+      <c r="AA5" s="44"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
-      <c r="B6" s="76" t="s">
+      <c r="B6" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="62"/>
-      <c r="M6" s="62"/>
-      <c r="N6" s="62"/>
-      <c r="O6" s="62"/>
-      <c r="P6" s="62"/>
-      <c r="Q6" s="62"/>
-      <c r="R6" s="62"/>
-      <c r="S6" s="62"/>
-      <c r="T6" s="62"/>
-      <c r="U6" s="62"/>
-      <c r="V6" s="62"/>
-      <c r="W6" s="62"/>
-      <c r="X6" s="62"/>
-      <c r="Y6" s="62"/>
-      <c r="Z6" s="62"/>
-      <c r="AA6" s="63"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="43"/>
+      <c r="Q6" s="43"/>
+      <c r="R6" s="43"/>
+      <c r="S6" s="43"/>
+      <c r="T6" s="43"/>
+      <c r="U6" s="43"/>
+      <c r="V6" s="43"/>
+      <c r="W6" s="43"/>
+      <c r="X6" s="43"/>
+      <c r="Y6" s="43"/>
+      <c r="Z6" s="43"/>
+      <c r="AA6" s="44"/>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2"/>
@@ -1448,25 +1469,25 @@
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="65"/>
-      <c r="J10" s="65"/>
-      <c r="K10" s="65"/>
-      <c r="L10" s="65"/>
-      <c r="M10" s="65"/>
-      <c r="N10" s="65"/>
-      <c r="O10" s="65"/>
-      <c r="P10" s="65"/>
-      <c r="Q10" s="65"/>
-      <c r="R10" s="65"/>
-      <c r="S10" s="65"/>
-      <c r="T10" s="65"/>
-      <c r="U10" s="65"/>
-      <c r="V10" s="65"/>
-      <c r="W10" s="65"/>
-      <c r="X10" s="65"/>
-      <c r="Y10" s="65"/>
-      <c r="Z10" s="66"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="49"/>
+      <c r="N10" s="49"/>
+      <c r="O10" s="49"/>
+      <c r="P10" s="49"/>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="49"/>
+      <c r="S10" s="49"/>
+      <c r="T10" s="49"/>
+      <c r="U10" s="49"/>
+      <c r="V10" s="49"/>
+      <c r="W10" s="49"/>
+      <c r="X10" s="49"/>
+      <c r="Y10" s="49"/>
+      <c r="Z10" s="50"/>
       <c r="AA10" s="11"/>
     </row>
     <row r="11" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1508,27 +1529,27 @@
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="65"/>
-      <c r="J12" s="65"/>
-      <c r="K12" s="65"/>
-      <c r="L12" s="65"/>
-      <c r="M12" s="65"/>
-      <c r="N12" s="65"/>
-      <c r="O12" s="65"/>
-      <c r="P12" s="65"/>
-      <c r="Q12" s="65"/>
-      <c r="R12" s="65"/>
-      <c r="S12" s="65"/>
-      <c r="T12" s="66"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="49"/>
+      <c r="K12" s="49"/>
+      <c r="L12" s="49"/>
+      <c r="M12" s="49"/>
+      <c r="N12" s="49"/>
+      <c r="O12" s="49"/>
+      <c r="P12" s="49"/>
+      <c r="Q12" s="49"/>
+      <c r="R12" s="49"/>
+      <c r="S12" s="49"/>
+      <c r="T12" s="50"/>
       <c r="U12" s="13"/>
       <c r="V12" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="W12" s="71"/>
-      <c r="X12" s="65"/>
-      <c r="Y12" s="65"/>
-      <c r="Z12" s="66"/>
+      <c r="W12" s="51"/>
+      <c r="X12" s="49"/>
+      <c r="Y12" s="49"/>
+      <c r="Z12" s="50"/>
       <c r="AA12" s="15"/>
     </row>
     <row r="13" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1562,63 +1583,63 @@
     </row>
     <row r="14" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
-      <c r="B14" s="72" t="s">
+      <c r="B14" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="59"/>
-      <c r="I14" s="59"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="59"/>
-      <c r="L14" s="59"/>
-      <c r="M14" s="59"/>
-      <c r="N14" s="59"/>
-      <c r="O14" s="59"/>
-      <c r="P14" s="59"/>
-      <c r="Q14" s="59"/>
-      <c r="R14" s="59"/>
-      <c r="S14" s="59"/>
-      <c r="T14" s="59"/>
-      <c r="U14" s="59"/>
-      <c r="V14" s="59"/>
-      <c r="W14" s="59"/>
-      <c r="X14" s="59"/>
-      <c r="Y14" s="59"/>
-      <c r="Z14" s="59"/>
-      <c r="AA14" s="60"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="53"/>
+      <c r="L14" s="53"/>
+      <c r="M14" s="53"/>
+      <c r="N14" s="53"/>
+      <c r="O14" s="53"/>
+      <c r="P14" s="53"/>
+      <c r="Q14" s="53"/>
+      <c r="R14" s="53"/>
+      <c r="S14" s="53"/>
+      <c r="T14" s="53"/>
+      <c r="U14" s="53"/>
+      <c r="V14" s="53"/>
+      <c r="W14" s="53"/>
+      <c r="X14" s="53"/>
+      <c r="Y14" s="53"/>
+      <c r="Z14" s="53"/>
+      <c r="AA14" s="54"/>
     </row>
     <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
-      <c r="B15" s="67"/>
-      <c r="C15" s="68"/>
-      <c r="D15" s="68"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="68"/>
-      <c r="G15" s="68"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="68"/>
-      <c r="K15" s="68"/>
-      <c r="L15" s="68"/>
-      <c r="M15" s="68"/>
-      <c r="N15" s="68"/>
-      <c r="O15" s="68"/>
-      <c r="P15" s="68"/>
-      <c r="Q15" s="68"/>
-      <c r="R15" s="68"/>
-      <c r="S15" s="68"/>
-      <c r="T15" s="68"/>
-      <c r="U15" s="68"/>
-      <c r="V15" s="68"/>
-      <c r="W15" s="68"/>
-      <c r="X15" s="68"/>
-      <c r="Y15" s="68"/>
-      <c r="Z15" s="68"/>
-      <c r="AA15" s="69"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="56"/>
+      <c r="K15" s="56"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="56"/>
+      <c r="N15" s="56"/>
+      <c r="O15" s="56"/>
+      <c r="P15" s="56"/>
+      <c r="Q15" s="56"/>
+      <c r="R15" s="56"/>
+      <c r="S15" s="56"/>
+      <c r="T15" s="56"/>
+      <c r="U15" s="56"/>
+      <c r="V15" s="56"/>
+      <c r="W15" s="56"/>
+      <c r="X15" s="56"/>
+      <c r="Y15" s="56"/>
+      <c r="Z15" s="56"/>
+      <c r="AA15" s="57"/>
     </row>
     <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
@@ -1651,33 +1672,33 @@
     </row>
     <row r="17" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
-      <c r="B17" s="61" t="s">
+      <c r="B17" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="63"/>
-      <c r="H17" s="64"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="65"/>
-      <c r="K17" s="65"/>
-      <c r="L17" s="65"/>
-      <c r="M17" s="65"/>
-      <c r="N17" s="65"/>
-      <c r="O17" s="65"/>
-      <c r="P17" s="65"/>
-      <c r="Q17" s="65"/>
-      <c r="R17" s="65"/>
-      <c r="S17" s="65"/>
-      <c r="T17" s="65"/>
-      <c r="U17" s="65"/>
-      <c r="V17" s="65"/>
-      <c r="W17" s="65"/>
-      <c r="X17" s="65"/>
-      <c r="Y17" s="65"/>
-      <c r="Z17" s="66"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="49"/>
+      <c r="J17" s="49"/>
+      <c r="K17" s="49"/>
+      <c r="L17" s="49"/>
+      <c r="M17" s="49"/>
+      <c r="N17" s="49"/>
+      <c r="O17" s="49"/>
+      <c r="P17" s="49"/>
+      <c r="Q17" s="49"/>
+      <c r="R17" s="49"/>
+      <c r="S17" s="49"/>
+      <c r="T17" s="49"/>
+      <c r="U17" s="49"/>
+      <c r="V17" s="49"/>
+      <c r="W17" s="49"/>
+      <c r="X17" s="49"/>
+      <c r="Y17" s="49"/>
+      <c r="Z17" s="50"/>
       <c r="AA17" s="24"/>
     </row>
     <row r="18" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1711,33 +1732,33 @@
     </row>
     <row r="19" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
-      <c r="B19" s="61" t="s">
+      <c r="B19" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="62"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="65"/>
-      <c r="K19" s="65"/>
-      <c r="L19" s="65"/>
-      <c r="M19" s="65"/>
-      <c r="N19" s="65"/>
-      <c r="O19" s="65"/>
-      <c r="P19" s="65"/>
-      <c r="Q19" s="65"/>
-      <c r="R19" s="65"/>
-      <c r="S19" s="65"/>
-      <c r="T19" s="65"/>
-      <c r="U19" s="65"/>
-      <c r="V19" s="65"/>
-      <c r="W19" s="65"/>
-      <c r="X19" s="65"/>
-      <c r="Y19" s="65"/>
-      <c r="Z19" s="66"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="49"/>
+      <c r="J19" s="49"/>
+      <c r="K19" s="49"/>
+      <c r="L19" s="49"/>
+      <c r="M19" s="49"/>
+      <c r="N19" s="49"/>
+      <c r="O19" s="49"/>
+      <c r="P19" s="49"/>
+      <c r="Q19" s="49"/>
+      <c r="R19" s="49"/>
+      <c r="S19" s="49"/>
+      <c r="T19" s="49"/>
+      <c r="U19" s="49"/>
+      <c r="V19" s="49"/>
+      <c r="W19" s="49"/>
+      <c r="X19" s="49"/>
+      <c r="Y19" s="49"/>
+      <c r="Z19" s="50"/>
       <c r="AA19" s="24"/>
     </row>
     <row r="20" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1771,33 +1792,33 @@
     </row>
     <row r="21" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
-      <c r="B21" s="61" t="s">
+      <c r="B21" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="62"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="63"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="65"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="65"/>
-      <c r="M21" s="65"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="65"/>
-      <c r="P21" s="65"/>
-      <c r="Q21" s="65"/>
-      <c r="R21" s="65"/>
-      <c r="S21" s="65"/>
-      <c r="T21" s="65"/>
-      <c r="U21" s="65"/>
-      <c r="V21" s="65"/>
-      <c r="W21" s="65"/>
-      <c r="X21" s="65"/>
-      <c r="Y21" s="65"/>
-      <c r="Z21" s="66"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="49"/>
+      <c r="K21" s="49"/>
+      <c r="L21" s="49"/>
+      <c r="M21" s="49"/>
+      <c r="N21" s="49"/>
+      <c r="O21" s="49"/>
+      <c r="P21" s="49"/>
+      <c r="Q21" s="49"/>
+      <c r="R21" s="49"/>
+      <c r="S21" s="49"/>
+      <c r="T21" s="49"/>
+      <c r="U21" s="49"/>
+      <c r="V21" s="49"/>
+      <c r="W21" s="49"/>
+      <c r="X21" s="49"/>
+      <c r="Y21" s="49"/>
+      <c r="Z21" s="50"/>
       <c r="AA21" s="24"/>
     </row>
     <row r="22" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1831,968 +1852,968 @@
     </row>
     <row r="23" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
-      <c r="B23" s="41" t="s">
+      <c r="B23" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="42"/>
-      <c r="K23" s="42"/>
-      <c r="L23" s="42"/>
-      <c r="M23" s="42"/>
-      <c r="N23" s="42"/>
-      <c r="O23" s="42"/>
-      <c r="P23" s="42"/>
-      <c r="Q23" s="42"/>
-      <c r="R23" s="42"/>
-      <c r="S23" s="42"/>
-      <c r="T23" s="42"/>
-      <c r="U23" s="42"/>
-      <c r="V23" s="42"/>
-      <c r="W23" s="42"/>
-      <c r="X23" s="42"/>
-      <c r="Y23" s="42"/>
-      <c r="Z23" s="42"/>
-      <c r="AA23" s="43"/>
+      <c r="C23" s="72"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="72"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="72"/>
+      <c r="M23" s="72"/>
+      <c r="N23" s="72"/>
+      <c r="O23" s="72"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="72"/>
+      <c r="T23" s="72"/>
+      <c r="U23" s="72"/>
+      <c r="V23" s="72"/>
+      <c r="W23" s="72"/>
+      <c r="X23" s="72"/>
+      <c r="Y23" s="72"/>
+      <c r="Z23" s="72"/>
+      <c r="AA23" s="73"/>
     </row>
     <row r="24" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
-      <c r="B24" s="44"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="36"/>
-      <c r="K24" s="36"/>
-      <c r="L24" s="36"/>
-      <c r="M24" s="36"/>
-      <c r="N24" s="36"/>
-      <c r="O24" s="36"/>
-      <c r="P24" s="36"/>
-      <c r="Q24" s="36"/>
-      <c r="R24" s="36"/>
-      <c r="S24" s="36"/>
-      <c r="T24" s="36"/>
-      <c r="U24" s="36"/>
-      <c r="V24" s="36"/>
-      <c r="W24" s="36"/>
-      <c r="X24" s="36"/>
-      <c r="Y24" s="36"/>
-      <c r="Z24" s="36"/>
-      <c r="AA24" s="45"/>
+      <c r="B24" s="60"/>
+      <c r="C24" s="83"/>
+      <c r="D24" s="83"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="83"/>
+      <c r="H24" s="83"/>
+      <c r="I24" s="83"/>
+      <c r="J24" s="83"/>
+      <c r="K24" s="83"/>
+      <c r="L24" s="83"/>
+      <c r="M24" s="83"/>
+      <c r="N24" s="83"/>
+      <c r="O24" s="83"/>
+      <c r="P24" s="83"/>
+      <c r="Q24" s="83"/>
+      <c r="R24" s="83"/>
+      <c r="S24" s="83"/>
+      <c r="T24" s="83"/>
+      <c r="U24" s="83"/>
+      <c r="V24" s="83"/>
+      <c r="W24" s="83"/>
+      <c r="X24" s="83"/>
+      <c r="Y24" s="83"/>
+      <c r="Z24" s="83"/>
+      <c r="AA24" s="84"/>
     </row>
     <row r="25" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
-      <c r="B25" s="46"/>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="47"/>
-      <c r="K25" s="47"/>
-      <c r="L25" s="47"/>
-      <c r="M25" s="47"/>
-      <c r="N25" s="47"/>
-      <c r="O25" s="47"/>
-      <c r="P25" s="47"/>
-      <c r="Q25" s="47"/>
-      <c r="R25" s="47"/>
-      <c r="S25" s="47"/>
-      <c r="T25" s="47"/>
-      <c r="U25" s="47"/>
-      <c r="V25" s="47"/>
-      <c r="W25" s="47"/>
-      <c r="X25" s="47"/>
-      <c r="Y25" s="47"/>
-      <c r="Z25" s="47"/>
-      <c r="AA25" s="48"/>
+      <c r="B25" s="85"/>
+      <c r="C25" s="86"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="86"/>
+      <c r="H25" s="86"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="K25" s="86"/>
+      <c r="L25" s="86"/>
+      <c r="M25" s="86"/>
+      <c r="N25" s="86"/>
+      <c r="O25" s="86"/>
+      <c r="P25" s="86"/>
+      <c r="Q25" s="86"/>
+      <c r="R25" s="86"/>
+      <c r="S25" s="86"/>
+      <c r="T25" s="86"/>
+      <c r="U25" s="86"/>
+      <c r="V25" s="86"/>
+      <c r="W25" s="86"/>
+      <c r="X25" s="86"/>
+      <c r="Y25" s="86"/>
+      <c r="Z25" s="86"/>
+      <c r="AA25" s="87"/>
     </row>
     <row r="26" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
-      <c r="B26" s="46"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="47"/>
-      <c r="K26" s="47"/>
-      <c r="L26" s="47"/>
-      <c r="M26" s="47"/>
-      <c r="N26" s="47"/>
-      <c r="O26" s="47"/>
-      <c r="P26" s="47"/>
-      <c r="Q26" s="47"/>
-      <c r="R26" s="47"/>
-      <c r="S26" s="47"/>
-      <c r="T26" s="47"/>
-      <c r="U26" s="47"/>
-      <c r="V26" s="47"/>
-      <c r="W26" s="47"/>
-      <c r="X26" s="47"/>
-      <c r="Y26" s="47"/>
-      <c r="Z26" s="47"/>
-      <c r="AA26" s="48"/>
+      <c r="B26" s="85"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="86"/>
+      <c r="E26" s="86"/>
+      <c r="F26" s="86"/>
+      <c r="G26" s="86"/>
+      <c r="H26" s="86"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="K26" s="86"/>
+      <c r="L26" s="86"/>
+      <c r="M26" s="86"/>
+      <c r="N26" s="86"/>
+      <c r="O26" s="86"/>
+      <c r="P26" s="86"/>
+      <c r="Q26" s="86"/>
+      <c r="R26" s="86"/>
+      <c r="S26" s="86"/>
+      <c r="T26" s="86"/>
+      <c r="U26" s="86"/>
+      <c r="V26" s="86"/>
+      <c r="W26" s="86"/>
+      <c r="X26" s="86"/>
+      <c r="Y26" s="86"/>
+      <c r="Z26" s="86"/>
+      <c r="AA26" s="87"/>
     </row>
     <row r="27" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
-      <c r="B27" s="46"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="47"/>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="47"/>
-      <c r="O27" s="47"/>
-      <c r="P27" s="47"/>
-      <c r="Q27" s="47"/>
-      <c r="R27" s="47"/>
-      <c r="S27" s="47"/>
-      <c r="T27" s="47"/>
-      <c r="U27" s="47"/>
-      <c r="V27" s="47"/>
-      <c r="W27" s="47"/>
-      <c r="X27" s="47"/>
-      <c r="Y27" s="47"/>
-      <c r="Z27" s="47"/>
-      <c r="AA27" s="48"/>
+      <c r="B27" s="85"/>
+      <c r="C27" s="86"/>
+      <c r="D27" s="86"/>
+      <c r="E27" s="86"/>
+      <c r="F27" s="86"/>
+      <c r="G27" s="86"/>
+      <c r="H27" s="86"/>
+      <c r="I27" s="86"/>
+      <c r="J27" s="86"/>
+      <c r="K27" s="86"/>
+      <c r="L27" s="86"/>
+      <c r="M27" s="86"/>
+      <c r="N27" s="86"/>
+      <c r="O27" s="86"/>
+      <c r="P27" s="86"/>
+      <c r="Q27" s="86"/>
+      <c r="R27" s="86"/>
+      <c r="S27" s="86"/>
+      <c r="T27" s="86"/>
+      <c r="U27" s="86"/>
+      <c r="V27" s="86"/>
+      <c r="W27" s="86"/>
+      <c r="X27" s="86"/>
+      <c r="Y27" s="86"/>
+      <c r="Z27" s="86"/>
+      <c r="AA27" s="87"/>
     </row>
     <row r="28" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
-      <c r="B28" s="46"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="47"/>
-      <c r="I28" s="47"/>
-      <c r="J28" s="47"/>
-      <c r="K28" s="47"/>
-      <c r="L28" s="47"/>
-      <c r="M28" s="47"/>
-      <c r="N28" s="47"/>
-      <c r="O28" s="47"/>
-      <c r="P28" s="47"/>
-      <c r="Q28" s="47"/>
-      <c r="R28" s="47"/>
-      <c r="S28" s="47"/>
-      <c r="T28" s="47"/>
-      <c r="U28" s="47"/>
-      <c r="V28" s="47"/>
-      <c r="W28" s="47"/>
-      <c r="X28" s="47"/>
-      <c r="Y28" s="47"/>
-      <c r="Z28" s="47"/>
-      <c r="AA28" s="48"/>
+      <c r="B28" s="85"/>
+      <c r="C28" s="86"/>
+      <c r="D28" s="86"/>
+      <c r="E28" s="86"/>
+      <c r="F28" s="86"/>
+      <c r="G28" s="86"/>
+      <c r="H28" s="86"/>
+      <c r="I28" s="86"/>
+      <c r="J28" s="86"/>
+      <c r="K28" s="86"/>
+      <c r="L28" s="86"/>
+      <c r="M28" s="86"/>
+      <c r="N28" s="86"/>
+      <c r="O28" s="86"/>
+      <c r="P28" s="86"/>
+      <c r="Q28" s="86"/>
+      <c r="R28" s="86"/>
+      <c r="S28" s="86"/>
+      <c r="T28" s="86"/>
+      <c r="U28" s="86"/>
+      <c r="V28" s="86"/>
+      <c r="W28" s="86"/>
+      <c r="X28" s="86"/>
+      <c r="Y28" s="86"/>
+      <c r="Z28" s="86"/>
+      <c r="AA28" s="87"/>
     </row>
     <row r="29" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
-      <c r="B29" s="46"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47"/>
-      <c r="M29" s="47"/>
-      <c r="N29" s="47"/>
-      <c r="O29" s="47"/>
-      <c r="P29" s="47"/>
-      <c r="Q29" s="47"/>
-      <c r="R29" s="47"/>
-      <c r="S29" s="47"/>
-      <c r="T29" s="47"/>
-      <c r="U29" s="47"/>
-      <c r="V29" s="47"/>
-      <c r="W29" s="47"/>
-      <c r="X29" s="47"/>
-      <c r="Y29" s="47"/>
-      <c r="Z29" s="47"/>
-      <c r="AA29" s="48"/>
+      <c r="B29" s="85"/>
+      <c r="C29" s="86"/>
+      <c r="D29" s="86"/>
+      <c r="E29" s="86"/>
+      <c r="F29" s="86"/>
+      <c r="G29" s="86"/>
+      <c r="H29" s="86"/>
+      <c r="I29" s="86"/>
+      <c r="J29" s="86"/>
+      <c r="K29" s="86"/>
+      <c r="L29" s="86"/>
+      <c r="M29" s="86"/>
+      <c r="N29" s="86"/>
+      <c r="O29" s="86"/>
+      <c r="P29" s="86"/>
+      <c r="Q29" s="86"/>
+      <c r="R29" s="86"/>
+      <c r="S29" s="86"/>
+      <c r="T29" s="86"/>
+      <c r="U29" s="86"/>
+      <c r="V29" s="86"/>
+      <c r="W29" s="86"/>
+      <c r="X29" s="86"/>
+      <c r="Y29" s="86"/>
+      <c r="Z29" s="86"/>
+      <c r="AA29" s="87"/>
     </row>
     <row r="30" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
-      <c r="B30" s="46"/>
-      <c r="C30" s="47"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="47"/>
-      <c r="F30" s="47"/>
-      <c r="G30" s="47"/>
-      <c r="H30" s="47"/>
-      <c r="I30" s="47"/>
-      <c r="J30" s="47"/>
-      <c r="K30" s="47"/>
-      <c r="L30" s="47"/>
-      <c r="M30" s="47"/>
-      <c r="N30" s="47"/>
-      <c r="O30" s="47"/>
-      <c r="P30" s="47"/>
-      <c r="Q30" s="47"/>
-      <c r="R30" s="47"/>
-      <c r="S30" s="47"/>
-      <c r="T30" s="47"/>
-      <c r="U30" s="47"/>
-      <c r="V30" s="47"/>
-      <c r="W30" s="47"/>
-      <c r="X30" s="47"/>
-      <c r="Y30" s="47"/>
-      <c r="Z30" s="47"/>
-      <c r="AA30" s="48"/>
+      <c r="B30" s="85"/>
+      <c r="C30" s="86"/>
+      <c r="D30" s="86"/>
+      <c r="E30" s="86"/>
+      <c r="F30" s="86"/>
+      <c r="G30" s="86"/>
+      <c r="H30" s="86"/>
+      <c r="I30" s="86"/>
+      <c r="J30" s="86"/>
+      <c r="K30" s="86"/>
+      <c r="L30" s="86"/>
+      <c r="M30" s="86"/>
+      <c r="N30" s="86"/>
+      <c r="O30" s="86"/>
+      <c r="P30" s="86"/>
+      <c r="Q30" s="86"/>
+      <c r="R30" s="86"/>
+      <c r="S30" s="86"/>
+      <c r="T30" s="86"/>
+      <c r="U30" s="86"/>
+      <c r="V30" s="86"/>
+      <c r="W30" s="86"/>
+      <c r="X30" s="86"/>
+      <c r="Y30" s="86"/>
+      <c r="Z30" s="86"/>
+      <c r="AA30" s="87"/>
     </row>
     <row r="31" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
-      <c r="B31" s="49"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="39"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="39"/>
-      <c r="J31" s="39"/>
-      <c r="K31" s="39"/>
-      <c r="L31" s="39"/>
-      <c r="M31" s="39"/>
-      <c r="N31" s="39"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="39"/>
-      <c r="Q31" s="39"/>
-      <c r="R31" s="39"/>
-      <c r="S31" s="39"/>
-      <c r="T31" s="39"/>
-      <c r="U31" s="39"/>
-      <c r="V31" s="39"/>
-      <c r="W31" s="39"/>
-      <c r="X31" s="39"/>
-      <c r="Y31" s="39"/>
-      <c r="Z31" s="39"/>
-      <c r="AA31" s="50"/>
+      <c r="B31" s="88"/>
+      <c r="C31" s="89"/>
+      <c r="D31" s="89"/>
+      <c r="E31" s="89"/>
+      <c r="F31" s="89"/>
+      <c r="G31" s="89"/>
+      <c r="H31" s="89"/>
+      <c r="I31" s="89"/>
+      <c r="J31" s="89"/>
+      <c r="K31" s="89"/>
+      <c r="L31" s="89"/>
+      <c r="M31" s="89"/>
+      <c r="N31" s="89"/>
+      <c r="O31" s="89"/>
+      <c r="P31" s="89"/>
+      <c r="Q31" s="89"/>
+      <c r="R31" s="89"/>
+      <c r="S31" s="89"/>
+      <c r="T31" s="89"/>
+      <c r="U31" s="89"/>
+      <c r="V31" s="89"/>
+      <c r="W31" s="89"/>
+      <c r="X31" s="89"/>
+      <c r="Y31" s="89"/>
+      <c r="Z31" s="89"/>
+      <c r="AA31" s="90"/>
     </row>
     <row r="32" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
-      <c r="B32" s="51" t="s">
+      <c r="B32" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="52"/>
-      <c r="K32" s="52"/>
-      <c r="L32" s="52"/>
-      <c r="M32" s="52"/>
-      <c r="N32" s="52"/>
-      <c r="O32" s="52"/>
-      <c r="P32" s="52"/>
-      <c r="Q32" s="52"/>
-      <c r="R32" s="52"/>
-      <c r="S32" s="52"/>
-      <c r="T32" s="52"/>
-      <c r="U32" s="52"/>
-      <c r="V32" s="52"/>
-      <c r="W32" s="52"/>
-      <c r="X32" s="52"/>
-      <c r="Y32" s="52"/>
-      <c r="Z32" s="52"/>
-      <c r="AA32" s="53"/>
+      <c r="C32" s="77"/>
+      <c r="D32" s="77"/>
+      <c r="E32" s="77"/>
+      <c r="F32" s="77"/>
+      <c r="G32" s="77"/>
+      <c r="H32" s="77"/>
+      <c r="I32" s="77"/>
+      <c r="J32" s="77"/>
+      <c r="K32" s="77"/>
+      <c r="L32" s="77"/>
+      <c r="M32" s="77"/>
+      <c r="N32" s="77"/>
+      <c r="O32" s="77"/>
+      <c r="P32" s="77"/>
+      <c r="Q32" s="77"/>
+      <c r="R32" s="77"/>
+      <c r="S32" s="77"/>
+      <c r="T32" s="77"/>
+      <c r="U32" s="77"/>
+      <c r="V32" s="77"/>
+      <c r="W32" s="77"/>
+      <c r="X32" s="77"/>
+      <c r="Y32" s="77"/>
+      <c r="Z32" s="77"/>
+      <c r="AA32" s="78"/>
     </row>
     <row r="33" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
-      <c r="B33" s="54"/>
-      <c r="C33" s="36"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
-      <c r="J33" s="36"/>
-      <c r="K33" s="36"/>
-      <c r="L33" s="36"/>
-      <c r="M33" s="36"/>
-      <c r="N33" s="36"/>
-      <c r="O33" s="36"/>
-      <c r="P33" s="36"/>
-      <c r="Q33" s="36"/>
-      <c r="R33" s="36"/>
-      <c r="S33" s="36"/>
-      <c r="T33" s="36"/>
-      <c r="U33" s="36"/>
-      <c r="V33" s="36"/>
-      <c r="W33" s="36"/>
-      <c r="X33" s="36"/>
-      <c r="Y33" s="36"/>
-      <c r="Z33" s="36"/>
-      <c r="AA33" s="45"/>
+      <c r="B33" s="60"/>
+      <c r="C33" s="61"/>
+      <c r="D33" s="61"/>
+      <c r="E33" s="61"/>
+      <c r="F33" s="61"/>
+      <c r="G33" s="61"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="61"/>
+      <c r="J33" s="61"/>
+      <c r="K33" s="61"/>
+      <c r="L33" s="61"/>
+      <c r="M33" s="61"/>
+      <c r="N33" s="61"/>
+      <c r="O33" s="61"/>
+      <c r="P33" s="61"/>
+      <c r="Q33" s="61"/>
+      <c r="R33" s="61"/>
+      <c r="S33" s="61"/>
+      <c r="T33" s="61"/>
+      <c r="U33" s="61"/>
+      <c r="V33" s="61"/>
+      <c r="W33" s="61"/>
+      <c r="X33" s="61"/>
+      <c r="Y33" s="61"/>
+      <c r="Z33" s="61"/>
+      <c r="AA33" s="62"/>
     </row>
     <row r="34" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
-      <c r="B34" s="46"/>
-      <c r="C34" s="47"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="47"/>
-      <c r="G34" s="47"/>
-      <c r="H34" s="47"/>
-      <c r="I34" s="47"/>
-      <c r="J34" s="47"/>
-      <c r="K34" s="47"/>
-      <c r="L34" s="47"/>
-      <c r="M34" s="47"/>
-      <c r="N34" s="47"/>
-      <c r="O34" s="47"/>
-      <c r="P34" s="47"/>
-      <c r="Q34" s="47"/>
-      <c r="R34" s="47"/>
-      <c r="S34" s="47"/>
-      <c r="T34" s="47"/>
-      <c r="U34" s="47"/>
-      <c r="V34" s="47"/>
-      <c r="W34" s="47"/>
-      <c r="X34" s="47"/>
-      <c r="Y34" s="47"/>
-      <c r="Z34" s="47"/>
-      <c r="AA34" s="48"/>
+      <c r="B34" s="63"/>
+      <c r="C34" s="64"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="64"/>
+      <c r="F34" s="64"/>
+      <c r="G34" s="64"/>
+      <c r="H34" s="64"/>
+      <c r="I34" s="64"/>
+      <c r="J34" s="64"/>
+      <c r="K34" s="64"/>
+      <c r="L34" s="64"/>
+      <c r="M34" s="64"/>
+      <c r="N34" s="64"/>
+      <c r="O34" s="64"/>
+      <c r="P34" s="64"/>
+      <c r="Q34" s="64"/>
+      <c r="R34" s="64"/>
+      <c r="S34" s="64"/>
+      <c r="T34" s="64"/>
+      <c r="U34" s="64"/>
+      <c r="V34" s="64"/>
+      <c r="W34" s="64"/>
+      <c r="X34" s="64"/>
+      <c r="Y34" s="64"/>
+      <c r="Z34" s="64"/>
+      <c r="AA34" s="65"/>
     </row>
     <row r="35" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
-      <c r="B35" s="46"/>
-      <c r="C35" s="47"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="47"/>
-      <c r="I35" s="47"/>
-      <c r="J35" s="47"/>
-      <c r="K35" s="47"/>
-      <c r="L35" s="47"/>
-      <c r="M35" s="47"/>
-      <c r="N35" s="47"/>
-      <c r="O35" s="47"/>
-      <c r="P35" s="47"/>
-      <c r="Q35" s="47"/>
-      <c r="R35" s="47"/>
-      <c r="S35" s="47"/>
-      <c r="T35" s="47"/>
-      <c r="U35" s="47"/>
-      <c r="V35" s="47"/>
-      <c r="W35" s="47"/>
-      <c r="X35" s="47"/>
-      <c r="Y35" s="47"/>
-      <c r="Z35" s="47"/>
-      <c r="AA35" s="48"/>
+      <c r="B35" s="63"/>
+      <c r="C35" s="64"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="64"/>
+      <c r="F35" s="64"/>
+      <c r="G35" s="64"/>
+      <c r="H35" s="64"/>
+      <c r="I35" s="64"/>
+      <c r="J35" s="64"/>
+      <c r="K35" s="64"/>
+      <c r="L35" s="64"/>
+      <c r="M35" s="64"/>
+      <c r="N35" s="64"/>
+      <c r="O35" s="64"/>
+      <c r="P35" s="64"/>
+      <c r="Q35" s="64"/>
+      <c r="R35" s="64"/>
+      <c r="S35" s="64"/>
+      <c r="T35" s="64"/>
+      <c r="U35" s="64"/>
+      <c r="V35" s="64"/>
+      <c r="W35" s="64"/>
+      <c r="X35" s="64"/>
+      <c r="Y35" s="64"/>
+      <c r="Z35" s="64"/>
+      <c r="AA35" s="65"/>
     </row>
     <row r="36" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
-      <c r="B36" s="46"/>
-      <c r="C36" s="47"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="47"/>
-      <c r="H36" s="47"/>
-      <c r="I36" s="47"/>
-      <c r="J36" s="47"/>
-      <c r="K36" s="47"/>
-      <c r="L36" s="47"/>
-      <c r="M36" s="47"/>
-      <c r="N36" s="47"/>
-      <c r="O36" s="47"/>
-      <c r="P36" s="47"/>
-      <c r="Q36" s="47"/>
-      <c r="R36" s="47"/>
-      <c r="S36" s="47"/>
-      <c r="T36" s="47"/>
-      <c r="U36" s="47"/>
-      <c r="V36" s="47"/>
-      <c r="W36" s="47"/>
-      <c r="X36" s="47"/>
-      <c r="Y36" s="47"/>
-      <c r="Z36" s="47"/>
-      <c r="AA36" s="48"/>
+      <c r="B36" s="63"/>
+      <c r="C36" s="64"/>
+      <c r="D36" s="64"/>
+      <c r="E36" s="64"/>
+      <c r="F36" s="64"/>
+      <c r="G36" s="64"/>
+      <c r="H36" s="64"/>
+      <c r="I36" s="64"/>
+      <c r="J36" s="64"/>
+      <c r="K36" s="64"/>
+      <c r="L36" s="64"/>
+      <c r="M36" s="64"/>
+      <c r="N36" s="64"/>
+      <c r="O36" s="64"/>
+      <c r="P36" s="64"/>
+      <c r="Q36" s="64"/>
+      <c r="R36" s="64"/>
+      <c r="S36" s="64"/>
+      <c r="T36" s="64"/>
+      <c r="U36" s="64"/>
+      <c r="V36" s="64"/>
+      <c r="W36" s="64"/>
+      <c r="X36" s="64"/>
+      <c r="Y36" s="64"/>
+      <c r="Z36" s="64"/>
+      <c r="AA36" s="65"/>
     </row>
     <row r="37" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
-      <c r="B37" s="46"/>
-      <c r="C37" s="47"/>
-      <c r="D37" s="47"/>
-      <c r="E37" s="47"/>
-      <c r="F37" s="47"/>
-      <c r="G37" s="47"/>
-      <c r="H37" s="47"/>
-      <c r="I37" s="47"/>
-      <c r="J37" s="47"/>
-      <c r="K37" s="47"/>
-      <c r="L37" s="47"/>
-      <c r="M37" s="47"/>
-      <c r="N37" s="47"/>
-      <c r="O37" s="47"/>
-      <c r="P37" s="47"/>
-      <c r="Q37" s="47"/>
-      <c r="R37" s="47"/>
-      <c r="S37" s="47"/>
-      <c r="T37" s="47"/>
-      <c r="U37" s="47"/>
-      <c r="V37" s="47"/>
-      <c r="W37" s="47"/>
-      <c r="X37" s="47"/>
-      <c r="Y37" s="47"/>
-      <c r="Z37" s="47"/>
-      <c r="AA37" s="48"/>
+      <c r="B37" s="63"/>
+      <c r="C37" s="64"/>
+      <c r="D37" s="64"/>
+      <c r="E37" s="64"/>
+      <c r="F37" s="64"/>
+      <c r="G37" s="64"/>
+      <c r="H37" s="64"/>
+      <c r="I37" s="64"/>
+      <c r="J37" s="64"/>
+      <c r="K37" s="64"/>
+      <c r="L37" s="64"/>
+      <c r="M37" s="64"/>
+      <c r="N37" s="64"/>
+      <c r="O37" s="64"/>
+      <c r="P37" s="64"/>
+      <c r="Q37" s="64"/>
+      <c r="R37" s="64"/>
+      <c r="S37" s="64"/>
+      <c r="T37" s="64"/>
+      <c r="U37" s="64"/>
+      <c r="V37" s="64"/>
+      <c r="W37" s="64"/>
+      <c r="X37" s="64"/>
+      <c r="Y37" s="64"/>
+      <c r="Z37" s="64"/>
+      <c r="AA37" s="65"/>
     </row>
     <row r="38" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
-      <c r="B38" s="46"/>
-      <c r="C38" s="47"/>
-      <c r="D38" s="47"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="47"/>
-      <c r="G38" s="47"/>
-      <c r="H38" s="47"/>
-      <c r="I38" s="47"/>
-      <c r="J38" s="47"/>
-      <c r="K38" s="47"/>
-      <c r="L38" s="47"/>
-      <c r="M38" s="47"/>
-      <c r="N38" s="47"/>
-      <c r="O38" s="47"/>
-      <c r="P38" s="47"/>
-      <c r="Q38" s="47"/>
-      <c r="R38" s="47"/>
-      <c r="S38" s="47"/>
-      <c r="T38" s="47"/>
-      <c r="U38" s="47"/>
-      <c r="V38" s="47"/>
-      <c r="W38" s="47"/>
-      <c r="X38" s="47"/>
-      <c r="Y38" s="47"/>
-      <c r="Z38" s="47"/>
-      <c r="AA38" s="48"/>
+      <c r="B38" s="63"/>
+      <c r="C38" s="64"/>
+      <c r="D38" s="64"/>
+      <c r="E38" s="64"/>
+      <c r="F38" s="64"/>
+      <c r="G38" s="64"/>
+      <c r="H38" s="64"/>
+      <c r="I38" s="64"/>
+      <c r="J38" s="64"/>
+      <c r="K38" s="64"/>
+      <c r="L38" s="64"/>
+      <c r="M38" s="64"/>
+      <c r="N38" s="64"/>
+      <c r="O38" s="64"/>
+      <c r="P38" s="64"/>
+      <c r="Q38" s="64"/>
+      <c r="R38" s="64"/>
+      <c r="S38" s="64"/>
+      <c r="T38" s="64"/>
+      <c r="U38" s="64"/>
+      <c r="V38" s="64"/>
+      <c r="W38" s="64"/>
+      <c r="X38" s="64"/>
+      <c r="Y38" s="64"/>
+      <c r="Z38" s="64"/>
+      <c r="AA38" s="65"/>
     </row>
     <row r="39" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
-      <c r="B39" s="49"/>
-      <c r="C39" s="39"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="39"/>
-      <c r="G39" s="39"/>
-      <c r="H39" s="39"/>
-      <c r="I39" s="39"/>
-      <c r="J39" s="39"/>
-      <c r="K39" s="39"/>
-      <c r="L39" s="39"/>
-      <c r="M39" s="39"/>
-      <c r="N39" s="39"/>
-      <c r="O39" s="39"/>
-      <c r="P39" s="39"/>
-      <c r="Q39" s="39"/>
-      <c r="R39" s="39"/>
-      <c r="S39" s="39"/>
-      <c r="T39" s="39"/>
-      <c r="U39" s="39"/>
-      <c r="V39" s="39"/>
-      <c r="W39" s="39"/>
-      <c r="X39" s="39"/>
-      <c r="Y39" s="39"/>
-      <c r="Z39" s="39"/>
-      <c r="AA39" s="50"/>
+      <c r="B39" s="74"/>
+      <c r="C39" s="69"/>
+      <c r="D39" s="69"/>
+      <c r="E39" s="69"/>
+      <c r="F39" s="69"/>
+      <c r="G39" s="69"/>
+      <c r="H39" s="69"/>
+      <c r="I39" s="69"/>
+      <c r="J39" s="69"/>
+      <c r="K39" s="69"/>
+      <c r="L39" s="69"/>
+      <c r="M39" s="69"/>
+      <c r="N39" s="69"/>
+      <c r="O39" s="69"/>
+      <c r="P39" s="69"/>
+      <c r="Q39" s="69"/>
+      <c r="R39" s="69"/>
+      <c r="S39" s="69"/>
+      <c r="T39" s="69"/>
+      <c r="U39" s="69"/>
+      <c r="V39" s="69"/>
+      <c r="W39" s="69"/>
+      <c r="X39" s="69"/>
+      <c r="Y39" s="69"/>
+      <c r="Z39" s="69"/>
+      <c r="AA39" s="75"/>
     </row>
     <row r="40" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
-      <c r="B40" s="51" t="s">
+      <c r="B40" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="52"/>
-      <c r="D40" s="52"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
-      <c r="G40" s="52"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="52"/>
-      <c r="J40" s="52"/>
-      <c r="K40" s="52"/>
-      <c r="L40" s="52"/>
-      <c r="M40" s="52"/>
-      <c r="N40" s="52"/>
-      <c r="O40" s="52"/>
-      <c r="P40" s="52"/>
-      <c r="Q40" s="52"/>
-      <c r="R40" s="52"/>
-      <c r="S40" s="52"/>
-      <c r="T40" s="52"/>
-      <c r="U40" s="52"/>
-      <c r="V40" s="52"/>
-      <c r="W40" s="52"/>
-      <c r="X40" s="52"/>
-      <c r="Y40" s="52"/>
-      <c r="Z40" s="52"/>
-      <c r="AA40" s="53"/>
+      <c r="C40" s="77"/>
+      <c r="D40" s="77"/>
+      <c r="E40" s="77"/>
+      <c r="F40" s="77"/>
+      <c r="G40" s="77"/>
+      <c r="H40" s="77"/>
+      <c r="I40" s="77"/>
+      <c r="J40" s="77"/>
+      <c r="K40" s="77"/>
+      <c r="L40" s="77"/>
+      <c r="M40" s="77"/>
+      <c r="N40" s="77"/>
+      <c r="O40" s="77"/>
+      <c r="P40" s="77"/>
+      <c r="Q40" s="77"/>
+      <c r="R40" s="77"/>
+      <c r="S40" s="77"/>
+      <c r="T40" s="77"/>
+      <c r="U40" s="77"/>
+      <c r="V40" s="77"/>
+      <c r="W40" s="77"/>
+      <c r="X40" s="77"/>
+      <c r="Y40" s="77"/>
+      <c r="Z40" s="77"/>
+      <c r="AA40" s="78"/>
     </row>
     <row r="41" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
-      <c r="B41" s="54"/>
-      <c r="C41" s="36"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="36"/>
-      <c r="G41" s="36"/>
-      <c r="H41" s="36"/>
-      <c r="I41" s="36"/>
-      <c r="J41" s="36"/>
-      <c r="K41" s="36"/>
-      <c r="L41" s="36"/>
-      <c r="M41" s="36"/>
-      <c r="N41" s="36"/>
-      <c r="O41" s="36"/>
-      <c r="P41" s="36"/>
-      <c r="Q41" s="36"/>
-      <c r="R41" s="36"/>
-      <c r="S41" s="36"/>
-      <c r="T41" s="36"/>
-      <c r="U41" s="36"/>
-      <c r="V41" s="36"/>
-      <c r="W41" s="36"/>
-      <c r="X41" s="36"/>
-      <c r="Y41" s="36"/>
-      <c r="Z41" s="36"/>
-      <c r="AA41" s="45"/>
+      <c r="B41" s="60"/>
+      <c r="C41" s="61"/>
+      <c r="D41" s="61"/>
+      <c r="E41" s="61"/>
+      <c r="F41" s="61"/>
+      <c r="G41" s="61"/>
+      <c r="H41" s="61"/>
+      <c r="I41" s="61"/>
+      <c r="J41" s="61"/>
+      <c r="K41" s="61"/>
+      <c r="L41" s="61"/>
+      <c r="M41" s="61"/>
+      <c r="N41" s="61"/>
+      <c r="O41" s="61"/>
+      <c r="P41" s="61"/>
+      <c r="Q41" s="61"/>
+      <c r="R41" s="61"/>
+      <c r="S41" s="61"/>
+      <c r="T41" s="61"/>
+      <c r="U41" s="61"/>
+      <c r="V41" s="61"/>
+      <c r="W41" s="61"/>
+      <c r="X41" s="61"/>
+      <c r="Y41" s="61"/>
+      <c r="Z41" s="61"/>
+      <c r="AA41" s="62"/>
     </row>
     <row r="42" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
-      <c r="B42" s="46"/>
-      <c r="C42" s="47"/>
-      <c r="D42" s="47"/>
-      <c r="E42" s="47"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="47"/>
-      <c r="H42" s="47"/>
-      <c r="I42" s="47"/>
-      <c r="J42" s="47"/>
-      <c r="K42" s="47"/>
-      <c r="L42" s="47"/>
-      <c r="M42" s="47"/>
-      <c r="N42" s="47"/>
-      <c r="O42" s="47"/>
-      <c r="P42" s="47"/>
-      <c r="Q42" s="47"/>
-      <c r="R42" s="47"/>
-      <c r="S42" s="47"/>
-      <c r="T42" s="47"/>
-      <c r="U42" s="47"/>
-      <c r="V42" s="47"/>
-      <c r="W42" s="47"/>
-      <c r="X42" s="47"/>
-      <c r="Y42" s="47"/>
-      <c r="Z42" s="47"/>
-      <c r="AA42" s="48"/>
+      <c r="B42" s="63"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="64"/>
+      <c r="H42" s="64"/>
+      <c r="I42" s="64"/>
+      <c r="J42" s="64"/>
+      <c r="K42" s="64"/>
+      <c r="L42" s="64"/>
+      <c r="M42" s="64"/>
+      <c r="N42" s="64"/>
+      <c r="O42" s="64"/>
+      <c r="P42" s="64"/>
+      <c r="Q42" s="64"/>
+      <c r="R42" s="64"/>
+      <c r="S42" s="64"/>
+      <c r="T42" s="64"/>
+      <c r="U42" s="64"/>
+      <c r="V42" s="64"/>
+      <c r="W42" s="64"/>
+      <c r="X42" s="64"/>
+      <c r="Y42" s="64"/>
+      <c r="Z42" s="64"/>
+      <c r="AA42" s="65"/>
     </row>
     <row r="43" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
-      <c r="B43" s="46"/>
-      <c r="C43" s="47"/>
-      <c r="D43" s="47"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="47"/>
-      <c r="G43" s="47"/>
-      <c r="H43" s="47"/>
-      <c r="I43" s="47"/>
-      <c r="J43" s="47"/>
-      <c r="K43" s="47"/>
-      <c r="L43" s="47"/>
-      <c r="M43" s="47"/>
-      <c r="N43" s="47"/>
-      <c r="O43" s="47"/>
-      <c r="P43" s="47"/>
-      <c r="Q43" s="47"/>
-      <c r="R43" s="47"/>
-      <c r="S43" s="47"/>
-      <c r="T43" s="47"/>
-      <c r="U43" s="47"/>
-      <c r="V43" s="47"/>
-      <c r="W43" s="47"/>
-      <c r="X43" s="47"/>
-      <c r="Y43" s="47"/>
-      <c r="Z43" s="47"/>
-      <c r="AA43" s="48"/>
+      <c r="B43" s="63"/>
+      <c r="C43" s="64"/>
+      <c r="D43" s="64"/>
+      <c r="E43" s="64"/>
+      <c r="F43" s="64"/>
+      <c r="G43" s="64"/>
+      <c r="H43" s="64"/>
+      <c r="I43" s="64"/>
+      <c r="J43" s="64"/>
+      <c r="K43" s="64"/>
+      <c r="L43" s="64"/>
+      <c r="M43" s="64"/>
+      <c r="N43" s="64"/>
+      <c r="O43" s="64"/>
+      <c r="P43" s="64"/>
+      <c r="Q43" s="64"/>
+      <c r="R43" s="64"/>
+      <c r="S43" s="64"/>
+      <c r="T43" s="64"/>
+      <c r="U43" s="64"/>
+      <c r="V43" s="64"/>
+      <c r="W43" s="64"/>
+      <c r="X43" s="64"/>
+      <c r="Y43" s="64"/>
+      <c r="Z43" s="64"/>
+      <c r="AA43" s="65"/>
     </row>
     <row r="44" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
-      <c r="B44" s="46"/>
-      <c r="C44" s="47"/>
-      <c r="D44" s="47"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="47"/>
-      <c r="G44" s="47"/>
-      <c r="H44" s="47"/>
-      <c r="I44" s="47"/>
-      <c r="J44" s="47"/>
-      <c r="K44" s="47"/>
-      <c r="L44" s="47"/>
-      <c r="M44" s="47"/>
-      <c r="N44" s="47"/>
-      <c r="O44" s="47"/>
-      <c r="P44" s="47"/>
-      <c r="Q44" s="47"/>
-      <c r="R44" s="47"/>
-      <c r="S44" s="47"/>
-      <c r="T44" s="47"/>
-      <c r="U44" s="47"/>
-      <c r="V44" s="47"/>
-      <c r="W44" s="47"/>
-      <c r="X44" s="47"/>
-      <c r="Y44" s="47"/>
-      <c r="Z44" s="47"/>
-      <c r="AA44" s="48"/>
+      <c r="B44" s="63"/>
+      <c r="C44" s="64"/>
+      <c r="D44" s="64"/>
+      <c r="E44" s="64"/>
+      <c r="F44" s="64"/>
+      <c r="G44" s="64"/>
+      <c r="H44" s="64"/>
+      <c r="I44" s="64"/>
+      <c r="J44" s="64"/>
+      <c r="K44" s="64"/>
+      <c r="L44" s="64"/>
+      <c r="M44" s="64"/>
+      <c r="N44" s="64"/>
+      <c r="O44" s="64"/>
+      <c r="P44" s="64"/>
+      <c r="Q44" s="64"/>
+      <c r="R44" s="64"/>
+      <c r="S44" s="64"/>
+      <c r="T44" s="64"/>
+      <c r="U44" s="64"/>
+      <c r="V44" s="64"/>
+      <c r="W44" s="64"/>
+      <c r="X44" s="64"/>
+      <c r="Y44" s="64"/>
+      <c r="Z44" s="64"/>
+      <c r="AA44" s="65"/>
     </row>
     <row r="45" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
-      <c r="B45" s="46"/>
-      <c r="C45" s="47"/>
-      <c r="D45" s="47"/>
-      <c r="E45" s="47"/>
-      <c r="F45" s="47"/>
-      <c r="G45" s="47"/>
-      <c r="H45" s="47"/>
-      <c r="I45" s="47"/>
-      <c r="J45" s="47"/>
-      <c r="K45" s="47"/>
-      <c r="L45" s="47"/>
-      <c r="M45" s="47"/>
-      <c r="N45" s="47"/>
-      <c r="O45" s="47"/>
-      <c r="P45" s="47"/>
-      <c r="Q45" s="47"/>
-      <c r="R45" s="47"/>
-      <c r="S45" s="47"/>
-      <c r="T45" s="47"/>
-      <c r="U45" s="47"/>
-      <c r="V45" s="47"/>
-      <c r="W45" s="47"/>
-      <c r="X45" s="47"/>
-      <c r="Y45" s="47"/>
-      <c r="Z45" s="47"/>
-      <c r="AA45" s="48"/>
+      <c r="B45" s="63"/>
+      <c r="C45" s="64"/>
+      <c r="D45" s="64"/>
+      <c r="E45" s="64"/>
+      <c r="F45" s="64"/>
+      <c r="G45" s="64"/>
+      <c r="H45" s="64"/>
+      <c r="I45" s="64"/>
+      <c r="J45" s="64"/>
+      <c r="K45" s="64"/>
+      <c r="L45" s="64"/>
+      <c r="M45" s="64"/>
+      <c r="N45" s="64"/>
+      <c r="O45" s="64"/>
+      <c r="P45" s="64"/>
+      <c r="Q45" s="64"/>
+      <c r="R45" s="64"/>
+      <c r="S45" s="64"/>
+      <c r="T45" s="64"/>
+      <c r="U45" s="64"/>
+      <c r="V45" s="64"/>
+      <c r="W45" s="64"/>
+      <c r="X45" s="64"/>
+      <c r="Y45" s="64"/>
+      <c r="Z45" s="64"/>
+      <c r="AA45" s="65"/>
     </row>
     <row r="46" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
-      <c r="B46" s="46"/>
-      <c r="C46" s="47"/>
-      <c r="D46" s="47"/>
-      <c r="E46" s="47"/>
-      <c r="F46" s="47"/>
-      <c r="G46" s="47"/>
-      <c r="H46" s="47"/>
-      <c r="I46" s="47"/>
-      <c r="J46" s="47"/>
-      <c r="K46" s="47"/>
-      <c r="L46" s="47"/>
-      <c r="M46" s="47"/>
-      <c r="N46" s="47"/>
-      <c r="O46" s="47"/>
-      <c r="P46" s="47"/>
-      <c r="Q46" s="47"/>
-      <c r="R46" s="47"/>
-      <c r="S46" s="47"/>
-      <c r="T46" s="47"/>
-      <c r="U46" s="47"/>
-      <c r="V46" s="47"/>
-      <c r="W46" s="47"/>
-      <c r="X46" s="47"/>
-      <c r="Y46" s="47"/>
-      <c r="Z46" s="47"/>
-      <c r="AA46" s="48"/>
+      <c r="B46" s="63"/>
+      <c r="C46" s="64"/>
+      <c r="D46" s="64"/>
+      <c r="E46" s="64"/>
+      <c r="F46" s="64"/>
+      <c r="G46" s="64"/>
+      <c r="H46" s="64"/>
+      <c r="I46" s="64"/>
+      <c r="J46" s="64"/>
+      <c r="K46" s="64"/>
+      <c r="L46" s="64"/>
+      <c r="M46" s="64"/>
+      <c r="N46" s="64"/>
+      <c r="O46" s="64"/>
+      <c r="P46" s="64"/>
+      <c r="Q46" s="64"/>
+      <c r="R46" s="64"/>
+      <c r="S46" s="64"/>
+      <c r="T46" s="64"/>
+      <c r="U46" s="64"/>
+      <c r="V46" s="64"/>
+      <c r="W46" s="64"/>
+      <c r="X46" s="64"/>
+      <c r="Y46" s="64"/>
+      <c r="Z46" s="64"/>
+      <c r="AA46" s="65"/>
     </row>
     <row r="47" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
-      <c r="B47" s="55"/>
-      <c r="C47" s="56"/>
-      <c r="D47" s="56"/>
-      <c r="E47" s="56"/>
-      <c r="F47" s="56"/>
-      <c r="G47" s="56"/>
-      <c r="H47" s="56"/>
-      <c r="I47" s="56"/>
-      <c r="J47" s="56"/>
-      <c r="K47" s="56"/>
-      <c r="L47" s="56"/>
-      <c r="M47" s="56"/>
-      <c r="N47" s="56"/>
-      <c r="O47" s="56"/>
-      <c r="P47" s="56"/>
-      <c r="Q47" s="56"/>
-      <c r="R47" s="56"/>
-      <c r="S47" s="56"/>
-      <c r="T47" s="56"/>
-      <c r="U47" s="56"/>
-      <c r="V47" s="56"/>
-      <c r="W47" s="56"/>
-      <c r="X47" s="56"/>
-      <c r="Y47" s="56"/>
-      <c r="Z47" s="56"/>
-      <c r="AA47" s="57"/>
+      <c r="B47" s="79"/>
+      <c r="C47" s="80"/>
+      <c r="D47" s="80"/>
+      <c r="E47" s="80"/>
+      <c r="F47" s="80"/>
+      <c r="G47" s="80"/>
+      <c r="H47" s="80"/>
+      <c r="I47" s="80"/>
+      <c r="J47" s="80"/>
+      <c r="K47" s="80"/>
+      <c r="L47" s="80"/>
+      <c r="M47" s="80"/>
+      <c r="N47" s="80"/>
+      <c r="O47" s="80"/>
+      <c r="P47" s="80"/>
+      <c r="Q47" s="80"/>
+      <c r="R47" s="80"/>
+      <c r="S47" s="80"/>
+      <c r="T47" s="80"/>
+      <c r="U47" s="80"/>
+      <c r="V47" s="80"/>
+      <c r="W47" s="80"/>
+      <c r="X47" s="80"/>
+      <c r="Y47" s="80"/>
+      <c r="Z47" s="80"/>
+      <c r="AA47" s="81"/>
     </row>
     <row r="48" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
-      <c r="B48" s="58" t="s">
+      <c r="B48" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="59"/>
-      <c r="D48" s="59"/>
-      <c r="E48" s="59"/>
-      <c r="F48" s="59"/>
-      <c r="G48" s="59"/>
-      <c r="H48" s="59"/>
-      <c r="I48" s="59"/>
-      <c r="J48" s="59"/>
-      <c r="K48" s="59"/>
-      <c r="L48" s="59"/>
-      <c r="M48" s="59"/>
-      <c r="N48" s="59"/>
-      <c r="O48" s="59"/>
-      <c r="P48" s="59"/>
-      <c r="Q48" s="59"/>
-      <c r="R48" s="59"/>
-      <c r="S48" s="59"/>
-      <c r="T48" s="59"/>
-      <c r="U48" s="59"/>
-      <c r="V48" s="59"/>
-      <c r="W48" s="59"/>
-      <c r="X48" s="59"/>
-      <c r="Y48" s="59"/>
-      <c r="Z48" s="59"/>
-      <c r="AA48" s="60"/>
+      <c r="C48" s="53"/>
+      <c r="D48" s="53"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="53"/>
+      <c r="G48" s="53"/>
+      <c r="H48" s="53"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="53"/>
+      <c r="L48" s="53"/>
+      <c r="M48" s="53"/>
+      <c r="N48" s="53"/>
+      <c r="O48" s="53"/>
+      <c r="P48" s="53"/>
+      <c r="Q48" s="53"/>
+      <c r="R48" s="53"/>
+      <c r="S48" s="53"/>
+      <c r="T48" s="53"/>
+      <c r="U48" s="53"/>
+      <c r="V48" s="53"/>
+      <c r="W48" s="53"/>
+      <c r="X48" s="53"/>
+      <c r="Y48" s="53"/>
+      <c r="Z48" s="53"/>
+      <c r="AA48" s="54"/>
     </row>
     <row r="49" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="30"/>
-      <c r="B49" s="54"/>
-      <c r="C49" s="36"/>
-      <c r="D49" s="36"/>
-      <c r="E49" s="36"/>
-      <c r="F49" s="36"/>
-      <c r="G49" s="36"/>
-      <c r="H49" s="36"/>
-      <c r="I49" s="36"/>
-      <c r="J49" s="36"/>
-      <c r="K49" s="36"/>
-      <c r="L49" s="36"/>
-      <c r="M49" s="36"/>
-      <c r="N49" s="36"/>
-      <c r="O49" s="36"/>
-      <c r="P49" s="36"/>
-      <c r="Q49" s="36"/>
-      <c r="R49" s="36"/>
-      <c r="S49" s="36"/>
-      <c r="T49" s="36"/>
-      <c r="U49" s="36"/>
-      <c r="V49" s="36"/>
-      <c r="W49" s="36"/>
-      <c r="X49" s="36"/>
-      <c r="Y49" s="36"/>
-      <c r="Z49" s="36"/>
-      <c r="AA49" s="45"/>
+      <c r="B49" s="60"/>
+      <c r="C49" s="61"/>
+      <c r="D49" s="61"/>
+      <c r="E49" s="61"/>
+      <c r="F49" s="61"/>
+      <c r="G49" s="61"/>
+      <c r="H49" s="61"/>
+      <c r="I49" s="61"/>
+      <c r="J49" s="61"/>
+      <c r="K49" s="61"/>
+      <c r="L49" s="61"/>
+      <c r="M49" s="61"/>
+      <c r="N49" s="61"/>
+      <c r="O49" s="61"/>
+      <c r="P49" s="61"/>
+      <c r="Q49" s="61"/>
+      <c r="R49" s="61"/>
+      <c r="S49" s="61"/>
+      <c r="T49" s="61"/>
+      <c r="U49" s="61"/>
+      <c r="V49" s="61"/>
+      <c r="W49" s="61"/>
+      <c r="X49" s="61"/>
+      <c r="Y49" s="61"/>
+      <c r="Z49" s="61"/>
+      <c r="AA49" s="62"/>
     </row>
     <row r="50" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="30"/>
-      <c r="B50" s="46"/>
-      <c r="C50" s="47"/>
-      <c r="D50" s="47"/>
-      <c r="E50" s="47"/>
-      <c r="F50" s="47"/>
-      <c r="G50" s="47"/>
-      <c r="H50" s="47"/>
-      <c r="I50" s="47"/>
-      <c r="J50" s="47"/>
-      <c r="K50" s="47"/>
-      <c r="L50" s="47"/>
-      <c r="M50" s="47"/>
-      <c r="N50" s="47"/>
-      <c r="O50" s="47"/>
-      <c r="P50" s="47"/>
-      <c r="Q50" s="47"/>
-      <c r="R50" s="47"/>
-      <c r="S50" s="47"/>
-      <c r="T50" s="47"/>
-      <c r="U50" s="47"/>
-      <c r="V50" s="47"/>
-      <c r="W50" s="47"/>
-      <c r="X50" s="47"/>
-      <c r="Y50" s="47"/>
-      <c r="Z50" s="47"/>
-      <c r="AA50" s="48"/>
+      <c r="B50" s="63"/>
+      <c r="C50" s="64"/>
+      <c r="D50" s="64"/>
+      <c r="E50" s="64"/>
+      <c r="F50" s="64"/>
+      <c r="G50" s="64"/>
+      <c r="H50" s="64"/>
+      <c r="I50" s="64"/>
+      <c r="J50" s="64"/>
+      <c r="K50" s="64"/>
+      <c r="L50" s="64"/>
+      <c r="M50" s="64"/>
+      <c r="N50" s="64"/>
+      <c r="O50" s="64"/>
+      <c r="P50" s="64"/>
+      <c r="Q50" s="64"/>
+      <c r="R50" s="64"/>
+      <c r="S50" s="64"/>
+      <c r="T50" s="64"/>
+      <c r="U50" s="64"/>
+      <c r="V50" s="64"/>
+      <c r="W50" s="64"/>
+      <c r="X50" s="64"/>
+      <c r="Y50" s="64"/>
+      <c r="Z50" s="64"/>
+      <c r="AA50" s="65"/>
     </row>
     <row r="51" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="30"/>
-      <c r="B51" s="46"/>
-      <c r="C51" s="47"/>
-      <c r="D51" s="47"/>
-      <c r="E51" s="47"/>
-      <c r="F51" s="47"/>
-      <c r="G51" s="47"/>
-      <c r="H51" s="47"/>
-      <c r="I51" s="47"/>
-      <c r="J51" s="47"/>
-      <c r="K51" s="47"/>
-      <c r="L51" s="47"/>
-      <c r="M51" s="47"/>
-      <c r="N51" s="47"/>
-      <c r="O51" s="47"/>
-      <c r="P51" s="47"/>
-      <c r="Q51" s="47"/>
-      <c r="R51" s="47"/>
-      <c r="S51" s="47"/>
-      <c r="T51" s="47"/>
-      <c r="U51" s="47"/>
-      <c r="V51" s="47"/>
-      <c r="W51" s="47"/>
-      <c r="X51" s="47"/>
-      <c r="Y51" s="47"/>
-      <c r="Z51" s="47"/>
-      <c r="AA51" s="48"/>
+      <c r="B51" s="63"/>
+      <c r="C51" s="64"/>
+      <c r="D51" s="64"/>
+      <c r="E51" s="64"/>
+      <c r="F51" s="64"/>
+      <c r="G51" s="64"/>
+      <c r="H51" s="64"/>
+      <c r="I51" s="64"/>
+      <c r="J51" s="64"/>
+      <c r="K51" s="64"/>
+      <c r="L51" s="64"/>
+      <c r="M51" s="64"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="64"/>
+      <c r="P51" s="64"/>
+      <c r="Q51" s="64"/>
+      <c r="R51" s="64"/>
+      <c r="S51" s="64"/>
+      <c r="T51" s="64"/>
+      <c r="U51" s="64"/>
+      <c r="V51" s="64"/>
+      <c r="W51" s="64"/>
+      <c r="X51" s="64"/>
+      <c r="Y51" s="64"/>
+      <c r="Z51" s="64"/>
+      <c r="AA51" s="65"/>
     </row>
     <row r="52" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="30"/>
-      <c r="B52" s="46"/>
-      <c r="C52" s="47"/>
-      <c r="D52" s="47"/>
-      <c r="E52" s="47"/>
-      <c r="F52" s="47"/>
-      <c r="G52" s="47"/>
-      <c r="H52" s="47"/>
-      <c r="I52" s="47"/>
-      <c r="J52" s="47"/>
-      <c r="K52" s="47"/>
-      <c r="L52" s="47"/>
-      <c r="M52" s="47"/>
-      <c r="N52" s="47"/>
-      <c r="O52" s="47"/>
-      <c r="P52" s="47"/>
-      <c r="Q52" s="47"/>
-      <c r="R52" s="47"/>
-      <c r="S52" s="47"/>
-      <c r="T52" s="47"/>
-      <c r="U52" s="47"/>
-      <c r="V52" s="47"/>
-      <c r="W52" s="47"/>
-      <c r="X52" s="47"/>
-      <c r="Y52" s="47"/>
-      <c r="Z52" s="47"/>
-      <c r="AA52" s="48"/>
+      <c r="B52" s="63"/>
+      <c r="C52" s="64"/>
+      <c r="D52" s="64"/>
+      <c r="E52" s="64"/>
+      <c r="F52" s="64"/>
+      <c r="G52" s="64"/>
+      <c r="H52" s="64"/>
+      <c r="I52" s="64"/>
+      <c r="J52" s="64"/>
+      <c r="K52" s="64"/>
+      <c r="L52" s="64"/>
+      <c r="M52" s="64"/>
+      <c r="N52" s="64"/>
+      <c r="O52" s="64"/>
+      <c r="P52" s="64"/>
+      <c r="Q52" s="64"/>
+      <c r="R52" s="64"/>
+      <c r="S52" s="64"/>
+      <c r="T52" s="64"/>
+      <c r="U52" s="64"/>
+      <c r="V52" s="64"/>
+      <c r="W52" s="64"/>
+      <c r="X52" s="64"/>
+      <c r="Y52" s="64"/>
+      <c r="Z52" s="64"/>
+      <c r="AA52" s="65"/>
     </row>
     <row r="53" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="30"/>
-      <c r="B53" s="46"/>
-      <c r="C53" s="47"/>
-      <c r="D53" s="47"/>
-      <c r="E53" s="47"/>
-      <c r="F53" s="47"/>
-      <c r="G53" s="47"/>
-      <c r="H53" s="47"/>
-      <c r="I53" s="47"/>
-      <c r="J53" s="47"/>
-      <c r="K53" s="47"/>
-      <c r="L53" s="47"/>
-      <c r="M53" s="47"/>
-      <c r="N53" s="47"/>
-      <c r="O53" s="47"/>
-      <c r="P53" s="47"/>
-      <c r="Q53" s="47"/>
-      <c r="R53" s="47"/>
-      <c r="S53" s="47"/>
-      <c r="T53" s="47"/>
-      <c r="U53" s="47"/>
-      <c r="V53" s="47"/>
-      <c r="W53" s="47"/>
-      <c r="X53" s="47"/>
-      <c r="Y53" s="47"/>
-      <c r="Z53" s="47"/>
-      <c r="AA53" s="48"/>
+      <c r="B53" s="63"/>
+      <c r="C53" s="64"/>
+      <c r="D53" s="64"/>
+      <c r="E53" s="64"/>
+      <c r="F53" s="64"/>
+      <c r="G53" s="64"/>
+      <c r="H53" s="64"/>
+      <c r="I53" s="64"/>
+      <c r="J53" s="64"/>
+      <c r="K53" s="64"/>
+      <c r="L53" s="64"/>
+      <c r="M53" s="64"/>
+      <c r="N53" s="64"/>
+      <c r="O53" s="64"/>
+      <c r="P53" s="64"/>
+      <c r="Q53" s="64"/>
+      <c r="R53" s="64"/>
+      <c r="S53" s="64"/>
+      <c r="T53" s="64"/>
+      <c r="U53" s="64"/>
+      <c r="V53" s="64"/>
+      <c r="W53" s="64"/>
+      <c r="X53" s="64"/>
+      <c r="Y53" s="64"/>
+      <c r="Z53" s="64"/>
+      <c r="AA53" s="65"/>
     </row>
     <row r="54" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="30"/>
-      <c r="B54" s="46"/>
-      <c r="C54" s="47"/>
-      <c r="D54" s="47"/>
-      <c r="E54" s="47"/>
-      <c r="F54" s="47"/>
-      <c r="G54" s="47"/>
-      <c r="H54" s="47"/>
-      <c r="I54" s="47"/>
-      <c r="J54" s="47"/>
-      <c r="K54" s="47"/>
-      <c r="L54" s="47"/>
-      <c r="M54" s="47"/>
-      <c r="N54" s="47"/>
-      <c r="O54" s="47"/>
-      <c r="P54" s="47"/>
-      <c r="Q54" s="47"/>
-      <c r="R54" s="47"/>
-      <c r="S54" s="47"/>
-      <c r="T54" s="47"/>
-      <c r="U54" s="47"/>
-      <c r="V54" s="47"/>
-      <c r="W54" s="47"/>
-      <c r="X54" s="47"/>
-      <c r="Y54" s="47"/>
-      <c r="Z54" s="47"/>
-      <c r="AA54" s="48"/>
+      <c r="B54" s="63"/>
+      <c r="C54" s="64"/>
+      <c r="D54" s="64"/>
+      <c r="E54" s="64"/>
+      <c r="F54" s="64"/>
+      <c r="G54" s="64"/>
+      <c r="H54" s="64"/>
+      <c r="I54" s="64"/>
+      <c r="J54" s="64"/>
+      <c r="K54" s="64"/>
+      <c r="L54" s="64"/>
+      <c r="M54" s="64"/>
+      <c r="N54" s="64"/>
+      <c r="O54" s="64"/>
+      <c r="P54" s="64"/>
+      <c r="Q54" s="64"/>
+      <c r="R54" s="64"/>
+      <c r="S54" s="64"/>
+      <c r="T54" s="64"/>
+      <c r="U54" s="64"/>
+      <c r="V54" s="64"/>
+      <c r="W54" s="64"/>
+      <c r="X54" s="64"/>
+      <c r="Y54" s="64"/>
+      <c r="Z54" s="64"/>
+      <c r="AA54" s="65"/>
     </row>
     <row r="55" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A55" s="30"/>
-      <c r="B55" s="67"/>
-      <c r="C55" s="68"/>
-      <c r="D55" s="68"/>
-      <c r="E55" s="68"/>
-      <c r="F55" s="68"/>
-      <c r="G55" s="68"/>
-      <c r="H55" s="68"/>
-      <c r="I55" s="68"/>
-      <c r="J55" s="68"/>
-      <c r="K55" s="68"/>
-      <c r="L55" s="68"/>
-      <c r="M55" s="68"/>
-      <c r="N55" s="68"/>
-      <c r="O55" s="68"/>
-      <c r="P55" s="68"/>
-      <c r="Q55" s="68"/>
-      <c r="R55" s="68"/>
-      <c r="S55" s="68"/>
-      <c r="T55" s="68"/>
-      <c r="U55" s="68"/>
-      <c r="V55" s="68"/>
-      <c r="W55" s="68"/>
-      <c r="X55" s="68"/>
-      <c r="Y55" s="68"/>
-      <c r="Z55" s="68"/>
-      <c r="AA55" s="69"/>
+      <c r="B55" s="55"/>
+      <c r="C55" s="56"/>
+      <c r="D55" s="56"/>
+      <c r="E55" s="56"/>
+      <c r="F55" s="56"/>
+      <c r="G55" s="56"/>
+      <c r="H55" s="56"/>
+      <c r="I55" s="56"/>
+      <c r="J55" s="56"/>
+      <c r="K55" s="56"/>
+      <c r="L55" s="56"/>
+      <c r="M55" s="56"/>
+      <c r="N55" s="56"/>
+      <c r="O55" s="56"/>
+      <c r="P55" s="56"/>
+      <c r="Q55" s="56"/>
+      <c r="R55" s="56"/>
+      <c r="S55" s="56"/>
+      <c r="T55" s="56"/>
+      <c r="U55" s="56"/>
+      <c r="V55" s="56"/>
+      <c r="W55" s="56"/>
+      <c r="X55" s="56"/>
+      <c r="Y55" s="56"/>
+      <c r="Z55" s="56"/>
+      <c r="AA55" s="57"/>
     </row>
     <row r="56" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
@@ -2856,91 +2877,91 @@
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
-      <c r="D58" s="77"/>
-      <c r="E58" s="77"/>
-      <c r="F58" s="77"/>
-      <c r="G58" s="77"/>
-      <c r="H58" s="77"/>
-      <c r="I58" s="77"/>
-      <c r="J58" s="77"/>
-      <c r="K58" s="77"/>
-      <c r="L58" s="77"/>
-      <c r="M58" s="77"/>
-      <c r="N58" s="77"/>
-      <c r="O58" s="77"/>
-      <c r="P58" s="77"/>
-      <c r="Q58" s="77"/>
-      <c r="R58" s="77"/>
-      <c r="S58" s="77"/>
-      <c r="T58" s="77"/>
-      <c r="U58" s="77"/>
-      <c r="V58" s="77"/>
-      <c r="W58" s="77"/>
-      <c r="X58" s="77"/>
-      <c r="Y58" s="77"/>
+      <c r="D58" s="36"/>
+      <c r="E58" s="36"/>
+      <c r="F58" s="36"/>
+      <c r="G58" s="36"/>
+      <c r="H58" s="36"/>
+      <c r="I58" s="36"/>
+      <c r="J58" s="36"/>
+      <c r="K58" s="36"/>
+      <c r="L58" s="36"/>
+      <c r="M58" s="36"/>
+      <c r="N58" s="36"/>
+      <c r="O58" s="36"/>
+      <c r="P58" s="36"/>
+      <c r="Q58" s="36"/>
+      <c r="R58" s="36"/>
+      <c r="S58" s="36"/>
+      <c r="T58" s="36"/>
+      <c r="U58" s="36"/>
+      <c r="V58" s="36"/>
+      <c r="W58" s="36"/>
+      <c r="X58" s="36"/>
+      <c r="Y58" s="36"/>
       <c r="Z58" s="1"/>
       <c r="AA58" s="1"/>
     </row>
     <row r="59" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
-      <c r="B59" s="78"/>
-      <c r="C59" s="78"/>
-      <c r="D59" s="78"/>
-      <c r="E59" s="78"/>
-      <c r="F59" s="82"/>
-      <c r="G59" s="82"/>
-      <c r="H59" s="82"/>
-      <c r="I59" s="79"/>
-      <c r="J59" s="79"/>
-      <c r="K59" s="82"/>
-      <c r="L59" s="82"/>
-      <c r="M59" s="82"/>
-      <c r="N59" s="82"/>
-      <c r="O59" s="82"/>
-      <c r="P59" s="82"/>
-      <c r="Q59" s="82"/>
-      <c r="R59" s="79"/>
-      <c r="S59" s="82"/>
-      <c r="T59" s="82"/>
-      <c r="U59" s="82"/>
-      <c r="V59" s="82"/>
-      <c r="W59" s="82"/>
-      <c r="X59" s="82"/>
-      <c r="Y59" s="78"/>
-      <c r="Z59" s="78"/>
+      <c r="B59" s="37"/>
+      <c r="C59" s="37"/>
+      <c r="D59" s="37"/>
+      <c r="E59" s="37"/>
+      <c r="F59" s="40"/>
+      <c r="G59" s="40"/>
+      <c r="H59" s="40"/>
+      <c r="I59" s="35"/>
+      <c r="J59" s="35"/>
+      <c r="K59" s="40"/>
+      <c r="L59" s="40"/>
+      <c r="M59" s="40"/>
+      <c r="N59" s="40"/>
+      <c r="O59" s="40"/>
+      <c r="P59" s="40"/>
+      <c r="Q59" s="40"/>
+      <c r="R59" s="35"/>
+      <c r="S59" s="40"/>
+      <c r="T59" s="40"/>
+      <c r="U59" s="40"/>
+      <c r="V59" s="40"/>
+      <c r="W59" s="40"/>
+      <c r="X59" s="40"/>
+      <c r="Y59" s="37"/>
+      <c r="Z59" s="37"/>
       <c r="AA59" s="1"/>
     </row>
     <row r="60" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
-      <c r="D60" s="81" t="s">
+      <c r="D60" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="E60" s="80"/>
-      <c r="F60" s="79"/>
-      <c r="G60" s="79"/>
-      <c r="H60" s="79"/>
-      <c r="I60" s="79"/>
-      <c r="J60" s="79"/>
-      <c r="K60" s="79"/>
-      <c r="L60" s="79"/>
-      <c r="M60" s="79"/>
-      <c r="N60" s="83" t="s">
+      <c r="E60" s="38"/>
+      <c r="F60" s="35"/>
+      <c r="G60" s="35"/>
+      <c r="H60" s="35"/>
+      <c r="I60" s="35"/>
+      <c r="J60" s="35"/>
+      <c r="K60" s="35"/>
+      <c r="L60" s="35"/>
+      <c r="M60" s="35"/>
+      <c r="N60" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="O60" s="79"/>
-      <c r="P60" s="79"/>
-      <c r="Q60" s="79"/>
-      <c r="R60" s="79"/>
-      <c r="S60" s="79"/>
-      <c r="T60" s="79"/>
-      <c r="V60" s="79"/>
-      <c r="W60" s="83" t="s">
+      <c r="O60" s="35"/>
+      <c r="P60" s="35"/>
+      <c r="Q60" s="35"/>
+      <c r="R60" s="35"/>
+      <c r="S60" s="35"/>
+      <c r="T60" s="35"/>
+      <c r="V60" s="35"/>
+      <c r="W60" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="X60" s="79"/>
-      <c r="Y60" s="77"/>
+      <c r="X60" s="35"/>
+      <c r="Y60" s="36"/>
       <c r="Z60" s="1"/>
       <c r="AA60" s="1"/>
     </row>
@@ -3065,61 +3086,61 @@
     <row r="65" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
       <c r="B65" s="34"/>
-      <c r="C65" s="35" t="s">
+      <c r="C65" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="D65" s="36"/>
-      <c r="E65" s="36"/>
-      <c r="F65" s="36"/>
-      <c r="G65" s="36"/>
-      <c r="H65" s="36"/>
-      <c r="I65" s="36"/>
-      <c r="J65" s="36"/>
-      <c r="K65" s="36"/>
-      <c r="L65" s="36"/>
-      <c r="M65" s="36"/>
-      <c r="N65" s="36"/>
-      <c r="O65" s="36"/>
-      <c r="P65" s="36"/>
-      <c r="Q65" s="36"/>
-      <c r="R65" s="36"/>
-      <c r="S65" s="36"/>
-      <c r="T65" s="36"/>
-      <c r="U65" s="36"/>
-      <c r="V65" s="36"/>
-      <c r="W65" s="36"/>
-      <c r="X65" s="36"/>
-      <c r="Y65" s="36"/>
-      <c r="Z65" s="37"/>
+      <c r="D65" s="61"/>
+      <c r="E65" s="61"/>
+      <c r="F65" s="61"/>
+      <c r="G65" s="61"/>
+      <c r="H65" s="61"/>
+      <c r="I65" s="61"/>
+      <c r="J65" s="61"/>
+      <c r="K65" s="61"/>
+      <c r="L65" s="61"/>
+      <c r="M65" s="61"/>
+      <c r="N65" s="61"/>
+      <c r="O65" s="61"/>
+      <c r="P65" s="61"/>
+      <c r="Q65" s="61"/>
+      <c r="R65" s="61"/>
+      <c r="S65" s="61"/>
+      <c r="T65" s="61"/>
+      <c r="U65" s="61"/>
+      <c r="V65" s="61"/>
+      <c r="W65" s="61"/>
+      <c r="X65" s="61"/>
+      <c r="Y65" s="61"/>
+      <c r="Z65" s="67"/>
       <c r="AA65" s="34"/>
     </row>
     <row r="66" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
       <c r="B66" s="34"/>
-      <c r="C66" s="38"/>
-      <c r="D66" s="39"/>
-      <c r="E66" s="39"/>
-      <c r="F66" s="39"/>
-      <c r="G66" s="39"/>
-      <c r="H66" s="39"/>
-      <c r="I66" s="39"/>
-      <c r="J66" s="39"/>
-      <c r="K66" s="39"/>
-      <c r="L66" s="39"/>
-      <c r="M66" s="39"/>
-      <c r="N66" s="39"/>
-      <c r="O66" s="39"/>
-      <c r="P66" s="39"/>
-      <c r="Q66" s="39"/>
-      <c r="R66" s="39"/>
-      <c r="S66" s="39"/>
-      <c r="T66" s="39"/>
-      <c r="U66" s="39"/>
-      <c r="V66" s="39"/>
-      <c r="W66" s="39"/>
-      <c r="X66" s="39"/>
-      <c r="Y66" s="39"/>
-      <c r="Z66" s="40"/>
+      <c r="C66" s="68"/>
+      <c r="D66" s="69"/>
+      <c r="E66" s="69"/>
+      <c r="F66" s="69"/>
+      <c r="G66" s="69"/>
+      <c r="H66" s="69"/>
+      <c r="I66" s="69"/>
+      <c r="J66" s="69"/>
+      <c r="K66" s="69"/>
+      <c r="L66" s="69"/>
+      <c r="M66" s="69"/>
+      <c r="N66" s="69"/>
+      <c r="O66" s="69"/>
+      <c r="P66" s="69"/>
+      <c r="Q66" s="69"/>
+      <c r="R66" s="69"/>
+      <c r="S66" s="69"/>
+      <c r="T66" s="69"/>
+      <c r="U66" s="69"/>
+      <c r="V66" s="69"/>
+      <c r="W66" s="69"/>
+      <c r="X66" s="69"/>
+      <c r="Y66" s="69"/>
+      <c r="Z66" s="70"/>
       <c r="AA66" s="34"/>
     </row>
     <row r="67" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30210,21 +30231,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="B3:AA3"/>
-    <mergeCell ref="B4:AA4"/>
-    <mergeCell ref="B5:AA5"/>
-    <mergeCell ref="B6:AA6"/>
-    <mergeCell ref="H10:Z10"/>
-    <mergeCell ref="H12:T12"/>
-    <mergeCell ref="W12:Z12"/>
-    <mergeCell ref="B14:AA15"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="H17:Z17"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="H19:Z19"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="H21:Z21"/>
-    <mergeCell ref="B49:AA55"/>
     <mergeCell ref="C65:Z66"/>
     <mergeCell ref="B23:AA23"/>
     <mergeCell ref="B24:AA31"/>
@@ -30233,6 +30239,21 @@
     <mergeCell ref="B40:AA40"/>
     <mergeCell ref="B41:AA47"/>
     <mergeCell ref="B48:AA48"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="H19:Z19"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="H21:Z21"/>
+    <mergeCell ref="B49:AA55"/>
+    <mergeCell ref="H12:T12"/>
+    <mergeCell ref="W12:Z12"/>
+    <mergeCell ref="B14:AA15"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="H17:Z17"/>
+    <mergeCell ref="B3:AA3"/>
+    <mergeCell ref="B4:AA4"/>
+    <mergeCell ref="B5:AA5"/>
+    <mergeCell ref="B6:AA6"/>
+    <mergeCell ref="H10:Z10"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.98425196850393704" header="0" footer="0"/>

--- a/static/templates/tec02-A_template.xlsx
+++ b/static/templates/tec02-A_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\diseño-afk\static\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4715DAA5-2055-4E49-8F4A-752C0D578400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8F54D8-BC0D-4A3F-8855-4ADE185DB10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -716,7 +716,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -835,53 +835,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
@@ -891,18 +848,8 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -927,6 +874,65 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1252,125 +1258,125 @@
     </row>
     <row r="3" spans="1:27" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="43"/>
-      <c r="U3" s="43"/>
-      <c r="V3" s="43"/>
-      <c r="W3" s="43"/>
-      <c r="X3" s="43"/>
-      <c r="Y3" s="43"/>
-      <c r="Z3" s="43"/>
-      <c r="AA3" s="44"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
+      <c r="K3" s="76"/>
+      <c r="L3" s="76"/>
+      <c r="M3" s="76"/>
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="W3" s="76"/>
+      <c r="X3" s="76"/>
+      <c r="Y3" s="76"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="43"/>
-      <c r="T4" s="43"/>
-      <c r="U4" s="43"/>
-      <c r="V4" s="43"/>
-      <c r="W4" s="43"/>
-      <c r="X4" s="43"/>
-      <c r="Y4" s="43"/>
-      <c r="Z4" s="43"/>
-      <c r="AA4" s="44"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="76"/>
+      <c r="L4" s="76"/>
+      <c r="M4" s="76"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="W4" s="76"/>
+      <c r="X4" s="76"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="20" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43"/>
-      <c r="N5" s="43"/>
-      <c r="O5" s="43"/>
-      <c r="P5" s="43"/>
-      <c r="Q5" s="43"/>
-      <c r="R5" s="43"/>
-      <c r="S5" s="43"/>
-      <c r="T5" s="43"/>
-      <c r="U5" s="43"/>
-      <c r="V5" s="43"/>
-      <c r="W5" s="43"/>
-      <c r="X5" s="43"/>
-      <c r="Y5" s="43"/>
-      <c r="Z5" s="43"/>
-      <c r="AA5" s="44"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
+      <c r="K5" s="76"/>
+      <c r="L5" s="76"/>
+      <c r="M5" s="76"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
+      <c r="W5" s="76"/>
+      <c r="X5" s="76"/>
+      <c r="Y5" s="76"/>
+      <c r="Z5" s="76"/>
+      <c r="AA5" s="77"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="43"/>
-      <c r="L6" s="43"/>
-      <c r="M6" s="43"/>
-      <c r="N6" s="43"/>
-      <c r="O6" s="43"/>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="43"/>
-      <c r="R6" s="43"/>
-      <c r="S6" s="43"/>
-      <c r="T6" s="43"/>
-      <c r="U6" s="43"/>
-      <c r="V6" s="43"/>
-      <c r="W6" s="43"/>
-      <c r="X6" s="43"/>
-      <c r="Y6" s="43"/>
-      <c r="Z6" s="43"/>
-      <c r="AA6" s="44"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="76"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
+      <c r="L6" s="76"/>
+      <c r="M6" s="76"/>
+      <c r="N6" s="76"/>
+      <c r="O6" s="76"/>
+      <c r="P6" s="76"/>
+      <c r="Q6" s="76"/>
+      <c r="R6" s="76"/>
+      <c r="S6" s="76"/>
+      <c r="T6" s="76"/>
+      <c r="U6" s="76"/>
+      <c r="V6" s="76"/>
+      <c r="W6" s="76"/>
+      <c r="X6" s="76"/>
+      <c r="Y6" s="76"/>
+      <c r="Z6" s="76"/>
+      <c r="AA6" s="77"/>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2"/>
@@ -1469,25 +1475,25 @@
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="49"/>
-      <c r="M10" s="49"/>
-      <c r="N10" s="49"/>
-      <c r="O10" s="49"/>
-      <c r="P10" s="49"/>
-      <c r="Q10" s="49"/>
-      <c r="R10" s="49"/>
-      <c r="S10" s="49"/>
-      <c r="T10" s="49"/>
-      <c r="U10" s="49"/>
-      <c r="V10" s="49"/>
-      <c r="W10" s="49"/>
-      <c r="X10" s="49"/>
-      <c r="Y10" s="49"/>
-      <c r="Z10" s="50"/>
+      <c r="H10" s="84"/>
+      <c r="I10" s="79"/>
+      <c r="J10" s="79"/>
+      <c r="K10" s="79"/>
+      <c r="L10" s="79"/>
+      <c r="M10" s="79"/>
+      <c r="N10" s="79"/>
+      <c r="O10" s="79"/>
+      <c r="P10" s="79"/>
+      <c r="Q10" s="79"/>
+      <c r="R10" s="79"/>
+      <c r="S10" s="79"/>
+      <c r="T10" s="79"/>
+      <c r="U10" s="79"/>
+      <c r="V10" s="79"/>
+      <c r="W10" s="79"/>
+      <c r="X10" s="79"/>
+      <c r="Y10" s="79"/>
+      <c r="Z10" s="80"/>
       <c r="AA10" s="11"/>
     </row>
     <row r="11" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1529,27 +1535,27 @@
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="49"/>
-      <c r="K12" s="49"/>
-      <c r="L12" s="49"/>
-      <c r="M12" s="49"/>
-      <c r="N12" s="49"/>
-      <c r="O12" s="49"/>
-      <c r="P12" s="49"/>
-      <c r="Q12" s="49"/>
-      <c r="R12" s="49"/>
-      <c r="S12" s="49"/>
-      <c r="T12" s="50"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="79"/>
+      <c r="K12" s="79"/>
+      <c r="L12" s="79"/>
+      <c r="M12" s="79"/>
+      <c r="N12" s="79"/>
+      <c r="O12" s="79"/>
+      <c r="P12" s="79"/>
+      <c r="Q12" s="79"/>
+      <c r="R12" s="79"/>
+      <c r="S12" s="79"/>
+      <c r="T12" s="80"/>
       <c r="U12" s="13"/>
       <c r="V12" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="W12" s="51"/>
-      <c r="X12" s="49"/>
-      <c r="Y12" s="49"/>
-      <c r="Z12" s="50"/>
+      <c r="W12" s="85"/>
+      <c r="X12" s="79"/>
+      <c r="Y12" s="79"/>
+      <c r="Z12" s="80"/>
       <c r="AA12" s="15"/>
     </row>
     <row r="13" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1583,63 +1589,63 @@
     </row>
     <row r="14" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
-      <c r="B14" s="52" t="s">
+      <c r="B14" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="53"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="53"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="53"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="53"/>
-      <c r="M14" s="53"/>
-      <c r="N14" s="53"/>
-      <c r="O14" s="53"/>
-      <c r="P14" s="53"/>
-      <c r="Q14" s="53"/>
-      <c r="R14" s="53"/>
-      <c r="S14" s="53"/>
-      <c r="T14" s="53"/>
-      <c r="U14" s="53"/>
-      <c r="V14" s="53"/>
-      <c r="W14" s="53"/>
-      <c r="X14" s="53"/>
-      <c r="Y14" s="53"/>
-      <c r="Z14" s="53"/>
-      <c r="AA14" s="54"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="73"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="73"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="73"/>
+      <c r="O14" s="73"/>
+      <c r="P14" s="73"/>
+      <c r="Q14" s="73"/>
+      <c r="R14" s="73"/>
+      <c r="S14" s="73"/>
+      <c r="T14" s="73"/>
+      <c r="U14" s="73"/>
+      <c r="V14" s="73"/>
+      <c r="W14" s="73"/>
+      <c r="X14" s="73"/>
+      <c r="Y14" s="73"/>
+      <c r="Z14" s="73"/>
+      <c r="AA14" s="74"/>
     </row>
     <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
-      <c r="B15" s="55"/>
-      <c r="C15" s="56"/>
-      <c r="D15" s="56"/>
-      <c r="E15" s="56"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="56"/>
-      <c r="H15" s="56"/>
-      <c r="I15" s="56"/>
-      <c r="J15" s="56"/>
-      <c r="K15" s="56"/>
-      <c r="L15" s="56"/>
-      <c r="M15" s="56"/>
-      <c r="N15" s="56"/>
-      <c r="O15" s="56"/>
-      <c r="P15" s="56"/>
-      <c r="Q15" s="56"/>
-      <c r="R15" s="56"/>
-      <c r="S15" s="56"/>
-      <c r="T15" s="56"/>
-      <c r="U15" s="56"/>
-      <c r="V15" s="56"/>
-      <c r="W15" s="56"/>
-      <c r="X15" s="56"/>
-      <c r="Y15" s="56"/>
-      <c r="Z15" s="56"/>
-      <c r="AA15" s="57"/>
+      <c r="B15" s="81"/>
+      <c r="C15" s="82"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="82"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="82"/>
+      <c r="H15" s="82"/>
+      <c r="I15" s="82"/>
+      <c r="J15" s="82"/>
+      <c r="K15" s="82"/>
+      <c r="L15" s="82"/>
+      <c r="M15" s="82"/>
+      <c r="N15" s="82"/>
+      <c r="O15" s="82"/>
+      <c r="P15" s="82"/>
+      <c r="Q15" s="82"/>
+      <c r="R15" s="82"/>
+      <c r="S15" s="82"/>
+      <c r="T15" s="82"/>
+      <c r="U15" s="82"/>
+      <c r="V15" s="82"/>
+      <c r="W15" s="82"/>
+      <c r="X15" s="82"/>
+      <c r="Y15" s="82"/>
+      <c r="Z15" s="82"/>
+      <c r="AA15" s="83"/>
     </row>
     <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
@@ -1672,33 +1678,33 @@
     </row>
     <row r="17" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
-      <c r="B17" s="58" t="s">
+      <c r="B17" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="59"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="49"/>
-      <c r="K17" s="49"/>
-      <c r="L17" s="49"/>
-      <c r="M17" s="49"/>
-      <c r="N17" s="49"/>
-      <c r="O17" s="49"/>
-      <c r="P17" s="49"/>
-      <c r="Q17" s="49"/>
-      <c r="R17" s="49"/>
-      <c r="S17" s="49"/>
-      <c r="T17" s="49"/>
-      <c r="U17" s="49"/>
-      <c r="V17" s="49"/>
-      <c r="W17" s="49"/>
-      <c r="X17" s="49"/>
-      <c r="Y17" s="49"/>
-      <c r="Z17" s="50"/>
+      <c r="C17" s="76"/>
+      <c r="D17" s="76"/>
+      <c r="E17" s="76"/>
+      <c r="F17" s="76"/>
+      <c r="G17" s="77"/>
+      <c r="H17" s="78"/>
+      <c r="I17" s="79"/>
+      <c r="J17" s="79"/>
+      <c r="K17" s="79"/>
+      <c r="L17" s="79"/>
+      <c r="M17" s="79"/>
+      <c r="N17" s="79"/>
+      <c r="O17" s="79"/>
+      <c r="P17" s="79"/>
+      <c r="Q17" s="79"/>
+      <c r="R17" s="79"/>
+      <c r="S17" s="79"/>
+      <c r="T17" s="79"/>
+      <c r="U17" s="79"/>
+      <c r="V17" s="79"/>
+      <c r="W17" s="79"/>
+      <c r="X17" s="79"/>
+      <c r="Y17" s="79"/>
+      <c r="Z17" s="80"/>
       <c r="AA17" s="24"/>
     </row>
     <row r="18" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1732,33 +1738,33 @@
     </row>
     <row r="19" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
-      <c r="B19" s="58" t="s">
+      <c r="B19" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="49"/>
-      <c r="K19" s="49"/>
-      <c r="L19" s="49"/>
-      <c r="M19" s="49"/>
-      <c r="N19" s="49"/>
-      <c r="O19" s="49"/>
-      <c r="P19" s="49"/>
-      <c r="Q19" s="49"/>
-      <c r="R19" s="49"/>
-      <c r="S19" s="49"/>
-      <c r="T19" s="49"/>
-      <c r="U19" s="49"/>
-      <c r="V19" s="49"/>
-      <c r="W19" s="49"/>
-      <c r="X19" s="49"/>
-      <c r="Y19" s="49"/>
-      <c r="Z19" s="50"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="76"/>
+      <c r="E19" s="76"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="78"/>
+      <c r="I19" s="79"/>
+      <c r="J19" s="79"/>
+      <c r="K19" s="79"/>
+      <c r="L19" s="79"/>
+      <c r="M19" s="79"/>
+      <c r="N19" s="79"/>
+      <c r="O19" s="79"/>
+      <c r="P19" s="79"/>
+      <c r="Q19" s="79"/>
+      <c r="R19" s="79"/>
+      <c r="S19" s="79"/>
+      <c r="T19" s="79"/>
+      <c r="U19" s="79"/>
+      <c r="V19" s="79"/>
+      <c r="W19" s="79"/>
+      <c r="X19" s="79"/>
+      <c r="Y19" s="79"/>
+      <c r="Z19" s="80"/>
       <c r="AA19" s="24"/>
     </row>
     <row r="20" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1792,33 +1798,33 @@
     </row>
     <row r="21" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
-      <c r="B21" s="58" t="s">
+      <c r="B21" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="49"/>
-      <c r="K21" s="49"/>
-      <c r="L21" s="49"/>
-      <c r="M21" s="49"/>
-      <c r="N21" s="49"/>
-      <c r="O21" s="49"/>
-      <c r="P21" s="49"/>
-      <c r="Q21" s="49"/>
-      <c r="R21" s="49"/>
-      <c r="S21" s="49"/>
-      <c r="T21" s="49"/>
-      <c r="U21" s="49"/>
-      <c r="V21" s="49"/>
-      <c r="W21" s="49"/>
-      <c r="X21" s="49"/>
-      <c r="Y21" s="49"/>
-      <c r="Z21" s="50"/>
+      <c r="C21" s="76"/>
+      <c r="D21" s="76"/>
+      <c r="E21" s="76"/>
+      <c r="F21" s="76"/>
+      <c r="G21" s="77"/>
+      <c r="H21" s="78"/>
+      <c r="I21" s="79"/>
+      <c r="J21" s="79"/>
+      <c r="K21" s="79"/>
+      <c r="L21" s="79"/>
+      <c r="M21" s="79"/>
+      <c r="N21" s="79"/>
+      <c r="O21" s="79"/>
+      <c r="P21" s="79"/>
+      <c r="Q21" s="79"/>
+      <c r="R21" s="79"/>
+      <c r="S21" s="79"/>
+      <c r="T21" s="79"/>
+      <c r="U21" s="79"/>
+      <c r="V21" s="79"/>
+      <c r="W21" s="79"/>
+      <c r="X21" s="79"/>
+      <c r="Y21" s="79"/>
+      <c r="Z21" s="80"/>
       <c r="AA21" s="24"/>
     </row>
     <row r="22" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1852,968 +1858,968 @@
     </row>
     <row r="23" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
-      <c r="B23" s="71" t="s">
+      <c r="B23" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="72"/>
-      <c r="D23" s="72"/>
-      <c r="E23" s="72"/>
-      <c r="F23" s="72"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="72"/>
-      <c r="J23" s="72"/>
-      <c r="K23" s="72"/>
-      <c r="L23" s="72"/>
-      <c r="M23" s="72"/>
-      <c r="N23" s="72"/>
-      <c r="O23" s="72"/>
-      <c r="P23" s="72"/>
-      <c r="Q23" s="72"/>
-      <c r="R23" s="72"/>
-      <c r="S23" s="72"/>
-      <c r="T23" s="72"/>
-      <c r="U23" s="72"/>
-      <c r="V23" s="72"/>
-      <c r="W23" s="72"/>
-      <c r="X23" s="72"/>
-      <c r="Y23" s="72"/>
-      <c r="Z23" s="72"/>
-      <c r="AA23" s="73"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="49"/>
+      <c r="J23" s="49"/>
+      <c r="K23" s="49"/>
+      <c r="L23" s="49"/>
+      <c r="M23" s="49"/>
+      <c r="N23" s="49"/>
+      <c r="O23" s="49"/>
+      <c r="P23" s="49"/>
+      <c r="Q23" s="49"/>
+      <c r="R23" s="49"/>
+      <c r="S23" s="49"/>
+      <c r="T23" s="49"/>
+      <c r="U23" s="49"/>
+      <c r="V23" s="49"/>
+      <c r="W23" s="49"/>
+      <c r="X23" s="49"/>
+      <c r="Y23" s="49"/>
+      <c r="Z23" s="49"/>
+      <c r="AA23" s="50"/>
     </row>
     <row r="24" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
-      <c r="B24" s="60"/>
-      <c r="C24" s="83"/>
-      <c r="D24" s="83"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="83"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="83"/>
-      <c r="J24" s="83"/>
-      <c r="K24" s="83"/>
-      <c r="L24" s="83"/>
-      <c r="M24" s="83"/>
-      <c r="N24" s="83"/>
-      <c r="O24" s="83"/>
-      <c r="P24" s="83"/>
-      <c r="Q24" s="83"/>
-      <c r="R24" s="83"/>
-      <c r="S24" s="83"/>
-      <c r="T24" s="83"/>
-      <c r="U24" s="83"/>
-      <c r="V24" s="83"/>
-      <c r="W24" s="83"/>
-      <c r="X24" s="83"/>
-      <c r="Y24" s="83"/>
-      <c r="Z24" s="83"/>
-      <c r="AA24" s="84"/>
+      <c r="B24" s="51"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="52"/>
+      <c r="J24" s="52"/>
+      <c r="K24" s="52"/>
+      <c r="L24" s="52"/>
+      <c r="M24" s="52"/>
+      <c r="N24" s="52"/>
+      <c r="O24" s="52"/>
+      <c r="P24" s="52"/>
+      <c r="Q24" s="52"/>
+      <c r="R24" s="52"/>
+      <c r="S24" s="52"/>
+      <c r="T24" s="52"/>
+      <c r="U24" s="52"/>
+      <c r="V24" s="52"/>
+      <c r="W24" s="52"/>
+      <c r="X24" s="52"/>
+      <c r="Y24" s="52"/>
+      <c r="Z24" s="52"/>
+      <c r="AA24" s="53"/>
     </row>
     <row r="25" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
-      <c r="B25" s="85"/>
-      <c r="C25" s="86"/>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="86"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="86"/>
-      <c r="J25" s="86"/>
-      <c r="K25" s="86"/>
-      <c r="L25" s="86"/>
-      <c r="M25" s="86"/>
-      <c r="N25" s="86"/>
-      <c r="O25" s="86"/>
-      <c r="P25" s="86"/>
-      <c r="Q25" s="86"/>
-      <c r="R25" s="86"/>
-      <c r="S25" s="86"/>
-      <c r="T25" s="86"/>
-      <c r="U25" s="86"/>
-      <c r="V25" s="86"/>
-      <c r="W25" s="86"/>
-      <c r="X25" s="86"/>
-      <c r="Y25" s="86"/>
-      <c r="Z25" s="86"/>
-      <c r="AA25" s="87"/>
+      <c r="B25" s="54"/>
+      <c r="C25" s="55"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="55"/>
+      <c r="H25" s="55"/>
+      <c r="I25" s="55"/>
+      <c r="J25" s="55"/>
+      <c r="K25" s="55"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="55"/>
+      <c r="N25" s="55"/>
+      <c r="O25" s="55"/>
+      <c r="P25" s="55"/>
+      <c r="Q25" s="55"/>
+      <c r="R25" s="55"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="55"/>
+      <c r="U25" s="55"/>
+      <c r="V25" s="55"/>
+      <c r="W25" s="55"/>
+      <c r="X25" s="55"/>
+      <c r="Y25" s="55"/>
+      <c r="Z25" s="55"/>
+      <c r="AA25" s="56"/>
     </row>
     <row r="26" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
-      <c r="B26" s="85"/>
-      <c r="C26" s="86"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="86"/>
-      <c r="G26" s="86"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="86"/>
-      <c r="J26" s="86"/>
-      <c r="K26" s="86"/>
-      <c r="L26" s="86"/>
-      <c r="M26" s="86"/>
-      <c r="N26" s="86"/>
-      <c r="O26" s="86"/>
-      <c r="P26" s="86"/>
-      <c r="Q26" s="86"/>
-      <c r="R26" s="86"/>
-      <c r="S26" s="86"/>
-      <c r="T26" s="86"/>
-      <c r="U26" s="86"/>
-      <c r="V26" s="86"/>
-      <c r="W26" s="86"/>
-      <c r="X26" s="86"/>
-      <c r="Y26" s="86"/>
-      <c r="Z26" s="86"/>
-      <c r="AA26" s="87"/>
+      <c r="B26" s="54"/>
+      <c r="C26" s="55"/>
+      <c r="D26" s="55"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="55"/>
+      <c r="H26" s="55"/>
+      <c r="I26" s="55"/>
+      <c r="J26" s="55"/>
+      <c r="K26" s="55"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="55"/>
+      <c r="N26" s="55"/>
+      <c r="O26" s="55"/>
+      <c r="P26" s="55"/>
+      <c r="Q26" s="55"/>
+      <c r="R26" s="55"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="55"/>
+      <c r="U26" s="55"/>
+      <c r="V26" s="55"/>
+      <c r="W26" s="55"/>
+      <c r="X26" s="55"/>
+      <c r="Y26" s="55"/>
+      <c r="Z26" s="55"/>
+      <c r="AA26" s="56"/>
     </row>
     <row r="27" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
-      <c r="B27" s="85"/>
-      <c r="C27" s="86"/>
-      <c r="D27" s="86"/>
-      <c r="E27" s="86"/>
-      <c r="F27" s="86"/>
-      <c r="G27" s="86"/>
-      <c r="H27" s="86"/>
-      <c r="I27" s="86"/>
-      <c r="J27" s="86"/>
-      <c r="K27" s="86"/>
-      <c r="L27" s="86"/>
-      <c r="M27" s="86"/>
-      <c r="N27" s="86"/>
-      <c r="O27" s="86"/>
-      <c r="P27" s="86"/>
-      <c r="Q27" s="86"/>
-      <c r="R27" s="86"/>
-      <c r="S27" s="86"/>
-      <c r="T27" s="86"/>
-      <c r="U27" s="86"/>
-      <c r="V27" s="86"/>
-      <c r="W27" s="86"/>
-      <c r="X27" s="86"/>
-      <c r="Y27" s="86"/>
-      <c r="Z27" s="86"/>
-      <c r="AA27" s="87"/>
+      <c r="B27" s="54"/>
+      <c r="C27" s="55"/>
+      <c r="D27" s="55"/>
+      <c r="E27" s="55"/>
+      <c r="F27" s="55"/>
+      <c r="G27" s="55"/>
+      <c r="H27" s="55"/>
+      <c r="I27" s="55"/>
+      <c r="J27" s="55"/>
+      <c r="K27" s="55"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="55"/>
+      <c r="N27" s="55"/>
+      <c r="O27" s="55"/>
+      <c r="P27" s="55"/>
+      <c r="Q27" s="55"/>
+      <c r="R27" s="55"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="55"/>
+      <c r="U27" s="55"/>
+      <c r="V27" s="55"/>
+      <c r="W27" s="55"/>
+      <c r="X27" s="55"/>
+      <c r="Y27" s="55"/>
+      <c r="Z27" s="55"/>
+      <c r="AA27" s="56"/>
     </row>
     <row r="28" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
-      <c r="B28" s="85"/>
-      <c r="C28" s="86"/>
-      <c r="D28" s="86"/>
-      <c r="E28" s="86"/>
-      <c r="F28" s="86"/>
-      <c r="G28" s="86"/>
-      <c r="H28" s="86"/>
-      <c r="I28" s="86"/>
-      <c r="J28" s="86"/>
-      <c r="K28" s="86"/>
-      <c r="L28" s="86"/>
-      <c r="M28" s="86"/>
-      <c r="N28" s="86"/>
-      <c r="O28" s="86"/>
-      <c r="P28" s="86"/>
-      <c r="Q28" s="86"/>
-      <c r="R28" s="86"/>
-      <c r="S28" s="86"/>
-      <c r="T28" s="86"/>
-      <c r="U28" s="86"/>
-      <c r="V28" s="86"/>
-      <c r="W28" s="86"/>
-      <c r="X28" s="86"/>
-      <c r="Y28" s="86"/>
-      <c r="Z28" s="86"/>
-      <c r="AA28" s="87"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="55"/>
+      <c r="K28" s="55"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="55"/>
+      <c r="N28" s="55"/>
+      <c r="O28" s="55"/>
+      <c r="P28" s="55"/>
+      <c r="Q28" s="55"/>
+      <c r="R28" s="55"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="55"/>
+      <c r="U28" s="55"/>
+      <c r="V28" s="55"/>
+      <c r="W28" s="55"/>
+      <c r="X28" s="55"/>
+      <c r="Y28" s="55"/>
+      <c r="Z28" s="55"/>
+      <c r="AA28" s="56"/>
     </row>
     <row r="29" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
-      <c r="B29" s="85"/>
-      <c r="C29" s="86"/>
-      <c r="D29" s="86"/>
-      <c r="E29" s="86"/>
-      <c r="F29" s="86"/>
-      <c r="G29" s="86"/>
-      <c r="H29" s="86"/>
-      <c r="I29" s="86"/>
-      <c r="J29" s="86"/>
-      <c r="K29" s="86"/>
-      <c r="L29" s="86"/>
-      <c r="M29" s="86"/>
-      <c r="N29" s="86"/>
-      <c r="O29" s="86"/>
-      <c r="P29" s="86"/>
-      <c r="Q29" s="86"/>
-      <c r="R29" s="86"/>
-      <c r="S29" s="86"/>
-      <c r="T29" s="86"/>
-      <c r="U29" s="86"/>
-      <c r="V29" s="86"/>
-      <c r="W29" s="86"/>
-      <c r="X29" s="86"/>
-      <c r="Y29" s="86"/>
-      <c r="Z29" s="86"/>
-      <c r="AA29" s="87"/>
+      <c r="B29" s="54"/>
+      <c r="C29" s="55"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="55"/>
+      <c r="G29" s="55"/>
+      <c r="H29" s="55"/>
+      <c r="I29" s="55"/>
+      <c r="J29" s="55"/>
+      <c r="K29" s="55"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="55"/>
+      <c r="N29" s="55"/>
+      <c r="O29" s="55"/>
+      <c r="P29" s="55"/>
+      <c r="Q29" s="55"/>
+      <c r="R29" s="55"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="55"/>
+      <c r="U29" s="55"/>
+      <c r="V29" s="55"/>
+      <c r="W29" s="55"/>
+      <c r="X29" s="55"/>
+      <c r="Y29" s="55"/>
+      <c r="Z29" s="55"/>
+      <c r="AA29" s="56"/>
     </row>
     <row r="30" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
-      <c r="B30" s="85"/>
-      <c r="C30" s="86"/>
-      <c r="D30" s="86"/>
-      <c r="E30" s="86"/>
-      <c r="F30" s="86"/>
-      <c r="G30" s="86"/>
-      <c r="H30" s="86"/>
-      <c r="I30" s="86"/>
-      <c r="J30" s="86"/>
-      <c r="K30" s="86"/>
-      <c r="L30" s="86"/>
-      <c r="M30" s="86"/>
-      <c r="N30" s="86"/>
-      <c r="O30" s="86"/>
-      <c r="P30" s="86"/>
-      <c r="Q30" s="86"/>
-      <c r="R30" s="86"/>
-      <c r="S30" s="86"/>
-      <c r="T30" s="86"/>
-      <c r="U30" s="86"/>
-      <c r="V30" s="86"/>
-      <c r="W30" s="86"/>
-      <c r="X30" s="86"/>
-      <c r="Y30" s="86"/>
-      <c r="Z30" s="86"/>
-      <c r="AA30" s="87"/>
+      <c r="B30" s="54"/>
+      <c r="C30" s="55"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="55"/>
+      <c r="G30" s="55"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="55"/>
+      <c r="J30" s="55"/>
+      <c r="K30" s="55"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="55"/>
+      <c r="N30" s="55"/>
+      <c r="O30" s="55"/>
+      <c r="P30" s="55"/>
+      <c r="Q30" s="55"/>
+      <c r="R30" s="55"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="55"/>
+      <c r="U30" s="55"/>
+      <c r="V30" s="55"/>
+      <c r="W30" s="55"/>
+      <c r="X30" s="55"/>
+      <c r="Y30" s="55"/>
+      <c r="Z30" s="55"/>
+      <c r="AA30" s="56"/>
     </row>
     <row r="31" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
-      <c r="B31" s="88"/>
-      <c r="C31" s="89"/>
-      <c r="D31" s="89"/>
-      <c r="E31" s="89"/>
-      <c r="F31" s="89"/>
-      <c r="G31" s="89"/>
-      <c r="H31" s="89"/>
-      <c r="I31" s="89"/>
-      <c r="J31" s="89"/>
-      <c r="K31" s="89"/>
-      <c r="L31" s="89"/>
-      <c r="M31" s="89"/>
-      <c r="N31" s="89"/>
-      <c r="O31" s="89"/>
-      <c r="P31" s="89"/>
-      <c r="Q31" s="89"/>
-      <c r="R31" s="89"/>
-      <c r="S31" s="89"/>
-      <c r="T31" s="89"/>
-      <c r="U31" s="89"/>
-      <c r="V31" s="89"/>
-      <c r="W31" s="89"/>
-      <c r="X31" s="89"/>
-      <c r="Y31" s="89"/>
-      <c r="Z31" s="89"/>
-      <c r="AA31" s="90"/>
+      <c r="B31" s="57"/>
+      <c r="C31" s="58"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="58"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="58"/>
+      <c r="K31" s="58"/>
+      <c r="L31" s="58"/>
+      <c r="M31" s="58"/>
+      <c r="N31" s="58"/>
+      <c r="O31" s="58"/>
+      <c r="P31" s="58"/>
+      <c r="Q31" s="58"/>
+      <c r="R31" s="58"/>
+      <c r="S31" s="58"/>
+      <c r="T31" s="58"/>
+      <c r="U31" s="58"/>
+      <c r="V31" s="58"/>
+      <c r="W31" s="58"/>
+      <c r="X31" s="58"/>
+      <c r="Y31" s="58"/>
+      <c r="Z31" s="58"/>
+      <c r="AA31" s="59"/>
     </row>
     <row r="32" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
-      <c r="B32" s="76" t="s">
+      <c r="B32" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="77"/>
-      <c r="D32" s="77"/>
-      <c r="E32" s="77"/>
-      <c r="F32" s="77"/>
-      <c r="G32" s="77"/>
-      <c r="H32" s="77"/>
-      <c r="I32" s="77"/>
-      <c r="J32" s="77"/>
-      <c r="K32" s="77"/>
-      <c r="L32" s="77"/>
-      <c r="M32" s="77"/>
-      <c r="N32" s="77"/>
-      <c r="O32" s="77"/>
-      <c r="P32" s="77"/>
-      <c r="Q32" s="77"/>
-      <c r="R32" s="77"/>
-      <c r="S32" s="77"/>
-      <c r="T32" s="77"/>
-      <c r="U32" s="77"/>
-      <c r="V32" s="77"/>
-      <c r="W32" s="77"/>
-      <c r="X32" s="77"/>
-      <c r="Y32" s="77"/>
-      <c r="Z32" s="77"/>
-      <c r="AA32" s="78"/>
+      <c r="C32" s="61"/>
+      <c r="D32" s="61"/>
+      <c r="E32" s="61"/>
+      <c r="F32" s="61"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="61"/>
+      <c r="J32" s="61"/>
+      <c r="K32" s="61"/>
+      <c r="L32" s="61"/>
+      <c r="M32" s="61"/>
+      <c r="N32" s="61"/>
+      <c r="O32" s="61"/>
+      <c r="P32" s="61"/>
+      <c r="Q32" s="61"/>
+      <c r="R32" s="61"/>
+      <c r="S32" s="61"/>
+      <c r="T32" s="61"/>
+      <c r="U32" s="61"/>
+      <c r="V32" s="61"/>
+      <c r="W32" s="61"/>
+      <c r="X32" s="61"/>
+      <c r="Y32" s="61"/>
+      <c r="Z32" s="61"/>
+      <c r="AA32" s="62"/>
     </row>
     <row r="33" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
-      <c r="B33" s="60"/>
-      <c r="C33" s="61"/>
-      <c r="D33" s="61"/>
-      <c r="E33" s="61"/>
-      <c r="F33" s="61"/>
-      <c r="G33" s="61"/>
-      <c r="H33" s="61"/>
-      <c r="I33" s="61"/>
-      <c r="J33" s="61"/>
-      <c r="K33" s="61"/>
-      <c r="L33" s="61"/>
-      <c r="M33" s="61"/>
-      <c r="N33" s="61"/>
-      <c r="O33" s="61"/>
-      <c r="P33" s="61"/>
-      <c r="Q33" s="61"/>
-      <c r="R33" s="61"/>
-      <c r="S33" s="61"/>
-      <c r="T33" s="61"/>
-      <c r="U33" s="61"/>
-      <c r="V33" s="61"/>
-      <c r="W33" s="61"/>
-      <c r="X33" s="61"/>
-      <c r="Y33" s="61"/>
-      <c r="Z33" s="61"/>
-      <c r="AA33" s="62"/>
+      <c r="B33" s="51"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="43"/>
+      <c r="L33" s="43"/>
+      <c r="M33" s="43"/>
+      <c r="N33" s="43"/>
+      <c r="O33" s="43"/>
+      <c r="P33" s="43"/>
+      <c r="Q33" s="43"/>
+      <c r="R33" s="43"/>
+      <c r="S33" s="43"/>
+      <c r="T33" s="43"/>
+      <c r="U33" s="43"/>
+      <c r="V33" s="43"/>
+      <c r="W33" s="43"/>
+      <c r="X33" s="43"/>
+      <c r="Y33" s="43"/>
+      <c r="Z33" s="43"/>
+      <c r="AA33" s="63"/>
     </row>
     <row r="34" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
-      <c r="B34" s="63"/>
-      <c r="C34" s="64"/>
-      <c r="D34" s="64"/>
-      <c r="E34" s="64"/>
-      <c r="F34" s="64"/>
-      <c r="G34" s="64"/>
-      <c r="H34" s="64"/>
-      <c r="I34" s="64"/>
-      <c r="J34" s="64"/>
-      <c r="K34" s="64"/>
-      <c r="L34" s="64"/>
-      <c r="M34" s="64"/>
-      <c r="N34" s="64"/>
-      <c r="O34" s="64"/>
-      <c r="P34" s="64"/>
-      <c r="Q34" s="64"/>
-      <c r="R34" s="64"/>
-      <c r="S34" s="64"/>
-      <c r="T34" s="64"/>
-      <c r="U34" s="64"/>
-      <c r="V34" s="64"/>
-      <c r="W34" s="64"/>
-      <c r="X34" s="64"/>
-      <c r="Y34" s="64"/>
-      <c r="Z34" s="64"/>
-      <c r="AA34" s="65"/>
+      <c r="B34" s="64"/>
+      <c r="C34" s="65"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="65"/>
+      <c r="F34" s="65"/>
+      <c r="G34" s="65"/>
+      <c r="H34" s="65"/>
+      <c r="I34" s="65"/>
+      <c r="J34" s="65"/>
+      <c r="K34" s="65"/>
+      <c r="L34" s="65"/>
+      <c r="M34" s="65"/>
+      <c r="N34" s="65"/>
+      <c r="O34" s="65"/>
+      <c r="P34" s="65"/>
+      <c r="Q34" s="65"/>
+      <c r="R34" s="65"/>
+      <c r="S34" s="65"/>
+      <c r="T34" s="65"/>
+      <c r="U34" s="65"/>
+      <c r="V34" s="65"/>
+      <c r="W34" s="65"/>
+      <c r="X34" s="65"/>
+      <c r="Y34" s="65"/>
+      <c r="Z34" s="65"/>
+      <c r="AA34" s="66"/>
     </row>
     <row r="35" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
-      <c r="B35" s="63"/>
-      <c r="C35" s="64"/>
-      <c r="D35" s="64"/>
-      <c r="E35" s="64"/>
-      <c r="F35" s="64"/>
-      <c r="G35" s="64"/>
-      <c r="H35" s="64"/>
-      <c r="I35" s="64"/>
-      <c r="J35" s="64"/>
-      <c r="K35" s="64"/>
-      <c r="L35" s="64"/>
-      <c r="M35" s="64"/>
-      <c r="N35" s="64"/>
-      <c r="O35" s="64"/>
-      <c r="P35" s="64"/>
-      <c r="Q35" s="64"/>
-      <c r="R35" s="64"/>
-      <c r="S35" s="64"/>
-      <c r="T35" s="64"/>
-      <c r="U35" s="64"/>
-      <c r="V35" s="64"/>
-      <c r="W35" s="64"/>
-      <c r="X35" s="64"/>
-      <c r="Y35" s="64"/>
-      <c r="Z35" s="64"/>
-      <c r="AA35" s="65"/>
+      <c r="B35" s="64"/>
+      <c r="C35" s="65"/>
+      <c r="D35" s="65"/>
+      <c r="E35" s="65"/>
+      <c r="F35" s="65"/>
+      <c r="G35" s="65"/>
+      <c r="H35" s="65"/>
+      <c r="I35" s="65"/>
+      <c r="J35" s="65"/>
+      <c r="K35" s="65"/>
+      <c r="L35" s="65"/>
+      <c r="M35" s="65"/>
+      <c r="N35" s="65"/>
+      <c r="O35" s="65"/>
+      <c r="P35" s="65"/>
+      <c r="Q35" s="65"/>
+      <c r="R35" s="65"/>
+      <c r="S35" s="65"/>
+      <c r="T35" s="65"/>
+      <c r="U35" s="65"/>
+      <c r="V35" s="65"/>
+      <c r="W35" s="65"/>
+      <c r="X35" s="65"/>
+      <c r="Y35" s="65"/>
+      <c r="Z35" s="65"/>
+      <c r="AA35" s="66"/>
     </row>
     <row r="36" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
-      <c r="B36" s="63"/>
-      <c r="C36" s="64"/>
-      <c r="D36" s="64"/>
-      <c r="E36" s="64"/>
-      <c r="F36" s="64"/>
-      <c r="G36" s="64"/>
-      <c r="H36" s="64"/>
-      <c r="I36" s="64"/>
-      <c r="J36" s="64"/>
-      <c r="K36" s="64"/>
-      <c r="L36" s="64"/>
-      <c r="M36" s="64"/>
-      <c r="N36" s="64"/>
-      <c r="O36" s="64"/>
-      <c r="P36" s="64"/>
-      <c r="Q36" s="64"/>
-      <c r="R36" s="64"/>
-      <c r="S36" s="64"/>
-      <c r="T36" s="64"/>
-      <c r="U36" s="64"/>
-      <c r="V36" s="64"/>
-      <c r="W36" s="64"/>
-      <c r="X36" s="64"/>
-      <c r="Y36" s="64"/>
-      <c r="Z36" s="64"/>
-      <c r="AA36" s="65"/>
+      <c r="B36" s="64"/>
+      <c r="C36" s="65"/>
+      <c r="D36" s="65"/>
+      <c r="E36" s="65"/>
+      <c r="F36" s="65"/>
+      <c r="G36" s="65"/>
+      <c r="H36" s="65"/>
+      <c r="I36" s="65"/>
+      <c r="J36" s="65"/>
+      <c r="K36" s="65"/>
+      <c r="L36" s="65"/>
+      <c r="M36" s="65"/>
+      <c r="N36" s="65"/>
+      <c r="O36" s="65"/>
+      <c r="P36" s="65"/>
+      <c r="Q36" s="65"/>
+      <c r="R36" s="65"/>
+      <c r="S36" s="65"/>
+      <c r="T36" s="65"/>
+      <c r="U36" s="65"/>
+      <c r="V36" s="65"/>
+      <c r="W36" s="65"/>
+      <c r="X36" s="65"/>
+      <c r="Y36" s="65"/>
+      <c r="Z36" s="65"/>
+      <c r="AA36" s="66"/>
     </row>
     <row r="37" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
-      <c r="B37" s="63"/>
-      <c r="C37" s="64"/>
-      <c r="D37" s="64"/>
-      <c r="E37" s="64"/>
-      <c r="F37" s="64"/>
-      <c r="G37" s="64"/>
-      <c r="H37" s="64"/>
-      <c r="I37" s="64"/>
-      <c r="J37" s="64"/>
-      <c r="K37" s="64"/>
-      <c r="L37" s="64"/>
-      <c r="M37" s="64"/>
-      <c r="N37" s="64"/>
-      <c r="O37" s="64"/>
-      <c r="P37" s="64"/>
-      <c r="Q37" s="64"/>
-      <c r="R37" s="64"/>
-      <c r="S37" s="64"/>
-      <c r="T37" s="64"/>
-      <c r="U37" s="64"/>
-      <c r="V37" s="64"/>
-      <c r="W37" s="64"/>
-      <c r="X37" s="64"/>
-      <c r="Y37" s="64"/>
-      <c r="Z37" s="64"/>
-      <c r="AA37" s="65"/>
+      <c r="B37" s="64"/>
+      <c r="C37" s="65"/>
+      <c r="D37" s="65"/>
+      <c r="E37" s="65"/>
+      <c r="F37" s="65"/>
+      <c r="G37" s="65"/>
+      <c r="H37" s="65"/>
+      <c r="I37" s="65"/>
+      <c r="J37" s="65"/>
+      <c r="K37" s="65"/>
+      <c r="L37" s="65"/>
+      <c r="M37" s="65"/>
+      <c r="N37" s="65"/>
+      <c r="O37" s="65"/>
+      <c r="P37" s="65"/>
+      <c r="Q37" s="65"/>
+      <c r="R37" s="65"/>
+      <c r="S37" s="65"/>
+      <c r="T37" s="65"/>
+      <c r="U37" s="65"/>
+      <c r="V37" s="65"/>
+      <c r="W37" s="65"/>
+      <c r="X37" s="65"/>
+      <c r="Y37" s="65"/>
+      <c r="Z37" s="65"/>
+      <c r="AA37" s="66"/>
     </row>
     <row r="38" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
-      <c r="B38" s="63"/>
-      <c r="C38" s="64"/>
-      <c r="D38" s="64"/>
-      <c r="E38" s="64"/>
-      <c r="F38" s="64"/>
-      <c r="G38" s="64"/>
-      <c r="H38" s="64"/>
-      <c r="I38" s="64"/>
-      <c r="J38" s="64"/>
-      <c r="K38" s="64"/>
-      <c r="L38" s="64"/>
-      <c r="M38" s="64"/>
-      <c r="N38" s="64"/>
-      <c r="O38" s="64"/>
-      <c r="P38" s="64"/>
-      <c r="Q38" s="64"/>
-      <c r="R38" s="64"/>
-      <c r="S38" s="64"/>
-      <c r="T38" s="64"/>
-      <c r="U38" s="64"/>
-      <c r="V38" s="64"/>
-      <c r="W38" s="64"/>
-      <c r="X38" s="64"/>
-      <c r="Y38" s="64"/>
-      <c r="Z38" s="64"/>
-      <c r="AA38" s="65"/>
+      <c r="B38" s="64"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="65"/>
+      <c r="H38" s="65"/>
+      <c r="I38" s="65"/>
+      <c r="J38" s="65"/>
+      <c r="K38" s="65"/>
+      <c r="L38" s="65"/>
+      <c r="M38" s="65"/>
+      <c r="N38" s="65"/>
+      <c r="O38" s="65"/>
+      <c r="P38" s="65"/>
+      <c r="Q38" s="65"/>
+      <c r="R38" s="65"/>
+      <c r="S38" s="65"/>
+      <c r="T38" s="65"/>
+      <c r="U38" s="65"/>
+      <c r="V38" s="65"/>
+      <c r="W38" s="65"/>
+      <c r="X38" s="65"/>
+      <c r="Y38" s="65"/>
+      <c r="Z38" s="65"/>
+      <c r="AA38" s="66"/>
     </row>
     <row r="39" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
-      <c r="B39" s="74"/>
-      <c r="C39" s="69"/>
-      <c r="D39" s="69"/>
-      <c r="E39" s="69"/>
-      <c r="F39" s="69"/>
-      <c r="G39" s="69"/>
-      <c r="H39" s="69"/>
-      <c r="I39" s="69"/>
-      <c r="J39" s="69"/>
-      <c r="K39" s="69"/>
-      <c r="L39" s="69"/>
-      <c r="M39" s="69"/>
-      <c r="N39" s="69"/>
-      <c r="O39" s="69"/>
-      <c r="P39" s="69"/>
-      <c r="Q39" s="69"/>
-      <c r="R39" s="69"/>
-      <c r="S39" s="69"/>
-      <c r="T39" s="69"/>
-      <c r="U39" s="69"/>
-      <c r="V39" s="69"/>
-      <c r="W39" s="69"/>
-      <c r="X39" s="69"/>
-      <c r="Y39" s="69"/>
-      <c r="Z39" s="69"/>
-      <c r="AA39" s="75"/>
+      <c r="B39" s="67"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="46"/>
+      <c r="F39" s="46"/>
+      <c r="G39" s="46"/>
+      <c r="H39" s="46"/>
+      <c r="I39" s="46"/>
+      <c r="J39" s="46"/>
+      <c r="K39" s="46"/>
+      <c r="L39" s="46"/>
+      <c r="M39" s="46"/>
+      <c r="N39" s="46"/>
+      <c r="O39" s="46"/>
+      <c r="P39" s="46"/>
+      <c r="Q39" s="46"/>
+      <c r="R39" s="46"/>
+      <c r="S39" s="46"/>
+      <c r="T39" s="46"/>
+      <c r="U39" s="46"/>
+      <c r="V39" s="46"/>
+      <c r="W39" s="46"/>
+      <c r="X39" s="46"/>
+      <c r="Y39" s="46"/>
+      <c r="Z39" s="46"/>
+      <c r="AA39" s="68"/>
     </row>
     <row r="40" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
-      <c r="B40" s="76" t="s">
+      <c r="B40" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="77"/>
-      <c r="D40" s="77"/>
-      <c r="E40" s="77"/>
-      <c r="F40" s="77"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="77"/>
-      <c r="I40" s="77"/>
-      <c r="J40" s="77"/>
-      <c r="K40" s="77"/>
-      <c r="L40" s="77"/>
-      <c r="M40" s="77"/>
-      <c r="N40" s="77"/>
-      <c r="O40" s="77"/>
-      <c r="P40" s="77"/>
-      <c r="Q40" s="77"/>
-      <c r="R40" s="77"/>
-      <c r="S40" s="77"/>
-      <c r="T40" s="77"/>
-      <c r="U40" s="77"/>
-      <c r="V40" s="77"/>
-      <c r="W40" s="77"/>
-      <c r="X40" s="77"/>
-      <c r="Y40" s="77"/>
-      <c r="Z40" s="77"/>
-      <c r="AA40" s="78"/>
+      <c r="C40" s="61"/>
+      <c r="D40" s="61"/>
+      <c r="E40" s="61"/>
+      <c r="F40" s="61"/>
+      <c r="G40" s="61"/>
+      <c r="H40" s="61"/>
+      <c r="I40" s="61"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="61"/>
+      <c r="L40" s="61"/>
+      <c r="M40" s="61"/>
+      <c r="N40" s="61"/>
+      <c r="O40" s="61"/>
+      <c r="P40" s="61"/>
+      <c r="Q40" s="61"/>
+      <c r="R40" s="61"/>
+      <c r="S40" s="61"/>
+      <c r="T40" s="61"/>
+      <c r="U40" s="61"/>
+      <c r="V40" s="61"/>
+      <c r="W40" s="61"/>
+      <c r="X40" s="61"/>
+      <c r="Y40" s="61"/>
+      <c r="Z40" s="61"/>
+      <c r="AA40" s="62"/>
     </row>
     <row r="41" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
-      <c r="B41" s="60"/>
-      <c r="C41" s="61"/>
-      <c r="D41" s="61"/>
-      <c r="E41" s="61"/>
-      <c r="F41" s="61"/>
-      <c r="G41" s="61"/>
-      <c r="H41" s="61"/>
-      <c r="I41" s="61"/>
-      <c r="J41" s="61"/>
-      <c r="K41" s="61"/>
-      <c r="L41" s="61"/>
-      <c r="M41" s="61"/>
-      <c r="N41" s="61"/>
-      <c r="O41" s="61"/>
-      <c r="P41" s="61"/>
-      <c r="Q41" s="61"/>
-      <c r="R41" s="61"/>
-      <c r="S41" s="61"/>
-      <c r="T41" s="61"/>
-      <c r="U41" s="61"/>
-      <c r="V41" s="61"/>
-      <c r="W41" s="61"/>
-      <c r="X41" s="61"/>
-      <c r="Y41" s="61"/>
-      <c r="Z41" s="61"/>
-      <c r="AA41" s="62"/>
+      <c r="B41" s="51"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="43"/>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
+      <c r="L41" s="43"/>
+      <c r="M41" s="43"/>
+      <c r="N41" s="43"/>
+      <c r="O41" s="43"/>
+      <c r="P41" s="43"/>
+      <c r="Q41" s="43"/>
+      <c r="R41" s="43"/>
+      <c r="S41" s="43"/>
+      <c r="T41" s="43"/>
+      <c r="U41" s="43"/>
+      <c r="V41" s="43"/>
+      <c r="W41" s="43"/>
+      <c r="X41" s="43"/>
+      <c r="Y41" s="43"/>
+      <c r="Z41" s="43"/>
+      <c r="AA41" s="63"/>
     </row>
     <row r="42" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
-      <c r="B42" s="63"/>
-      <c r="C42" s="64"/>
-      <c r="D42" s="64"/>
-      <c r="E42" s="64"/>
-      <c r="F42" s="64"/>
-      <c r="G42" s="64"/>
-      <c r="H42" s="64"/>
-      <c r="I42" s="64"/>
-      <c r="J42" s="64"/>
-      <c r="K42" s="64"/>
-      <c r="L42" s="64"/>
-      <c r="M42" s="64"/>
-      <c r="N42" s="64"/>
-      <c r="O42" s="64"/>
-      <c r="P42" s="64"/>
-      <c r="Q42" s="64"/>
-      <c r="R42" s="64"/>
-      <c r="S42" s="64"/>
-      <c r="T42" s="64"/>
-      <c r="U42" s="64"/>
-      <c r="V42" s="64"/>
-      <c r="W42" s="64"/>
-      <c r="X42" s="64"/>
-      <c r="Y42" s="64"/>
-      <c r="Z42" s="64"/>
-      <c r="AA42" s="65"/>
+      <c r="B42" s="64"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="65"/>
+      <c r="H42" s="65"/>
+      <c r="I42" s="65"/>
+      <c r="J42" s="65"/>
+      <c r="K42" s="65"/>
+      <c r="L42" s="65"/>
+      <c r="M42" s="65"/>
+      <c r="N42" s="65"/>
+      <c r="O42" s="65"/>
+      <c r="P42" s="65"/>
+      <c r="Q42" s="65"/>
+      <c r="R42" s="65"/>
+      <c r="S42" s="65"/>
+      <c r="T42" s="65"/>
+      <c r="U42" s="65"/>
+      <c r="V42" s="65"/>
+      <c r="W42" s="65"/>
+      <c r="X42" s="65"/>
+      <c r="Y42" s="65"/>
+      <c r="Z42" s="65"/>
+      <c r="AA42" s="66"/>
     </row>
     <row r="43" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
-      <c r="B43" s="63"/>
-      <c r="C43" s="64"/>
-      <c r="D43" s="64"/>
-      <c r="E43" s="64"/>
-      <c r="F43" s="64"/>
-      <c r="G43" s="64"/>
-      <c r="H43" s="64"/>
-      <c r="I43" s="64"/>
-      <c r="J43" s="64"/>
-      <c r="K43" s="64"/>
-      <c r="L43" s="64"/>
-      <c r="M43" s="64"/>
-      <c r="N43" s="64"/>
-      <c r="O43" s="64"/>
-      <c r="P43" s="64"/>
-      <c r="Q43" s="64"/>
-      <c r="R43" s="64"/>
-      <c r="S43" s="64"/>
-      <c r="T43" s="64"/>
-      <c r="U43" s="64"/>
-      <c r="V43" s="64"/>
-      <c r="W43" s="64"/>
-      <c r="X43" s="64"/>
-      <c r="Y43" s="64"/>
-      <c r="Z43" s="64"/>
-      <c r="AA43" s="65"/>
+      <c r="B43" s="64"/>
+      <c r="C43" s="65"/>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65"/>
+      <c r="I43" s="65"/>
+      <c r="J43" s="65"/>
+      <c r="K43" s="65"/>
+      <c r="L43" s="65"/>
+      <c r="M43" s="65"/>
+      <c r="N43" s="65"/>
+      <c r="O43" s="65"/>
+      <c r="P43" s="65"/>
+      <c r="Q43" s="65"/>
+      <c r="R43" s="65"/>
+      <c r="S43" s="65"/>
+      <c r="T43" s="65"/>
+      <c r="U43" s="65"/>
+      <c r="V43" s="65"/>
+      <c r="W43" s="65"/>
+      <c r="X43" s="65"/>
+      <c r="Y43" s="65"/>
+      <c r="Z43" s="65"/>
+      <c r="AA43" s="66"/>
     </row>
     <row r="44" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
-      <c r="B44" s="63"/>
-      <c r="C44" s="64"/>
-      <c r="D44" s="64"/>
-      <c r="E44" s="64"/>
-      <c r="F44" s="64"/>
-      <c r="G44" s="64"/>
-      <c r="H44" s="64"/>
-      <c r="I44" s="64"/>
-      <c r="J44" s="64"/>
-      <c r="K44" s="64"/>
-      <c r="L44" s="64"/>
-      <c r="M44" s="64"/>
-      <c r="N44" s="64"/>
-      <c r="O44" s="64"/>
-      <c r="P44" s="64"/>
-      <c r="Q44" s="64"/>
-      <c r="R44" s="64"/>
-      <c r="S44" s="64"/>
-      <c r="T44" s="64"/>
-      <c r="U44" s="64"/>
-      <c r="V44" s="64"/>
-      <c r="W44" s="64"/>
-      <c r="X44" s="64"/>
-      <c r="Y44" s="64"/>
-      <c r="Z44" s="64"/>
-      <c r="AA44" s="65"/>
+      <c r="B44" s="64"/>
+      <c r="C44" s="65"/>
+      <c r="D44" s="65"/>
+      <c r="E44" s="65"/>
+      <c r="F44" s="65"/>
+      <c r="G44" s="65"/>
+      <c r="H44" s="65"/>
+      <c r="I44" s="65"/>
+      <c r="J44" s="65"/>
+      <c r="K44" s="65"/>
+      <c r="L44" s="65"/>
+      <c r="M44" s="65"/>
+      <c r="N44" s="65"/>
+      <c r="O44" s="65"/>
+      <c r="P44" s="65"/>
+      <c r="Q44" s="65"/>
+      <c r="R44" s="65"/>
+      <c r="S44" s="65"/>
+      <c r="T44" s="65"/>
+      <c r="U44" s="65"/>
+      <c r="V44" s="65"/>
+      <c r="W44" s="65"/>
+      <c r="X44" s="65"/>
+      <c r="Y44" s="65"/>
+      <c r="Z44" s="65"/>
+      <c r="AA44" s="66"/>
     </row>
     <row r="45" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
-      <c r="B45" s="63"/>
-      <c r="C45" s="64"/>
-      <c r="D45" s="64"/>
-      <c r="E45" s="64"/>
-      <c r="F45" s="64"/>
-      <c r="G45" s="64"/>
-      <c r="H45" s="64"/>
-      <c r="I45" s="64"/>
-      <c r="J45" s="64"/>
-      <c r="K45" s="64"/>
-      <c r="L45" s="64"/>
-      <c r="M45" s="64"/>
-      <c r="N45" s="64"/>
-      <c r="O45" s="64"/>
-      <c r="P45" s="64"/>
-      <c r="Q45" s="64"/>
-      <c r="R45" s="64"/>
-      <c r="S45" s="64"/>
-      <c r="T45" s="64"/>
-      <c r="U45" s="64"/>
-      <c r="V45" s="64"/>
-      <c r="W45" s="64"/>
-      <c r="X45" s="64"/>
-      <c r="Y45" s="64"/>
-      <c r="Z45" s="64"/>
-      <c r="AA45" s="65"/>
+      <c r="B45" s="64"/>
+      <c r="C45" s="65"/>
+      <c r="D45" s="65"/>
+      <c r="E45" s="65"/>
+      <c r="F45" s="65"/>
+      <c r="G45" s="65"/>
+      <c r="H45" s="65"/>
+      <c r="I45" s="65"/>
+      <c r="J45" s="65"/>
+      <c r="K45" s="65"/>
+      <c r="L45" s="65"/>
+      <c r="M45" s="65"/>
+      <c r="N45" s="65"/>
+      <c r="O45" s="65"/>
+      <c r="P45" s="65"/>
+      <c r="Q45" s="65"/>
+      <c r="R45" s="65"/>
+      <c r="S45" s="65"/>
+      <c r="T45" s="65"/>
+      <c r="U45" s="65"/>
+      <c r="V45" s="65"/>
+      <c r="W45" s="65"/>
+      <c r="X45" s="65"/>
+      <c r="Y45" s="65"/>
+      <c r="Z45" s="65"/>
+      <c r="AA45" s="66"/>
     </row>
     <row r="46" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
-      <c r="B46" s="63"/>
-      <c r="C46" s="64"/>
-      <c r="D46" s="64"/>
-      <c r="E46" s="64"/>
-      <c r="F46" s="64"/>
-      <c r="G46" s="64"/>
-      <c r="H46" s="64"/>
-      <c r="I46" s="64"/>
-      <c r="J46" s="64"/>
-      <c r="K46" s="64"/>
-      <c r="L46" s="64"/>
-      <c r="M46" s="64"/>
-      <c r="N46" s="64"/>
-      <c r="O46" s="64"/>
-      <c r="P46" s="64"/>
-      <c r="Q46" s="64"/>
-      <c r="R46" s="64"/>
-      <c r="S46" s="64"/>
-      <c r="T46" s="64"/>
-      <c r="U46" s="64"/>
-      <c r="V46" s="64"/>
-      <c r="W46" s="64"/>
-      <c r="X46" s="64"/>
-      <c r="Y46" s="64"/>
-      <c r="Z46" s="64"/>
-      <c r="AA46" s="65"/>
+      <c r="B46" s="64"/>
+      <c r="C46" s="65"/>
+      <c r="D46" s="65"/>
+      <c r="E46" s="65"/>
+      <c r="F46" s="65"/>
+      <c r="G46" s="65"/>
+      <c r="H46" s="65"/>
+      <c r="I46" s="65"/>
+      <c r="J46" s="65"/>
+      <c r="K46" s="65"/>
+      <c r="L46" s="65"/>
+      <c r="M46" s="65"/>
+      <c r="N46" s="65"/>
+      <c r="O46" s="65"/>
+      <c r="P46" s="65"/>
+      <c r="Q46" s="65"/>
+      <c r="R46" s="65"/>
+      <c r="S46" s="65"/>
+      <c r="T46" s="65"/>
+      <c r="U46" s="65"/>
+      <c r="V46" s="65"/>
+      <c r="W46" s="65"/>
+      <c r="X46" s="65"/>
+      <c r="Y46" s="65"/>
+      <c r="Z46" s="65"/>
+      <c r="AA46" s="66"/>
     </row>
     <row r="47" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
-      <c r="B47" s="79"/>
-      <c r="C47" s="80"/>
-      <c r="D47" s="80"/>
-      <c r="E47" s="80"/>
-      <c r="F47" s="80"/>
-      <c r="G47" s="80"/>
-      <c r="H47" s="80"/>
-      <c r="I47" s="80"/>
-      <c r="J47" s="80"/>
-      <c r="K47" s="80"/>
-      <c r="L47" s="80"/>
-      <c r="M47" s="80"/>
-      <c r="N47" s="80"/>
-      <c r="O47" s="80"/>
-      <c r="P47" s="80"/>
-      <c r="Q47" s="80"/>
-      <c r="R47" s="80"/>
-      <c r="S47" s="80"/>
-      <c r="T47" s="80"/>
-      <c r="U47" s="80"/>
-      <c r="V47" s="80"/>
-      <c r="W47" s="80"/>
-      <c r="X47" s="80"/>
-      <c r="Y47" s="80"/>
-      <c r="Z47" s="80"/>
-      <c r="AA47" s="81"/>
+      <c r="B47" s="69"/>
+      <c r="C47" s="70"/>
+      <c r="D47" s="70"/>
+      <c r="E47" s="70"/>
+      <c r="F47" s="70"/>
+      <c r="G47" s="70"/>
+      <c r="H47" s="70"/>
+      <c r="I47" s="70"/>
+      <c r="J47" s="70"/>
+      <c r="K47" s="70"/>
+      <c r="L47" s="70"/>
+      <c r="M47" s="70"/>
+      <c r="N47" s="70"/>
+      <c r="O47" s="70"/>
+      <c r="P47" s="70"/>
+      <c r="Q47" s="70"/>
+      <c r="R47" s="70"/>
+      <c r="S47" s="70"/>
+      <c r="T47" s="70"/>
+      <c r="U47" s="70"/>
+      <c r="V47" s="70"/>
+      <c r="W47" s="70"/>
+      <c r="X47" s="70"/>
+      <c r="Y47" s="70"/>
+      <c r="Z47" s="70"/>
+      <c r="AA47" s="71"/>
     </row>
     <row r="48" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
-      <c r="B48" s="82" t="s">
+      <c r="B48" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="53"/>
-      <c r="D48" s="53"/>
-      <c r="E48" s="53"/>
-      <c r="F48" s="53"/>
-      <c r="G48" s="53"/>
-      <c r="H48" s="53"/>
-      <c r="I48" s="53"/>
-      <c r="J48" s="53"/>
-      <c r="K48" s="53"/>
-      <c r="L48" s="53"/>
-      <c r="M48" s="53"/>
-      <c r="N48" s="53"/>
-      <c r="O48" s="53"/>
-      <c r="P48" s="53"/>
-      <c r="Q48" s="53"/>
-      <c r="R48" s="53"/>
-      <c r="S48" s="53"/>
-      <c r="T48" s="53"/>
-      <c r="U48" s="53"/>
-      <c r="V48" s="53"/>
-      <c r="W48" s="53"/>
-      <c r="X48" s="53"/>
-      <c r="Y48" s="53"/>
-      <c r="Z48" s="53"/>
-      <c r="AA48" s="54"/>
+      <c r="C48" s="73"/>
+      <c r="D48" s="73"/>
+      <c r="E48" s="73"/>
+      <c r="F48" s="73"/>
+      <c r="G48" s="73"/>
+      <c r="H48" s="73"/>
+      <c r="I48" s="73"/>
+      <c r="J48" s="73"/>
+      <c r="K48" s="73"/>
+      <c r="L48" s="73"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="73"/>
+      <c r="O48" s="73"/>
+      <c r="P48" s="73"/>
+      <c r="Q48" s="73"/>
+      <c r="R48" s="73"/>
+      <c r="S48" s="73"/>
+      <c r="T48" s="73"/>
+      <c r="U48" s="73"/>
+      <c r="V48" s="73"/>
+      <c r="W48" s="73"/>
+      <c r="X48" s="73"/>
+      <c r="Y48" s="73"/>
+      <c r="Z48" s="73"/>
+      <c r="AA48" s="74"/>
     </row>
     <row r="49" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="30"/>
-      <c r="B49" s="60"/>
-      <c r="C49" s="61"/>
-      <c r="D49" s="61"/>
-      <c r="E49" s="61"/>
-      <c r="F49" s="61"/>
-      <c r="G49" s="61"/>
-      <c r="H49" s="61"/>
-      <c r="I49" s="61"/>
-      <c r="J49" s="61"/>
-      <c r="K49" s="61"/>
-      <c r="L49" s="61"/>
-      <c r="M49" s="61"/>
-      <c r="N49" s="61"/>
-      <c r="O49" s="61"/>
-      <c r="P49" s="61"/>
-      <c r="Q49" s="61"/>
-      <c r="R49" s="61"/>
-      <c r="S49" s="61"/>
-      <c r="T49" s="61"/>
-      <c r="U49" s="61"/>
-      <c r="V49" s="61"/>
-      <c r="W49" s="61"/>
-      <c r="X49" s="61"/>
-      <c r="Y49" s="61"/>
-      <c r="Z49" s="61"/>
-      <c r="AA49" s="62"/>
+      <c r="B49" s="51"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="43"/>
+      <c r="F49" s="43"/>
+      <c r="G49" s="43"/>
+      <c r="H49" s="43"/>
+      <c r="I49" s="43"/>
+      <c r="J49" s="43"/>
+      <c r="K49" s="43"/>
+      <c r="L49" s="43"/>
+      <c r="M49" s="43"/>
+      <c r="N49" s="43"/>
+      <c r="O49" s="43"/>
+      <c r="P49" s="43"/>
+      <c r="Q49" s="43"/>
+      <c r="R49" s="43"/>
+      <c r="S49" s="43"/>
+      <c r="T49" s="43"/>
+      <c r="U49" s="43"/>
+      <c r="V49" s="43"/>
+      <c r="W49" s="43"/>
+      <c r="X49" s="43"/>
+      <c r="Y49" s="43"/>
+      <c r="Z49" s="43"/>
+      <c r="AA49" s="63"/>
     </row>
     <row r="50" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="30"/>
-      <c r="B50" s="63"/>
-      <c r="C50" s="64"/>
-      <c r="D50" s="64"/>
-      <c r="E50" s="64"/>
-      <c r="F50" s="64"/>
-      <c r="G50" s="64"/>
-      <c r="H50" s="64"/>
-      <c r="I50" s="64"/>
-      <c r="J50" s="64"/>
-      <c r="K50" s="64"/>
-      <c r="L50" s="64"/>
-      <c r="M50" s="64"/>
-      <c r="N50" s="64"/>
-      <c r="O50" s="64"/>
-      <c r="P50" s="64"/>
-      <c r="Q50" s="64"/>
-      <c r="R50" s="64"/>
-      <c r="S50" s="64"/>
-      <c r="T50" s="64"/>
-      <c r="U50" s="64"/>
-      <c r="V50" s="64"/>
-      <c r="W50" s="64"/>
-      <c r="X50" s="64"/>
-      <c r="Y50" s="64"/>
-      <c r="Z50" s="64"/>
-      <c r="AA50" s="65"/>
+      <c r="B50" s="64"/>
+      <c r="C50" s="65"/>
+      <c r="D50" s="65"/>
+      <c r="E50" s="65"/>
+      <c r="F50" s="65"/>
+      <c r="G50" s="65"/>
+      <c r="H50" s="65"/>
+      <c r="I50" s="65"/>
+      <c r="J50" s="65"/>
+      <c r="K50" s="65"/>
+      <c r="L50" s="65"/>
+      <c r="M50" s="65"/>
+      <c r="N50" s="65"/>
+      <c r="O50" s="65"/>
+      <c r="P50" s="65"/>
+      <c r="Q50" s="65"/>
+      <c r="R50" s="65"/>
+      <c r="S50" s="65"/>
+      <c r="T50" s="65"/>
+      <c r="U50" s="65"/>
+      <c r="V50" s="65"/>
+      <c r="W50" s="65"/>
+      <c r="X50" s="65"/>
+      <c r="Y50" s="65"/>
+      <c r="Z50" s="65"/>
+      <c r="AA50" s="66"/>
     </row>
     <row r="51" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="30"/>
-      <c r="B51" s="63"/>
-      <c r="C51" s="64"/>
-      <c r="D51" s="64"/>
-      <c r="E51" s="64"/>
-      <c r="F51" s="64"/>
-      <c r="G51" s="64"/>
-      <c r="H51" s="64"/>
-      <c r="I51" s="64"/>
-      <c r="J51" s="64"/>
-      <c r="K51" s="64"/>
-      <c r="L51" s="64"/>
-      <c r="M51" s="64"/>
-      <c r="N51" s="64"/>
-      <c r="O51" s="64"/>
-      <c r="P51" s="64"/>
-      <c r="Q51" s="64"/>
-      <c r="R51" s="64"/>
-      <c r="S51" s="64"/>
-      <c r="T51" s="64"/>
-      <c r="U51" s="64"/>
-      <c r="V51" s="64"/>
-      <c r="W51" s="64"/>
-      <c r="X51" s="64"/>
-      <c r="Y51" s="64"/>
-      <c r="Z51" s="64"/>
-      <c r="AA51" s="65"/>
+      <c r="B51" s="64"/>
+      <c r="C51" s="65"/>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="65"/>
+      <c r="K51" s="65"/>
+      <c r="L51" s="65"/>
+      <c r="M51" s="65"/>
+      <c r="N51" s="65"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="65"/>
+      <c r="Q51" s="65"/>
+      <c r="R51" s="65"/>
+      <c r="S51" s="65"/>
+      <c r="T51" s="65"/>
+      <c r="U51" s="65"/>
+      <c r="V51" s="65"/>
+      <c r="W51" s="65"/>
+      <c r="X51" s="65"/>
+      <c r="Y51" s="65"/>
+      <c r="Z51" s="65"/>
+      <c r="AA51" s="66"/>
     </row>
     <row r="52" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="30"/>
-      <c r="B52" s="63"/>
-      <c r="C52" s="64"/>
-      <c r="D52" s="64"/>
-      <c r="E52" s="64"/>
-      <c r="F52" s="64"/>
-      <c r="G52" s="64"/>
-      <c r="H52" s="64"/>
-      <c r="I52" s="64"/>
-      <c r="J52" s="64"/>
-      <c r="K52" s="64"/>
-      <c r="L52" s="64"/>
-      <c r="M52" s="64"/>
-      <c r="N52" s="64"/>
-      <c r="O52" s="64"/>
-      <c r="P52" s="64"/>
-      <c r="Q52" s="64"/>
-      <c r="R52" s="64"/>
-      <c r="S52" s="64"/>
-      <c r="T52" s="64"/>
-      <c r="U52" s="64"/>
-      <c r="V52" s="64"/>
-      <c r="W52" s="64"/>
-      <c r="X52" s="64"/>
-      <c r="Y52" s="64"/>
-      <c r="Z52" s="64"/>
-      <c r="AA52" s="65"/>
+      <c r="B52" s="64"/>
+      <c r="C52" s="65"/>
+      <c r="D52" s="65"/>
+      <c r="E52" s="65"/>
+      <c r="F52" s="65"/>
+      <c r="G52" s="65"/>
+      <c r="H52" s="65"/>
+      <c r="I52" s="65"/>
+      <c r="J52" s="65"/>
+      <c r="K52" s="65"/>
+      <c r="L52" s="65"/>
+      <c r="M52" s="65"/>
+      <c r="N52" s="65"/>
+      <c r="O52" s="65"/>
+      <c r="P52" s="65"/>
+      <c r="Q52" s="65"/>
+      <c r="R52" s="65"/>
+      <c r="S52" s="65"/>
+      <c r="T52" s="65"/>
+      <c r="U52" s="65"/>
+      <c r="V52" s="65"/>
+      <c r="W52" s="65"/>
+      <c r="X52" s="65"/>
+      <c r="Y52" s="65"/>
+      <c r="Z52" s="65"/>
+      <c r="AA52" s="66"/>
     </row>
     <row r="53" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="30"/>
-      <c r="B53" s="63"/>
-      <c r="C53" s="64"/>
-      <c r="D53" s="64"/>
-      <c r="E53" s="64"/>
-      <c r="F53" s="64"/>
-      <c r="G53" s="64"/>
-      <c r="H53" s="64"/>
-      <c r="I53" s="64"/>
-      <c r="J53" s="64"/>
-      <c r="K53" s="64"/>
-      <c r="L53" s="64"/>
-      <c r="M53" s="64"/>
-      <c r="N53" s="64"/>
-      <c r="O53" s="64"/>
-      <c r="P53" s="64"/>
-      <c r="Q53" s="64"/>
-      <c r="R53" s="64"/>
-      <c r="S53" s="64"/>
-      <c r="T53" s="64"/>
-      <c r="U53" s="64"/>
-      <c r="V53" s="64"/>
-      <c r="W53" s="64"/>
-      <c r="X53" s="64"/>
-      <c r="Y53" s="64"/>
-      <c r="Z53" s="64"/>
-      <c r="AA53" s="65"/>
+      <c r="B53" s="64"/>
+      <c r="C53" s="65"/>
+      <c r="D53" s="65"/>
+      <c r="E53" s="65"/>
+      <c r="F53" s="65"/>
+      <c r="G53" s="65"/>
+      <c r="H53" s="65"/>
+      <c r="I53" s="65"/>
+      <c r="J53" s="65"/>
+      <c r="K53" s="65"/>
+      <c r="L53" s="65"/>
+      <c r="M53" s="65"/>
+      <c r="N53" s="65"/>
+      <c r="O53" s="65"/>
+      <c r="P53" s="65"/>
+      <c r="Q53" s="65"/>
+      <c r="R53" s="65"/>
+      <c r="S53" s="65"/>
+      <c r="T53" s="65"/>
+      <c r="U53" s="65"/>
+      <c r="V53" s="65"/>
+      <c r="W53" s="65"/>
+      <c r="X53" s="65"/>
+      <c r="Y53" s="65"/>
+      <c r="Z53" s="65"/>
+      <c r="AA53" s="66"/>
     </row>
     <row r="54" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="30"/>
-      <c r="B54" s="63"/>
-      <c r="C54" s="64"/>
-      <c r="D54" s="64"/>
-      <c r="E54" s="64"/>
-      <c r="F54" s="64"/>
-      <c r="G54" s="64"/>
-      <c r="H54" s="64"/>
-      <c r="I54" s="64"/>
-      <c r="J54" s="64"/>
-      <c r="K54" s="64"/>
-      <c r="L54" s="64"/>
-      <c r="M54" s="64"/>
-      <c r="N54" s="64"/>
-      <c r="O54" s="64"/>
-      <c r="P54" s="64"/>
-      <c r="Q54" s="64"/>
-      <c r="R54" s="64"/>
-      <c r="S54" s="64"/>
-      <c r="T54" s="64"/>
-      <c r="U54" s="64"/>
-      <c r="V54" s="64"/>
-      <c r="W54" s="64"/>
-      <c r="X54" s="64"/>
-      <c r="Y54" s="64"/>
-      <c r="Z54" s="64"/>
-      <c r="AA54" s="65"/>
+      <c r="B54" s="64"/>
+      <c r="C54" s="65"/>
+      <c r="D54" s="65"/>
+      <c r="E54" s="65"/>
+      <c r="F54" s="65"/>
+      <c r="G54" s="65"/>
+      <c r="H54" s="65"/>
+      <c r="I54" s="65"/>
+      <c r="J54" s="65"/>
+      <c r="K54" s="65"/>
+      <c r="L54" s="65"/>
+      <c r="M54" s="65"/>
+      <c r="N54" s="65"/>
+      <c r="O54" s="65"/>
+      <c r="P54" s="65"/>
+      <c r="Q54" s="65"/>
+      <c r="R54" s="65"/>
+      <c r="S54" s="65"/>
+      <c r="T54" s="65"/>
+      <c r="U54" s="65"/>
+      <c r="V54" s="65"/>
+      <c r="W54" s="65"/>
+      <c r="X54" s="65"/>
+      <c r="Y54" s="65"/>
+      <c r="Z54" s="65"/>
+      <c r="AA54" s="66"/>
     </row>
     <row r="55" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A55" s="30"/>
-      <c r="B55" s="55"/>
-      <c r="C55" s="56"/>
-      <c r="D55" s="56"/>
-      <c r="E55" s="56"/>
-      <c r="F55" s="56"/>
-      <c r="G55" s="56"/>
-      <c r="H55" s="56"/>
-      <c r="I55" s="56"/>
-      <c r="J55" s="56"/>
-      <c r="K55" s="56"/>
-      <c r="L55" s="56"/>
-      <c r="M55" s="56"/>
-      <c r="N55" s="56"/>
-      <c r="O55" s="56"/>
-      <c r="P55" s="56"/>
-      <c r="Q55" s="56"/>
-      <c r="R55" s="56"/>
-      <c r="S55" s="56"/>
-      <c r="T55" s="56"/>
-      <c r="U55" s="56"/>
-      <c r="V55" s="56"/>
-      <c r="W55" s="56"/>
-      <c r="X55" s="56"/>
-      <c r="Y55" s="56"/>
-      <c r="Z55" s="56"/>
-      <c r="AA55" s="57"/>
+      <c r="B55" s="81"/>
+      <c r="C55" s="82"/>
+      <c r="D55" s="82"/>
+      <c r="E55" s="82"/>
+      <c r="F55" s="82"/>
+      <c r="G55" s="82"/>
+      <c r="H55" s="82"/>
+      <c r="I55" s="82"/>
+      <c r="J55" s="82"/>
+      <c r="K55" s="82"/>
+      <c r="L55" s="82"/>
+      <c r="M55" s="82"/>
+      <c r="N55" s="82"/>
+      <c r="O55" s="82"/>
+      <c r="P55" s="82"/>
+      <c r="Q55" s="82"/>
+      <c r="R55" s="82"/>
+      <c r="S55" s="82"/>
+      <c r="T55" s="82"/>
+      <c r="U55" s="82"/>
+      <c r="V55" s="82"/>
+      <c r="W55" s="82"/>
+      <c r="X55" s="82"/>
+      <c r="Y55" s="82"/>
+      <c r="Z55" s="82"/>
+      <c r="AA55" s="83"/>
     </row>
     <row r="56" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
@@ -2904,22 +2910,22 @@
     </row>
     <row r="59" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
-      <c r="B59" s="37"/>
-      <c r="C59" s="37"/>
-      <c r="D59" s="37"/>
-      <c r="E59" s="37"/>
-      <c r="F59" s="40"/>
-      <c r="G59" s="40"/>
-      <c r="H59" s="40"/>
+      <c r="B59" s="91"/>
+      <c r="C59" s="91"/>
+      <c r="D59" s="91"/>
+      <c r="E59" s="91"/>
+      <c r="F59" s="91"/>
+      <c r="G59" s="91"/>
+      <c r="H59" s="91"/>
       <c r="I59" s="35"/>
       <c r="J59" s="35"/>
-      <c r="K59" s="40"/>
-      <c r="L59" s="40"/>
-      <c r="M59" s="40"/>
-      <c r="N59" s="40"/>
-      <c r="O59" s="40"/>
-      <c r="P59" s="40"/>
-      <c r="Q59" s="40"/>
+      <c r="K59" s="92"/>
+      <c r="L59" s="92"/>
+      <c r="M59" s="92"/>
+      <c r="N59" s="92"/>
+      <c r="O59" s="92"/>
+      <c r="P59" s="92"/>
+      <c r="Q59" s="92"/>
       <c r="R59" s="35"/>
       <c r="S59" s="40"/>
       <c r="T59" s="40"/>
@@ -3086,61 +3092,61 @@
     <row r="65" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
       <c r="B65" s="34"/>
-      <c r="C65" s="66" t="s">
+      <c r="C65" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="D65" s="61"/>
-      <c r="E65" s="61"/>
-      <c r="F65" s="61"/>
-      <c r="G65" s="61"/>
-      <c r="H65" s="61"/>
-      <c r="I65" s="61"/>
-      <c r="J65" s="61"/>
-      <c r="K65" s="61"/>
-      <c r="L65" s="61"/>
-      <c r="M65" s="61"/>
-      <c r="N65" s="61"/>
-      <c r="O65" s="61"/>
-      <c r="P65" s="61"/>
-      <c r="Q65" s="61"/>
-      <c r="R65" s="61"/>
-      <c r="S65" s="61"/>
-      <c r="T65" s="61"/>
-      <c r="U65" s="61"/>
-      <c r="V65" s="61"/>
-      <c r="W65" s="61"/>
-      <c r="X65" s="61"/>
-      <c r="Y65" s="61"/>
-      <c r="Z65" s="67"/>
+      <c r="D65" s="43"/>
+      <c r="E65" s="43"/>
+      <c r="F65" s="43"/>
+      <c r="G65" s="43"/>
+      <c r="H65" s="43"/>
+      <c r="I65" s="43"/>
+      <c r="J65" s="43"/>
+      <c r="K65" s="43"/>
+      <c r="L65" s="43"/>
+      <c r="M65" s="43"/>
+      <c r="N65" s="43"/>
+      <c r="O65" s="43"/>
+      <c r="P65" s="43"/>
+      <c r="Q65" s="43"/>
+      <c r="R65" s="43"/>
+      <c r="S65" s="43"/>
+      <c r="T65" s="43"/>
+      <c r="U65" s="43"/>
+      <c r="V65" s="43"/>
+      <c r="W65" s="43"/>
+      <c r="X65" s="43"/>
+      <c r="Y65" s="43"/>
+      <c r="Z65" s="44"/>
       <c r="AA65" s="34"/>
     </row>
     <row r="66" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
       <c r="B66" s="34"/>
-      <c r="C66" s="68"/>
-      <c r="D66" s="69"/>
-      <c r="E66" s="69"/>
-      <c r="F66" s="69"/>
-      <c r="G66" s="69"/>
-      <c r="H66" s="69"/>
-      <c r="I66" s="69"/>
-      <c r="J66" s="69"/>
-      <c r="K66" s="69"/>
-      <c r="L66" s="69"/>
-      <c r="M66" s="69"/>
-      <c r="N66" s="69"/>
-      <c r="O66" s="69"/>
-      <c r="P66" s="69"/>
-      <c r="Q66" s="69"/>
-      <c r="R66" s="69"/>
-      <c r="S66" s="69"/>
-      <c r="T66" s="69"/>
-      <c r="U66" s="69"/>
-      <c r="V66" s="69"/>
-      <c r="W66" s="69"/>
-      <c r="X66" s="69"/>
-      <c r="Y66" s="69"/>
-      <c r="Z66" s="70"/>
+      <c r="C66" s="45"/>
+      <c r="D66" s="46"/>
+      <c r="E66" s="46"/>
+      <c r="F66" s="46"/>
+      <c r="G66" s="46"/>
+      <c r="H66" s="46"/>
+      <c r="I66" s="46"/>
+      <c r="J66" s="46"/>
+      <c r="K66" s="46"/>
+      <c r="L66" s="46"/>
+      <c r="M66" s="46"/>
+      <c r="N66" s="46"/>
+      <c r="O66" s="46"/>
+      <c r="P66" s="46"/>
+      <c r="Q66" s="46"/>
+      <c r="R66" s="46"/>
+      <c r="S66" s="46"/>
+      <c r="T66" s="46"/>
+      <c r="U66" s="46"/>
+      <c r="V66" s="46"/>
+      <c r="W66" s="46"/>
+      <c r="X66" s="46"/>
+      <c r="Y66" s="46"/>
+      <c r="Z66" s="47"/>
       <c r="AA66" s="34"/>
     </row>
     <row r="67" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30230,7 +30236,22 @@
       <c r="AA1000" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="25">
+    <mergeCell ref="B3:AA3"/>
+    <mergeCell ref="B4:AA4"/>
+    <mergeCell ref="B5:AA5"/>
+    <mergeCell ref="B6:AA6"/>
+    <mergeCell ref="H10:Z10"/>
+    <mergeCell ref="H12:T12"/>
+    <mergeCell ref="W12:Z12"/>
+    <mergeCell ref="B14:AA15"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="H17:Z17"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="H19:Z19"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="H21:Z21"/>
+    <mergeCell ref="B49:AA55"/>
     <mergeCell ref="C65:Z66"/>
     <mergeCell ref="B23:AA23"/>
     <mergeCell ref="B24:AA31"/>
@@ -30239,21 +30260,8 @@
     <mergeCell ref="B40:AA40"/>
     <mergeCell ref="B41:AA47"/>
     <mergeCell ref="B48:AA48"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="H19:Z19"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="H21:Z21"/>
-    <mergeCell ref="B49:AA55"/>
-    <mergeCell ref="H12:T12"/>
-    <mergeCell ref="W12:Z12"/>
-    <mergeCell ref="B14:AA15"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="H17:Z17"/>
-    <mergeCell ref="B3:AA3"/>
-    <mergeCell ref="B4:AA4"/>
-    <mergeCell ref="B5:AA5"/>
-    <mergeCell ref="B6:AA6"/>
-    <mergeCell ref="H10:Z10"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="K59:Q59"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.98425196850393704" header="0" footer="0"/>

--- a/static/templates/tec02-A_template.xlsx
+++ b/static/templates/tec02-A_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\diseño-afk\static\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8F54D8-BC0D-4A3F-8855-4ADE185DB10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{905F0EEA-1F5C-4F22-83A0-C156D5DCF618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -835,10 +835,46 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
@@ -848,24 +884,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -880,52 +898,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -933,6 +906,51 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1258,125 +1276,125 @@
     </row>
     <row r="3" spans="1:27" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
-      <c r="B3" s="87" t="s">
+      <c r="B3" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
-      <c r="K3" s="76"/>
-      <c r="L3" s="76"/>
-      <c r="M3" s="76"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="W3" s="76"/>
-      <c r="X3" s="76"/>
-      <c r="Y3" s="76"/>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="77"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="43"/>
+      <c r="V3" s="43"/>
+      <c r="W3" s="43"/>
+      <c r="X3" s="43"/>
+      <c r="Y3" s="43"/>
+      <c r="Z3" s="43"/>
+      <c r="AA3" s="44"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
-      <c r="K4" s="76"/>
-      <c r="L4" s="76"/>
-      <c r="M4" s="76"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="W4" s="76"/>
-      <c r="X4" s="76"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="77"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="43"/>
+      <c r="T4" s="43"/>
+      <c r="U4" s="43"/>
+      <c r="V4" s="43"/>
+      <c r="W4" s="43"/>
+      <c r="X4" s="43"/>
+      <c r="Y4" s="43"/>
+      <c r="Z4" s="43"/>
+      <c r="AA4" s="44"/>
     </row>
     <row r="5" spans="1:27" ht="20" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
-      <c r="B5" s="89" t="s">
+      <c r="B5" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
-      <c r="K5" s="76"/>
-      <c r="L5" s="76"/>
-      <c r="M5" s="76"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
-      <c r="W5" s="76"/>
-      <c r="X5" s="76"/>
-      <c r="Y5" s="76"/>
-      <c r="Z5" s="76"/>
-      <c r="AA5" s="77"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="43"/>
+      <c r="P5" s="43"/>
+      <c r="Q5" s="43"/>
+      <c r="R5" s="43"/>
+      <c r="S5" s="43"/>
+      <c r="T5" s="43"/>
+      <c r="U5" s="43"/>
+      <c r="V5" s="43"/>
+      <c r="W5" s="43"/>
+      <c r="X5" s="43"/>
+      <c r="Y5" s="43"/>
+      <c r="Z5" s="43"/>
+      <c r="AA5" s="44"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
-      <c r="B6" s="90" t="s">
+      <c r="B6" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76"/>
-      <c r="K6" s="76"/>
-      <c r="L6" s="76"/>
-      <c r="M6" s="76"/>
-      <c r="N6" s="76"/>
-      <c r="O6" s="76"/>
-      <c r="P6" s="76"/>
-      <c r="Q6" s="76"/>
-      <c r="R6" s="76"/>
-      <c r="S6" s="76"/>
-      <c r="T6" s="76"/>
-      <c r="U6" s="76"/>
-      <c r="V6" s="76"/>
-      <c r="W6" s="76"/>
-      <c r="X6" s="76"/>
-      <c r="Y6" s="76"/>
-      <c r="Z6" s="76"/>
-      <c r="AA6" s="77"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="43"/>
+      <c r="Q6" s="43"/>
+      <c r="R6" s="43"/>
+      <c r="S6" s="43"/>
+      <c r="T6" s="43"/>
+      <c r="U6" s="43"/>
+      <c r="V6" s="43"/>
+      <c r="W6" s="43"/>
+      <c r="X6" s="43"/>
+      <c r="Y6" s="43"/>
+      <c r="Z6" s="43"/>
+      <c r="AA6" s="44"/>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2"/>
@@ -1475,25 +1493,25 @@
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
-      <c r="H10" s="84"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="79"/>
-      <c r="K10" s="79"/>
-      <c r="L10" s="79"/>
-      <c r="M10" s="79"/>
-      <c r="N10" s="79"/>
-      <c r="O10" s="79"/>
-      <c r="P10" s="79"/>
-      <c r="Q10" s="79"/>
-      <c r="R10" s="79"/>
-      <c r="S10" s="79"/>
-      <c r="T10" s="79"/>
-      <c r="U10" s="79"/>
-      <c r="V10" s="79"/>
-      <c r="W10" s="79"/>
-      <c r="X10" s="79"/>
-      <c r="Y10" s="79"/>
-      <c r="Z10" s="80"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="49"/>
+      <c r="N10" s="49"/>
+      <c r="O10" s="49"/>
+      <c r="P10" s="49"/>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="49"/>
+      <c r="S10" s="49"/>
+      <c r="T10" s="49"/>
+      <c r="U10" s="49"/>
+      <c r="V10" s="49"/>
+      <c r="W10" s="49"/>
+      <c r="X10" s="49"/>
+      <c r="Y10" s="49"/>
+      <c r="Z10" s="50"/>
       <c r="AA10" s="11"/>
     </row>
     <row r="11" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1535,27 +1553,27 @@
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
-      <c r="H12" s="84"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="79"/>
-      <c r="K12" s="79"/>
-      <c r="L12" s="79"/>
-      <c r="M12" s="79"/>
-      <c r="N12" s="79"/>
-      <c r="O12" s="79"/>
-      <c r="P12" s="79"/>
-      <c r="Q12" s="79"/>
-      <c r="R12" s="79"/>
-      <c r="S12" s="79"/>
-      <c r="T12" s="80"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="49"/>
+      <c r="K12" s="49"/>
+      <c r="L12" s="49"/>
+      <c r="M12" s="49"/>
+      <c r="N12" s="49"/>
+      <c r="O12" s="49"/>
+      <c r="P12" s="49"/>
+      <c r="Q12" s="49"/>
+      <c r="R12" s="49"/>
+      <c r="S12" s="49"/>
+      <c r="T12" s="50"/>
       <c r="U12" s="13"/>
       <c r="V12" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="W12" s="85"/>
-      <c r="X12" s="79"/>
-      <c r="Y12" s="79"/>
-      <c r="Z12" s="80"/>
+      <c r="W12" s="51"/>
+      <c r="X12" s="49"/>
+      <c r="Y12" s="49"/>
+      <c r="Z12" s="50"/>
       <c r="AA12" s="15"/>
     </row>
     <row r="13" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1589,63 +1607,63 @@
     </row>
     <row r="14" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
-      <c r="B14" s="86" t="s">
+      <c r="B14" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="73"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="73"/>
-      <c r="G14" s="73"/>
-      <c r="H14" s="73"/>
-      <c r="I14" s="73"/>
-      <c r="J14" s="73"/>
-      <c r="K14" s="73"/>
-      <c r="L14" s="73"/>
-      <c r="M14" s="73"/>
-      <c r="N14" s="73"/>
-      <c r="O14" s="73"/>
-      <c r="P14" s="73"/>
-      <c r="Q14" s="73"/>
-      <c r="R14" s="73"/>
-      <c r="S14" s="73"/>
-      <c r="T14" s="73"/>
-      <c r="U14" s="73"/>
-      <c r="V14" s="73"/>
-      <c r="W14" s="73"/>
-      <c r="X14" s="73"/>
-      <c r="Y14" s="73"/>
-      <c r="Z14" s="73"/>
-      <c r="AA14" s="74"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="53"/>
+      <c r="L14" s="53"/>
+      <c r="M14" s="53"/>
+      <c r="N14" s="53"/>
+      <c r="O14" s="53"/>
+      <c r="P14" s="53"/>
+      <c r="Q14" s="53"/>
+      <c r="R14" s="53"/>
+      <c r="S14" s="53"/>
+      <c r="T14" s="53"/>
+      <c r="U14" s="53"/>
+      <c r="V14" s="53"/>
+      <c r="W14" s="53"/>
+      <c r="X14" s="53"/>
+      <c r="Y14" s="53"/>
+      <c r="Z14" s="53"/>
+      <c r="AA14" s="54"/>
     </row>
     <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
-      <c r="B15" s="81"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="82"/>
-      <c r="H15" s="82"/>
-      <c r="I15" s="82"/>
-      <c r="J15" s="82"/>
-      <c r="K15" s="82"/>
-      <c r="L15" s="82"/>
-      <c r="M15" s="82"/>
-      <c r="N15" s="82"/>
-      <c r="O15" s="82"/>
-      <c r="P15" s="82"/>
-      <c r="Q15" s="82"/>
-      <c r="R15" s="82"/>
-      <c r="S15" s="82"/>
-      <c r="T15" s="82"/>
-      <c r="U15" s="82"/>
-      <c r="V15" s="82"/>
-      <c r="W15" s="82"/>
-      <c r="X15" s="82"/>
-      <c r="Y15" s="82"/>
-      <c r="Z15" s="82"/>
-      <c r="AA15" s="83"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="56"/>
+      <c r="K15" s="56"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="56"/>
+      <c r="N15" s="56"/>
+      <c r="O15" s="56"/>
+      <c r="P15" s="56"/>
+      <c r="Q15" s="56"/>
+      <c r="R15" s="56"/>
+      <c r="S15" s="56"/>
+      <c r="T15" s="56"/>
+      <c r="U15" s="56"/>
+      <c r="V15" s="56"/>
+      <c r="W15" s="56"/>
+      <c r="X15" s="56"/>
+      <c r="Y15" s="56"/>
+      <c r="Z15" s="56"/>
+      <c r="AA15" s="57"/>
     </row>
     <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
@@ -1678,33 +1696,33 @@
     </row>
     <row r="17" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
-      <c r="B17" s="75" t="s">
+      <c r="B17" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="76"/>
-      <c r="D17" s="76"/>
-      <c r="E17" s="76"/>
-      <c r="F17" s="76"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="78"/>
-      <c r="I17" s="79"/>
-      <c r="J17" s="79"/>
-      <c r="K17" s="79"/>
-      <c r="L17" s="79"/>
-      <c r="M17" s="79"/>
-      <c r="N17" s="79"/>
-      <c r="O17" s="79"/>
-      <c r="P17" s="79"/>
-      <c r="Q17" s="79"/>
-      <c r="R17" s="79"/>
-      <c r="S17" s="79"/>
-      <c r="T17" s="79"/>
-      <c r="U17" s="79"/>
-      <c r="V17" s="79"/>
-      <c r="W17" s="79"/>
-      <c r="X17" s="79"/>
-      <c r="Y17" s="79"/>
-      <c r="Z17" s="80"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="49"/>
+      <c r="J17" s="49"/>
+      <c r="K17" s="49"/>
+      <c r="L17" s="49"/>
+      <c r="M17" s="49"/>
+      <c r="N17" s="49"/>
+      <c r="O17" s="49"/>
+      <c r="P17" s="49"/>
+      <c r="Q17" s="49"/>
+      <c r="R17" s="49"/>
+      <c r="S17" s="49"/>
+      <c r="T17" s="49"/>
+      <c r="U17" s="49"/>
+      <c r="V17" s="49"/>
+      <c r="W17" s="49"/>
+      <c r="X17" s="49"/>
+      <c r="Y17" s="49"/>
+      <c r="Z17" s="50"/>
       <c r="AA17" s="24"/>
     </row>
     <row r="18" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1738,33 +1756,33 @@
     </row>
     <row r="19" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
-      <c r="B19" s="75" t="s">
+      <c r="B19" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="76"/>
-      <c r="D19" s="76"/>
-      <c r="E19" s="76"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="77"/>
-      <c r="H19" s="78"/>
-      <c r="I19" s="79"/>
-      <c r="J19" s="79"/>
-      <c r="K19" s="79"/>
-      <c r="L19" s="79"/>
-      <c r="M19" s="79"/>
-      <c r="N19" s="79"/>
-      <c r="O19" s="79"/>
-      <c r="P19" s="79"/>
-      <c r="Q19" s="79"/>
-      <c r="R19" s="79"/>
-      <c r="S19" s="79"/>
-      <c r="T19" s="79"/>
-      <c r="U19" s="79"/>
-      <c r="V19" s="79"/>
-      <c r="W19" s="79"/>
-      <c r="X19" s="79"/>
-      <c r="Y19" s="79"/>
-      <c r="Z19" s="80"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="49"/>
+      <c r="J19" s="49"/>
+      <c r="K19" s="49"/>
+      <c r="L19" s="49"/>
+      <c r="M19" s="49"/>
+      <c r="N19" s="49"/>
+      <c r="O19" s="49"/>
+      <c r="P19" s="49"/>
+      <c r="Q19" s="49"/>
+      <c r="R19" s="49"/>
+      <c r="S19" s="49"/>
+      <c r="T19" s="49"/>
+      <c r="U19" s="49"/>
+      <c r="V19" s="49"/>
+      <c r="W19" s="49"/>
+      <c r="X19" s="49"/>
+      <c r="Y19" s="49"/>
+      <c r="Z19" s="50"/>
       <c r="AA19" s="24"/>
     </row>
     <row r="20" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1798,33 +1816,33 @@
     </row>
     <row r="21" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
-      <c r="B21" s="75" t="s">
+      <c r="B21" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="76"/>
-      <c r="D21" s="76"/>
-      <c r="E21" s="76"/>
-      <c r="F21" s="76"/>
-      <c r="G21" s="77"/>
-      <c r="H21" s="78"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="79"/>
-      <c r="K21" s="79"/>
-      <c r="L21" s="79"/>
-      <c r="M21" s="79"/>
-      <c r="N21" s="79"/>
-      <c r="O21" s="79"/>
-      <c r="P21" s="79"/>
-      <c r="Q21" s="79"/>
-      <c r="R21" s="79"/>
-      <c r="S21" s="79"/>
-      <c r="T21" s="79"/>
-      <c r="U21" s="79"/>
-      <c r="V21" s="79"/>
-      <c r="W21" s="79"/>
-      <c r="X21" s="79"/>
-      <c r="Y21" s="79"/>
-      <c r="Z21" s="80"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="49"/>
+      <c r="K21" s="49"/>
+      <c r="L21" s="49"/>
+      <c r="M21" s="49"/>
+      <c r="N21" s="49"/>
+      <c r="O21" s="49"/>
+      <c r="P21" s="49"/>
+      <c r="Q21" s="49"/>
+      <c r="R21" s="49"/>
+      <c r="S21" s="49"/>
+      <c r="T21" s="49"/>
+      <c r="U21" s="49"/>
+      <c r="V21" s="49"/>
+      <c r="W21" s="49"/>
+      <c r="X21" s="49"/>
+      <c r="Y21" s="49"/>
+      <c r="Z21" s="50"/>
       <c r="AA21" s="24"/>
     </row>
     <row r="22" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1858,968 +1876,968 @@
     </row>
     <row r="23" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
-      <c r="B23" s="48" t="s">
+      <c r="B23" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="49"/>
-      <c r="K23" s="49"/>
-      <c r="L23" s="49"/>
-      <c r="M23" s="49"/>
-      <c r="N23" s="49"/>
-      <c r="O23" s="49"/>
-      <c r="P23" s="49"/>
-      <c r="Q23" s="49"/>
-      <c r="R23" s="49"/>
-      <c r="S23" s="49"/>
-      <c r="T23" s="49"/>
-      <c r="U23" s="49"/>
-      <c r="V23" s="49"/>
-      <c r="W23" s="49"/>
-      <c r="X23" s="49"/>
-      <c r="Y23" s="49"/>
-      <c r="Z23" s="49"/>
-      <c r="AA23" s="50"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="67"/>
+      <c r="J23" s="67"/>
+      <c r="K23" s="67"/>
+      <c r="L23" s="67"/>
+      <c r="M23" s="67"/>
+      <c r="N23" s="67"/>
+      <c r="O23" s="67"/>
+      <c r="P23" s="67"/>
+      <c r="Q23" s="67"/>
+      <c r="R23" s="67"/>
+      <c r="S23" s="67"/>
+      <c r="T23" s="67"/>
+      <c r="U23" s="67"/>
+      <c r="V23" s="67"/>
+      <c r="W23" s="67"/>
+      <c r="X23" s="67"/>
+      <c r="Y23" s="67"/>
+      <c r="Z23" s="67"/>
+      <c r="AA23" s="68"/>
     </row>
     <row r="24" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
-      <c r="B24" s="51"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="52"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="52"/>
-      <c r="J24" s="52"/>
-      <c r="K24" s="52"/>
-      <c r="L24" s="52"/>
-      <c r="M24" s="52"/>
-      <c r="N24" s="52"/>
-      <c r="O24" s="52"/>
-      <c r="P24" s="52"/>
-      <c r="Q24" s="52"/>
-      <c r="R24" s="52"/>
-      <c r="S24" s="52"/>
-      <c r="T24" s="52"/>
-      <c r="U24" s="52"/>
-      <c r="V24" s="52"/>
-      <c r="W24" s="52"/>
-      <c r="X24" s="52"/>
-      <c r="Y24" s="52"/>
-      <c r="Z24" s="52"/>
-      <c r="AA24" s="53"/>
+      <c r="B24" s="78"/>
+      <c r="C24" s="79"/>
+      <c r="D24" s="79"/>
+      <c r="E24" s="79"/>
+      <c r="F24" s="79"/>
+      <c r="G24" s="79"/>
+      <c r="H24" s="79"/>
+      <c r="I24" s="79"/>
+      <c r="J24" s="79"/>
+      <c r="K24" s="79"/>
+      <c r="L24" s="79"/>
+      <c r="M24" s="79"/>
+      <c r="N24" s="79"/>
+      <c r="O24" s="79"/>
+      <c r="P24" s="79"/>
+      <c r="Q24" s="79"/>
+      <c r="R24" s="79"/>
+      <c r="S24" s="79"/>
+      <c r="T24" s="79"/>
+      <c r="U24" s="79"/>
+      <c r="V24" s="79"/>
+      <c r="W24" s="79"/>
+      <c r="X24" s="79"/>
+      <c r="Y24" s="79"/>
+      <c r="Z24" s="79"/>
+      <c r="AA24" s="80"/>
     </row>
     <row r="25" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
-      <c r="B25" s="54"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="55"/>
-      <c r="H25" s="55"/>
-      <c r="I25" s="55"/>
-      <c r="J25" s="55"/>
-      <c r="K25" s="55"/>
-      <c r="L25" s="55"/>
-      <c r="M25" s="55"/>
-      <c r="N25" s="55"/>
-      <c r="O25" s="55"/>
-      <c r="P25" s="55"/>
-      <c r="Q25" s="55"/>
-      <c r="R25" s="55"/>
-      <c r="S25" s="55"/>
-      <c r="T25" s="55"/>
-      <c r="U25" s="55"/>
-      <c r="V25" s="55"/>
-      <c r="W25" s="55"/>
-      <c r="X25" s="55"/>
-      <c r="Y25" s="55"/>
-      <c r="Z25" s="55"/>
-      <c r="AA25" s="56"/>
+      <c r="B25" s="81"/>
+      <c r="C25" s="82"/>
+      <c r="D25" s="82"/>
+      <c r="E25" s="82"/>
+      <c r="F25" s="82"/>
+      <c r="G25" s="82"/>
+      <c r="H25" s="82"/>
+      <c r="I25" s="82"/>
+      <c r="J25" s="82"/>
+      <c r="K25" s="82"/>
+      <c r="L25" s="82"/>
+      <c r="M25" s="82"/>
+      <c r="N25" s="82"/>
+      <c r="O25" s="82"/>
+      <c r="P25" s="82"/>
+      <c r="Q25" s="82"/>
+      <c r="R25" s="82"/>
+      <c r="S25" s="82"/>
+      <c r="T25" s="82"/>
+      <c r="U25" s="82"/>
+      <c r="V25" s="82"/>
+      <c r="W25" s="82"/>
+      <c r="X25" s="82"/>
+      <c r="Y25" s="82"/>
+      <c r="Z25" s="82"/>
+      <c r="AA25" s="83"/>
     </row>
     <row r="26" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
-      <c r="B26" s="54"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="55"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="55"/>
-      <c r="H26" s="55"/>
-      <c r="I26" s="55"/>
-      <c r="J26" s="55"/>
-      <c r="K26" s="55"/>
-      <c r="L26" s="55"/>
-      <c r="M26" s="55"/>
-      <c r="N26" s="55"/>
-      <c r="O26" s="55"/>
-      <c r="P26" s="55"/>
-      <c r="Q26" s="55"/>
-      <c r="R26" s="55"/>
-      <c r="S26" s="55"/>
-      <c r="T26" s="55"/>
-      <c r="U26" s="55"/>
-      <c r="V26" s="55"/>
-      <c r="W26" s="55"/>
-      <c r="X26" s="55"/>
-      <c r="Y26" s="55"/>
-      <c r="Z26" s="55"/>
-      <c r="AA26" s="56"/>
+      <c r="B26" s="81"/>
+      <c r="C26" s="82"/>
+      <c r="D26" s="82"/>
+      <c r="E26" s="82"/>
+      <c r="F26" s="82"/>
+      <c r="G26" s="82"/>
+      <c r="H26" s="82"/>
+      <c r="I26" s="82"/>
+      <c r="J26" s="82"/>
+      <c r="K26" s="82"/>
+      <c r="L26" s="82"/>
+      <c r="M26" s="82"/>
+      <c r="N26" s="82"/>
+      <c r="O26" s="82"/>
+      <c r="P26" s="82"/>
+      <c r="Q26" s="82"/>
+      <c r="R26" s="82"/>
+      <c r="S26" s="82"/>
+      <c r="T26" s="82"/>
+      <c r="U26" s="82"/>
+      <c r="V26" s="82"/>
+      <c r="W26" s="82"/>
+      <c r="X26" s="82"/>
+      <c r="Y26" s="82"/>
+      <c r="Z26" s="82"/>
+      <c r="AA26" s="83"/>
     </row>
     <row r="27" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
-      <c r="B27" s="54"/>
-      <c r="C27" s="55"/>
-      <c r="D27" s="55"/>
-      <c r="E27" s="55"/>
-      <c r="F27" s="55"/>
-      <c r="G27" s="55"/>
-      <c r="H27" s="55"/>
-      <c r="I27" s="55"/>
-      <c r="J27" s="55"/>
-      <c r="K27" s="55"/>
-      <c r="L27" s="55"/>
-      <c r="M27" s="55"/>
-      <c r="N27" s="55"/>
-      <c r="O27" s="55"/>
-      <c r="P27" s="55"/>
-      <c r="Q27" s="55"/>
-      <c r="R27" s="55"/>
-      <c r="S27" s="55"/>
-      <c r="T27" s="55"/>
-      <c r="U27" s="55"/>
-      <c r="V27" s="55"/>
-      <c r="W27" s="55"/>
-      <c r="X27" s="55"/>
-      <c r="Y27" s="55"/>
-      <c r="Z27" s="55"/>
-      <c r="AA27" s="56"/>
+      <c r="B27" s="81"/>
+      <c r="C27" s="82"/>
+      <c r="D27" s="82"/>
+      <c r="E27" s="82"/>
+      <c r="F27" s="82"/>
+      <c r="G27" s="82"/>
+      <c r="H27" s="82"/>
+      <c r="I27" s="82"/>
+      <c r="J27" s="82"/>
+      <c r="K27" s="82"/>
+      <c r="L27" s="82"/>
+      <c r="M27" s="82"/>
+      <c r="N27" s="82"/>
+      <c r="O27" s="82"/>
+      <c r="P27" s="82"/>
+      <c r="Q27" s="82"/>
+      <c r="R27" s="82"/>
+      <c r="S27" s="82"/>
+      <c r="T27" s="82"/>
+      <c r="U27" s="82"/>
+      <c r="V27" s="82"/>
+      <c r="W27" s="82"/>
+      <c r="X27" s="82"/>
+      <c r="Y27" s="82"/>
+      <c r="Z27" s="82"/>
+      <c r="AA27" s="83"/>
     </row>
     <row r="28" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="55"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="55"/>
-      <c r="J28" s="55"/>
-      <c r="K28" s="55"/>
-      <c r="L28" s="55"/>
-      <c r="M28" s="55"/>
-      <c r="N28" s="55"/>
-      <c r="O28" s="55"/>
-      <c r="P28" s="55"/>
-      <c r="Q28" s="55"/>
-      <c r="R28" s="55"/>
-      <c r="S28" s="55"/>
-      <c r="T28" s="55"/>
-      <c r="U28" s="55"/>
-      <c r="V28" s="55"/>
-      <c r="W28" s="55"/>
-      <c r="X28" s="55"/>
-      <c r="Y28" s="55"/>
-      <c r="Z28" s="55"/>
-      <c r="AA28" s="56"/>
+      <c r="B28" s="81"/>
+      <c r="C28" s="82"/>
+      <c r="D28" s="82"/>
+      <c r="E28" s="82"/>
+      <c r="F28" s="82"/>
+      <c r="G28" s="82"/>
+      <c r="H28" s="82"/>
+      <c r="I28" s="82"/>
+      <c r="J28" s="82"/>
+      <c r="K28" s="82"/>
+      <c r="L28" s="82"/>
+      <c r="M28" s="82"/>
+      <c r="N28" s="82"/>
+      <c r="O28" s="82"/>
+      <c r="P28" s="82"/>
+      <c r="Q28" s="82"/>
+      <c r="R28" s="82"/>
+      <c r="S28" s="82"/>
+      <c r="T28" s="82"/>
+      <c r="U28" s="82"/>
+      <c r="V28" s="82"/>
+      <c r="W28" s="82"/>
+      <c r="X28" s="82"/>
+      <c r="Y28" s="82"/>
+      <c r="Z28" s="82"/>
+      <c r="AA28" s="83"/>
     </row>
     <row r="29" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
-      <c r="B29" s="54"/>
-      <c r="C29" s="55"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="55"/>
-      <c r="F29" s="55"/>
-      <c r="G29" s="55"/>
-      <c r="H29" s="55"/>
-      <c r="I29" s="55"/>
-      <c r="J29" s="55"/>
-      <c r="K29" s="55"/>
-      <c r="L29" s="55"/>
-      <c r="M29" s="55"/>
-      <c r="N29" s="55"/>
-      <c r="O29" s="55"/>
-      <c r="P29" s="55"/>
-      <c r="Q29" s="55"/>
-      <c r="R29" s="55"/>
-      <c r="S29" s="55"/>
-      <c r="T29" s="55"/>
-      <c r="U29" s="55"/>
-      <c r="V29" s="55"/>
-      <c r="W29" s="55"/>
-      <c r="X29" s="55"/>
-      <c r="Y29" s="55"/>
-      <c r="Z29" s="55"/>
-      <c r="AA29" s="56"/>
+      <c r="B29" s="81"/>
+      <c r="C29" s="82"/>
+      <c r="D29" s="82"/>
+      <c r="E29" s="82"/>
+      <c r="F29" s="82"/>
+      <c r="G29" s="82"/>
+      <c r="H29" s="82"/>
+      <c r="I29" s="82"/>
+      <c r="J29" s="82"/>
+      <c r="K29" s="82"/>
+      <c r="L29" s="82"/>
+      <c r="M29" s="82"/>
+      <c r="N29" s="82"/>
+      <c r="O29" s="82"/>
+      <c r="P29" s="82"/>
+      <c r="Q29" s="82"/>
+      <c r="R29" s="82"/>
+      <c r="S29" s="82"/>
+      <c r="T29" s="82"/>
+      <c r="U29" s="82"/>
+      <c r="V29" s="82"/>
+      <c r="W29" s="82"/>
+      <c r="X29" s="82"/>
+      <c r="Y29" s="82"/>
+      <c r="Z29" s="82"/>
+      <c r="AA29" s="83"/>
     </row>
     <row r="30" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
-      <c r="B30" s="54"/>
-      <c r="C30" s="55"/>
-      <c r="D30" s="55"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="55"/>
-      <c r="G30" s="55"/>
-      <c r="H30" s="55"/>
-      <c r="I30" s="55"/>
-      <c r="J30" s="55"/>
-      <c r="K30" s="55"/>
-      <c r="L30" s="55"/>
-      <c r="M30" s="55"/>
-      <c r="N30" s="55"/>
-      <c r="O30" s="55"/>
-      <c r="P30" s="55"/>
-      <c r="Q30" s="55"/>
-      <c r="R30" s="55"/>
-      <c r="S30" s="55"/>
-      <c r="T30" s="55"/>
-      <c r="U30" s="55"/>
-      <c r="V30" s="55"/>
-      <c r="W30" s="55"/>
-      <c r="X30" s="55"/>
-      <c r="Y30" s="55"/>
-      <c r="Z30" s="55"/>
-      <c r="AA30" s="56"/>
+      <c r="B30" s="81"/>
+      <c r="C30" s="82"/>
+      <c r="D30" s="82"/>
+      <c r="E30" s="82"/>
+      <c r="F30" s="82"/>
+      <c r="G30" s="82"/>
+      <c r="H30" s="82"/>
+      <c r="I30" s="82"/>
+      <c r="J30" s="82"/>
+      <c r="K30" s="82"/>
+      <c r="L30" s="82"/>
+      <c r="M30" s="82"/>
+      <c r="N30" s="82"/>
+      <c r="O30" s="82"/>
+      <c r="P30" s="82"/>
+      <c r="Q30" s="82"/>
+      <c r="R30" s="82"/>
+      <c r="S30" s="82"/>
+      <c r="T30" s="82"/>
+      <c r="U30" s="82"/>
+      <c r="V30" s="82"/>
+      <c r="W30" s="82"/>
+      <c r="X30" s="82"/>
+      <c r="Y30" s="82"/>
+      <c r="Z30" s="82"/>
+      <c r="AA30" s="83"/>
     </row>
     <row r="31" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
-      <c r="B31" s="57"/>
-      <c r="C31" s="58"/>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="58"/>
-      <c r="K31" s="58"/>
-      <c r="L31" s="58"/>
-      <c r="M31" s="58"/>
-      <c r="N31" s="58"/>
-      <c r="O31" s="58"/>
-      <c r="P31" s="58"/>
-      <c r="Q31" s="58"/>
-      <c r="R31" s="58"/>
-      <c r="S31" s="58"/>
-      <c r="T31" s="58"/>
-      <c r="U31" s="58"/>
-      <c r="V31" s="58"/>
-      <c r="W31" s="58"/>
-      <c r="X31" s="58"/>
-      <c r="Y31" s="58"/>
-      <c r="Z31" s="58"/>
-      <c r="AA31" s="59"/>
+      <c r="B31" s="69"/>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="70"/>
+      <c r="K31" s="70"/>
+      <c r="L31" s="70"/>
+      <c r="M31" s="70"/>
+      <c r="N31" s="70"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="70"/>
+      <c r="Q31" s="70"/>
+      <c r="R31" s="70"/>
+      <c r="S31" s="70"/>
+      <c r="T31" s="70"/>
+      <c r="U31" s="70"/>
+      <c r="V31" s="70"/>
+      <c r="W31" s="70"/>
+      <c r="X31" s="70"/>
+      <c r="Y31" s="70"/>
+      <c r="Z31" s="70"/>
+      <c r="AA31" s="71"/>
     </row>
     <row r="32" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
-      <c r="B32" s="60" t="s">
+      <c r="B32" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="61"/>
-      <c r="D32" s="61"/>
-      <c r="E32" s="61"/>
-      <c r="F32" s="61"/>
-      <c r="G32" s="61"/>
-      <c r="H32" s="61"/>
-      <c r="I32" s="61"/>
-      <c r="J32" s="61"/>
-      <c r="K32" s="61"/>
-      <c r="L32" s="61"/>
-      <c r="M32" s="61"/>
-      <c r="N32" s="61"/>
-      <c r="O32" s="61"/>
-      <c r="P32" s="61"/>
-      <c r="Q32" s="61"/>
-      <c r="R32" s="61"/>
-      <c r="S32" s="61"/>
-      <c r="T32" s="61"/>
-      <c r="U32" s="61"/>
-      <c r="V32" s="61"/>
-      <c r="W32" s="61"/>
-      <c r="X32" s="61"/>
-      <c r="Y32" s="61"/>
-      <c r="Z32" s="61"/>
-      <c r="AA32" s="62"/>
+      <c r="C32" s="73"/>
+      <c r="D32" s="73"/>
+      <c r="E32" s="73"/>
+      <c r="F32" s="73"/>
+      <c r="G32" s="73"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73"/>
+      <c r="J32" s="73"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="73"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="73"/>
+      <c r="O32" s="73"/>
+      <c r="P32" s="73"/>
+      <c r="Q32" s="73"/>
+      <c r="R32" s="73"/>
+      <c r="S32" s="73"/>
+      <c r="T32" s="73"/>
+      <c r="U32" s="73"/>
+      <c r="V32" s="73"/>
+      <c r="W32" s="73"/>
+      <c r="X32" s="73"/>
+      <c r="Y32" s="73"/>
+      <c r="Z32" s="73"/>
+      <c r="AA32" s="74"/>
     </row>
     <row r="33" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
-      <c r="B33" s="51"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="43"/>
-      <c r="H33" s="43"/>
-      <c r="I33" s="43"/>
-      <c r="J33" s="43"/>
-      <c r="K33" s="43"/>
-      <c r="L33" s="43"/>
-      <c r="M33" s="43"/>
-      <c r="N33" s="43"/>
-      <c r="O33" s="43"/>
-      <c r="P33" s="43"/>
-      <c r="Q33" s="43"/>
-      <c r="R33" s="43"/>
-      <c r="S33" s="43"/>
-      <c r="T33" s="43"/>
-      <c r="U33" s="43"/>
-      <c r="V33" s="43"/>
-      <c r="W33" s="43"/>
-      <c r="X33" s="43"/>
-      <c r="Y33" s="43"/>
-      <c r="Z33" s="43"/>
-      <c r="AA33" s="63"/>
+      <c r="B33" s="78"/>
+      <c r="C33" s="79"/>
+      <c r="D33" s="79"/>
+      <c r="E33" s="79"/>
+      <c r="F33" s="79"/>
+      <c r="G33" s="79"/>
+      <c r="H33" s="79"/>
+      <c r="I33" s="79"/>
+      <c r="J33" s="79"/>
+      <c r="K33" s="79"/>
+      <c r="L33" s="79"/>
+      <c r="M33" s="79"/>
+      <c r="N33" s="79"/>
+      <c r="O33" s="79"/>
+      <c r="P33" s="79"/>
+      <c r="Q33" s="79"/>
+      <c r="R33" s="79"/>
+      <c r="S33" s="79"/>
+      <c r="T33" s="79"/>
+      <c r="U33" s="79"/>
+      <c r="V33" s="79"/>
+      <c r="W33" s="79"/>
+      <c r="X33" s="79"/>
+      <c r="Y33" s="79"/>
+      <c r="Z33" s="79"/>
+      <c r="AA33" s="80"/>
     </row>
     <row r="34" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
-      <c r="B34" s="64"/>
-      <c r="C34" s="65"/>
-      <c r="D34" s="65"/>
-      <c r="E34" s="65"/>
-      <c r="F34" s="65"/>
-      <c r="G34" s="65"/>
-      <c r="H34" s="65"/>
-      <c r="I34" s="65"/>
-      <c r="J34" s="65"/>
-      <c r="K34" s="65"/>
-      <c r="L34" s="65"/>
-      <c r="M34" s="65"/>
-      <c r="N34" s="65"/>
-      <c r="O34" s="65"/>
-      <c r="P34" s="65"/>
-      <c r="Q34" s="65"/>
-      <c r="R34" s="65"/>
-      <c r="S34" s="65"/>
-      <c r="T34" s="65"/>
-      <c r="U34" s="65"/>
-      <c r="V34" s="65"/>
-      <c r="W34" s="65"/>
-      <c r="X34" s="65"/>
-      <c r="Y34" s="65"/>
-      <c r="Z34" s="65"/>
-      <c r="AA34" s="66"/>
+      <c r="B34" s="81"/>
+      <c r="C34" s="82"/>
+      <c r="D34" s="82"/>
+      <c r="E34" s="82"/>
+      <c r="F34" s="82"/>
+      <c r="G34" s="82"/>
+      <c r="H34" s="82"/>
+      <c r="I34" s="82"/>
+      <c r="J34" s="82"/>
+      <c r="K34" s="82"/>
+      <c r="L34" s="82"/>
+      <c r="M34" s="82"/>
+      <c r="N34" s="82"/>
+      <c r="O34" s="82"/>
+      <c r="P34" s="82"/>
+      <c r="Q34" s="82"/>
+      <c r="R34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="82"/>
+      <c r="V34" s="82"/>
+      <c r="W34" s="82"/>
+      <c r="X34" s="82"/>
+      <c r="Y34" s="82"/>
+      <c r="Z34" s="82"/>
+      <c r="AA34" s="83"/>
     </row>
     <row r="35" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
-      <c r="B35" s="64"/>
-      <c r="C35" s="65"/>
-      <c r="D35" s="65"/>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="65"/>
-      <c r="H35" s="65"/>
-      <c r="I35" s="65"/>
-      <c r="J35" s="65"/>
-      <c r="K35" s="65"/>
-      <c r="L35" s="65"/>
-      <c r="M35" s="65"/>
-      <c r="N35" s="65"/>
-      <c r="O35" s="65"/>
-      <c r="P35" s="65"/>
-      <c r="Q35" s="65"/>
-      <c r="R35" s="65"/>
-      <c r="S35" s="65"/>
-      <c r="T35" s="65"/>
-      <c r="U35" s="65"/>
-      <c r="V35" s="65"/>
-      <c r="W35" s="65"/>
-      <c r="X35" s="65"/>
-      <c r="Y35" s="65"/>
-      <c r="Z35" s="65"/>
-      <c r="AA35" s="66"/>
+      <c r="B35" s="81"/>
+      <c r="C35" s="82"/>
+      <c r="D35" s="82"/>
+      <c r="E35" s="82"/>
+      <c r="F35" s="82"/>
+      <c r="G35" s="82"/>
+      <c r="H35" s="82"/>
+      <c r="I35" s="82"/>
+      <c r="J35" s="82"/>
+      <c r="K35" s="82"/>
+      <c r="L35" s="82"/>
+      <c r="M35" s="82"/>
+      <c r="N35" s="82"/>
+      <c r="O35" s="82"/>
+      <c r="P35" s="82"/>
+      <c r="Q35" s="82"/>
+      <c r="R35" s="82"/>
+      <c r="S35" s="82"/>
+      <c r="T35" s="82"/>
+      <c r="U35" s="82"/>
+      <c r="V35" s="82"/>
+      <c r="W35" s="82"/>
+      <c r="X35" s="82"/>
+      <c r="Y35" s="82"/>
+      <c r="Z35" s="82"/>
+      <c r="AA35" s="83"/>
     </row>
     <row r="36" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
-      <c r="B36" s="64"/>
-      <c r="C36" s="65"/>
-      <c r="D36" s="65"/>
-      <c r="E36" s="65"/>
-      <c r="F36" s="65"/>
-      <c r="G36" s="65"/>
-      <c r="H36" s="65"/>
-      <c r="I36" s="65"/>
-      <c r="J36" s="65"/>
-      <c r="K36" s="65"/>
-      <c r="L36" s="65"/>
-      <c r="M36" s="65"/>
-      <c r="N36" s="65"/>
-      <c r="O36" s="65"/>
-      <c r="P36" s="65"/>
-      <c r="Q36" s="65"/>
-      <c r="R36" s="65"/>
-      <c r="S36" s="65"/>
-      <c r="T36" s="65"/>
-      <c r="U36" s="65"/>
-      <c r="V36" s="65"/>
-      <c r="W36" s="65"/>
-      <c r="X36" s="65"/>
-      <c r="Y36" s="65"/>
-      <c r="Z36" s="65"/>
-      <c r="AA36" s="66"/>
+      <c r="B36" s="81"/>
+      <c r="C36" s="82"/>
+      <c r="D36" s="82"/>
+      <c r="E36" s="82"/>
+      <c r="F36" s="82"/>
+      <c r="G36" s="82"/>
+      <c r="H36" s="82"/>
+      <c r="I36" s="82"/>
+      <c r="J36" s="82"/>
+      <c r="K36" s="82"/>
+      <c r="L36" s="82"/>
+      <c r="M36" s="82"/>
+      <c r="N36" s="82"/>
+      <c r="O36" s="82"/>
+      <c r="P36" s="82"/>
+      <c r="Q36" s="82"/>
+      <c r="R36" s="82"/>
+      <c r="S36" s="82"/>
+      <c r="T36" s="82"/>
+      <c r="U36" s="82"/>
+      <c r="V36" s="82"/>
+      <c r="W36" s="82"/>
+      <c r="X36" s="82"/>
+      <c r="Y36" s="82"/>
+      <c r="Z36" s="82"/>
+      <c r="AA36" s="83"/>
     </row>
     <row r="37" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
-      <c r="B37" s="64"/>
-      <c r="C37" s="65"/>
-      <c r="D37" s="65"/>
-      <c r="E37" s="65"/>
-      <c r="F37" s="65"/>
-      <c r="G37" s="65"/>
-      <c r="H37" s="65"/>
-      <c r="I37" s="65"/>
-      <c r="J37" s="65"/>
-      <c r="K37" s="65"/>
-      <c r="L37" s="65"/>
-      <c r="M37" s="65"/>
-      <c r="N37" s="65"/>
-      <c r="O37" s="65"/>
-      <c r="P37" s="65"/>
-      <c r="Q37" s="65"/>
-      <c r="R37" s="65"/>
-      <c r="S37" s="65"/>
-      <c r="T37" s="65"/>
-      <c r="U37" s="65"/>
-      <c r="V37" s="65"/>
-      <c r="W37" s="65"/>
-      <c r="X37" s="65"/>
-      <c r="Y37" s="65"/>
-      <c r="Z37" s="65"/>
-      <c r="AA37" s="66"/>
+      <c r="B37" s="81"/>
+      <c r="C37" s="82"/>
+      <c r="D37" s="82"/>
+      <c r="E37" s="82"/>
+      <c r="F37" s="82"/>
+      <c r="G37" s="82"/>
+      <c r="H37" s="82"/>
+      <c r="I37" s="82"/>
+      <c r="J37" s="82"/>
+      <c r="K37" s="82"/>
+      <c r="L37" s="82"/>
+      <c r="M37" s="82"/>
+      <c r="N37" s="82"/>
+      <c r="O37" s="82"/>
+      <c r="P37" s="82"/>
+      <c r="Q37" s="82"/>
+      <c r="R37" s="82"/>
+      <c r="S37" s="82"/>
+      <c r="T37" s="82"/>
+      <c r="U37" s="82"/>
+      <c r="V37" s="82"/>
+      <c r="W37" s="82"/>
+      <c r="X37" s="82"/>
+      <c r="Y37" s="82"/>
+      <c r="Z37" s="82"/>
+      <c r="AA37" s="83"/>
     </row>
     <row r="38" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
-      <c r="B38" s="64"/>
-      <c r="C38" s="65"/>
-      <c r="D38" s="65"/>
-      <c r="E38" s="65"/>
-      <c r="F38" s="65"/>
-      <c r="G38" s="65"/>
-      <c r="H38" s="65"/>
-      <c r="I38" s="65"/>
-      <c r="J38" s="65"/>
-      <c r="K38" s="65"/>
-      <c r="L38" s="65"/>
-      <c r="M38" s="65"/>
-      <c r="N38" s="65"/>
-      <c r="O38" s="65"/>
-      <c r="P38" s="65"/>
-      <c r="Q38" s="65"/>
-      <c r="R38" s="65"/>
-      <c r="S38" s="65"/>
-      <c r="T38" s="65"/>
-      <c r="U38" s="65"/>
-      <c r="V38" s="65"/>
-      <c r="W38" s="65"/>
-      <c r="X38" s="65"/>
-      <c r="Y38" s="65"/>
-      <c r="Z38" s="65"/>
-      <c r="AA38" s="66"/>
+      <c r="B38" s="81"/>
+      <c r="C38" s="82"/>
+      <c r="D38" s="82"/>
+      <c r="E38" s="82"/>
+      <c r="F38" s="82"/>
+      <c r="G38" s="82"/>
+      <c r="H38" s="82"/>
+      <c r="I38" s="82"/>
+      <c r="J38" s="82"/>
+      <c r="K38" s="82"/>
+      <c r="L38" s="82"/>
+      <c r="M38" s="82"/>
+      <c r="N38" s="82"/>
+      <c r="O38" s="82"/>
+      <c r="P38" s="82"/>
+      <c r="Q38" s="82"/>
+      <c r="R38" s="82"/>
+      <c r="S38" s="82"/>
+      <c r="T38" s="82"/>
+      <c r="U38" s="82"/>
+      <c r="V38" s="82"/>
+      <c r="W38" s="82"/>
+      <c r="X38" s="82"/>
+      <c r="Y38" s="82"/>
+      <c r="Z38" s="82"/>
+      <c r="AA38" s="83"/>
     </row>
     <row r="39" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
-      <c r="B39" s="67"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="46"/>
-      <c r="E39" s="46"/>
-      <c r="F39" s="46"/>
-      <c r="G39" s="46"/>
-      <c r="H39" s="46"/>
-      <c r="I39" s="46"/>
-      <c r="J39" s="46"/>
-      <c r="K39" s="46"/>
-      <c r="L39" s="46"/>
-      <c r="M39" s="46"/>
-      <c r="N39" s="46"/>
-      <c r="O39" s="46"/>
-      <c r="P39" s="46"/>
-      <c r="Q39" s="46"/>
-      <c r="R39" s="46"/>
-      <c r="S39" s="46"/>
-      <c r="T39" s="46"/>
-      <c r="U39" s="46"/>
-      <c r="V39" s="46"/>
-      <c r="W39" s="46"/>
-      <c r="X39" s="46"/>
-      <c r="Y39" s="46"/>
-      <c r="Z39" s="46"/>
-      <c r="AA39" s="68"/>
+      <c r="B39" s="84"/>
+      <c r="C39" s="85"/>
+      <c r="D39" s="85"/>
+      <c r="E39" s="85"/>
+      <c r="F39" s="85"/>
+      <c r="G39" s="85"/>
+      <c r="H39" s="85"/>
+      <c r="I39" s="85"/>
+      <c r="J39" s="85"/>
+      <c r="K39" s="85"/>
+      <c r="L39" s="85"/>
+      <c r="M39" s="85"/>
+      <c r="N39" s="85"/>
+      <c r="O39" s="85"/>
+      <c r="P39" s="85"/>
+      <c r="Q39" s="85"/>
+      <c r="R39" s="85"/>
+      <c r="S39" s="85"/>
+      <c r="T39" s="85"/>
+      <c r="U39" s="85"/>
+      <c r="V39" s="85"/>
+      <c r="W39" s="85"/>
+      <c r="X39" s="85"/>
+      <c r="Y39" s="85"/>
+      <c r="Z39" s="85"/>
+      <c r="AA39" s="86"/>
     </row>
     <row r="40" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
-      <c r="B40" s="60" t="s">
+      <c r="B40" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="61"/>
-      <c r="D40" s="61"/>
-      <c r="E40" s="61"/>
-      <c r="F40" s="61"/>
-      <c r="G40" s="61"/>
-      <c r="H40" s="61"/>
-      <c r="I40" s="61"/>
-      <c r="J40" s="61"/>
-      <c r="K40" s="61"/>
-      <c r="L40" s="61"/>
-      <c r="M40" s="61"/>
-      <c r="N40" s="61"/>
-      <c r="O40" s="61"/>
-      <c r="P40" s="61"/>
-      <c r="Q40" s="61"/>
-      <c r="R40" s="61"/>
-      <c r="S40" s="61"/>
-      <c r="T40" s="61"/>
-      <c r="U40" s="61"/>
-      <c r="V40" s="61"/>
-      <c r="W40" s="61"/>
-      <c r="X40" s="61"/>
-      <c r="Y40" s="61"/>
-      <c r="Z40" s="61"/>
-      <c r="AA40" s="62"/>
+      <c r="C40" s="73"/>
+      <c r="D40" s="73"/>
+      <c r="E40" s="73"/>
+      <c r="F40" s="73"/>
+      <c r="G40" s="73"/>
+      <c r="H40" s="73"/>
+      <c r="I40" s="73"/>
+      <c r="J40" s="73"/>
+      <c r="K40" s="73"/>
+      <c r="L40" s="73"/>
+      <c r="M40" s="73"/>
+      <c r="N40" s="73"/>
+      <c r="O40" s="73"/>
+      <c r="P40" s="73"/>
+      <c r="Q40" s="73"/>
+      <c r="R40" s="73"/>
+      <c r="S40" s="73"/>
+      <c r="T40" s="73"/>
+      <c r="U40" s="73"/>
+      <c r="V40" s="73"/>
+      <c r="W40" s="73"/>
+      <c r="X40" s="73"/>
+      <c r="Y40" s="73"/>
+      <c r="Z40" s="73"/>
+      <c r="AA40" s="74"/>
     </row>
     <row r="41" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
-      <c r="B41" s="51"/>
-      <c r="C41" s="43"/>
-      <c r="D41" s="43"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="43"/>
-      <c r="H41" s="43"/>
-      <c r="I41" s="43"/>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
-      <c r="L41" s="43"/>
-      <c r="M41" s="43"/>
-      <c r="N41" s="43"/>
-      <c r="O41" s="43"/>
-      <c r="P41" s="43"/>
-      <c r="Q41" s="43"/>
-      <c r="R41" s="43"/>
-      <c r="S41" s="43"/>
-      <c r="T41" s="43"/>
-      <c r="U41" s="43"/>
-      <c r="V41" s="43"/>
-      <c r="W41" s="43"/>
-      <c r="X41" s="43"/>
-      <c r="Y41" s="43"/>
-      <c r="Z41" s="43"/>
-      <c r="AA41" s="63"/>
+      <c r="B41" s="78"/>
+      <c r="C41" s="79"/>
+      <c r="D41" s="79"/>
+      <c r="E41" s="79"/>
+      <c r="F41" s="79"/>
+      <c r="G41" s="79"/>
+      <c r="H41" s="79"/>
+      <c r="I41" s="79"/>
+      <c r="J41" s="79"/>
+      <c r="K41" s="79"/>
+      <c r="L41" s="79"/>
+      <c r="M41" s="79"/>
+      <c r="N41" s="79"/>
+      <c r="O41" s="79"/>
+      <c r="P41" s="79"/>
+      <c r="Q41" s="79"/>
+      <c r="R41" s="79"/>
+      <c r="S41" s="79"/>
+      <c r="T41" s="79"/>
+      <c r="U41" s="79"/>
+      <c r="V41" s="79"/>
+      <c r="W41" s="79"/>
+      <c r="X41" s="79"/>
+      <c r="Y41" s="79"/>
+      <c r="Z41" s="79"/>
+      <c r="AA41" s="80"/>
     </row>
     <row r="42" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
-      <c r="B42" s="64"/>
-      <c r="C42" s="65"/>
-      <c r="D42" s="65"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="65"/>
-      <c r="H42" s="65"/>
-      <c r="I42" s="65"/>
-      <c r="J42" s="65"/>
-      <c r="K42" s="65"/>
-      <c r="L42" s="65"/>
-      <c r="M42" s="65"/>
-      <c r="N42" s="65"/>
-      <c r="O42" s="65"/>
-      <c r="P42" s="65"/>
-      <c r="Q42" s="65"/>
-      <c r="R42" s="65"/>
-      <c r="S42" s="65"/>
-      <c r="T42" s="65"/>
-      <c r="U42" s="65"/>
-      <c r="V42" s="65"/>
-      <c r="W42" s="65"/>
-      <c r="X42" s="65"/>
-      <c r="Y42" s="65"/>
-      <c r="Z42" s="65"/>
-      <c r="AA42" s="66"/>
+      <c r="B42" s="81"/>
+      <c r="C42" s="82"/>
+      <c r="D42" s="82"/>
+      <c r="E42" s="82"/>
+      <c r="F42" s="82"/>
+      <c r="G42" s="82"/>
+      <c r="H42" s="82"/>
+      <c r="I42" s="82"/>
+      <c r="J42" s="82"/>
+      <c r="K42" s="82"/>
+      <c r="L42" s="82"/>
+      <c r="M42" s="82"/>
+      <c r="N42" s="82"/>
+      <c r="O42" s="82"/>
+      <c r="P42" s="82"/>
+      <c r="Q42" s="82"/>
+      <c r="R42" s="82"/>
+      <c r="S42" s="82"/>
+      <c r="T42" s="82"/>
+      <c r="U42" s="82"/>
+      <c r="V42" s="82"/>
+      <c r="W42" s="82"/>
+      <c r="X42" s="82"/>
+      <c r="Y42" s="82"/>
+      <c r="Z42" s="82"/>
+      <c r="AA42" s="83"/>
     </row>
     <row r="43" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
-      <c r="B43" s="64"/>
-      <c r="C43" s="65"/>
-      <c r="D43" s="65"/>
-      <c r="E43" s="65"/>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="65"/>
-      <c r="K43" s="65"/>
-      <c r="L43" s="65"/>
-      <c r="M43" s="65"/>
-      <c r="N43" s="65"/>
-      <c r="O43" s="65"/>
-      <c r="P43" s="65"/>
-      <c r="Q43" s="65"/>
-      <c r="R43" s="65"/>
-      <c r="S43" s="65"/>
-      <c r="T43" s="65"/>
-      <c r="U43" s="65"/>
-      <c r="V43" s="65"/>
-      <c r="W43" s="65"/>
-      <c r="X43" s="65"/>
-      <c r="Y43" s="65"/>
-      <c r="Z43" s="65"/>
-      <c r="AA43" s="66"/>
+      <c r="B43" s="81"/>
+      <c r="C43" s="82"/>
+      <c r="D43" s="82"/>
+      <c r="E43" s="82"/>
+      <c r="F43" s="82"/>
+      <c r="G43" s="82"/>
+      <c r="H43" s="82"/>
+      <c r="I43" s="82"/>
+      <c r="J43" s="82"/>
+      <c r="K43" s="82"/>
+      <c r="L43" s="82"/>
+      <c r="M43" s="82"/>
+      <c r="N43" s="82"/>
+      <c r="O43" s="82"/>
+      <c r="P43" s="82"/>
+      <c r="Q43" s="82"/>
+      <c r="R43" s="82"/>
+      <c r="S43" s="82"/>
+      <c r="T43" s="82"/>
+      <c r="U43" s="82"/>
+      <c r="V43" s="82"/>
+      <c r="W43" s="82"/>
+      <c r="X43" s="82"/>
+      <c r="Y43" s="82"/>
+      <c r="Z43" s="82"/>
+      <c r="AA43" s="83"/>
     </row>
     <row r="44" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
-      <c r="B44" s="64"/>
-      <c r="C44" s="65"/>
-      <c r="D44" s="65"/>
-      <c r="E44" s="65"/>
-      <c r="F44" s="65"/>
-      <c r="G44" s="65"/>
-      <c r="H44" s="65"/>
-      <c r="I44" s="65"/>
-      <c r="J44" s="65"/>
-      <c r="K44" s="65"/>
-      <c r="L44" s="65"/>
-      <c r="M44" s="65"/>
-      <c r="N44" s="65"/>
-      <c r="O44" s="65"/>
-      <c r="P44" s="65"/>
-      <c r="Q44" s="65"/>
-      <c r="R44" s="65"/>
-      <c r="S44" s="65"/>
-      <c r="T44" s="65"/>
-      <c r="U44" s="65"/>
-      <c r="V44" s="65"/>
-      <c r="W44" s="65"/>
-      <c r="X44" s="65"/>
-      <c r="Y44" s="65"/>
-      <c r="Z44" s="65"/>
-      <c r="AA44" s="66"/>
+      <c r="B44" s="81"/>
+      <c r="C44" s="82"/>
+      <c r="D44" s="82"/>
+      <c r="E44" s="82"/>
+      <c r="F44" s="82"/>
+      <c r="G44" s="82"/>
+      <c r="H44" s="82"/>
+      <c r="I44" s="82"/>
+      <c r="J44" s="82"/>
+      <c r="K44" s="82"/>
+      <c r="L44" s="82"/>
+      <c r="M44" s="82"/>
+      <c r="N44" s="82"/>
+      <c r="O44" s="82"/>
+      <c r="P44" s="82"/>
+      <c r="Q44" s="82"/>
+      <c r="R44" s="82"/>
+      <c r="S44" s="82"/>
+      <c r="T44" s="82"/>
+      <c r="U44" s="82"/>
+      <c r="V44" s="82"/>
+      <c r="W44" s="82"/>
+      <c r="X44" s="82"/>
+      <c r="Y44" s="82"/>
+      <c r="Z44" s="82"/>
+      <c r="AA44" s="83"/>
     </row>
     <row r="45" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
-      <c r="B45" s="64"/>
-      <c r="C45" s="65"/>
-      <c r="D45" s="65"/>
-      <c r="E45" s="65"/>
-      <c r="F45" s="65"/>
-      <c r="G45" s="65"/>
-      <c r="H45" s="65"/>
-      <c r="I45" s="65"/>
-      <c r="J45" s="65"/>
-      <c r="K45" s="65"/>
-      <c r="L45" s="65"/>
-      <c r="M45" s="65"/>
-      <c r="N45" s="65"/>
-      <c r="O45" s="65"/>
-      <c r="P45" s="65"/>
-      <c r="Q45" s="65"/>
-      <c r="R45" s="65"/>
-      <c r="S45" s="65"/>
-      <c r="T45" s="65"/>
-      <c r="U45" s="65"/>
-      <c r="V45" s="65"/>
-      <c r="W45" s="65"/>
-      <c r="X45" s="65"/>
-      <c r="Y45" s="65"/>
-      <c r="Z45" s="65"/>
-      <c r="AA45" s="66"/>
+      <c r="B45" s="81"/>
+      <c r="C45" s="82"/>
+      <c r="D45" s="82"/>
+      <c r="E45" s="82"/>
+      <c r="F45" s="82"/>
+      <c r="G45" s="82"/>
+      <c r="H45" s="82"/>
+      <c r="I45" s="82"/>
+      <c r="J45" s="82"/>
+      <c r="K45" s="82"/>
+      <c r="L45" s="82"/>
+      <c r="M45" s="82"/>
+      <c r="N45" s="82"/>
+      <c r="O45" s="82"/>
+      <c r="P45" s="82"/>
+      <c r="Q45" s="82"/>
+      <c r="R45" s="82"/>
+      <c r="S45" s="82"/>
+      <c r="T45" s="82"/>
+      <c r="U45" s="82"/>
+      <c r="V45" s="82"/>
+      <c r="W45" s="82"/>
+      <c r="X45" s="82"/>
+      <c r="Y45" s="82"/>
+      <c r="Z45" s="82"/>
+      <c r="AA45" s="83"/>
     </row>
     <row r="46" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
-      <c r="B46" s="64"/>
-      <c r="C46" s="65"/>
-      <c r="D46" s="65"/>
-      <c r="E46" s="65"/>
-      <c r="F46" s="65"/>
-      <c r="G46" s="65"/>
-      <c r="H46" s="65"/>
-      <c r="I46" s="65"/>
-      <c r="J46" s="65"/>
-      <c r="K46" s="65"/>
-      <c r="L46" s="65"/>
-      <c r="M46" s="65"/>
-      <c r="N46" s="65"/>
-      <c r="O46" s="65"/>
-      <c r="P46" s="65"/>
-      <c r="Q46" s="65"/>
-      <c r="R46" s="65"/>
-      <c r="S46" s="65"/>
-      <c r="T46" s="65"/>
-      <c r="U46" s="65"/>
-      <c r="V46" s="65"/>
-      <c r="W46" s="65"/>
-      <c r="X46" s="65"/>
-      <c r="Y46" s="65"/>
-      <c r="Z46" s="65"/>
-      <c r="AA46" s="66"/>
+      <c r="B46" s="81"/>
+      <c r="C46" s="82"/>
+      <c r="D46" s="82"/>
+      <c r="E46" s="82"/>
+      <c r="F46" s="82"/>
+      <c r="G46" s="82"/>
+      <c r="H46" s="82"/>
+      <c r="I46" s="82"/>
+      <c r="J46" s="82"/>
+      <c r="K46" s="82"/>
+      <c r="L46" s="82"/>
+      <c r="M46" s="82"/>
+      <c r="N46" s="82"/>
+      <c r="O46" s="82"/>
+      <c r="P46" s="82"/>
+      <c r="Q46" s="82"/>
+      <c r="R46" s="82"/>
+      <c r="S46" s="82"/>
+      <c r="T46" s="82"/>
+      <c r="U46" s="82"/>
+      <c r="V46" s="82"/>
+      <c r="W46" s="82"/>
+      <c r="X46" s="82"/>
+      <c r="Y46" s="82"/>
+      <c r="Z46" s="82"/>
+      <c r="AA46" s="83"/>
     </row>
     <row r="47" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
-      <c r="B47" s="69"/>
-      <c r="C47" s="70"/>
-      <c r="D47" s="70"/>
-      <c r="E47" s="70"/>
-      <c r="F47" s="70"/>
-      <c r="G47" s="70"/>
-      <c r="H47" s="70"/>
-      <c r="I47" s="70"/>
-      <c r="J47" s="70"/>
-      <c r="K47" s="70"/>
-      <c r="L47" s="70"/>
-      <c r="M47" s="70"/>
-      <c r="N47" s="70"/>
-      <c r="O47" s="70"/>
-      <c r="P47" s="70"/>
-      <c r="Q47" s="70"/>
-      <c r="R47" s="70"/>
-      <c r="S47" s="70"/>
-      <c r="T47" s="70"/>
-      <c r="U47" s="70"/>
-      <c r="V47" s="70"/>
-      <c r="W47" s="70"/>
-      <c r="X47" s="70"/>
-      <c r="Y47" s="70"/>
-      <c r="Z47" s="70"/>
-      <c r="AA47" s="71"/>
+      <c r="B47" s="87"/>
+      <c r="C47" s="88"/>
+      <c r="D47" s="88"/>
+      <c r="E47" s="88"/>
+      <c r="F47" s="88"/>
+      <c r="G47" s="88"/>
+      <c r="H47" s="88"/>
+      <c r="I47" s="88"/>
+      <c r="J47" s="88"/>
+      <c r="K47" s="88"/>
+      <c r="L47" s="88"/>
+      <c r="M47" s="88"/>
+      <c r="N47" s="88"/>
+      <c r="O47" s="88"/>
+      <c r="P47" s="88"/>
+      <c r="Q47" s="88"/>
+      <c r="R47" s="88"/>
+      <c r="S47" s="88"/>
+      <c r="T47" s="88"/>
+      <c r="U47" s="88"/>
+      <c r="V47" s="88"/>
+      <c r="W47" s="88"/>
+      <c r="X47" s="88"/>
+      <c r="Y47" s="88"/>
+      <c r="Z47" s="88"/>
+      <c r="AA47" s="89"/>
     </row>
     <row r="48" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
-      <c r="B48" s="72" t="s">
+      <c r="B48" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="73"/>
-      <c r="D48" s="73"/>
-      <c r="E48" s="73"/>
-      <c r="F48" s="73"/>
-      <c r="G48" s="73"/>
-      <c r="H48" s="73"/>
-      <c r="I48" s="73"/>
-      <c r="J48" s="73"/>
-      <c r="K48" s="73"/>
-      <c r="L48" s="73"/>
-      <c r="M48" s="73"/>
-      <c r="N48" s="73"/>
-      <c r="O48" s="73"/>
-      <c r="P48" s="73"/>
-      <c r="Q48" s="73"/>
-      <c r="R48" s="73"/>
-      <c r="S48" s="73"/>
-      <c r="T48" s="73"/>
-      <c r="U48" s="73"/>
-      <c r="V48" s="73"/>
-      <c r="W48" s="73"/>
-      <c r="X48" s="73"/>
-      <c r="Y48" s="73"/>
-      <c r="Z48" s="73"/>
-      <c r="AA48" s="74"/>
+      <c r="C48" s="53"/>
+      <c r="D48" s="53"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="53"/>
+      <c r="G48" s="53"/>
+      <c r="H48" s="53"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="53"/>
+      <c r="L48" s="53"/>
+      <c r="M48" s="53"/>
+      <c r="N48" s="53"/>
+      <c r="O48" s="53"/>
+      <c r="P48" s="53"/>
+      <c r="Q48" s="53"/>
+      <c r="R48" s="53"/>
+      <c r="S48" s="53"/>
+      <c r="T48" s="53"/>
+      <c r="U48" s="53"/>
+      <c r="V48" s="53"/>
+      <c r="W48" s="53"/>
+      <c r="X48" s="53"/>
+      <c r="Y48" s="53"/>
+      <c r="Z48" s="53"/>
+      <c r="AA48" s="54"/>
     </row>
     <row r="49" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="30"/>
-      <c r="B49" s="51"/>
-      <c r="C49" s="43"/>
-      <c r="D49" s="43"/>
-      <c r="E49" s="43"/>
-      <c r="F49" s="43"/>
-      <c r="G49" s="43"/>
-      <c r="H49" s="43"/>
-      <c r="I49" s="43"/>
-      <c r="J49" s="43"/>
-      <c r="K49" s="43"/>
-      <c r="L49" s="43"/>
-      <c r="M49" s="43"/>
-      <c r="N49" s="43"/>
-      <c r="O49" s="43"/>
-      <c r="P49" s="43"/>
-      <c r="Q49" s="43"/>
-      <c r="R49" s="43"/>
-      <c r="S49" s="43"/>
-      <c r="T49" s="43"/>
-      <c r="U49" s="43"/>
-      <c r="V49" s="43"/>
-      <c r="W49" s="43"/>
-      <c r="X49" s="43"/>
-      <c r="Y49" s="43"/>
-      <c r="Z49" s="43"/>
-      <c r="AA49" s="63"/>
+      <c r="B49" s="78"/>
+      <c r="C49" s="79"/>
+      <c r="D49" s="79"/>
+      <c r="E49" s="79"/>
+      <c r="F49" s="79"/>
+      <c r="G49" s="79"/>
+      <c r="H49" s="79"/>
+      <c r="I49" s="79"/>
+      <c r="J49" s="79"/>
+      <c r="K49" s="79"/>
+      <c r="L49" s="79"/>
+      <c r="M49" s="79"/>
+      <c r="N49" s="79"/>
+      <c r="O49" s="79"/>
+      <c r="P49" s="79"/>
+      <c r="Q49" s="79"/>
+      <c r="R49" s="79"/>
+      <c r="S49" s="79"/>
+      <c r="T49" s="79"/>
+      <c r="U49" s="79"/>
+      <c r="V49" s="79"/>
+      <c r="W49" s="79"/>
+      <c r="X49" s="79"/>
+      <c r="Y49" s="79"/>
+      <c r="Z49" s="79"/>
+      <c r="AA49" s="80"/>
     </row>
     <row r="50" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="30"/>
-      <c r="B50" s="64"/>
-      <c r="C50" s="65"/>
-      <c r="D50" s="65"/>
-      <c r="E50" s="65"/>
-      <c r="F50" s="65"/>
-      <c r="G50" s="65"/>
-      <c r="H50" s="65"/>
-      <c r="I50" s="65"/>
-      <c r="J50" s="65"/>
-      <c r="K50" s="65"/>
-      <c r="L50" s="65"/>
-      <c r="M50" s="65"/>
-      <c r="N50" s="65"/>
-      <c r="O50" s="65"/>
-      <c r="P50" s="65"/>
-      <c r="Q50" s="65"/>
-      <c r="R50" s="65"/>
-      <c r="S50" s="65"/>
-      <c r="T50" s="65"/>
-      <c r="U50" s="65"/>
-      <c r="V50" s="65"/>
-      <c r="W50" s="65"/>
-      <c r="X50" s="65"/>
-      <c r="Y50" s="65"/>
-      <c r="Z50" s="65"/>
-      <c r="AA50" s="66"/>
+      <c r="B50" s="81"/>
+      <c r="C50" s="82"/>
+      <c r="D50" s="82"/>
+      <c r="E50" s="82"/>
+      <c r="F50" s="82"/>
+      <c r="G50" s="82"/>
+      <c r="H50" s="82"/>
+      <c r="I50" s="82"/>
+      <c r="J50" s="82"/>
+      <c r="K50" s="82"/>
+      <c r="L50" s="82"/>
+      <c r="M50" s="82"/>
+      <c r="N50" s="82"/>
+      <c r="O50" s="82"/>
+      <c r="P50" s="82"/>
+      <c r="Q50" s="82"/>
+      <c r="R50" s="82"/>
+      <c r="S50" s="82"/>
+      <c r="T50" s="82"/>
+      <c r="U50" s="82"/>
+      <c r="V50" s="82"/>
+      <c r="W50" s="82"/>
+      <c r="X50" s="82"/>
+      <c r="Y50" s="82"/>
+      <c r="Z50" s="82"/>
+      <c r="AA50" s="83"/>
     </row>
     <row r="51" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="30"/>
-      <c r="B51" s="64"/>
-      <c r="C51" s="65"/>
-      <c r="D51" s="65"/>
-      <c r="E51" s="65"/>
-      <c r="F51" s="65"/>
-      <c r="G51" s="65"/>
-      <c r="H51" s="65"/>
-      <c r="I51" s="65"/>
-      <c r="J51" s="65"/>
-      <c r="K51" s="65"/>
-      <c r="L51" s="65"/>
-      <c r="M51" s="65"/>
-      <c r="N51" s="65"/>
-      <c r="O51" s="65"/>
-      <c r="P51" s="65"/>
-      <c r="Q51" s="65"/>
-      <c r="R51" s="65"/>
-      <c r="S51" s="65"/>
-      <c r="T51" s="65"/>
-      <c r="U51" s="65"/>
-      <c r="V51" s="65"/>
-      <c r="W51" s="65"/>
-      <c r="X51" s="65"/>
-      <c r="Y51" s="65"/>
-      <c r="Z51" s="65"/>
-      <c r="AA51" s="66"/>
+      <c r="B51" s="81"/>
+      <c r="C51" s="82"/>
+      <c r="D51" s="82"/>
+      <c r="E51" s="82"/>
+      <c r="F51" s="82"/>
+      <c r="G51" s="82"/>
+      <c r="H51" s="82"/>
+      <c r="I51" s="82"/>
+      <c r="J51" s="82"/>
+      <c r="K51" s="82"/>
+      <c r="L51" s="82"/>
+      <c r="M51" s="82"/>
+      <c r="N51" s="82"/>
+      <c r="O51" s="82"/>
+      <c r="P51" s="82"/>
+      <c r="Q51" s="82"/>
+      <c r="R51" s="82"/>
+      <c r="S51" s="82"/>
+      <c r="T51" s="82"/>
+      <c r="U51" s="82"/>
+      <c r="V51" s="82"/>
+      <c r="W51" s="82"/>
+      <c r="X51" s="82"/>
+      <c r="Y51" s="82"/>
+      <c r="Z51" s="82"/>
+      <c r="AA51" s="83"/>
     </row>
     <row r="52" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="30"/>
-      <c r="B52" s="64"/>
-      <c r="C52" s="65"/>
-      <c r="D52" s="65"/>
-      <c r="E52" s="65"/>
-      <c r="F52" s="65"/>
-      <c r="G52" s="65"/>
-      <c r="H52" s="65"/>
-      <c r="I52" s="65"/>
-      <c r="J52" s="65"/>
-      <c r="K52" s="65"/>
-      <c r="L52" s="65"/>
-      <c r="M52" s="65"/>
-      <c r="N52" s="65"/>
-      <c r="O52" s="65"/>
-      <c r="P52" s="65"/>
-      <c r="Q52" s="65"/>
-      <c r="R52" s="65"/>
-      <c r="S52" s="65"/>
-      <c r="T52" s="65"/>
-      <c r="U52" s="65"/>
-      <c r="V52" s="65"/>
-      <c r="W52" s="65"/>
-      <c r="X52" s="65"/>
-      <c r="Y52" s="65"/>
-      <c r="Z52" s="65"/>
-      <c r="AA52" s="66"/>
+      <c r="B52" s="81"/>
+      <c r="C52" s="82"/>
+      <c r="D52" s="82"/>
+      <c r="E52" s="82"/>
+      <c r="F52" s="82"/>
+      <c r="G52" s="82"/>
+      <c r="H52" s="82"/>
+      <c r="I52" s="82"/>
+      <c r="J52" s="82"/>
+      <c r="K52" s="82"/>
+      <c r="L52" s="82"/>
+      <c r="M52" s="82"/>
+      <c r="N52" s="82"/>
+      <c r="O52" s="82"/>
+      <c r="P52" s="82"/>
+      <c r="Q52" s="82"/>
+      <c r="R52" s="82"/>
+      <c r="S52" s="82"/>
+      <c r="T52" s="82"/>
+      <c r="U52" s="82"/>
+      <c r="V52" s="82"/>
+      <c r="W52" s="82"/>
+      <c r="X52" s="82"/>
+      <c r="Y52" s="82"/>
+      <c r="Z52" s="82"/>
+      <c r="AA52" s="83"/>
     </row>
     <row r="53" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="30"/>
-      <c r="B53" s="64"/>
-      <c r="C53" s="65"/>
-      <c r="D53" s="65"/>
-      <c r="E53" s="65"/>
-      <c r="F53" s="65"/>
-      <c r="G53" s="65"/>
-      <c r="H53" s="65"/>
-      <c r="I53" s="65"/>
-      <c r="J53" s="65"/>
-      <c r="K53" s="65"/>
-      <c r="L53" s="65"/>
-      <c r="M53" s="65"/>
-      <c r="N53" s="65"/>
-      <c r="O53" s="65"/>
-      <c r="P53" s="65"/>
-      <c r="Q53" s="65"/>
-      <c r="R53" s="65"/>
-      <c r="S53" s="65"/>
-      <c r="T53" s="65"/>
-      <c r="U53" s="65"/>
-      <c r="V53" s="65"/>
-      <c r="W53" s="65"/>
-      <c r="X53" s="65"/>
-      <c r="Y53" s="65"/>
-      <c r="Z53" s="65"/>
-      <c r="AA53" s="66"/>
+      <c r="B53" s="81"/>
+      <c r="C53" s="82"/>
+      <c r="D53" s="82"/>
+      <c r="E53" s="82"/>
+      <c r="F53" s="82"/>
+      <c r="G53" s="82"/>
+      <c r="H53" s="82"/>
+      <c r="I53" s="82"/>
+      <c r="J53" s="82"/>
+      <c r="K53" s="82"/>
+      <c r="L53" s="82"/>
+      <c r="M53" s="82"/>
+      <c r="N53" s="82"/>
+      <c r="O53" s="82"/>
+      <c r="P53" s="82"/>
+      <c r="Q53" s="82"/>
+      <c r="R53" s="82"/>
+      <c r="S53" s="82"/>
+      <c r="T53" s="82"/>
+      <c r="U53" s="82"/>
+      <c r="V53" s="82"/>
+      <c r="W53" s="82"/>
+      <c r="X53" s="82"/>
+      <c r="Y53" s="82"/>
+      <c r="Z53" s="82"/>
+      <c r="AA53" s="83"/>
     </row>
     <row r="54" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="30"/>
-      <c r="B54" s="64"/>
-      <c r="C54" s="65"/>
-      <c r="D54" s="65"/>
-      <c r="E54" s="65"/>
-      <c r="F54" s="65"/>
-      <c r="G54" s="65"/>
-      <c r="H54" s="65"/>
-      <c r="I54" s="65"/>
-      <c r="J54" s="65"/>
-      <c r="K54" s="65"/>
-      <c r="L54" s="65"/>
-      <c r="M54" s="65"/>
-      <c r="N54" s="65"/>
-      <c r="O54" s="65"/>
-      <c r="P54" s="65"/>
-      <c r="Q54" s="65"/>
-      <c r="R54" s="65"/>
-      <c r="S54" s="65"/>
-      <c r="T54" s="65"/>
-      <c r="U54" s="65"/>
-      <c r="V54" s="65"/>
-      <c r="W54" s="65"/>
-      <c r="X54" s="65"/>
-      <c r="Y54" s="65"/>
-      <c r="Z54" s="65"/>
-      <c r="AA54" s="66"/>
+      <c r="B54" s="81"/>
+      <c r="C54" s="82"/>
+      <c r="D54" s="82"/>
+      <c r="E54" s="82"/>
+      <c r="F54" s="82"/>
+      <c r="G54" s="82"/>
+      <c r="H54" s="82"/>
+      <c r="I54" s="82"/>
+      <c r="J54" s="82"/>
+      <c r="K54" s="82"/>
+      <c r="L54" s="82"/>
+      <c r="M54" s="82"/>
+      <c r="N54" s="82"/>
+      <c r="O54" s="82"/>
+      <c r="P54" s="82"/>
+      <c r="Q54" s="82"/>
+      <c r="R54" s="82"/>
+      <c r="S54" s="82"/>
+      <c r="T54" s="82"/>
+      <c r="U54" s="82"/>
+      <c r="V54" s="82"/>
+      <c r="W54" s="82"/>
+      <c r="X54" s="82"/>
+      <c r="Y54" s="82"/>
+      <c r="Z54" s="82"/>
+      <c r="AA54" s="83"/>
     </row>
     <row r="55" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A55" s="30"/>
-      <c r="B55" s="81"/>
-      <c r="C55" s="82"/>
-      <c r="D55" s="82"/>
-      <c r="E55" s="82"/>
-      <c r="F55" s="82"/>
-      <c r="G55" s="82"/>
-      <c r="H55" s="82"/>
-      <c r="I55" s="82"/>
-      <c r="J55" s="82"/>
-      <c r="K55" s="82"/>
-      <c r="L55" s="82"/>
-      <c r="M55" s="82"/>
-      <c r="N55" s="82"/>
-      <c r="O55" s="82"/>
-      <c r="P55" s="82"/>
-      <c r="Q55" s="82"/>
-      <c r="R55" s="82"/>
-      <c r="S55" s="82"/>
-      <c r="T55" s="82"/>
-      <c r="U55" s="82"/>
-      <c r="V55" s="82"/>
-      <c r="W55" s="82"/>
-      <c r="X55" s="82"/>
-      <c r="Y55" s="82"/>
-      <c r="Z55" s="82"/>
-      <c r="AA55" s="83"/>
+      <c r="B55" s="90"/>
+      <c r="C55" s="91"/>
+      <c r="D55" s="91"/>
+      <c r="E55" s="91"/>
+      <c r="F55" s="91"/>
+      <c r="G55" s="91"/>
+      <c r="H55" s="91"/>
+      <c r="I55" s="91"/>
+      <c r="J55" s="91"/>
+      <c r="K55" s="91"/>
+      <c r="L55" s="91"/>
+      <c r="M55" s="91"/>
+      <c r="N55" s="91"/>
+      <c r="O55" s="91"/>
+      <c r="P55" s="91"/>
+      <c r="Q55" s="91"/>
+      <c r="R55" s="91"/>
+      <c r="S55" s="91"/>
+      <c r="T55" s="91"/>
+      <c r="U55" s="91"/>
+      <c r="V55" s="91"/>
+      <c r="W55" s="91"/>
+      <c r="X55" s="91"/>
+      <c r="Y55" s="91"/>
+      <c r="Z55" s="91"/>
+      <c r="AA55" s="92"/>
     </row>
     <row r="56" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
@@ -2910,22 +2928,22 @@
     </row>
     <row r="59" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
-      <c r="B59" s="91"/>
-      <c r="C59" s="91"/>
-      <c r="D59" s="91"/>
-      <c r="E59" s="91"/>
-      <c r="F59" s="91"/>
-      <c r="G59" s="91"/>
-      <c r="H59" s="91"/>
+      <c r="B59" s="76"/>
+      <c r="C59" s="76"/>
+      <c r="D59" s="76"/>
+      <c r="E59" s="76"/>
+      <c r="F59" s="76"/>
+      <c r="G59" s="76"/>
+      <c r="H59" s="76"/>
       <c r="I59" s="35"/>
       <c r="J59" s="35"/>
-      <c r="K59" s="92"/>
-      <c r="L59" s="92"/>
-      <c r="M59" s="92"/>
-      <c r="N59" s="92"/>
-      <c r="O59" s="92"/>
-      <c r="P59" s="92"/>
-      <c r="Q59" s="92"/>
+      <c r="K59" s="77"/>
+      <c r="L59" s="77"/>
+      <c r="M59" s="77"/>
+      <c r="N59" s="77"/>
+      <c r="O59" s="77"/>
+      <c r="P59" s="77"/>
+      <c r="Q59" s="77"/>
       <c r="R59" s="35"/>
       <c r="S59" s="40"/>
       <c r="T59" s="40"/>
@@ -3092,61 +3110,61 @@
     <row r="65" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
       <c r="B65" s="34"/>
-      <c r="C65" s="42" t="s">
+      <c r="C65" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="D65" s="43"/>
-      <c r="E65" s="43"/>
-      <c r="F65" s="43"/>
-      <c r="G65" s="43"/>
-      <c r="H65" s="43"/>
-      <c r="I65" s="43"/>
-      <c r="J65" s="43"/>
-      <c r="K65" s="43"/>
-      <c r="L65" s="43"/>
-      <c r="M65" s="43"/>
-      <c r="N65" s="43"/>
-      <c r="O65" s="43"/>
-      <c r="P65" s="43"/>
-      <c r="Q65" s="43"/>
-      <c r="R65" s="43"/>
-      <c r="S65" s="43"/>
-      <c r="T65" s="43"/>
-      <c r="U65" s="43"/>
-      <c r="V65" s="43"/>
-      <c r="W65" s="43"/>
-      <c r="X65" s="43"/>
-      <c r="Y65" s="43"/>
-      <c r="Z65" s="44"/>
+      <c r="D65" s="60"/>
+      <c r="E65" s="60"/>
+      <c r="F65" s="60"/>
+      <c r="G65" s="60"/>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="60"/>
+      <c r="K65" s="60"/>
+      <c r="L65" s="60"/>
+      <c r="M65" s="60"/>
+      <c r="N65" s="60"/>
+      <c r="O65" s="60"/>
+      <c r="P65" s="60"/>
+      <c r="Q65" s="60"/>
+      <c r="R65" s="60"/>
+      <c r="S65" s="60"/>
+      <c r="T65" s="60"/>
+      <c r="U65" s="60"/>
+      <c r="V65" s="60"/>
+      <c r="W65" s="60"/>
+      <c r="X65" s="60"/>
+      <c r="Y65" s="60"/>
+      <c r="Z65" s="62"/>
       <c r="AA65" s="34"/>
     </row>
     <row r="66" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
       <c r="B66" s="34"/>
-      <c r="C66" s="45"/>
-      <c r="D66" s="46"/>
-      <c r="E66" s="46"/>
-      <c r="F66" s="46"/>
-      <c r="G66" s="46"/>
-      <c r="H66" s="46"/>
-      <c r="I66" s="46"/>
-      <c r="J66" s="46"/>
-      <c r="K66" s="46"/>
-      <c r="L66" s="46"/>
-      <c r="M66" s="46"/>
-      <c r="N66" s="46"/>
-      <c r="O66" s="46"/>
-      <c r="P66" s="46"/>
-      <c r="Q66" s="46"/>
-      <c r="R66" s="46"/>
-      <c r="S66" s="46"/>
-      <c r="T66" s="46"/>
-      <c r="U66" s="46"/>
-      <c r="V66" s="46"/>
-      <c r="W66" s="46"/>
-      <c r="X66" s="46"/>
-      <c r="Y66" s="46"/>
-      <c r="Z66" s="47"/>
+      <c r="C66" s="63"/>
+      <c r="D66" s="64"/>
+      <c r="E66" s="64"/>
+      <c r="F66" s="64"/>
+      <c r="G66" s="64"/>
+      <c r="H66" s="64"/>
+      <c r="I66" s="64"/>
+      <c r="J66" s="64"/>
+      <c r="K66" s="64"/>
+      <c r="L66" s="64"/>
+      <c r="M66" s="64"/>
+      <c r="N66" s="64"/>
+      <c r="O66" s="64"/>
+      <c r="P66" s="64"/>
+      <c r="Q66" s="64"/>
+      <c r="R66" s="64"/>
+      <c r="S66" s="64"/>
+      <c r="T66" s="64"/>
+      <c r="U66" s="64"/>
+      <c r="V66" s="64"/>
+      <c r="W66" s="64"/>
+      <c r="X66" s="64"/>
+      <c r="Y66" s="64"/>
+      <c r="Z66" s="65"/>
       <c r="AA66" s="34"/>
     </row>
     <row r="67" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30237,21 +30255,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B3:AA3"/>
-    <mergeCell ref="B4:AA4"/>
-    <mergeCell ref="B5:AA5"/>
-    <mergeCell ref="B6:AA6"/>
-    <mergeCell ref="H10:Z10"/>
-    <mergeCell ref="H12:T12"/>
-    <mergeCell ref="W12:Z12"/>
-    <mergeCell ref="B14:AA15"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="H17:Z17"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="H19:Z19"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="H21:Z21"/>
-    <mergeCell ref="B49:AA55"/>
     <mergeCell ref="C65:Z66"/>
     <mergeCell ref="B23:AA23"/>
     <mergeCell ref="B24:AA31"/>
@@ -30262,6 +30265,21 @@
     <mergeCell ref="B48:AA48"/>
     <mergeCell ref="B59:H59"/>
     <mergeCell ref="K59:Q59"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="H19:Z19"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="H21:Z21"/>
+    <mergeCell ref="B49:AA55"/>
+    <mergeCell ref="H12:T12"/>
+    <mergeCell ref="W12:Z12"/>
+    <mergeCell ref="B14:AA15"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="H17:Z17"/>
+    <mergeCell ref="B3:AA3"/>
+    <mergeCell ref="B4:AA4"/>
+    <mergeCell ref="B5:AA5"/>
+    <mergeCell ref="B6:AA6"/>
+    <mergeCell ref="H10:Z10"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.98425196850393704" header="0" footer="0"/>

--- a/static/templates/tec02-A_template.xlsx
+++ b/static/templates/tec02-A_template.xlsx
@@ -176,7 +176,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="57">
+  <borders count="60">
     <border>
       <left/>
       <right/>
@@ -736,11 +736,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1037,6 +1061,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1957,36 +1986,235 @@
     </row>
     <row r="24" ht="14.5" customHeight="1">
       <c r="A24" s="1" t="n"/>
-      <c r="B24" s="110" t="n"/>
-      <c r="AA24" s="111" t="n"/>
+      <c r="B24" s="122" t="n"/>
+      <c r="C24" s="123" t="n"/>
+      <c r="D24" s="123" t="n"/>
+      <c r="E24" s="123" t="n"/>
+      <c r="F24" s="123" t="n"/>
+      <c r="G24" s="123" t="n"/>
+      <c r="H24" s="123" t="n"/>
+      <c r="I24" s="123" t="n"/>
+      <c r="J24" s="123" t="n"/>
+      <c r="K24" s="123" t="n"/>
+      <c r="L24" s="123" t="n"/>
+      <c r="M24" s="123" t="n"/>
+      <c r="N24" s="123" t="n"/>
+      <c r="O24" s="123" t="n"/>
+      <c r="P24" s="123" t="n"/>
+      <c r="Q24" s="123" t="n"/>
+      <c r="R24" s="123" t="n"/>
+      <c r="S24" s="123" t="n"/>
+      <c r="T24" s="123" t="n"/>
+      <c r="U24" s="123" t="n"/>
+      <c r="V24" s="123" t="n"/>
+      <c r="W24" s="123" t="n"/>
+      <c r="X24" s="123" t="n"/>
+      <c r="Y24" s="123" t="n"/>
+      <c r="Z24" s="123" t="n"/>
+      <c r="AA24" s="124" t="n"/>
     </row>
     <row r="25" ht="14.5" customHeight="1">
       <c r="A25" s="1" t="n"/>
-      <c r="B25" s="110" t="n"/>
+      <c r="B25" s="122" t="n"/>
+      <c r="C25" s="123" t="n"/>
+      <c r="D25" s="123" t="n"/>
+      <c r="E25" s="123" t="n"/>
+      <c r="F25" s="123" t="n"/>
+      <c r="G25" s="123" t="n"/>
+      <c r="H25" s="123" t="n"/>
+      <c r="I25" s="123" t="n"/>
+      <c r="J25" s="123" t="n"/>
+      <c r="K25" s="123" t="n"/>
+      <c r="L25" s="123" t="n"/>
+      <c r="M25" s="123" t="n"/>
+      <c r="N25" s="123" t="n"/>
+      <c r="O25" s="123" t="n"/>
+      <c r="P25" s="123" t="n"/>
+      <c r="Q25" s="123" t="n"/>
+      <c r="R25" s="123" t="n"/>
+      <c r="S25" s="123" t="n"/>
+      <c r="T25" s="123" t="n"/>
+      <c r="U25" s="123" t="n"/>
+      <c r="V25" s="123" t="n"/>
+      <c r="W25" s="123" t="n"/>
+      <c r="X25" s="123" t="n"/>
+      <c r="Y25" s="123" t="n"/>
+      <c r="Z25" s="123" t="n"/>
+      <c r="AA25" s="124" t="n"/>
     </row>
     <row r="26" ht="14.5" customHeight="1">
       <c r="A26" s="1" t="n"/>
-      <c r="B26" s="110" t="n"/>
+      <c r="B26" s="122" t="n"/>
+      <c r="C26" s="123" t="n"/>
+      <c r="D26" s="123" t="n"/>
+      <c r="E26" s="123" t="n"/>
+      <c r="F26" s="123" t="n"/>
+      <c r="G26" s="123" t="n"/>
+      <c r="H26" s="123" t="n"/>
+      <c r="I26" s="123" t="n"/>
+      <c r="J26" s="123" t="n"/>
+      <c r="K26" s="123" t="n"/>
+      <c r="L26" s="123" t="n"/>
+      <c r="M26" s="123" t="n"/>
+      <c r="N26" s="123" t="n"/>
+      <c r="O26" s="123" t="n"/>
+      <c r="P26" s="123" t="n"/>
+      <c r="Q26" s="123" t="n"/>
+      <c r="R26" s="123" t="n"/>
+      <c r="S26" s="123" t="n"/>
+      <c r="T26" s="123" t="n"/>
+      <c r="U26" s="123" t="n"/>
+      <c r="V26" s="123" t="n"/>
+      <c r="W26" s="123" t="n"/>
+      <c r="X26" s="123" t="n"/>
+      <c r="Y26" s="123" t="n"/>
+      <c r="Z26" s="123" t="n"/>
+      <c r="AA26" s="124" t="n"/>
     </row>
     <row r="27" ht="14.5" customHeight="1">
       <c r="A27" s="1" t="n"/>
-      <c r="B27" s="110" t="n"/>
+      <c r="B27" s="122" t="n"/>
+      <c r="C27" s="123" t="n"/>
+      <c r="D27" s="123" t="n"/>
+      <c r="E27" s="123" t="n"/>
+      <c r="F27" s="123" t="n"/>
+      <c r="G27" s="123" t="n"/>
+      <c r="H27" s="123" t="n"/>
+      <c r="I27" s="123" t="n"/>
+      <c r="J27" s="123" t="n"/>
+      <c r="K27" s="123" t="n"/>
+      <c r="L27" s="123" t="n"/>
+      <c r="M27" s="123" t="n"/>
+      <c r="N27" s="123" t="n"/>
+      <c r="O27" s="123" t="n"/>
+      <c r="P27" s="123" t="n"/>
+      <c r="Q27" s="123" t="n"/>
+      <c r="R27" s="123" t="n"/>
+      <c r="S27" s="123" t="n"/>
+      <c r="T27" s="123" t="n"/>
+      <c r="U27" s="123" t="n"/>
+      <c r="V27" s="123" t="n"/>
+      <c r="W27" s="123" t="n"/>
+      <c r="X27" s="123" t="n"/>
+      <c r="Y27" s="123" t="n"/>
+      <c r="Z27" s="123" t="n"/>
+      <c r="AA27" s="124" t="n"/>
     </row>
     <row r="28" ht="14.5" customHeight="1">
       <c r="A28" s="1" t="n"/>
-      <c r="B28" s="110" t="n"/>
+      <c r="B28" s="122" t="n"/>
+      <c r="C28" s="123" t="n"/>
+      <c r="D28" s="123" t="n"/>
+      <c r="E28" s="123" t="n"/>
+      <c r="F28" s="123" t="n"/>
+      <c r="G28" s="123" t="n"/>
+      <c r="H28" s="123" t="n"/>
+      <c r="I28" s="123" t="n"/>
+      <c r="J28" s="123" t="n"/>
+      <c r="K28" s="123" t="n"/>
+      <c r="L28" s="123" t="n"/>
+      <c r="M28" s="123" t="n"/>
+      <c r="N28" s="123" t="n"/>
+      <c r="O28" s="123" t="n"/>
+      <c r="P28" s="123" t="n"/>
+      <c r="Q28" s="123" t="n"/>
+      <c r="R28" s="123" t="n"/>
+      <c r="S28" s="123" t="n"/>
+      <c r="T28" s="123" t="n"/>
+      <c r="U28" s="123" t="n"/>
+      <c r="V28" s="123" t="n"/>
+      <c r="W28" s="123" t="n"/>
+      <c r="X28" s="123" t="n"/>
+      <c r="Y28" s="123" t="n"/>
+      <c r="Z28" s="123" t="n"/>
+      <c r="AA28" s="124" t="n"/>
     </row>
     <row r="29" ht="14.5" customHeight="1">
       <c r="A29" s="1" t="n"/>
-      <c r="B29" s="110" t="n"/>
+      <c r="B29" s="122" t="n"/>
+      <c r="C29" s="123" t="n"/>
+      <c r="D29" s="123" t="n"/>
+      <c r="E29" s="123" t="n"/>
+      <c r="F29" s="123" t="n"/>
+      <c r="G29" s="123" t="n"/>
+      <c r="H29" s="123" t="n"/>
+      <c r="I29" s="123" t="n"/>
+      <c r="J29" s="123" t="n"/>
+      <c r="K29" s="123" t="n"/>
+      <c r="L29" s="123" t="n"/>
+      <c r="M29" s="123" t="n"/>
+      <c r="N29" s="123" t="n"/>
+      <c r="O29" s="123" t="n"/>
+      <c r="P29" s="123" t="n"/>
+      <c r="Q29" s="123" t="n"/>
+      <c r="R29" s="123" t="n"/>
+      <c r="S29" s="123" t="n"/>
+      <c r="T29" s="123" t="n"/>
+      <c r="U29" s="123" t="n"/>
+      <c r="V29" s="123" t="n"/>
+      <c r="W29" s="123" t="n"/>
+      <c r="X29" s="123" t="n"/>
+      <c r="Y29" s="123" t="n"/>
+      <c r="Z29" s="123" t="n"/>
+      <c r="AA29" s="124" t="n"/>
     </row>
     <row r="30" ht="14.5" customHeight="1">
       <c r="A30" s="1" t="n"/>
-      <c r="B30" s="110" t="n"/>
+      <c r="B30" s="122" t="n"/>
+      <c r="C30" s="123" t="n"/>
+      <c r="D30" s="123" t="n"/>
+      <c r="E30" s="123" t="n"/>
+      <c r="F30" s="123" t="n"/>
+      <c r="G30" s="123" t="n"/>
+      <c r="H30" s="123" t="n"/>
+      <c r="I30" s="123" t="n"/>
+      <c r="J30" s="123" t="n"/>
+      <c r="K30" s="123" t="n"/>
+      <c r="L30" s="123" t="n"/>
+      <c r="M30" s="123" t="n"/>
+      <c r="N30" s="123" t="n"/>
+      <c r="O30" s="123" t="n"/>
+      <c r="P30" s="123" t="n"/>
+      <c r="Q30" s="123" t="n"/>
+      <c r="R30" s="123" t="n"/>
+      <c r="S30" s="123" t="n"/>
+      <c r="T30" s="123" t="n"/>
+      <c r="U30" s="123" t="n"/>
+      <c r="V30" s="123" t="n"/>
+      <c r="W30" s="123" t="n"/>
+      <c r="X30" s="123" t="n"/>
+      <c r="Y30" s="123" t="n"/>
+      <c r="Z30" s="123" t="n"/>
+      <c r="AA30" s="124" t="n"/>
     </row>
     <row r="31" ht="14.5" customHeight="1">
       <c r="A31" s="1" t="n"/>
-      <c r="B31" s="110" t="n"/>
+      <c r="B31" s="122" t="n"/>
+      <c r="C31" s="123" t="n"/>
+      <c r="D31" s="123" t="n"/>
+      <c r="E31" s="123" t="n"/>
+      <c r="F31" s="123" t="n"/>
+      <c r="G31" s="123" t="n"/>
+      <c r="H31" s="123" t="n"/>
+      <c r="I31" s="123" t="n"/>
+      <c r="J31" s="123" t="n"/>
+      <c r="K31" s="123" t="n"/>
+      <c r="L31" s="123" t="n"/>
+      <c r="M31" s="123" t="n"/>
+      <c r="N31" s="123" t="n"/>
+      <c r="O31" s="123" t="n"/>
+      <c r="P31" s="123" t="n"/>
+      <c r="Q31" s="123" t="n"/>
+      <c r="R31" s="123" t="n"/>
+      <c r="S31" s="123" t="n"/>
+      <c r="T31" s="123" t="n"/>
+      <c r="U31" s="123" t="n"/>
+      <c r="V31" s="123" t="n"/>
+      <c r="W31" s="123" t="n"/>
+      <c r="X31" s="123" t="n"/>
+      <c r="Y31" s="123" t="n"/>
+      <c r="Z31" s="123" t="n"/>
+      <c r="AA31" s="124" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="1" t="n"/>
@@ -2023,32 +2251,206 @@
     </row>
     <row r="33" ht="14.5" customHeight="1">
       <c r="A33" s="1" t="n"/>
-      <c r="B33" s="110" t="n"/>
-      <c r="AA33" s="111" t="n"/>
+      <c r="B33" s="122" t="n"/>
+      <c r="C33" s="123" t="n"/>
+      <c r="D33" s="123" t="n"/>
+      <c r="E33" s="123" t="n"/>
+      <c r="F33" s="123" t="n"/>
+      <c r="G33" s="123" t="n"/>
+      <c r="H33" s="123" t="n"/>
+      <c r="I33" s="123" t="n"/>
+      <c r="J33" s="123" t="n"/>
+      <c r="K33" s="123" t="n"/>
+      <c r="L33" s="123" t="n"/>
+      <c r="M33" s="123" t="n"/>
+      <c r="N33" s="123" t="n"/>
+      <c r="O33" s="123" t="n"/>
+      <c r="P33" s="123" t="n"/>
+      <c r="Q33" s="123" t="n"/>
+      <c r="R33" s="123" t="n"/>
+      <c r="S33" s="123" t="n"/>
+      <c r="T33" s="123" t="n"/>
+      <c r="U33" s="123" t="n"/>
+      <c r="V33" s="123" t="n"/>
+      <c r="W33" s="123" t="n"/>
+      <c r="X33" s="123" t="n"/>
+      <c r="Y33" s="123" t="n"/>
+      <c r="Z33" s="123" t="n"/>
+      <c r="AA33" s="124" t="n"/>
     </row>
     <row r="34" ht="14.5" customHeight="1">
       <c r="A34" s="1" t="n"/>
-      <c r="B34" s="110" t="n"/>
+      <c r="B34" s="122" t="n"/>
+      <c r="C34" s="123" t="n"/>
+      <c r="D34" s="123" t="n"/>
+      <c r="E34" s="123" t="n"/>
+      <c r="F34" s="123" t="n"/>
+      <c r="G34" s="123" t="n"/>
+      <c r="H34" s="123" t="n"/>
+      <c r="I34" s="123" t="n"/>
+      <c r="J34" s="123" t="n"/>
+      <c r="K34" s="123" t="n"/>
+      <c r="L34" s="123" t="n"/>
+      <c r="M34" s="123" t="n"/>
+      <c r="N34" s="123" t="n"/>
+      <c r="O34" s="123" t="n"/>
+      <c r="P34" s="123" t="n"/>
+      <c r="Q34" s="123" t="n"/>
+      <c r="R34" s="123" t="n"/>
+      <c r="S34" s="123" t="n"/>
+      <c r="T34" s="123" t="n"/>
+      <c r="U34" s="123" t="n"/>
+      <c r="V34" s="123" t="n"/>
+      <c r="W34" s="123" t="n"/>
+      <c r="X34" s="123" t="n"/>
+      <c r="Y34" s="123" t="n"/>
+      <c r="Z34" s="123" t="n"/>
+      <c r="AA34" s="124" t="n"/>
     </row>
     <row r="35" ht="14.5" customHeight="1">
       <c r="A35" s="1" t="n"/>
-      <c r="B35" s="110" t="n"/>
+      <c r="B35" s="122" t="n"/>
+      <c r="C35" s="123" t="n"/>
+      <c r="D35" s="123" t="n"/>
+      <c r="E35" s="123" t="n"/>
+      <c r="F35" s="123" t="n"/>
+      <c r="G35" s="123" t="n"/>
+      <c r="H35" s="123" t="n"/>
+      <c r="I35" s="123" t="n"/>
+      <c r="J35" s="123" t="n"/>
+      <c r="K35" s="123" t="n"/>
+      <c r="L35" s="123" t="n"/>
+      <c r="M35" s="123" t="n"/>
+      <c r="N35" s="123" t="n"/>
+      <c r="O35" s="123" t="n"/>
+      <c r="P35" s="123" t="n"/>
+      <c r="Q35" s="123" t="n"/>
+      <c r="R35" s="123" t="n"/>
+      <c r="S35" s="123" t="n"/>
+      <c r="T35" s="123" t="n"/>
+      <c r="U35" s="123" t="n"/>
+      <c r="V35" s="123" t="n"/>
+      <c r="W35" s="123" t="n"/>
+      <c r="X35" s="123" t="n"/>
+      <c r="Y35" s="123" t="n"/>
+      <c r="Z35" s="123" t="n"/>
+      <c r="AA35" s="124" t="n"/>
     </row>
     <row r="36" ht="14.5" customHeight="1">
       <c r="A36" s="1" t="n"/>
-      <c r="B36" s="110" t="n"/>
+      <c r="B36" s="122" t="n"/>
+      <c r="C36" s="123" t="n"/>
+      <c r="D36" s="123" t="n"/>
+      <c r="E36" s="123" t="n"/>
+      <c r="F36" s="123" t="n"/>
+      <c r="G36" s="123" t="n"/>
+      <c r="H36" s="123" t="n"/>
+      <c r="I36" s="123" t="n"/>
+      <c r="J36" s="123" t="n"/>
+      <c r="K36" s="123" t="n"/>
+      <c r="L36" s="123" t="n"/>
+      <c r="M36" s="123" t="n"/>
+      <c r="N36" s="123" t="n"/>
+      <c r="O36" s="123" t="n"/>
+      <c r="P36" s="123" t="n"/>
+      <c r="Q36" s="123" t="n"/>
+      <c r="R36" s="123" t="n"/>
+      <c r="S36" s="123" t="n"/>
+      <c r="T36" s="123" t="n"/>
+      <c r="U36" s="123" t="n"/>
+      <c r="V36" s="123" t="n"/>
+      <c r="W36" s="123" t="n"/>
+      <c r="X36" s="123" t="n"/>
+      <c r="Y36" s="123" t="n"/>
+      <c r="Z36" s="123" t="n"/>
+      <c r="AA36" s="124" t="n"/>
     </row>
     <row r="37" ht="14.5" customHeight="1">
       <c r="A37" s="1" t="n"/>
-      <c r="B37" s="110" t="n"/>
+      <c r="B37" s="122" t="n"/>
+      <c r="C37" s="123" t="n"/>
+      <c r="D37" s="123" t="n"/>
+      <c r="E37" s="123" t="n"/>
+      <c r="F37" s="123" t="n"/>
+      <c r="G37" s="123" t="n"/>
+      <c r="H37" s="123" t="n"/>
+      <c r="I37" s="123" t="n"/>
+      <c r="J37" s="123" t="n"/>
+      <c r="K37" s="123" t="n"/>
+      <c r="L37" s="123" t="n"/>
+      <c r="M37" s="123" t="n"/>
+      <c r="N37" s="123" t="n"/>
+      <c r="O37" s="123" t="n"/>
+      <c r="P37" s="123" t="n"/>
+      <c r="Q37" s="123" t="n"/>
+      <c r="R37" s="123" t="n"/>
+      <c r="S37" s="123" t="n"/>
+      <c r="T37" s="123" t="n"/>
+      <c r="U37" s="123" t="n"/>
+      <c r="V37" s="123" t="n"/>
+      <c r="W37" s="123" t="n"/>
+      <c r="X37" s="123" t="n"/>
+      <c r="Y37" s="123" t="n"/>
+      <c r="Z37" s="123" t="n"/>
+      <c r="AA37" s="124" t="n"/>
     </row>
     <row r="38" ht="14.5" customHeight="1">
       <c r="A38" s="1" t="n"/>
-      <c r="B38" s="110" t="n"/>
+      <c r="B38" s="122" t="n"/>
+      <c r="C38" s="123" t="n"/>
+      <c r="D38" s="123" t="n"/>
+      <c r="E38" s="123" t="n"/>
+      <c r="F38" s="123" t="n"/>
+      <c r="G38" s="123" t="n"/>
+      <c r="H38" s="123" t="n"/>
+      <c r="I38" s="123" t="n"/>
+      <c r="J38" s="123" t="n"/>
+      <c r="K38" s="123" t="n"/>
+      <c r="L38" s="123" t="n"/>
+      <c r="M38" s="123" t="n"/>
+      <c r="N38" s="123" t="n"/>
+      <c r="O38" s="123" t="n"/>
+      <c r="P38" s="123" t="n"/>
+      <c r="Q38" s="123" t="n"/>
+      <c r="R38" s="123" t="n"/>
+      <c r="S38" s="123" t="n"/>
+      <c r="T38" s="123" t="n"/>
+      <c r="U38" s="123" t="n"/>
+      <c r="V38" s="123" t="n"/>
+      <c r="W38" s="123" t="n"/>
+      <c r="X38" s="123" t="n"/>
+      <c r="Y38" s="123" t="n"/>
+      <c r="Z38" s="123" t="n"/>
+      <c r="AA38" s="124" t="n"/>
     </row>
     <row r="39" ht="14.5" customHeight="1">
       <c r="A39" s="1" t="n"/>
-      <c r="B39" s="110" t="n"/>
+      <c r="B39" s="122" t="n"/>
+      <c r="C39" s="123" t="n"/>
+      <c r="D39" s="123" t="n"/>
+      <c r="E39" s="123" t="n"/>
+      <c r="F39" s="123" t="n"/>
+      <c r="G39" s="123" t="n"/>
+      <c r="H39" s="123" t="n"/>
+      <c r="I39" s="123" t="n"/>
+      <c r="J39" s="123" t="n"/>
+      <c r="K39" s="123" t="n"/>
+      <c r="L39" s="123" t="n"/>
+      <c r="M39" s="123" t="n"/>
+      <c r="N39" s="123" t="n"/>
+      <c r="O39" s="123" t="n"/>
+      <c r="P39" s="123" t="n"/>
+      <c r="Q39" s="123" t="n"/>
+      <c r="R39" s="123" t="n"/>
+      <c r="S39" s="123" t="n"/>
+      <c r="T39" s="123" t="n"/>
+      <c r="U39" s="123" t="n"/>
+      <c r="V39" s="123" t="n"/>
+      <c r="W39" s="123" t="n"/>
+      <c r="X39" s="123" t="n"/>
+      <c r="Y39" s="123" t="n"/>
+      <c r="Z39" s="123" t="n"/>
+      <c r="AA39" s="124" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="1" t="n"/>
@@ -2085,56 +2487,206 @@
     </row>
     <row r="41" ht="14.5" customHeight="1">
       <c r="A41" s="1" t="n"/>
-      <c r="B41" s="115" t="n"/>
-      <c r="C41" s="116" t="n"/>
-      <c r="D41" s="116" t="n"/>
-      <c r="E41" s="116" t="n"/>
-      <c r="F41" s="116" t="n"/>
-      <c r="G41" s="116" t="n"/>
-      <c r="H41" s="116" t="n"/>
-      <c r="I41" s="116" t="n"/>
-      <c r="J41" s="116" t="n"/>
-      <c r="K41" s="116" t="n"/>
-      <c r="L41" s="116" t="n"/>
-      <c r="M41" s="116" t="n"/>
-      <c r="N41" s="116" t="n"/>
-      <c r="O41" s="116" t="n"/>
-      <c r="P41" s="116" t="n"/>
-      <c r="Q41" s="116" t="n"/>
-      <c r="R41" s="116" t="n"/>
-      <c r="S41" s="116" t="n"/>
-      <c r="T41" s="116" t="n"/>
-      <c r="U41" s="116" t="n"/>
-      <c r="V41" s="116" t="n"/>
-      <c r="W41" s="116" t="n"/>
-      <c r="X41" s="116" t="n"/>
-      <c r="Y41" s="116" t="n"/>
-      <c r="Z41" s="116" t="n"/>
-      <c r="AA41" s="117" t="n"/>
+      <c r="B41" s="122" t="n"/>
+      <c r="C41" s="123" t="n"/>
+      <c r="D41" s="123" t="n"/>
+      <c r="E41" s="123" t="n"/>
+      <c r="F41" s="123" t="n"/>
+      <c r="G41" s="123" t="n"/>
+      <c r="H41" s="123" t="n"/>
+      <c r="I41" s="123" t="n"/>
+      <c r="J41" s="123" t="n"/>
+      <c r="K41" s="123" t="n"/>
+      <c r="L41" s="123" t="n"/>
+      <c r="M41" s="123" t="n"/>
+      <c r="N41" s="123" t="n"/>
+      <c r="O41" s="123" t="n"/>
+      <c r="P41" s="123" t="n"/>
+      <c r="Q41" s="123" t="n"/>
+      <c r="R41" s="123" t="n"/>
+      <c r="S41" s="123" t="n"/>
+      <c r="T41" s="123" t="n"/>
+      <c r="U41" s="123" t="n"/>
+      <c r="V41" s="123" t="n"/>
+      <c r="W41" s="123" t="n"/>
+      <c r="X41" s="123" t="n"/>
+      <c r="Y41" s="123" t="n"/>
+      <c r="Z41" s="123" t="n"/>
+      <c r="AA41" s="124" t="n"/>
     </row>
     <row r="42" ht="14.5" customHeight="1">
       <c r="A42" s="1" t="n"/>
-      <c r="B42" s="115" t="n"/>
+      <c r="B42" s="122" t="n"/>
+      <c r="C42" s="123" t="n"/>
+      <c r="D42" s="123" t="n"/>
+      <c r="E42" s="123" t="n"/>
+      <c r="F42" s="123" t="n"/>
+      <c r="G42" s="123" t="n"/>
+      <c r="H42" s="123" t="n"/>
+      <c r="I42" s="123" t="n"/>
+      <c r="J42" s="123" t="n"/>
+      <c r="K42" s="123" t="n"/>
+      <c r="L42" s="123" t="n"/>
+      <c r="M42" s="123" t="n"/>
+      <c r="N42" s="123" t="n"/>
+      <c r="O42" s="123" t="n"/>
+      <c r="P42" s="123" t="n"/>
+      <c r="Q42" s="123" t="n"/>
+      <c r="R42" s="123" t="n"/>
+      <c r="S42" s="123" t="n"/>
+      <c r="T42" s="123" t="n"/>
+      <c r="U42" s="123" t="n"/>
+      <c r="V42" s="123" t="n"/>
+      <c r="W42" s="123" t="n"/>
+      <c r="X42" s="123" t="n"/>
+      <c r="Y42" s="123" t="n"/>
+      <c r="Z42" s="123" t="n"/>
+      <c r="AA42" s="124" t="n"/>
     </row>
     <row r="43" ht="14.5" customHeight="1">
       <c r="A43" s="1" t="n"/>
-      <c r="B43" s="115" t="n"/>
+      <c r="B43" s="122" t="n"/>
+      <c r="C43" s="123" t="n"/>
+      <c r="D43" s="123" t="n"/>
+      <c r="E43" s="123" t="n"/>
+      <c r="F43" s="123" t="n"/>
+      <c r="G43" s="123" t="n"/>
+      <c r="H43" s="123" t="n"/>
+      <c r="I43" s="123" t="n"/>
+      <c r="J43" s="123" t="n"/>
+      <c r="K43" s="123" t="n"/>
+      <c r="L43" s="123" t="n"/>
+      <c r="M43" s="123" t="n"/>
+      <c r="N43" s="123" t="n"/>
+      <c r="O43" s="123" t="n"/>
+      <c r="P43" s="123" t="n"/>
+      <c r="Q43" s="123" t="n"/>
+      <c r="R43" s="123" t="n"/>
+      <c r="S43" s="123" t="n"/>
+      <c r="T43" s="123" t="n"/>
+      <c r="U43" s="123" t="n"/>
+      <c r="V43" s="123" t="n"/>
+      <c r="W43" s="123" t="n"/>
+      <c r="X43" s="123" t="n"/>
+      <c r="Y43" s="123" t="n"/>
+      <c r="Z43" s="123" t="n"/>
+      <c r="AA43" s="124" t="n"/>
     </row>
     <row r="44" ht="14.5" customHeight="1">
       <c r="A44" s="1" t="n"/>
-      <c r="B44" s="115" t="n"/>
+      <c r="B44" s="122" t="n"/>
+      <c r="C44" s="123" t="n"/>
+      <c r="D44" s="123" t="n"/>
+      <c r="E44" s="123" t="n"/>
+      <c r="F44" s="123" t="n"/>
+      <c r="G44" s="123" t="n"/>
+      <c r="H44" s="123" t="n"/>
+      <c r="I44" s="123" t="n"/>
+      <c r="J44" s="123" t="n"/>
+      <c r="K44" s="123" t="n"/>
+      <c r="L44" s="123" t="n"/>
+      <c r="M44" s="123" t="n"/>
+      <c r="N44" s="123" t="n"/>
+      <c r="O44" s="123" t="n"/>
+      <c r="P44" s="123" t="n"/>
+      <c r="Q44" s="123" t="n"/>
+      <c r="R44" s="123" t="n"/>
+      <c r="S44" s="123" t="n"/>
+      <c r="T44" s="123" t="n"/>
+      <c r="U44" s="123" t="n"/>
+      <c r="V44" s="123" t="n"/>
+      <c r="W44" s="123" t="n"/>
+      <c r="X44" s="123" t="n"/>
+      <c r="Y44" s="123" t="n"/>
+      <c r="Z44" s="123" t="n"/>
+      <c r="AA44" s="124" t="n"/>
     </row>
     <row r="45" ht="14.5" customHeight="1">
       <c r="A45" s="1" t="n"/>
-      <c r="B45" s="115" t="n"/>
+      <c r="B45" s="122" t="n"/>
+      <c r="C45" s="123" t="n"/>
+      <c r="D45" s="123" t="n"/>
+      <c r="E45" s="123" t="n"/>
+      <c r="F45" s="123" t="n"/>
+      <c r="G45" s="123" t="n"/>
+      <c r="H45" s="123" t="n"/>
+      <c r="I45" s="123" t="n"/>
+      <c r="J45" s="123" t="n"/>
+      <c r="K45" s="123" t="n"/>
+      <c r="L45" s="123" t="n"/>
+      <c r="M45" s="123" t="n"/>
+      <c r="N45" s="123" t="n"/>
+      <c r="O45" s="123" t="n"/>
+      <c r="P45" s="123" t="n"/>
+      <c r="Q45" s="123" t="n"/>
+      <c r="R45" s="123" t="n"/>
+      <c r="S45" s="123" t="n"/>
+      <c r="T45" s="123" t="n"/>
+      <c r="U45" s="123" t="n"/>
+      <c r="V45" s="123" t="n"/>
+      <c r="W45" s="123" t="n"/>
+      <c r="X45" s="123" t="n"/>
+      <c r="Y45" s="123" t="n"/>
+      <c r="Z45" s="123" t="n"/>
+      <c r="AA45" s="124" t="n"/>
     </row>
     <row r="46" ht="14.5" customHeight="1">
       <c r="A46" s="1" t="n"/>
-      <c r="B46" s="115" t="n"/>
+      <c r="B46" s="122" t="n"/>
+      <c r="C46" s="123" t="n"/>
+      <c r="D46" s="123" t="n"/>
+      <c r="E46" s="123" t="n"/>
+      <c r="F46" s="123" t="n"/>
+      <c r="G46" s="123" t="n"/>
+      <c r="H46" s="123" t="n"/>
+      <c r="I46" s="123" t="n"/>
+      <c r="J46" s="123" t="n"/>
+      <c r="K46" s="123" t="n"/>
+      <c r="L46" s="123" t="n"/>
+      <c r="M46" s="123" t="n"/>
+      <c r="N46" s="123" t="n"/>
+      <c r="O46" s="123" t="n"/>
+      <c r="P46" s="123" t="n"/>
+      <c r="Q46" s="123" t="n"/>
+      <c r="R46" s="123" t="n"/>
+      <c r="S46" s="123" t="n"/>
+      <c r="T46" s="123" t="n"/>
+      <c r="U46" s="123" t="n"/>
+      <c r="V46" s="123" t="n"/>
+      <c r="W46" s="123" t="n"/>
+      <c r="X46" s="123" t="n"/>
+      <c r="Y46" s="123" t="n"/>
+      <c r="Z46" s="123" t="n"/>
+      <c r="AA46" s="124" t="n"/>
     </row>
     <row r="47" ht="14.5" customHeight="1">
       <c r="A47" s="1" t="n"/>
-      <c r="B47" s="115" t="n"/>
+      <c r="B47" s="122" t="n"/>
+      <c r="C47" s="123" t="n"/>
+      <c r="D47" s="123" t="n"/>
+      <c r="E47" s="123" t="n"/>
+      <c r="F47" s="123" t="n"/>
+      <c r="G47" s="123" t="n"/>
+      <c r="H47" s="123" t="n"/>
+      <c r="I47" s="123" t="n"/>
+      <c r="J47" s="123" t="n"/>
+      <c r="K47" s="123" t="n"/>
+      <c r="L47" s="123" t="n"/>
+      <c r="M47" s="123" t="n"/>
+      <c r="N47" s="123" t="n"/>
+      <c r="O47" s="123" t="n"/>
+      <c r="P47" s="123" t="n"/>
+      <c r="Q47" s="123" t="n"/>
+      <c r="R47" s="123" t="n"/>
+      <c r="S47" s="123" t="n"/>
+      <c r="T47" s="123" t="n"/>
+      <c r="U47" s="123" t="n"/>
+      <c r="V47" s="123" t="n"/>
+      <c r="W47" s="123" t="n"/>
+      <c r="X47" s="123" t="n"/>
+      <c r="Y47" s="123" t="n"/>
+      <c r="Z47" s="123" t="n"/>
+      <c r="AA47" s="124" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="1" t="n"/>
@@ -2171,56 +2723,206 @@
     </row>
     <row r="49" ht="14.5" customHeight="1">
       <c r="A49" s="30" t="n"/>
-      <c r="B49" s="119" t="n"/>
-      <c r="C49" s="105" t="n"/>
-      <c r="D49" s="105" t="n"/>
-      <c r="E49" s="105" t="n"/>
-      <c r="F49" s="105" t="n"/>
-      <c r="G49" s="105" t="n"/>
-      <c r="H49" s="105" t="n"/>
-      <c r="I49" s="105" t="n"/>
-      <c r="J49" s="105" t="n"/>
-      <c r="K49" s="105" t="n"/>
-      <c r="L49" s="105" t="n"/>
-      <c r="M49" s="105" t="n"/>
-      <c r="N49" s="105" t="n"/>
-      <c r="O49" s="105" t="n"/>
-      <c r="P49" s="105" t="n"/>
-      <c r="Q49" s="105" t="n"/>
-      <c r="R49" s="105" t="n"/>
-      <c r="S49" s="105" t="n"/>
-      <c r="T49" s="105" t="n"/>
-      <c r="U49" s="105" t="n"/>
-      <c r="V49" s="105" t="n"/>
-      <c r="W49" s="105" t="n"/>
-      <c r="X49" s="105" t="n"/>
-      <c r="Y49" s="105" t="n"/>
-      <c r="Z49" s="105" t="n"/>
-      <c r="AA49" s="106" t="n"/>
+      <c r="B49" s="122" t="n"/>
+      <c r="C49" s="123" t="n"/>
+      <c r="D49" s="123" t="n"/>
+      <c r="E49" s="123" t="n"/>
+      <c r="F49" s="123" t="n"/>
+      <c r="G49" s="123" t="n"/>
+      <c r="H49" s="123" t="n"/>
+      <c r="I49" s="123" t="n"/>
+      <c r="J49" s="123" t="n"/>
+      <c r="K49" s="123" t="n"/>
+      <c r="L49" s="123" t="n"/>
+      <c r="M49" s="123" t="n"/>
+      <c r="N49" s="123" t="n"/>
+      <c r="O49" s="123" t="n"/>
+      <c r="P49" s="123" t="n"/>
+      <c r="Q49" s="123" t="n"/>
+      <c r="R49" s="123" t="n"/>
+      <c r="S49" s="123" t="n"/>
+      <c r="T49" s="123" t="n"/>
+      <c r="U49" s="123" t="n"/>
+      <c r="V49" s="123" t="n"/>
+      <c r="W49" s="123" t="n"/>
+      <c r="X49" s="123" t="n"/>
+      <c r="Y49" s="123" t="n"/>
+      <c r="Z49" s="123" t="n"/>
+      <c r="AA49" s="124" t="n"/>
     </row>
     <row r="50" ht="14.5" customHeight="1">
       <c r="A50" s="30" t="n"/>
-      <c r="B50" s="119" t="n"/>
+      <c r="B50" s="122" t="n"/>
+      <c r="C50" s="123" t="n"/>
+      <c r="D50" s="123" t="n"/>
+      <c r="E50" s="123" t="n"/>
+      <c r="F50" s="123" t="n"/>
+      <c r="G50" s="123" t="n"/>
+      <c r="H50" s="123" t="n"/>
+      <c r="I50" s="123" t="n"/>
+      <c r="J50" s="123" t="n"/>
+      <c r="K50" s="123" t="n"/>
+      <c r="L50" s="123" t="n"/>
+      <c r="M50" s="123" t="n"/>
+      <c r="N50" s="123" t="n"/>
+      <c r="O50" s="123" t="n"/>
+      <c r="P50" s="123" t="n"/>
+      <c r="Q50" s="123" t="n"/>
+      <c r="R50" s="123" t="n"/>
+      <c r="S50" s="123" t="n"/>
+      <c r="T50" s="123" t="n"/>
+      <c r="U50" s="123" t="n"/>
+      <c r="V50" s="123" t="n"/>
+      <c r="W50" s="123" t="n"/>
+      <c r="X50" s="123" t="n"/>
+      <c r="Y50" s="123" t="n"/>
+      <c r="Z50" s="123" t="n"/>
+      <c r="AA50" s="124" t="n"/>
     </row>
     <row r="51" ht="14.5" customHeight="1">
       <c r="A51" s="30" t="n"/>
-      <c r="B51" s="119" t="n"/>
+      <c r="B51" s="122" t="n"/>
+      <c r="C51" s="123" t="n"/>
+      <c r="D51" s="123" t="n"/>
+      <c r="E51" s="123" t="n"/>
+      <c r="F51" s="123" t="n"/>
+      <c r="G51" s="123" t="n"/>
+      <c r="H51" s="123" t="n"/>
+      <c r="I51" s="123" t="n"/>
+      <c r="J51" s="123" t="n"/>
+      <c r="K51" s="123" t="n"/>
+      <c r="L51" s="123" t="n"/>
+      <c r="M51" s="123" t="n"/>
+      <c r="N51" s="123" t="n"/>
+      <c r="O51" s="123" t="n"/>
+      <c r="P51" s="123" t="n"/>
+      <c r="Q51" s="123" t="n"/>
+      <c r="R51" s="123" t="n"/>
+      <c r="S51" s="123" t="n"/>
+      <c r="T51" s="123" t="n"/>
+      <c r="U51" s="123" t="n"/>
+      <c r="V51" s="123" t="n"/>
+      <c r="W51" s="123" t="n"/>
+      <c r="X51" s="123" t="n"/>
+      <c r="Y51" s="123" t="n"/>
+      <c r="Z51" s="123" t="n"/>
+      <c r="AA51" s="124" t="n"/>
     </row>
     <row r="52" ht="14.5" customHeight="1">
       <c r="A52" s="30" t="n"/>
-      <c r="B52" s="119" t="n"/>
+      <c r="B52" s="122" t="n"/>
+      <c r="C52" s="123" t="n"/>
+      <c r="D52" s="123" t="n"/>
+      <c r="E52" s="123" t="n"/>
+      <c r="F52" s="123" t="n"/>
+      <c r="G52" s="123" t="n"/>
+      <c r="H52" s="123" t="n"/>
+      <c r="I52" s="123" t="n"/>
+      <c r="J52" s="123" t="n"/>
+      <c r="K52" s="123" t="n"/>
+      <c r="L52" s="123" t="n"/>
+      <c r="M52" s="123" t="n"/>
+      <c r="N52" s="123" t="n"/>
+      <c r="O52" s="123" t="n"/>
+      <c r="P52" s="123" t="n"/>
+      <c r="Q52" s="123" t="n"/>
+      <c r="R52" s="123" t="n"/>
+      <c r="S52" s="123" t="n"/>
+      <c r="T52" s="123" t="n"/>
+      <c r="U52" s="123" t="n"/>
+      <c r="V52" s="123" t="n"/>
+      <c r="W52" s="123" t="n"/>
+      <c r="X52" s="123" t="n"/>
+      <c r="Y52" s="123" t="n"/>
+      <c r="Z52" s="123" t="n"/>
+      <c r="AA52" s="124" t="n"/>
     </row>
     <row r="53" ht="14.5" customHeight="1">
       <c r="A53" s="30" t="n"/>
-      <c r="B53" s="119" t="n"/>
+      <c r="B53" s="122" t="n"/>
+      <c r="C53" s="123" t="n"/>
+      <c r="D53" s="123" t="n"/>
+      <c r="E53" s="123" t="n"/>
+      <c r="F53" s="123" t="n"/>
+      <c r="G53" s="123" t="n"/>
+      <c r="H53" s="123" t="n"/>
+      <c r="I53" s="123" t="n"/>
+      <c r="J53" s="123" t="n"/>
+      <c r="K53" s="123" t="n"/>
+      <c r="L53" s="123" t="n"/>
+      <c r="M53" s="123" t="n"/>
+      <c r="N53" s="123" t="n"/>
+      <c r="O53" s="123" t="n"/>
+      <c r="P53" s="123" t="n"/>
+      <c r="Q53" s="123" t="n"/>
+      <c r="R53" s="123" t="n"/>
+      <c r="S53" s="123" t="n"/>
+      <c r="T53" s="123" t="n"/>
+      <c r="U53" s="123" t="n"/>
+      <c r="V53" s="123" t="n"/>
+      <c r="W53" s="123" t="n"/>
+      <c r="X53" s="123" t="n"/>
+      <c r="Y53" s="123" t="n"/>
+      <c r="Z53" s="123" t="n"/>
+      <c r="AA53" s="124" t="n"/>
     </row>
     <row r="54" ht="14.5" customHeight="1">
       <c r="A54" s="30" t="n"/>
-      <c r="B54" s="119" t="n"/>
+      <c r="B54" s="122" t="n"/>
+      <c r="C54" s="123" t="n"/>
+      <c r="D54" s="123" t="n"/>
+      <c r="E54" s="123" t="n"/>
+      <c r="F54" s="123" t="n"/>
+      <c r="G54" s="123" t="n"/>
+      <c r="H54" s="123" t="n"/>
+      <c r="I54" s="123" t="n"/>
+      <c r="J54" s="123" t="n"/>
+      <c r="K54" s="123" t="n"/>
+      <c r="L54" s="123" t="n"/>
+      <c r="M54" s="123" t="n"/>
+      <c r="N54" s="123" t="n"/>
+      <c r="O54" s="123" t="n"/>
+      <c r="P54" s="123" t="n"/>
+      <c r="Q54" s="123" t="n"/>
+      <c r="R54" s="123" t="n"/>
+      <c r="S54" s="123" t="n"/>
+      <c r="T54" s="123" t="n"/>
+      <c r="U54" s="123" t="n"/>
+      <c r="V54" s="123" t="n"/>
+      <c r="W54" s="123" t="n"/>
+      <c r="X54" s="123" t="n"/>
+      <c r="Y54" s="123" t="n"/>
+      <c r="Z54" s="123" t="n"/>
+      <c r="AA54" s="124" t="n"/>
     </row>
     <row r="55" ht="14.5" customHeight="1">
       <c r="A55" s="30" t="n"/>
-      <c r="B55" s="119" t="n"/>
+      <c r="B55" s="122" t="n"/>
+      <c r="C55" s="123" t="n"/>
+      <c r="D55" s="123" t="n"/>
+      <c r="E55" s="123" t="n"/>
+      <c r="F55" s="123" t="n"/>
+      <c r="G55" s="123" t="n"/>
+      <c r="H55" s="123" t="n"/>
+      <c r="I55" s="123" t="n"/>
+      <c r="J55" s="123" t="n"/>
+      <c r="K55" s="123" t="n"/>
+      <c r="L55" s="123" t="n"/>
+      <c r="M55" s="123" t="n"/>
+      <c r="N55" s="123" t="n"/>
+      <c r="O55" s="123" t="n"/>
+      <c r="P55" s="123" t="n"/>
+      <c r="Q55" s="123" t="n"/>
+      <c r="R55" s="123" t="n"/>
+      <c r="S55" s="123" t="n"/>
+      <c r="T55" s="123" t="n"/>
+      <c r="U55" s="123" t="n"/>
+      <c r="V55" s="123" t="n"/>
+      <c r="W55" s="123" t="n"/>
+      <c r="X55" s="123" t="n"/>
+      <c r="Y55" s="123" t="n"/>
+      <c r="Z55" s="123" t="n"/>
+      <c r="AA55" s="124" t="n"/>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="1" t="n"/>
@@ -29607,9 +30309,9 @@
     <mergeCell ref="B50:AA50"/>
     <mergeCell ref="B14:AA15"/>
     <mergeCell ref="B26:AA26"/>
+    <mergeCell ref="B41:AA41"/>
+    <mergeCell ref="H19:Z19"/>
     <mergeCell ref="B33:AA33"/>
-    <mergeCell ref="H19:Z19"/>
-    <mergeCell ref="B41:AA41"/>
     <mergeCell ref="B17:G17"/>
     <mergeCell ref="B4:AA4"/>
     <mergeCell ref="B35:AA35"/>

--- a/static/templates/tec02-A_template.xlsx
+++ b/static/templates/tec02-A_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\diseño-afk\static\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17826A5A-FD32-4DF9-861B-ABE0C2EF2E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33338C00-D7BC-4F50-86CF-DF14F583533A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2737,14 +2737,14 @@
     <row r="59" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
       <c r="B59" s="66"/>
-      <c r="C59" s="41"/>
-      <c r="D59" s="41"/>
-      <c r="E59" s="41"/>
-      <c r="F59" s="41"/>
-      <c r="G59" s="41"/>
-      <c r="H59" s="41"/>
-      <c r="I59" s="67"/>
-      <c r="J59" s="67"/>
+      <c r="C59" s="66"/>
+      <c r="D59" s="66"/>
+      <c r="E59" s="66"/>
+      <c r="F59" s="66"/>
+      <c r="G59" s="66"/>
+      <c r="H59" s="66"/>
+      <c r="I59" s="66"/>
+      <c r="J59" s="66"/>
       <c r="K59" s="68"/>
       <c r="L59" s="41"/>
       <c r="M59" s="41"/>
@@ -30062,7 +30062,7 @@
     <mergeCell ref="B49:AA49"/>
     <mergeCell ref="K59:Q59"/>
     <mergeCell ref="B55:AA55"/>
-    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B59:J59"/>
     <mergeCell ref="B42:AA42"/>
     <mergeCell ref="B23:AA23"/>
     <mergeCell ref="H10:Z10"/>

--- a/static/templates/tec02-A_template.xlsx
+++ b/static/templates/tec02-A_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\diseño-afk\static\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33338C00-D7BC-4F50-86CF-DF14F583533A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77373863-096B-4D07-99B7-A699D3FEDC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,7 +126,7 @@
     <t>1) El CV debe señalar en forma ordenada y cronológica, los proyectos en que ha participado, su cargo en éstos, y las características relevantes del proyecto: Plazo, Monto, Cantidades de obra, fechas, mandante, descripción general.</t>
   </si>
   <si>
-    <t>Nombre y Apellido, Fecha y Firma</t>
+    <t>Nombre, Fecha y Firma del Profesional</t>
   </si>
 </sst>
 </file>

--- a/static/templates/tec02-A_template.xlsx
+++ b/static/templates/tec02-A_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\diseño-afk\static\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77373863-096B-4D07-99B7-A699D3FEDC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F344B3-37F3-4148-A9F7-124F093272C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -578,7 +578,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -693,50 +693,38 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -747,14 +735,27 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -813,7 +814,283 @@
     </xdr:pic>
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>271939</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>64597</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>272299</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>64957</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="5" name="Ink 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10EFD980-1260-412C-BC68-193E489F545B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2475000" y="10056128"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="5" name="Ink 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10EFD980-1260-412C-BC68-193E489F545B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2468880" y="10050008"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>640</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>50160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1000</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>50520</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="6" name="Ink 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F48425A-B853-7780-9A94-2B770AEE406B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="4674240" y="14172560"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="6" name="Ink 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F48425A-B853-7780-9A94-2B770AEE406B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4668120" y="14166440"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>560</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>153040</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>1280</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="8" name="Ink 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40844642-0509-7425-329D-C4C68F6A777B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="1143000" y="11278160"/>
+            <a:ext cx="8560440" cy="720"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="8" name="Ink 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40844642-0509-7425-329D-C4C68F6A777B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1136755" y="11265920"/>
+              <a:ext cx="8572931" cy="25200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-05-02T04:22:14.385"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 0 24575,'0'0'-8191</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink2.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-05-02T04:23:52.445"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 24575,'0'0'-8191</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink3.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-05-02T04:24:07.281"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 22670,'23301'0'0</inkml:trace>
+</inkml:ink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1084,125 +1361,125 @@
     </row>
     <row r="3" spans="1:27" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="56"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="56"/>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="56"/>
-      <c r="S3" s="56"/>
-      <c r="T3" s="56"/>
-      <c r="U3" s="56"/>
-      <c r="V3" s="56"/>
-      <c r="W3" s="56"/>
-      <c r="X3" s="56"/>
-      <c r="Y3" s="56"/>
-      <c r="Z3" s="56"/>
-      <c r="AA3" s="56"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="41"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="41"/>
+      <c r="U3" s="41"/>
+      <c r="V3" s="41"/>
+      <c r="W3" s="41"/>
+      <c r="X3" s="41"/>
+      <c r="Y3" s="41"/>
+      <c r="Z3" s="41"/>
+      <c r="AA3" s="41"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="56"/>
-      <c r="Q4" s="56"/>
-      <c r="R4" s="56"/>
-      <c r="S4" s="56"/>
-      <c r="T4" s="56"/>
-      <c r="U4" s="56"/>
-      <c r="V4" s="56"/>
-      <c r="W4" s="56"/>
-      <c r="X4" s="56"/>
-      <c r="Y4" s="56"/>
-      <c r="Z4" s="56"/>
-      <c r="AA4" s="56"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="41"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="41"/>
+      <c r="U4" s="41"/>
+      <c r="V4" s="41"/>
+      <c r="W4" s="41"/>
+      <c r="X4" s="41"/>
+      <c r="Y4" s="41"/>
+      <c r="Z4" s="41"/>
+      <c r="AA4" s="41"/>
     </row>
     <row r="5" spans="1:27" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
-      <c r="B5" s="65" t="s">
+      <c r="B5" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
-      <c r="K5" s="56"/>
-      <c r="L5" s="56"/>
-      <c r="M5" s="56"/>
-      <c r="N5" s="56"/>
-      <c r="O5" s="56"/>
-      <c r="P5" s="56"/>
-      <c r="Q5" s="56"/>
-      <c r="R5" s="56"/>
-      <c r="S5" s="56"/>
-      <c r="T5" s="56"/>
-      <c r="U5" s="56"/>
-      <c r="V5" s="56"/>
-      <c r="W5" s="56"/>
-      <c r="X5" s="56"/>
-      <c r="Y5" s="56"/>
-      <c r="Z5" s="56"/>
-      <c r="AA5" s="56"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="41"/>
+      <c r="R5" s="41"/>
+      <c r="S5" s="41"/>
+      <c r="T5" s="41"/>
+      <c r="U5" s="41"/>
+      <c r="V5" s="41"/>
+      <c r="W5" s="41"/>
+      <c r="X5" s="41"/>
+      <c r="Y5" s="41"/>
+      <c r="Z5" s="41"/>
+      <c r="AA5" s="41"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
-      <c r="B6" s="63" t="s">
+      <c r="B6" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
-      <c r="M6" s="56"/>
-      <c r="N6" s="56"/>
-      <c r="O6" s="56"/>
-      <c r="P6" s="56"/>
-      <c r="Q6" s="56"/>
-      <c r="R6" s="56"/>
-      <c r="S6" s="56"/>
-      <c r="T6" s="56"/>
-      <c r="U6" s="56"/>
-      <c r="V6" s="56"/>
-      <c r="W6" s="56"/>
-      <c r="X6" s="56"/>
-      <c r="Y6" s="56"/>
-      <c r="Z6" s="56"/>
-      <c r="AA6" s="56"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="41"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="41"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="41"/>
+      <c r="V6" s="41"/>
+      <c r="W6" s="41"/>
+      <c r="X6" s="41"/>
+      <c r="Y6" s="41"/>
+      <c r="Z6" s="41"/>
+      <c r="AA6" s="41"/>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2"/>
@@ -1301,25 +1578,25 @@
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
-      <c r="H10" s="58"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="53"/>
-      <c r="N10" s="53"/>
-      <c r="O10" s="53"/>
-      <c r="P10" s="53"/>
-      <c r="Q10" s="53"/>
-      <c r="R10" s="53"/>
-      <c r="S10" s="53"/>
-      <c r="T10" s="53"/>
-      <c r="U10" s="53"/>
-      <c r="V10" s="53"/>
-      <c r="W10" s="53"/>
-      <c r="X10" s="53"/>
-      <c r="Y10" s="53"/>
-      <c r="Z10" s="54"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
+      <c r="K10" s="52"/>
+      <c r="L10" s="52"/>
+      <c r="M10" s="52"/>
+      <c r="N10" s="52"/>
+      <c r="O10" s="52"/>
+      <c r="P10" s="52"/>
+      <c r="Q10" s="52"/>
+      <c r="R10" s="52"/>
+      <c r="S10" s="52"/>
+      <c r="T10" s="52"/>
+      <c r="U10" s="52"/>
+      <c r="V10" s="52"/>
+      <c r="W10" s="52"/>
+      <c r="X10" s="52"/>
+      <c r="Y10" s="52"/>
+      <c r="Z10" s="53"/>
       <c r="AA10" s="11"/>
     </row>
     <row r="11" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1361,27 +1638,27 @@
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="53"/>
-      <c r="K12" s="53"/>
-      <c r="L12" s="53"/>
-      <c r="M12" s="53"/>
-      <c r="N12" s="53"/>
-      <c r="O12" s="53"/>
-      <c r="P12" s="53"/>
-      <c r="Q12" s="53"/>
-      <c r="R12" s="53"/>
-      <c r="S12" s="53"/>
-      <c r="T12" s="54"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="52"/>
+      <c r="K12" s="52"/>
+      <c r="L12" s="52"/>
+      <c r="M12" s="52"/>
+      <c r="N12" s="52"/>
+      <c r="O12" s="52"/>
+      <c r="P12" s="52"/>
+      <c r="Q12" s="52"/>
+      <c r="R12" s="52"/>
+      <c r="S12" s="52"/>
+      <c r="T12" s="53"/>
       <c r="U12" s="13"/>
       <c r="V12" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="W12" s="64"/>
-      <c r="X12" s="53"/>
-      <c r="Y12" s="53"/>
-      <c r="Z12" s="54"/>
+      <c r="W12" s="58"/>
+      <c r="X12" s="52"/>
+      <c r="Y12" s="52"/>
+      <c r="Z12" s="53"/>
       <c r="AA12" s="15"/>
     </row>
     <row r="13" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1415,63 +1692,63 @@
     </row>
     <row r="14" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="47"/>
-      <c r="L14" s="47"/>
-      <c r="M14" s="47"/>
-      <c r="N14" s="47"/>
-      <c r="O14" s="47"/>
-      <c r="P14" s="47"/>
-      <c r="Q14" s="47"/>
-      <c r="R14" s="47"/>
-      <c r="S14" s="47"/>
-      <c r="T14" s="47"/>
-      <c r="U14" s="47"/>
-      <c r="V14" s="47"/>
-      <c r="W14" s="47"/>
-      <c r="X14" s="47"/>
-      <c r="Y14" s="47"/>
-      <c r="Z14" s="47"/>
-      <c r="AA14" s="48"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="62"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="62"/>
+      <c r="M14" s="62"/>
+      <c r="N14" s="62"/>
+      <c r="O14" s="62"/>
+      <c r="P14" s="62"/>
+      <c r="Q14" s="62"/>
+      <c r="R14" s="62"/>
+      <c r="S14" s="62"/>
+      <c r="T14" s="62"/>
+      <c r="U14" s="62"/>
+      <c r="V14" s="62"/>
+      <c r="W14" s="62"/>
+      <c r="X14" s="62"/>
+      <c r="Y14" s="62"/>
+      <c r="Z14" s="62"/>
+      <c r="AA14" s="63"/>
     </row>
     <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
-      <c r="B15" s="49"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="50"/>
-      <c r="K15" s="50"/>
-      <c r="L15" s="50"/>
-      <c r="M15" s="50"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="50"/>
-      <c r="P15" s="50"/>
-      <c r="Q15" s="50"/>
-      <c r="R15" s="50"/>
-      <c r="S15" s="50"/>
-      <c r="T15" s="50"/>
-      <c r="U15" s="50"/>
-      <c r="V15" s="50"/>
-      <c r="W15" s="50"/>
-      <c r="X15" s="50"/>
-      <c r="Y15" s="50"/>
-      <c r="Z15" s="50"/>
-      <c r="AA15" s="51"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="49"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="49"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="49"/>
+      <c r="N15" s="49"/>
+      <c r="O15" s="49"/>
+      <c r="P15" s="49"/>
+      <c r="Q15" s="49"/>
+      <c r="R15" s="49"/>
+      <c r="S15" s="49"/>
+      <c r="T15" s="49"/>
+      <c r="U15" s="49"/>
+      <c r="V15" s="49"/>
+      <c r="W15" s="49"/>
+      <c r="X15" s="49"/>
+      <c r="Y15" s="49"/>
+      <c r="Z15" s="49"/>
+      <c r="AA15" s="50"/>
     </row>
     <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
@@ -1504,33 +1781,33 @@
     </row>
     <row r="17" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
-      <c r="B17" s="55" t="s">
+      <c r="B17" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="56"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="56"/>
-      <c r="G17" s="56"/>
-      <c r="H17" s="52"/>
-      <c r="I17" s="53"/>
-      <c r="J17" s="53"/>
-      <c r="K17" s="53"/>
-      <c r="L17" s="53"/>
-      <c r="M17" s="53"/>
-      <c r="N17" s="53"/>
-      <c r="O17" s="53"/>
-      <c r="P17" s="53"/>
-      <c r="Q17" s="53"/>
-      <c r="R17" s="53"/>
-      <c r="S17" s="53"/>
-      <c r="T17" s="53"/>
-      <c r="U17" s="53"/>
-      <c r="V17" s="53"/>
-      <c r="W17" s="53"/>
-      <c r="X17" s="53"/>
-      <c r="Y17" s="53"/>
-      <c r="Z17" s="54"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="52"/>
+      <c r="K17" s="52"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="52"/>
+      <c r="N17" s="52"/>
+      <c r="O17" s="52"/>
+      <c r="P17" s="52"/>
+      <c r="Q17" s="52"/>
+      <c r="R17" s="52"/>
+      <c r="S17" s="52"/>
+      <c r="T17" s="52"/>
+      <c r="U17" s="52"/>
+      <c r="V17" s="52"/>
+      <c r="W17" s="52"/>
+      <c r="X17" s="52"/>
+      <c r="Y17" s="52"/>
+      <c r="Z17" s="53"/>
       <c r="AA17" s="24"/>
     </row>
     <row r="18" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1564,33 +1841,33 @@
     </row>
     <row r="19" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
-      <c r="B19" s="55" t="s">
+      <c r="B19" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
-      <c r="H19" s="52"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="53"/>
-      <c r="K19" s="53"/>
-      <c r="L19" s="53"/>
-      <c r="M19" s="53"/>
-      <c r="N19" s="53"/>
-      <c r="O19" s="53"/>
-      <c r="P19" s="53"/>
-      <c r="Q19" s="53"/>
-      <c r="R19" s="53"/>
-      <c r="S19" s="53"/>
-      <c r="T19" s="53"/>
-      <c r="U19" s="53"/>
-      <c r="V19" s="53"/>
-      <c r="W19" s="53"/>
-      <c r="X19" s="53"/>
-      <c r="Y19" s="53"/>
-      <c r="Z19" s="54"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="52"/>
+      <c r="K19" s="52"/>
+      <c r="L19" s="52"/>
+      <c r="M19" s="52"/>
+      <c r="N19" s="52"/>
+      <c r="O19" s="52"/>
+      <c r="P19" s="52"/>
+      <c r="Q19" s="52"/>
+      <c r="R19" s="52"/>
+      <c r="S19" s="52"/>
+      <c r="T19" s="52"/>
+      <c r="U19" s="52"/>
+      <c r="V19" s="52"/>
+      <c r="W19" s="52"/>
+      <c r="X19" s="52"/>
+      <c r="Y19" s="52"/>
+      <c r="Z19" s="53"/>
       <c r="AA19" s="24"/>
     </row>
     <row r="20" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1624,33 +1901,33 @@
     </row>
     <row r="21" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
-      <c r="B21" s="55" t="s">
+      <c r="B21" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="53"/>
-      <c r="N21" s="53"/>
-      <c r="O21" s="53"/>
-      <c r="P21" s="53"/>
-      <c r="Q21" s="53"/>
-      <c r="R21" s="53"/>
-      <c r="S21" s="53"/>
-      <c r="T21" s="53"/>
-      <c r="U21" s="53"/>
-      <c r="V21" s="53"/>
-      <c r="W21" s="53"/>
-      <c r="X21" s="53"/>
-      <c r="Y21" s="53"/>
-      <c r="Z21" s="54"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="52"/>
+      <c r="K21" s="52"/>
+      <c r="L21" s="52"/>
+      <c r="M21" s="52"/>
+      <c r="N21" s="52"/>
+      <c r="O21" s="52"/>
+      <c r="P21" s="52"/>
+      <c r="Q21" s="52"/>
+      <c r="R21" s="52"/>
+      <c r="S21" s="52"/>
+      <c r="T21" s="52"/>
+      <c r="U21" s="52"/>
+      <c r="V21" s="52"/>
+      <c r="W21" s="52"/>
+      <c r="X21" s="52"/>
+      <c r="Y21" s="52"/>
+      <c r="Z21" s="53"/>
       <c r="AA21" s="24"/>
     </row>
     <row r="22" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1684,968 +1961,968 @@
     </row>
     <row r="23" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
-      <c r="B23" s="61" t="s">
+      <c r="B23" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="50"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="50"/>
-      <c r="H23" s="50"/>
-      <c r="I23" s="50"/>
-      <c r="J23" s="50"/>
-      <c r="K23" s="50"/>
-      <c r="L23" s="50"/>
-      <c r="M23" s="50"/>
-      <c r="N23" s="50"/>
-      <c r="O23" s="50"/>
-      <c r="P23" s="50"/>
-      <c r="Q23" s="50"/>
-      <c r="R23" s="50"/>
-      <c r="S23" s="50"/>
-      <c r="T23" s="50"/>
-      <c r="U23" s="50"/>
-      <c r="V23" s="50"/>
-      <c r="W23" s="50"/>
-      <c r="X23" s="50"/>
-      <c r="Y23" s="50"/>
-      <c r="Z23" s="50"/>
-      <c r="AA23" s="51"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="49"/>
+      <c r="J23" s="49"/>
+      <c r="K23" s="49"/>
+      <c r="L23" s="49"/>
+      <c r="M23" s="49"/>
+      <c r="N23" s="49"/>
+      <c r="O23" s="49"/>
+      <c r="P23" s="49"/>
+      <c r="Q23" s="49"/>
+      <c r="R23" s="49"/>
+      <c r="S23" s="49"/>
+      <c r="T23" s="49"/>
+      <c r="U23" s="49"/>
+      <c r="V23" s="49"/>
+      <c r="W23" s="49"/>
+      <c r="X23" s="49"/>
+      <c r="Y23" s="49"/>
+      <c r="Z23" s="49"/>
+      <c r="AA23" s="50"/>
     </row>
     <row r="24" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="41"/>
-      <c r="J24" s="41"/>
-      <c r="K24" s="41"/>
-      <c r="L24" s="41"/>
-      <c r="M24" s="41"/>
-      <c r="N24" s="41"/>
-      <c r="O24" s="41"/>
-      <c r="P24" s="41"/>
-      <c r="Q24" s="41"/>
-      <c r="R24" s="41"/>
-      <c r="S24" s="41"/>
-      <c r="T24" s="41"/>
-      <c r="U24" s="41"/>
-      <c r="V24" s="41"/>
-      <c r="W24" s="41"/>
-      <c r="X24" s="41"/>
-      <c r="Y24" s="41"/>
-      <c r="Z24" s="41"/>
-      <c r="AA24" s="42"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
+      <c r="L24" s="46"/>
+      <c r="M24" s="46"/>
+      <c r="N24" s="46"/>
+      <c r="O24" s="46"/>
+      <c r="P24" s="46"/>
+      <c r="Q24" s="46"/>
+      <c r="R24" s="46"/>
+      <c r="S24" s="46"/>
+      <c r="T24" s="46"/>
+      <c r="U24" s="46"/>
+      <c r="V24" s="46"/>
+      <c r="W24" s="46"/>
+      <c r="X24" s="46"/>
+      <c r="Y24" s="46"/>
+      <c r="Z24" s="46"/>
+      <c r="AA24" s="47"/>
     </row>
     <row r="25" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="41"/>
-      <c r="J25" s="41"/>
-      <c r="K25" s="41"/>
-      <c r="L25" s="41"/>
-      <c r="M25" s="41"/>
-      <c r="N25" s="41"/>
-      <c r="O25" s="41"/>
-      <c r="P25" s="41"/>
-      <c r="Q25" s="41"/>
-      <c r="R25" s="41"/>
-      <c r="S25" s="41"/>
-      <c r="T25" s="41"/>
-      <c r="U25" s="41"/>
-      <c r="V25" s="41"/>
-      <c r="W25" s="41"/>
-      <c r="X25" s="41"/>
-      <c r="Y25" s="41"/>
-      <c r="Z25" s="41"/>
-      <c r="AA25" s="42"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="46"/>
+      <c r="K25" s="46"/>
+      <c r="L25" s="46"/>
+      <c r="M25" s="46"/>
+      <c r="N25" s="46"/>
+      <c r="O25" s="46"/>
+      <c r="P25" s="46"/>
+      <c r="Q25" s="46"/>
+      <c r="R25" s="46"/>
+      <c r="S25" s="46"/>
+      <c r="T25" s="46"/>
+      <c r="U25" s="46"/>
+      <c r="V25" s="46"/>
+      <c r="W25" s="46"/>
+      <c r="X25" s="46"/>
+      <c r="Y25" s="46"/>
+      <c r="Z25" s="46"/>
+      <c r="AA25" s="47"/>
     </row>
     <row r="26" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="41"/>
-      <c r="J26" s="41"/>
-      <c r="K26" s="41"/>
-      <c r="L26" s="41"/>
-      <c r="M26" s="41"/>
-      <c r="N26" s="41"/>
-      <c r="O26" s="41"/>
-      <c r="P26" s="41"/>
-      <c r="Q26" s="41"/>
-      <c r="R26" s="41"/>
-      <c r="S26" s="41"/>
-      <c r="T26" s="41"/>
-      <c r="U26" s="41"/>
-      <c r="V26" s="41"/>
-      <c r="W26" s="41"/>
-      <c r="X26" s="41"/>
-      <c r="Y26" s="41"/>
-      <c r="Z26" s="41"/>
-      <c r="AA26" s="42"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="46"/>
+      <c r="K26" s="46"/>
+      <c r="L26" s="46"/>
+      <c r="M26" s="46"/>
+      <c r="N26" s="46"/>
+      <c r="O26" s="46"/>
+      <c r="P26" s="46"/>
+      <c r="Q26" s="46"/>
+      <c r="R26" s="46"/>
+      <c r="S26" s="46"/>
+      <c r="T26" s="46"/>
+      <c r="U26" s="46"/>
+      <c r="V26" s="46"/>
+      <c r="W26" s="46"/>
+      <c r="X26" s="46"/>
+      <c r="Y26" s="46"/>
+      <c r="Z26" s="46"/>
+      <c r="AA26" s="47"/>
     </row>
     <row r="27" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="41"/>
-      <c r="J27" s="41"/>
-      <c r="K27" s="41"/>
-      <c r="L27" s="41"/>
-      <c r="M27" s="41"/>
-      <c r="N27" s="41"/>
-      <c r="O27" s="41"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="41"/>
-      <c r="S27" s="41"/>
-      <c r="T27" s="41"/>
-      <c r="U27" s="41"/>
-      <c r="V27" s="41"/>
-      <c r="W27" s="41"/>
-      <c r="X27" s="41"/>
-      <c r="Y27" s="41"/>
-      <c r="Z27" s="41"/>
-      <c r="AA27" s="42"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="46"/>
+      <c r="J27" s="46"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="46"/>
+      <c r="M27" s="46"/>
+      <c r="N27" s="46"/>
+      <c r="O27" s="46"/>
+      <c r="P27" s="46"/>
+      <c r="Q27" s="46"/>
+      <c r="R27" s="46"/>
+      <c r="S27" s="46"/>
+      <c r="T27" s="46"/>
+      <c r="U27" s="46"/>
+      <c r="V27" s="46"/>
+      <c r="W27" s="46"/>
+      <c r="X27" s="46"/>
+      <c r="Y27" s="46"/>
+      <c r="Z27" s="46"/>
+      <c r="AA27" s="47"/>
     </row>
     <row r="28" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
-      <c r="B28" s="40"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="41"/>
-      <c r="K28" s="41"/>
-      <c r="L28" s="41"/>
-      <c r="M28" s="41"/>
-      <c r="N28" s="41"/>
-      <c r="O28" s="41"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="41"/>
-      <c r="S28" s="41"/>
-      <c r="T28" s="41"/>
-      <c r="U28" s="41"/>
-      <c r="V28" s="41"/>
-      <c r="W28" s="41"/>
-      <c r="X28" s="41"/>
-      <c r="Y28" s="41"/>
-      <c r="Z28" s="41"/>
-      <c r="AA28" s="42"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="46"/>
+      <c r="J28" s="46"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="46"/>
+      <c r="M28" s="46"/>
+      <c r="N28" s="46"/>
+      <c r="O28" s="46"/>
+      <c r="P28" s="46"/>
+      <c r="Q28" s="46"/>
+      <c r="R28" s="46"/>
+      <c r="S28" s="46"/>
+      <c r="T28" s="46"/>
+      <c r="U28" s="46"/>
+      <c r="V28" s="46"/>
+      <c r="W28" s="46"/>
+      <c r="X28" s="46"/>
+      <c r="Y28" s="46"/>
+      <c r="Z28" s="46"/>
+      <c r="AA28" s="47"/>
     </row>
     <row r="29" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
-      <c r="B29" s="40"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="41"/>
-      <c r="J29" s="41"/>
-      <c r="K29" s="41"/>
-      <c r="L29" s="41"/>
-      <c r="M29" s="41"/>
-      <c r="N29" s="41"/>
-      <c r="O29" s="41"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="41"/>
-      <c r="S29" s="41"/>
-      <c r="T29" s="41"/>
-      <c r="U29" s="41"/>
-      <c r="V29" s="41"/>
-      <c r="W29" s="41"/>
-      <c r="X29" s="41"/>
-      <c r="Y29" s="41"/>
-      <c r="Z29" s="41"/>
-      <c r="AA29" s="42"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="46"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="46"/>
+      <c r="J29" s="46"/>
+      <c r="K29" s="46"/>
+      <c r="L29" s="46"/>
+      <c r="M29" s="46"/>
+      <c r="N29" s="46"/>
+      <c r="O29" s="46"/>
+      <c r="P29" s="46"/>
+      <c r="Q29" s="46"/>
+      <c r="R29" s="46"/>
+      <c r="S29" s="46"/>
+      <c r="T29" s="46"/>
+      <c r="U29" s="46"/>
+      <c r="V29" s="46"/>
+      <c r="W29" s="46"/>
+      <c r="X29" s="46"/>
+      <c r="Y29" s="46"/>
+      <c r="Z29" s="46"/>
+      <c r="AA29" s="47"/>
     </row>
     <row r="30" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
-      <c r="B30" s="40"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="41"/>
-      <c r="J30" s="41"/>
-      <c r="K30" s="41"/>
-      <c r="L30" s="41"/>
-      <c r="M30" s="41"/>
-      <c r="N30" s="41"/>
-      <c r="O30" s="41"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="41"/>
-      <c r="S30" s="41"/>
-      <c r="T30" s="41"/>
-      <c r="U30" s="41"/>
-      <c r="V30" s="41"/>
-      <c r="W30" s="41"/>
-      <c r="X30" s="41"/>
-      <c r="Y30" s="41"/>
-      <c r="Z30" s="41"/>
-      <c r="AA30" s="42"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="46"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="46"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="46"/>
+      <c r="K30" s="46"/>
+      <c r="L30" s="46"/>
+      <c r="M30" s="46"/>
+      <c r="N30" s="46"/>
+      <c r="O30" s="46"/>
+      <c r="P30" s="46"/>
+      <c r="Q30" s="46"/>
+      <c r="R30" s="46"/>
+      <c r="S30" s="46"/>
+      <c r="T30" s="46"/>
+      <c r="U30" s="46"/>
+      <c r="V30" s="46"/>
+      <c r="W30" s="46"/>
+      <c r="X30" s="46"/>
+      <c r="Y30" s="46"/>
+      <c r="Z30" s="46"/>
+      <c r="AA30" s="47"/>
     </row>
     <row r="31" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
-      <c r="B31" s="40"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="41"/>
-      <c r="J31" s="41"/>
-      <c r="K31" s="41"/>
-      <c r="L31" s="41"/>
-      <c r="M31" s="41"/>
-      <c r="N31" s="41"/>
-      <c r="O31" s="41"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="41"/>
-      <c r="S31" s="41"/>
-      <c r="T31" s="41"/>
-      <c r="U31" s="41"/>
-      <c r="V31" s="41"/>
-      <c r="W31" s="41"/>
-      <c r="X31" s="41"/>
-      <c r="Y31" s="41"/>
-      <c r="Z31" s="41"/>
-      <c r="AA31" s="42"/>
+      <c r="B31" s="45"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="46"/>
+      <c r="I31" s="46"/>
+      <c r="J31" s="46"/>
+      <c r="K31" s="46"/>
+      <c r="L31" s="46"/>
+      <c r="M31" s="46"/>
+      <c r="N31" s="46"/>
+      <c r="O31" s="46"/>
+      <c r="P31" s="46"/>
+      <c r="Q31" s="46"/>
+      <c r="R31" s="46"/>
+      <c r="S31" s="46"/>
+      <c r="T31" s="46"/>
+      <c r="U31" s="46"/>
+      <c r="V31" s="46"/>
+      <c r="W31" s="46"/>
+      <c r="X31" s="46"/>
+      <c r="Y31" s="46"/>
+      <c r="Z31" s="46"/>
+      <c r="AA31" s="47"/>
     </row>
     <row r="32" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
-      <c r="B32" s="43" t="s">
+      <c r="B32" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="44"/>
-      <c r="D32" s="44"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="44"/>
-      <c r="G32" s="44"/>
-      <c r="H32" s="44"/>
-      <c r="I32" s="44"/>
-      <c r="J32" s="44"/>
-      <c r="K32" s="44"/>
-      <c r="L32" s="44"/>
-      <c r="M32" s="44"/>
-      <c r="N32" s="44"/>
-      <c r="O32" s="44"/>
-      <c r="P32" s="44"/>
-      <c r="Q32" s="44"/>
-      <c r="R32" s="44"/>
-      <c r="S32" s="44"/>
-      <c r="T32" s="44"/>
-      <c r="U32" s="44"/>
-      <c r="V32" s="44"/>
-      <c r="W32" s="44"/>
-      <c r="X32" s="44"/>
-      <c r="Y32" s="44"/>
-      <c r="Z32" s="44"/>
-      <c r="AA32" s="45"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="43"/>
+      <c r="L32" s="43"/>
+      <c r="M32" s="43"/>
+      <c r="N32" s="43"/>
+      <c r="O32" s="43"/>
+      <c r="P32" s="43"/>
+      <c r="Q32" s="43"/>
+      <c r="R32" s="43"/>
+      <c r="S32" s="43"/>
+      <c r="T32" s="43"/>
+      <c r="U32" s="43"/>
+      <c r="V32" s="43"/>
+      <c r="W32" s="43"/>
+      <c r="X32" s="43"/>
+      <c r="Y32" s="43"/>
+      <c r="Z32" s="43"/>
+      <c r="AA32" s="44"/>
     </row>
     <row r="33" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
-      <c r="B33" s="40"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="41"/>
-      <c r="J33" s="41"/>
-      <c r="K33" s="41"/>
-      <c r="L33" s="41"/>
-      <c r="M33" s="41"/>
-      <c r="N33" s="41"/>
-      <c r="O33" s="41"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="41"/>
-      <c r="S33" s="41"/>
-      <c r="T33" s="41"/>
-      <c r="U33" s="41"/>
-      <c r="V33" s="41"/>
-      <c r="W33" s="41"/>
-      <c r="X33" s="41"/>
-      <c r="Y33" s="41"/>
-      <c r="Z33" s="41"/>
-      <c r="AA33" s="42"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="46"/>
+      <c r="I33" s="46"/>
+      <c r="J33" s="46"/>
+      <c r="K33" s="46"/>
+      <c r="L33" s="46"/>
+      <c r="M33" s="46"/>
+      <c r="N33" s="46"/>
+      <c r="O33" s="46"/>
+      <c r="P33" s="46"/>
+      <c r="Q33" s="46"/>
+      <c r="R33" s="46"/>
+      <c r="S33" s="46"/>
+      <c r="T33" s="46"/>
+      <c r="U33" s="46"/>
+      <c r="V33" s="46"/>
+      <c r="W33" s="46"/>
+      <c r="X33" s="46"/>
+      <c r="Y33" s="46"/>
+      <c r="Z33" s="46"/>
+      <c r="AA33" s="47"/>
     </row>
     <row r="34" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
-      <c r="B34" s="40"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="41"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="41"/>
-      <c r="I34" s="41"/>
-      <c r="J34" s="41"/>
-      <c r="K34" s="41"/>
-      <c r="L34" s="41"/>
-      <c r="M34" s="41"/>
-      <c r="N34" s="41"/>
-      <c r="O34" s="41"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="41"/>
-      <c r="S34" s="41"/>
-      <c r="T34" s="41"/>
-      <c r="U34" s="41"/>
-      <c r="V34" s="41"/>
-      <c r="W34" s="41"/>
-      <c r="X34" s="41"/>
-      <c r="Y34" s="41"/>
-      <c r="Z34" s="41"/>
-      <c r="AA34" s="42"/>
+      <c r="B34" s="45"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="46"/>
+      <c r="I34" s="46"/>
+      <c r="J34" s="46"/>
+      <c r="K34" s="46"/>
+      <c r="L34" s="46"/>
+      <c r="M34" s="46"/>
+      <c r="N34" s="46"/>
+      <c r="O34" s="46"/>
+      <c r="P34" s="46"/>
+      <c r="Q34" s="46"/>
+      <c r="R34" s="46"/>
+      <c r="S34" s="46"/>
+      <c r="T34" s="46"/>
+      <c r="U34" s="46"/>
+      <c r="V34" s="46"/>
+      <c r="W34" s="46"/>
+      <c r="X34" s="46"/>
+      <c r="Y34" s="46"/>
+      <c r="Z34" s="46"/>
+      <c r="AA34" s="47"/>
     </row>
     <row r="35" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
-      <c r="B35" s="40"/>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="41"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="41"/>
-      <c r="I35" s="41"/>
-      <c r="J35" s="41"/>
-      <c r="K35" s="41"/>
-      <c r="L35" s="41"/>
-      <c r="M35" s="41"/>
-      <c r="N35" s="41"/>
-      <c r="O35" s="41"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="41"/>
-      <c r="S35" s="41"/>
-      <c r="T35" s="41"/>
-      <c r="U35" s="41"/>
-      <c r="V35" s="41"/>
-      <c r="W35" s="41"/>
-      <c r="X35" s="41"/>
-      <c r="Y35" s="41"/>
-      <c r="Z35" s="41"/>
-      <c r="AA35" s="42"/>
+      <c r="B35" s="45"/>
+      <c r="C35" s="46"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="46"/>
+      <c r="F35" s="46"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="46"/>
+      <c r="I35" s="46"/>
+      <c r="J35" s="46"/>
+      <c r="K35" s="46"/>
+      <c r="L35" s="46"/>
+      <c r="M35" s="46"/>
+      <c r="N35" s="46"/>
+      <c r="O35" s="46"/>
+      <c r="P35" s="46"/>
+      <c r="Q35" s="46"/>
+      <c r="R35" s="46"/>
+      <c r="S35" s="46"/>
+      <c r="T35" s="46"/>
+      <c r="U35" s="46"/>
+      <c r="V35" s="46"/>
+      <c r="W35" s="46"/>
+      <c r="X35" s="46"/>
+      <c r="Y35" s="46"/>
+      <c r="Z35" s="46"/>
+      <c r="AA35" s="47"/>
     </row>
     <row r="36" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
-      <c r="B36" s="40"/>
-      <c r="C36" s="41"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="41"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="41"/>
-      <c r="I36" s="41"/>
-      <c r="J36" s="41"/>
-      <c r="K36" s="41"/>
-      <c r="L36" s="41"/>
-      <c r="M36" s="41"/>
-      <c r="N36" s="41"/>
-      <c r="O36" s="41"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="41"/>
-      <c r="S36" s="41"/>
-      <c r="T36" s="41"/>
-      <c r="U36" s="41"/>
-      <c r="V36" s="41"/>
-      <c r="W36" s="41"/>
-      <c r="X36" s="41"/>
-      <c r="Y36" s="41"/>
-      <c r="Z36" s="41"/>
-      <c r="AA36" s="42"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="46"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="46"/>
+      <c r="I36" s="46"/>
+      <c r="J36" s="46"/>
+      <c r="K36" s="46"/>
+      <c r="L36" s="46"/>
+      <c r="M36" s="46"/>
+      <c r="N36" s="46"/>
+      <c r="O36" s="46"/>
+      <c r="P36" s="46"/>
+      <c r="Q36" s="46"/>
+      <c r="R36" s="46"/>
+      <c r="S36" s="46"/>
+      <c r="T36" s="46"/>
+      <c r="U36" s="46"/>
+      <c r="V36" s="46"/>
+      <c r="W36" s="46"/>
+      <c r="X36" s="46"/>
+      <c r="Y36" s="46"/>
+      <c r="Z36" s="46"/>
+      <c r="AA36" s="47"/>
     </row>
     <row r="37" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
-      <c r="B37" s="40"/>
-      <c r="C37" s="41"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="41"/>
-      <c r="G37" s="41"/>
-      <c r="H37" s="41"/>
-      <c r="I37" s="41"/>
-      <c r="J37" s="41"/>
-      <c r="K37" s="41"/>
-      <c r="L37" s="41"/>
-      <c r="M37" s="41"/>
-      <c r="N37" s="41"/>
-      <c r="O37" s="41"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="41"/>
-      <c r="S37" s="41"/>
-      <c r="T37" s="41"/>
-      <c r="U37" s="41"/>
-      <c r="V37" s="41"/>
-      <c r="W37" s="41"/>
-      <c r="X37" s="41"/>
-      <c r="Y37" s="41"/>
-      <c r="Z37" s="41"/>
-      <c r="AA37" s="42"/>
+      <c r="B37" s="45"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="46"/>
+      <c r="H37" s="46"/>
+      <c r="I37" s="46"/>
+      <c r="J37" s="46"/>
+      <c r="K37" s="46"/>
+      <c r="L37" s="46"/>
+      <c r="M37" s="46"/>
+      <c r="N37" s="46"/>
+      <c r="O37" s="46"/>
+      <c r="P37" s="46"/>
+      <c r="Q37" s="46"/>
+      <c r="R37" s="46"/>
+      <c r="S37" s="46"/>
+      <c r="T37" s="46"/>
+      <c r="U37" s="46"/>
+      <c r="V37" s="46"/>
+      <c r="W37" s="46"/>
+      <c r="X37" s="46"/>
+      <c r="Y37" s="46"/>
+      <c r="Z37" s="46"/>
+      <c r="AA37" s="47"/>
     </row>
     <row r="38" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
-      <c r="B38" s="40"/>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="41"/>
-      <c r="I38" s="41"/>
-      <c r="J38" s="41"/>
-      <c r="K38" s="41"/>
-      <c r="L38" s="41"/>
-      <c r="M38" s="41"/>
-      <c r="N38" s="41"/>
-      <c r="O38" s="41"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="41"/>
-      <c r="S38" s="41"/>
-      <c r="T38" s="41"/>
-      <c r="U38" s="41"/>
-      <c r="V38" s="41"/>
-      <c r="W38" s="41"/>
-      <c r="X38" s="41"/>
-      <c r="Y38" s="41"/>
-      <c r="Z38" s="41"/>
-      <c r="AA38" s="42"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="46"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="46"/>
+      <c r="F38" s="46"/>
+      <c r="G38" s="46"/>
+      <c r="H38" s="46"/>
+      <c r="I38" s="46"/>
+      <c r="J38" s="46"/>
+      <c r="K38" s="46"/>
+      <c r="L38" s="46"/>
+      <c r="M38" s="46"/>
+      <c r="N38" s="46"/>
+      <c r="O38" s="46"/>
+      <c r="P38" s="46"/>
+      <c r="Q38" s="46"/>
+      <c r="R38" s="46"/>
+      <c r="S38" s="46"/>
+      <c r="T38" s="46"/>
+      <c r="U38" s="46"/>
+      <c r="V38" s="46"/>
+      <c r="W38" s="46"/>
+      <c r="X38" s="46"/>
+      <c r="Y38" s="46"/>
+      <c r="Z38" s="46"/>
+      <c r="AA38" s="47"/>
     </row>
     <row r="39" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
-      <c r="B39" s="40"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="41"/>
-      <c r="I39" s="41"/>
-      <c r="J39" s="41"/>
-      <c r="K39" s="41"/>
-      <c r="L39" s="41"/>
-      <c r="M39" s="41"/>
-      <c r="N39" s="41"/>
-      <c r="O39" s="41"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="41"/>
-      <c r="S39" s="41"/>
-      <c r="T39" s="41"/>
-      <c r="U39" s="41"/>
-      <c r="V39" s="41"/>
-      <c r="W39" s="41"/>
-      <c r="X39" s="41"/>
-      <c r="Y39" s="41"/>
-      <c r="Z39" s="41"/>
-      <c r="AA39" s="42"/>
+      <c r="B39" s="45"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="46"/>
+      <c r="F39" s="46"/>
+      <c r="G39" s="46"/>
+      <c r="H39" s="46"/>
+      <c r="I39" s="46"/>
+      <c r="J39" s="46"/>
+      <c r="K39" s="46"/>
+      <c r="L39" s="46"/>
+      <c r="M39" s="46"/>
+      <c r="N39" s="46"/>
+      <c r="O39" s="46"/>
+      <c r="P39" s="46"/>
+      <c r="Q39" s="46"/>
+      <c r="R39" s="46"/>
+      <c r="S39" s="46"/>
+      <c r="T39" s="46"/>
+      <c r="U39" s="46"/>
+      <c r="V39" s="46"/>
+      <c r="W39" s="46"/>
+      <c r="X39" s="46"/>
+      <c r="Y39" s="46"/>
+      <c r="Z39" s="46"/>
+      <c r="AA39" s="47"/>
     </row>
     <row r="40" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
-      <c r="B40" s="43" t="s">
+      <c r="B40" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="44"/>
-      <c r="D40" s="44"/>
-      <c r="E40" s="44"/>
-      <c r="F40" s="44"/>
-      <c r="G40" s="44"/>
-      <c r="H40" s="44"/>
-      <c r="I40" s="44"/>
-      <c r="J40" s="44"/>
-      <c r="K40" s="44"/>
-      <c r="L40" s="44"/>
-      <c r="M40" s="44"/>
-      <c r="N40" s="44"/>
-      <c r="O40" s="44"/>
-      <c r="P40" s="44"/>
-      <c r="Q40" s="44"/>
-      <c r="R40" s="44"/>
-      <c r="S40" s="44"/>
-      <c r="T40" s="44"/>
-      <c r="U40" s="44"/>
-      <c r="V40" s="44"/>
-      <c r="W40" s="44"/>
-      <c r="X40" s="44"/>
-      <c r="Y40" s="44"/>
-      <c r="Z40" s="44"/>
-      <c r="AA40" s="45"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="43"/>
+      <c r="L40" s="43"/>
+      <c r="M40" s="43"/>
+      <c r="N40" s="43"/>
+      <c r="O40" s="43"/>
+      <c r="P40" s="43"/>
+      <c r="Q40" s="43"/>
+      <c r="R40" s="43"/>
+      <c r="S40" s="43"/>
+      <c r="T40" s="43"/>
+      <c r="U40" s="43"/>
+      <c r="V40" s="43"/>
+      <c r="W40" s="43"/>
+      <c r="X40" s="43"/>
+      <c r="Y40" s="43"/>
+      <c r="Z40" s="43"/>
+      <c r="AA40" s="44"/>
     </row>
     <row r="41" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
-      <c r="B41" s="40"/>
-      <c r="C41" s="41"/>
-      <c r="D41" s="41"/>
-      <c r="E41" s="41"/>
-      <c r="F41" s="41"/>
-      <c r="G41" s="41"/>
-      <c r="H41" s="41"/>
-      <c r="I41" s="41"/>
-      <c r="J41" s="41"/>
-      <c r="K41" s="41"/>
-      <c r="L41" s="41"/>
-      <c r="M41" s="41"/>
-      <c r="N41" s="41"/>
-      <c r="O41" s="41"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="41"/>
-      <c r="S41" s="41"/>
-      <c r="T41" s="41"/>
-      <c r="U41" s="41"/>
-      <c r="V41" s="41"/>
-      <c r="W41" s="41"/>
-      <c r="X41" s="41"/>
-      <c r="Y41" s="41"/>
-      <c r="Z41" s="41"/>
-      <c r="AA41" s="42"/>
+      <c r="B41" s="45"/>
+      <c r="C41" s="46"/>
+      <c r="D41" s="46"/>
+      <c r="E41" s="46"/>
+      <c r="F41" s="46"/>
+      <c r="G41" s="46"/>
+      <c r="H41" s="46"/>
+      <c r="I41" s="46"/>
+      <c r="J41" s="46"/>
+      <c r="K41" s="46"/>
+      <c r="L41" s="46"/>
+      <c r="M41" s="46"/>
+      <c r="N41" s="46"/>
+      <c r="O41" s="46"/>
+      <c r="P41" s="46"/>
+      <c r="Q41" s="46"/>
+      <c r="R41" s="46"/>
+      <c r="S41" s="46"/>
+      <c r="T41" s="46"/>
+      <c r="U41" s="46"/>
+      <c r="V41" s="46"/>
+      <c r="W41" s="46"/>
+      <c r="X41" s="46"/>
+      <c r="Y41" s="46"/>
+      <c r="Z41" s="46"/>
+      <c r="AA41" s="47"/>
     </row>
     <row r="42" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
-      <c r="B42" s="40"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="41"/>
-      <c r="F42" s="41"/>
-      <c r="G42" s="41"/>
-      <c r="H42" s="41"/>
-      <c r="I42" s="41"/>
-      <c r="J42" s="41"/>
-      <c r="K42" s="41"/>
-      <c r="L42" s="41"/>
-      <c r="M42" s="41"/>
-      <c r="N42" s="41"/>
-      <c r="O42" s="41"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="41"/>
-      <c r="S42" s="41"/>
-      <c r="T42" s="41"/>
-      <c r="U42" s="41"/>
-      <c r="V42" s="41"/>
-      <c r="W42" s="41"/>
-      <c r="X42" s="41"/>
-      <c r="Y42" s="41"/>
-      <c r="Z42" s="41"/>
-      <c r="AA42" s="42"/>
+      <c r="B42" s="45"/>
+      <c r="C42" s="46"/>
+      <c r="D42" s="46"/>
+      <c r="E42" s="46"/>
+      <c r="F42" s="46"/>
+      <c r="G42" s="46"/>
+      <c r="H42" s="46"/>
+      <c r="I42" s="46"/>
+      <c r="J42" s="46"/>
+      <c r="K42" s="46"/>
+      <c r="L42" s="46"/>
+      <c r="M42" s="46"/>
+      <c r="N42" s="46"/>
+      <c r="O42" s="46"/>
+      <c r="P42" s="46"/>
+      <c r="Q42" s="46"/>
+      <c r="R42" s="46"/>
+      <c r="S42" s="46"/>
+      <c r="T42" s="46"/>
+      <c r="U42" s="46"/>
+      <c r="V42" s="46"/>
+      <c r="W42" s="46"/>
+      <c r="X42" s="46"/>
+      <c r="Y42" s="46"/>
+      <c r="Z42" s="46"/>
+      <c r="AA42" s="47"/>
     </row>
     <row r="43" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
-      <c r="B43" s="40"/>
-      <c r="C43" s="41"/>
-      <c r="D43" s="41"/>
-      <c r="E43" s="41"/>
-      <c r="F43" s="41"/>
-      <c r="G43" s="41"/>
-      <c r="H43" s="41"/>
-      <c r="I43" s="41"/>
-      <c r="J43" s="41"/>
-      <c r="K43" s="41"/>
-      <c r="L43" s="41"/>
-      <c r="M43" s="41"/>
-      <c r="N43" s="41"/>
-      <c r="O43" s="41"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="41"/>
-      <c r="S43" s="41"/>
-      <c r="T43" s="41"/>
-      <c r="U43" s="41"/>
-      <c r="V43" s="41"/>
-      <c r="W43" s="41"/>
-      <c r="X43" s="41"/>
-      <c r="Y43" s="41"/>
-      <c r="Z43" s="41"/>
-      <c r="AA43" s="42"/>
+      <c r="B43" s="45"/>
+      <c r="C43" s="46"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="46"/>
+      <c r="F43" s="46"/>
+      <c r="G43" s="46"/>
+      <c r="H43" s="46"/>
+      <c r="I43" s="46"/>
+      <c r="J43" s="46"/>
+      <c r="K43" s="46"/>
+      <c r="L43" s="46"/>
+      <c r="M43" s="46"/>
+      <c r="N43" s="46"/>
+      <c r="O43" s="46"/>
+      <c r="P43" s="46"/>
+      <c r="Q43" s="46"/>
+      <c r="R43" s="46"/>
+      <c r="S43" s="46"/>
+      <c r="T43" s="46"/>
+      <c r="U43" s="46"/>
+      <c r="V43" s="46"/>
+      <c r="W43" s="46"/>
+      <c r="X43" s="46"/>
+      <c r="Y43" s="46"/>
+      <c r="Z43" s="46"/>
+      <c r="AA43" s="47"/>
     </row>
     <row r="44" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
-      <c r="B44" s="40"/>
-      <c r="C44" s="41"/>
-      <c r="D44" s="41"/>
-      <c r="E44" s="41"/>
-      <c r="F44" s="41"/>
-      <c r="G44" s="41"/>
-      <c r="H44" s="41"/>
-      <c r="I44" s="41"/>
-      <c r="J44" s="41"/>
-      <c r="K44" s="41"/>
-      <c r="L44" s="41"/>
-      <c r="M44" s="41"/>
-      <c r="N44" s="41"/>
-      <c r="O44" s="41"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="41"/>
-      <c r="S44" s="41"/>
-      <c r="T44" s="41"/>
-      <c r="U44" s="41"/>
-      <c r="V44" s="41"/>
-      <c r="W44" s="41"/>
-      <c r="X44" s="41"/>
-      <c r="Y44" s="41"/>
-      <c r="Z44" s="41"/>
-      <c r="AA44" s="42"/>
+      <c r="B44" s="45"/>
+      <c r="C44" s="46"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="46"/>
+      <c r="F44" s="46"/>
+      <c r="G44" s="46"/>
+      <c r="H44" s="46"/>
+      <c r="I44" s="46"/>
+      <c r="J44" s="46"/>
+      <c r="K44" s="46"/>
+      <c r="L44" s="46"/>
+      <c r="M44" s="46"/>
+      <c r="N44" s="46"/>
+      <c r="O44" s="46"/>
+      <c r="P44" s="46"/>
+      <c r="Q44" s="46"/>
+      <c r="R44" s="46"/>
+      <c r="S44" s="46"/>
+      <c r="T44" s="46"/>
+      <c r="U44" s="46"/>
+      <c r="V44" s="46"/>
+      <c r="W44" s="46"/>
+      <c r="X44" s="46"/>
+      <c r="Y44" s="46"/>
+      <c r="Z44" s="46"/>
+      <c r="AA44" s="47"/>
     </row>
     <row r="45" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
-      <c r="B45" s="40"/>
-      <c r="C45" s="41"/>
-      <c r="D45" s="41"/>
-      <c r="E45" s="41"/>
-      <c r="F45" s="41"/>
-      <c r="G45" s="41"/>
-      <c r="H45" s="41"/>
-      <c r="I45" s="41"/>
-      <c r="J45" s="41"/>
-      <c r="K45" s="41"/>
-      <c r="L45" s="41"/>
-      <c r="M45" s="41"/>
-      <c r="N45" s="41"/>
-      <c r="O45" s="41"/>
-      <c r="P45" s="41"/>
-      <c r="Q45" s="41"/>
-      <c r="R45" s="41"/>
-      <c r="S45" s="41"/>
-      <c r="T45" s="41"/>
-      <c r="U45" s="41"/>
-      <c r="V45" s="41"/>
-      <c r="W45" s="41"/>
-      <c r="X45" s="41"/>
-      <c r="Y45" s="41"/>
-      <c r="Z45" s="41"/>
-      <c r="AA45" s="42"/>
+      <c r="B45" s="45"/>
+      <c r="C45" s="46"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="46"/>
+      <c r="F45" s="46"/>
+      <c r="G45" s="46"/>
+      <c r="H45" s="46"/>
+      <c r="I45" s="46"/>
+      <c r="J45" s="46"/>
+      <c r="K45" s="46"/>
+      <c r="L45" s="46"/>
+      <c r="M45" s="46"/>
+      <c r="N45" s="46"/>
+      <c r="O45" s="46"/>
+      <c r="P45" s="46"/>
+      <c r="Q45" s="46"/>
+      <c r="R45" s="46"/>
+      <c r="S45" s="46"/>
+      <c r="T45" s="46"/>
+      <c r="U45" s="46"/>
+      <c r="V45" s="46"/>
+      <c r="W45" s="46"/>
+      <c r="X45" s="46"/>
+      <c r="Y45" s="46"/>
+      <c r="Z45" s="46"/>
+      <c r="AA45" s="47"/>
     </row>
     <row r="46" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
-      <c r="B46" s="40"/>
-      <c r="C46" s="41"/>
-      <c r="D46" s="41"/>
-      <c r="E46" s="41"/>
-      <c r="F46" s="41"/>
-      <c r="G46" s="41"/>
-      <c r="H46" s="41"/>
-      <c r="I46" s="41"/>
-      <c r="J46" s="41"/>
-      <c r="K46" s="41"/>
-      <c r="L46" s="41"/>
-      <c r="M46" s="41"/>
-      <c r="N46" s="41"/>
-      <c r="O46" s="41"/>
-      <c r="P46" s="41"/>
-      <c r="Q46" s="41"/>
-      <c r="R46" s="41"/>
-      <c r="S46" s="41"/>
-      <c r="T46" s="41"/>
-      <c r="U46" s="41"/>
-      <c r="V46" s="41"/>
-      <c r="W46" s="41"/>
-      <c r="X46" s="41"/>
-      <c r="Y46" s="41"/>
-      <c r="Z46" s="41"/>
-      <c r="AA46" s="42"/>
+      <c r="B46" s="45"/>
+      <c r="C46" s="46"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="46"/>
+      <c r="G46" s="46"/>
+      <c r="H46" s="46"/>
+      <c r="I46" s="46"/>
+      <c r="J46" s="46"/>
+      <c r="K46" s="46"/>
+      <c r="L46" s="46"/>
+      <c r="M46" s="46"/>
+      <c r="N46" s="46"/>
+      <c r="O46" s="46"/>
+      <c r="P46" s="46"/>
+      <c r="Q46" s="46"/>
+      <c r="R46" s="46"/>
+      <c r="S46" s="46"/>
+      <c r="T46" s="46"/>
+      <c r="U46" s="46"/>
+      <c r="V46" s="46"/>
+      <c r="W46" s="46"/>
+      <c r="X46" s="46"/>
+      <c r="Y46" s="46"/>
+      <c r="Z46" s="46"/>
+      <c r="AA46" s="47"/>
     </row>
     <row r="47" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
-      <c r="B47" s="40"/>
-      <c r="C47" s="41"/>
-      <c r="D47" s="41"/>
-      <c r="E47" s="41"/>
-      <c r="F47" s="41"/>
-      <c r="G47" s="41"/>
-      <c r="H47" s="41"/>
-      <c r="I47" s="41"/>
-      <c r="J47" s="41"/>
-      <c r="K47" s="41"/>
-      <c r="L47" s="41"/>
-      <c r="M47" s="41"/>
-      <c r="N47" s="41"/>
-      <c r="O47" s="41"/>
-      <c r="P47" s="41"/>
-      <c r="Q47" s="41"/>
-      <c r="R47" s="41"/>
-      <c r="S47" s="41"/>
-      <c r="T47" s="41"/>
-      <c r="U47" s="41"/>
-      <c r="V47" s="41"/>
-      <c r="W47" s="41"/>
-      <c r="X47" s="41"/>
-      <c r="Y47" s="41"/>
-      <c r="Z47" s="41"/>
-      <c r="AA47" s="42"/>
+      <c r="B47" s="45"/>
+      <c r="C47" s="46"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="46"/>
+      <c r="G47" s="46"/>
+      <c r="H47" s="46"/>
+      <c r="I47" s="46"/>
+      <c r="J47" s="46"/>
+      <c r="K47" s="46"/>
+      <c r="L47" s="46"/>
+      <c r="M47" s="46"/>
+      <c r="N47" s="46"/>
+      <c r="O47" s="46"/>
+      <c r="P47" s="46"/>
+      <c r="Q47" s="46"/>
+      <c r="R47" s="46"/>
+      <c r="S47" s="46"/>
+      <c r="T47" s="46"/>
+      <c r="U47" s="46"/>
+      <c r="V47" s="46"/>
+      <c r="W47" s="46"/>
+      <c r="X47" s="46"/>
+      <c r="Y47" s="46"/>
+      <c r="Z47" s="46"/>
+      <c r="AA47" s="47"/>
     </row>
     <row r="48" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
-      <c r="B48" s="60" t="s">
+      <c r="B48" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="47"/>
-      <c r="D48" s="47"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="47"/>
-      <c r="G48" s="47"/>
-      <c r="H48" s="47"/>
-      <c r="I48" s="47"/>
-      <c r="J48" s="47"/>
-      <c r="K48" s="47"/>
-      <c r="L48" s="47"/>
-      <c r="M48" s="47"/>
-      <c r="N48" s="47"/>
-      <c r="O48" s="47"/>
-      <c r="P48" s="47"/>
-      <c r="Q48" s="47"/>
-      <c r="R48" s="47"/>
-      <c r="S48" s="47"/>
-      <c r="T48" s="47"/>
-      <c r="U48" s="47"/>
-      <c r="V48" s="47"/>
-      <c r="W48" s="47"/>
-      <c r="X48" s="47"/>
-      <c r="Y48" s="47"/>
-      <c r="Z48" s="47"/>
-      <c r="AA48" s="48"/>
+      <c r="C48" s="62"/>
+      <c r="D48" s="62"/>
+      <c r="E48" s="62"/>
+      <c r="F48" s="62"/>
+      <c r="G48" s="62"/>
+      <c r="H48" s="62"/>
+      <c r="I48" s="62"/>
+      <c r="J48" s="62"/>
+      <c r="K48" s="62"/>
+      <c r="L48" s="62"/>
+      <c r="M48" s="62"/>
+      <c r="N48" s="62"/>
+      <c r="O48" s="62"/>
+      <c r="P48" s="62"/>
+      <c r="Q48" s="62"/>
+      <c r="R48" s="62"/>
+      <c r="S48" s="62"/>
+      <c r="T48" s="62"/>
+      <c r="U48" s="62"/>
+      <c r="V48" s="62"/>
+      <c r="W48" s="62"/>
+      <c r="X48" s="62"/>
+      <c r="Y48" s="62"/>
+      <c r="Z48" s="62"/>
+      <c r="AA48" s="63"/>
     </row>
     <row r="49" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="30"/>
-      <c r="B49" s="40"/>
-      <c r="C49" s="41"/>
-      <c r="D49" s="41"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="41"/>
-      <c r="I49" s="41"/>
-      <c r="J49" s="41"/>
-      <c r="K49" s="41"/>
-      <c r="L49" s="41"/>
-      <c r="M49" s="41"/>
-      <c r="N49" s="41"/>
-      <c r="O49" s="41"/>
-      <c r="P49" s="41"/>
-      <c r="Q49" s="41"/>
-      <c r="R49" s="41"/>
-      <c r="S49" s="41"/>
-      <c r="T49" s="41"/>
-      <c r="U49" s="41"/>
-      <c r="V49" s="41"/>
-      <c r="W49" s="41"/>
-      <c r="X49" s="41"/>
-      <c r="Y49" s="41"/>
-      <c r="Z49" s="41"/>
-      <c r="AA49" s="42"/>
+      <c r="B49" s="45"/>
+      <c r="C49" s="46"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="46"/>
+      <c r="G49" s="46"/>
+      <c r="H49" s="46"/>
+      <c r="I49" s="46"/>
+      <c r="J49" s="46"/>
+      <c r="K49" s="46"/>
+      <c r="L49" s="46"/>
+      <c r="M49" s="46"/>
+      <c r="N49" s="46"/>
+      <c r="O49" s="46"/>
+      <c r="P49" s="46"/>
+      <c r="Q49" s="46"/>
+      <c r="R49" s="46"/>
+      <c r="S49" s="46"/>
+      <c r="T49" s="46"/>
+      <c r="U49" s="46"/>
+      <c r="V49" s="46"/>
+      <c r="W49" s="46"/>
+      <c r="X49" s="46"/>
+      <c r="Y49" s="46"/>
+      <c r="Z49" s="46"/>
+      <c r="AA49" s="47"/>
     </row>
     <row r="50" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="30"/>
-      <c r="B50" s="40"/>
-      <c r="C50" s="41"/>
-      <c r="D50" s="41"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="41"/>
-      <c r="G50" s="41"/>
-      <c r="H50" s="41"/>
-      <c r="I50" s="41"/>
-      <c r="J50" s="41"/>
-      <c r="K50" s="41"/>
-      <c r="L50" s="41"/>
-      <c r="M50" s="41"/>
-      <c r="N50" s="41"/>
-      <c r="O50" s="41"/>
-      <c r="P50" s="41"/>
-      <c r="Q50" s="41"/>
-      <c r="R50" s="41"/>
-      <c r="S50" s="41"/>
-      <c r="T50" s="41"/>
-      <c r="U50" s="41"/>
-      <c r="V50" s="41"/>
-      <c r="W50" s="41"/>
-      <c r="X50" s="41"/>
-      <c r="Y50" s="41"/>
-      <c r="Z50" s="41"/>
-      <c r="AA50" s="42"/>
+      <c r="B50" s="45"/>
+      <c r="C50" s="46"/>
+      <c r="D50" s="46"/>
+      <c r="E50" s="46"/>
+      <c r="F50" s="46"/>
+      <c r="G50" s="46"/>
+      <c r="H50" s="46"/>
+      <c r="I50" s="46"/>
+      <c r="J50" s="46"/>
+      <c r="K50" s="46"/>
+      <c r="L50" s="46"/>
+      <c r="M50" s="46"/>
+      <c r="N50" s="46"/>
+      <c r="O50" s="46"/>
+      <c r="P50" s="46"/>
+      <c r="Q50" s="46"/>
+      <c r="R50" s="46"/>
+      <c r="S50" s="46"/>
+      <c r="T50" s="46"/>
+      <c r="U50" s="46"/>
+      <c r="V50" s="46"/>
+      <c r="W50" s="46"/>
+      <c r="X50" s="46"/>
+      <c r="Y50" s="46"/>
+      <c r="Z50" s="46"/>
+      <c r="AA50" s="47"/>
     </row>
     <row r="51" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="30"/>
-      <c r="B51" s="40"/>
-      <c r="C51" s="41"/>
-      <c r="D51" s="41"/>
-      <c r="E51" s="41"/>
-      <c r="F51" s="41"/>
-      <c r="G51" s="41"/>
-      <c r="H51" s="41"/>
-      <c r="I51" s="41"/>
-      <c r="J51" s="41"/>
-      <c r="K51" s="41"/>
-      <c r="L51" s="41"/>
-      <c r="M51" s="41"/>
-      <c r="N51" s="41"/>
-      <c r="O51" s="41"/>
-      <c r="P51" s="41"/>
-      <c r="Q51" s="41"/>
-      <c r="R51" s="41"/>
-      <c r="S51" s="41"/>
-      <c r="T51" s="41"/>
-      <c r="U51" s="41"/>
-      <c r="V51" s="41"/>
-      <c r="W51" s="41"/>
-      <c r="X51" s="41"/>
-      <c r="Y51" s="41"/>
-      <c r="Z51" s="41"/>
-      <c r="AA51" s="42"/>
+      <c r="B51" s="45"/>
+      <c r="C51" s="46"/>
+      <c r="D51" s="46"/>
+      <c r="E51" s="46"/>
+      <c r="F51" s="46"/>
+      <c r="G51" s="46"/>
+      <c r="H51" s="46"/>
+      <c r="I51" s="46"/>
+      <c r="J51" s="46"/>
+      <c r="K51" s="46"/>
+      <c r="L51" s="46"/>
+      <c r="M51" s="46"/>
+      <c r="N51" s="46"/>
+      <c r="O51" s="46"/>
+      <c r="P51" s="46"/>
+      <c r="Q51" s="46"/>
+      <c r="R51" s="46"/>
+      <c r="S51" s="46"/>
+      <c r="T51" s="46"/>
+      <c r="U51" s="46"/>
+      <c r="V51" s="46"/>
+      <c r="W51" s="46"/>
+      <c r="X51" s="46"/>
+      <c r="Y51" s="46"/>
+      <c r="Z51" s="46"/>
+      <c r="AA51" s="47"/>
     </row>
     <row r="52" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="30"/>
-      <c r="B52" s="40"/>
-      <c r="C52" s="41"/>
-      <c r="D52" s="41"/>
-      <c r="E52" s="41"/>
-      <c r="F52" s="41"/>
-      <c r="G52" s="41"/>
-      <c r="H52" s="41"/>
-      <c r="I52" s="41"/>
-      <c r="J52" s="41"/>
-      <c r="K52" s="41"/>
-      <c r="L52" s="41"/>
-      <c r="M52" s="41"/>
-      <c r="N52" s="41"/>
-      <c r="O52" s="41"/>
-      <c r="P52" s="41"/>
-      <c r="Q52" s="41"/>
-      <c r="R52" s="41"/>
-      <c r="S52" s="41"/>
-      <c r="T52" s="41"/>
-      <c r="U52" s="41"/>
-      <c r="V52" s="41"/>
-      <c r="W52" s="41"/>
-      <c r="X52" s="41"/>
-      <c r="Y52" s="41"/>
-      <c r="Z52" s="41"/>
-      <c r="AA52" s="42"/>
+      <c r="B52" s="45"/>
+      <c r="C52" s="46"/>
+      <c r="D52" s="46"/>
+      <c r="E52" s="46"/>
+      <c r="F52" s="46"/>
+      <c r="G52" s="46"/>
+      <c r="H52" s="46"/>
+      <c r="I52" s="46"/>
+      <c r="J52" s="46"/>
+      <c r="K52" s="46"/>
+      <c r="L52" s="46"/>
+      <c r="M52" s="46"/>
+      <c r="N52" s="46"/>
+      <c r="O52" s="46"/>
+      <c r="P52" s="46"/>
+      <c r="Q52" s="46"/>
+      <c r="R52" s="46"/>
+      <c r="S52" s="46"/>
+      <c r="T52" s="46"/>
+      <c r="U52" s="46"/>
+      <c r="V52" s="46"/>
+      <c r="W52" s="46"/>
+      <c r="X52" s="46"/>
+      <c r="Y52" s="46"/>
+      <c r="Z52" s="46"/>
+      <c r="AA52" s="47"/>
     </row>
     <row r="53" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="30"/>
-      <c r="B53" s="40"/>
-      <c r="C53" s="41"/>
-      <c r="D53" s="41"/>
-      <c r="E53" s="41"/>
-      <c r="F53" s="41"/>
-      <c r="G53" s="41"/>
-      <c r="H53" s="41"/>
-      <c r="I53" s="41"/>
-      <c r="J53" s="41"/>
-      <c r="K53" s="41"/>
-      <c r="L53" s="41"/>
-      <c r="M53" s="41"/>
-      <c r="N53" s="41"/>
-      <c r="O53" s="41"/>
-      <c r="P53" s="41"/>
-      <c r="Q53" s="41"/>
-      <c r="R53" s="41"/>
-      <c r="S53" s="41"/>
-      <c r="T53" s="41"/>
-      <c r="U53" s="41"/>
-      <c r="V53" s="41"/>
-      <c r="W53" s="41"/>
-      <c r="X53" s="41"/>
-      <c r="Y53" s="41"/>
-      <c r="Z53" s="41"/>
-      <c r="AA53" s="42"/>
+      <c r="B53" s="45"/>
+      <c r="C53" s="46"/>
+      <c r="D53" s="46"/>
+      <c r="E53" s="46"/>
+      <c r="F53" s="46"/>
+      <c r="G53" s="46"/>
+      <c r="H53" s="46"/>
+      <c r="I53" s="46"/>
+      <c r="J53" s="46"/>
+      <c r="K53" s="46"/>
+      <c r="L53" s="46"/>
+      <c r="M53" s="46"/>
+      <c r="N53" s="46"/>
+      <c r="O53" s="46"/>
+      <c r="P53" s="46"/>
+      <c r="Q53" s="46"/>
+      <c r="R53" s="46"/>
+      <c r="S53" s="46"/>
+      <c r="T53" s="46"/>
+      <c r="U53" s="46"/>
+      <c r="V53" s="46"/>
+      <c r="W53" s="46"/>
+      <c r="X53" s="46"/>
+      <c r="Y53" s="46"/>
+      <c r="Z53" s="46"/>
+      <c r="AA53" s="47"/>
     </row>
     <row r="54" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="30"/>
-      <c r="B54" s="40"/>
-      <c r="C54" s="41"/>
-      <c r="D54" s="41"/>
-      <c r="E54" s="41"/>
-      <c r="F54" s="41"/>
-      <c r="G54" s="41"/>
-      <c r="H54" s="41"/>
-      <c r="I54" s="41"/>
-      <c r="J54" s="41"/>
-      <c r="K54" s="41"/>
-      <c r="L54" s="41"/>
-      <c r="M54" s="41"/>
-      <c r="N54" s="41"/>
-      <c r="O54" s="41"/>
-      <c r="P54" s="41"/>
-      <c r="Q54" s="41"/>
-      <c r="R54" s="41"/>
-      <c r="S54" s="41"/>
-      <c r="T54" s="41"/>
-      <c r="U54" s="41"/>
-      <c r="V54" s="41"/>
-      <c r="W54" s="41"/>
-      <c r="X54" s="41"/>
-      <c r="Y54" s="41"/>
-      <c r="Z54" s="41"/>
-      <c r="AA54" s="42"/>
+      <c r="B54" s="45"/>
+      <c r="C54" s="46"/>
+      <c r="D54" s="46"/>
+      <c r="E54" s="46"/>
+      <c r="F54" s="46"/>
+      <c r="G54" s="46"/>
+      <c r="H54" s="46"/>
+      <c r="I54" s="46"/>
+      <c r="J54" s="46"/>
+      <c r="K54" s="46"/>
+      <c r="L54" s="46"/>
+      <c r="M54" s="46"/>
+      <c r="N54" s="46"/>
+      <c r="O54" s="46"/>
+      <c r="P54" s="46"/>
+      <c r="Q54" s="46"/>
+      <c r="R54" s="46"/>
+      <c r="S54" s="46"/>
+      <c r="T54" s="46"/>
+      <c r="U54" s="46"/>
+      <c r="V54" s="46"/>
+      <c r="W54" s="46"/>
+      <c r="X54" s="46"/>
+      <c r="Y54" s="46"/>
+      <c r="Z54" s="46"/>
+      <c r="AA54" s="47"/>
     </row>
     <row r="55" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="30"/>
-      <c r="B55" s="40"/>
-      <c r="C55" s="41"/>
-      <c r="D55" s="41"/>
-      <c r="E55" s="41"/>
-      <c r="F55" s="41"/>
-      <c r="G55" s="41"/>
-      <c r="H55" s="41"/>
-      <c r="I55" s="41"/>
-      <c r="J55" s="41"/>
-      <c r="K55" s="41"/>
-      <c r="L55" s="41"/>
-      <c r="M55" s="41"/>
-      <c r="N55" s="41"/>
-      <c r="O55" s="41"/>
-      <c r="P55" s="41"/>
-      <c r="Q55" s="41"/>
-      <c r="R55" s="41"/>
-      <c r="S55" s="41"/>
-      <c r="T55" s="41"/>
-      <c r="U55" s="41"/>
-      <c r="V55" s="41"/>
-      <c r="W55" s="41"/>
-      <c r="X55" s="41"/>
-      <c r="Y55" s="41"/>
-      <c r="Z55" s="41"/>
-      <c r="AA55" s="42"/>
+      <c r="B55" s="45"/>
+      <c r="C55" s="46"/>
+      <c r="D55" s="46"/>
+      <c r="E55" s="46"/>
+      <c r="F55" s="46"/>
+      <c r="G55" s="46"/>
+      <c r="H55" s="46"/>
+      <c r="I55" s="46"/>
+      <c r="J55" s="46"/>
+      <c r="K55" s="46"/>
+      <c r="L55" s="46"/>
+      <c r="M55" s="46"/>
+      <c r="N55" s="46"/>
+      <c r="O55" s="46"/>
+      <c r="P55" s="46"/>
+      <c r="Q55" s="46"/>
+      <c r="R55" s="46"/>
+      <c r="S55" s="46"/>
+      <c r="T55" s="46"/>
+      <c r="U55" s="46"/>
+      <c r="V55" s="46"/>
+      <c r="W55" s="46"/>
+      <c r="X55" s="46"/>
+      <c r="Y55" s="46"/>
+      <c r="Z55" s="46"/>
+      <c r="AA55" s="47"/>
     </row>
     <row r="56" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
@@ -2745,22 +3022,22 @@
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
       <c r="J59" s="66"/>
-      <c r="K59" s="68"/>
-      <c r="L59" s="41"/>
-      <c r="M59" s="41"/>
-      <c r="N59" s="41"/>
-      <c r="O59" s="41"/>
-      <c r="P59" s="41"/>
-      <c r="Q59" s="41"/>
-      <c r="R59" s="67"/>
-      <c r="S59" s="67"/>
-      <c r="T59" s="67"/>
-      <c r="U59" s="67"/>
-      <c r="V59" s="67"/>
-      <c r="W59" s="67"/>
-      <c r="X59" s="67"/>
-      <c r="Y59" s="69"/>
-      <c r="Z59" s="69"/>
+      <c r="K59" s="67"/>
+      <c r="L59" s="68"/>
+      <c r="M59" s="68"/>
+      <c r="N59" s="68"/>
+      <c r="O59" s="68"/>
+      <c r="P59" s="68"/>
+      <c r="Q59" s="68"/>
+      <c r="R59" s="69"/>
+      <c r="S59" s="69"/>
+      <c r="T59" s="69"/>
+      <c r="U59" s="69"/>
+      <c r="V59" s="69"/>
+      <c r="W59" s="69"/>
+      <c r="X59" s="69"/>
+      <c r="Y59" s="70"/>
+      <c r="Z59" s="70"/>
       <c r="AA59" s="1"/>
     </row>
     <row r="60" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2912,61 +3189,61 @@
     <row r="65" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
       <c r="B65" s="34"/>
-      <c r="C65" s="62" t="s">
+      <c r="C65" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="D65" s="56"/>
-      <c r="E65" s="56"/>
-      <c r="F65" s="56"/>
-      <c r="G65" s="56"/>
-      <c r="H65" s="56"/>
-      <c r="I65" s="56"/>
-      <c r="J65" s="56"/>
-      <c r="K65" s="56"/>
-      <c r="L65" s="56"/>
-      <c r="M65" s="56"/>
-      <c r="N65" s="56"/>
-      <c r="O65" s="56"/>
-      <c r="P65" s="56"/>
-      <c r="Q65" s="56"/>
-      <c r="R65" s="56"/>
-      <c r="S65" s="56"/>
-      <c r="T65" s="56"/>
-      <c r="U65" s="56"/>
-      <c r="V65" s="56"/>
-      <c r="W65" s="56"/>
-      <c r="X65" s="56"/>
-      <c r="Y65" s="56"/>
-      <c r="Z65" s="56"/>
+      <c r="D65" s="41"/>
+      <c r="E65" s="41"/>
+      <c r="F65" s="41"/>
+      <c r="G65" s="41"/>
+      <c r="H65" s="41"/>
+      <c r="I65" s="41"/>
+      <c r="J65" s="41"/>
+      <c r="K65" s="41"/>
+      <c r="L65" s="41"/>
+      <c r="M65" s="41"/>
+      <c r="N65" s="41"/>
+      <c r="O65" s="41"/>
+      <c r="P65" s="41"/>
+      <c r="Q65" s="41"/>
+      <c r="R65" s="41"/>
+      <c r="S65" s="41"/>
+      <c r="T65" s="41"/>
+      <c r="U65" s="41"/>
+      <c r="V65" s="41"/>
+      <c r="W65" s="41"/>
+      <c r="X65" s="41"/>
+      <c r="Y65" s="41"/>
+      <c r="Z65" s="41"/>
       <c r="AA65" s="34"/>
     </row>
     <row r="66" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
       <c r="B66" s="34"/>
-      <c r="C66" s="56"/>
-      <c r="D66" s="56"/>
-      <c r="E66" s="56"/>
-      <c r="F66" s="56"/>
-      <c r="G66" s="56"/>
-      <c r="H66" s="56"/>
-      <c r="I66" s="56"/>
-      <c r="J66" s="56"/>
-      <c r="K66" s="56"/>
-      <c r="L66" s="56"/>
-      <c r="M66" s="56"/>
-      <c r="N66" s="56"/>
-      <c r="O66" s="56"/>
-      <c r="P66" s="56"/>
-      <c r="Q66" s="56"/>
-      <c r="R66" s="56"/>
-      <c r="S66" s="56"/>
-      <c r="T66" s="56"/>
-      <c r="U66" s="56"/>
-      <c r="V66" s="56"/>
-      <c r="W66" s="56"/>
-      <c r="X66" s="56"/>
-      <c r="Y66" s="56"/>
-      <c r="Z66" s="56"/>
+      <c r="C66" s="41"/>
+      <c r="D66" s="41"/>
+      <c r="E66" s="41"/>
+      <c r="F66" s="41"/>
+      <c r="G66" s="41"/>
+      <c r="H66" s="41"/>
+      <c r="I66" s="41"/>
+      <c r="J66" s="41"/>
+      <c r="K66" s="41"/>
+      <c r="L66" s="41"/>
+      <c r="M66" s="41"/>
+      <c r="N66" s="41"/>
+      <c r="O66" s="41"/>
+      <c r="P66" s="41"/>
+      <c r="Q66" s="41"/>
+      <c r="R66" s="41"/>
+      <c r="S66" s="41"/>
+      <c r="T66" s="41"/>
+      <c r="U66" s="41"/>
+      <c r="V66" s="41"/>
+      <c r="W66" s="41"/>
+      <c r="X66" s="41"/>
+      <c r="Y66" s="41"/>
+      <c r="Z66" s="41"/>
       <c r="AA66" s="34"/>
     </row>
     <row r="67" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30057,13 +30334,31 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="C65:Z66"/>
-    <mergeCell ref="B40:AA40"/>
-    <mergeCell ref="B49:AA49"/>
-    <mergeCell ref="K59:Q59"/>
-    <mergeCell ref="B55:AA55"/>
-    <mergeCell ref="B59:J59"/>
-    <mergeCell ref="B42:AA42"/>
+    <mergeCell ref="B36:AA36"/>
+    <mergeCell ref="B32:AA32"/>
+    <mergeCell ref="B50:AA50"/>
+    <mergeCell ref="B14:AA15"/>
+    <mergeCell ref="B26:AA26"/>
+    <mergeCell ref="B41:AA41"/>
+    <mergeCell ref="H19:Z19"/>
+    <mergeCell ref="B33:AA33"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B3:AA3"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B31:AA31"/>
+    <mergeCell ref="B46:AA46"/>
+    <mergeCell ref="B27:AA27"/>
+    <mergeCell ref="B43:AA43"/>
+    <mergeCell ref="B39:AA39"/>
+    <mergeCell ref="B6:AA6"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="W12:Z12"/>
+    <mergeCell ref="B5:AA5"/>
+    <mergeCell ref="B4:AA4"/>
+    <mergeCell ref="B35:AA35"/>
+    <mergeCell ref="H12:T12"/>
+    <mergeCell ref="B25:AA25"/>
+    <mergeCell ref="B45:AA45"/>
     <mergeCell ref="B23:AA23"/>
     <mergeCell ref="H10:Z10"/>
     <mergeCell ref="B51:AA51"/>
@@ -30078,35 +30373,17 @@
     <mergeCell ref="B24:AA24"/>
     <mergeCell ref="B30:AA30"/>
     <mergeCell ref="H17:Z17"/>
-    <mergeCell ref="B3:AA3"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="B31:AA31"/>
-    <mergeCell ref="B46:AA46"/>
-    <mergeCell ref="B27:AA27"/>
-    <mergeCell ref="B43:AA43"/>
-    <mergeCell ref="B39:AA39"/>
-    <mergeCell ref="B6:AA6"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="W12:Z12"/>
-    <mergeCell ref="B5:AA5"/>
-    <mergeCell ref="B4:AA4"/>
-    <mergeCell ref="B35:AA35"/>
-    <mergeCell ref="H12:T12"/>
     <mergeCell ref="B47:AA47"/>
+    <mergeCell ref="B52:AA52"/>
+    <mergeCell ref="C65:Z66"/>
+    <mergeCell ref="B40:AA40"/>
+    <mergeCell ref="B49:AA49"/>
+    <mergeCell ref="K59:Q59"/>
+    <mergeCell ref="B55:AA55"/>
+    <mergeCell ref="B59:J59"/>
+    <mergeCell ref="B42:AA42"/>
     <mergeCell ref="B54:AA54"/>
-    <mergeCell ref="B25:AA25"/>
-    <mergeCell ref="B52:AA52"/>
     <mergeCell ref="B48:AA48"/>
-    <mergeCell ref="B45:AA45"/>
-    <mergeCell ref="B36:AA36"/>
-    <mergeCell ref="B32:AA32"/>
-    <mergeCell ref="B50:AA50"/>
-    <mergeCell ref="B14:AA15"/>
-    <mergeCell ref="B26:AA26"/>
-    <mergeCell ref="B41:AA41"/>
-    <mergeCell ref="H19:Z19"/>
-    <mergeCell ref="B33:AA33"/>
-    <mergeCell ref="B17:G17"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.98425196850393704" header="0" footer="0"/>

--- a/static/templates/tec02-A_template.xlsx
+++ b/static/templates/tec02-A_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\diseño-afk\static\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F344B3-37F3-4148-A9F7-124F093272C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98859015-B9ED-41CE-91F3-10E462BC177F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -578,7 +578,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -700,13 +700,6 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -757,6 +750,33 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1361,7 +1381,7 @@
     </row>
     <row r="3" spans="1:27" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="50" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="41"/>
@@ -1392,7 +1412,7 @@
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
-      <c r="B4" s="60"/>
+      <c r="B4" s="55"/>
       <c r="C4" s="41"/>
       <c r="D4" s="41"/>
       <c r="E4" s="41"/>
@@ -1421,7 +1441,7 @@
     </row>
     <row r="5" spans="1:27" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
-      <c r="B5" s="59" t="s">
+      <c r="B5" s="54" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="41"/>
@@ -1452,7 +1472,7 @@
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="52" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="41"/>
@@ -1578,25 +1598,25 @@
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="52"/>
-      <c r="K10" s="52"/>
-      <c r="L10" s="52"/>
-      <c r="M10" s="52"/>
-      <c r="N10" s="52"/>
-      <c r="O10" s="52"/>
-      <c r="P10" s="52"/>
-      <c r="Q10" s="52"/>
-      <c r="R10" s="52"/>
-      <c r="S10" s="52"/>
-      <c r="T10" s="52"/>
-      <c r="U10" s="52"/>
-      <c r="V10" s="52"/>
-      <c r="W10" s="52"/>
-      <c r="X10" s="52"/>
-      <c r="Y10" s="52"/>
-      <c r="Z10" s="53"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="47"/>
+      <c r="K10" s="47"/>
+      <c r="L10" s="47"/>
+      <c r="M10" s="47"/>
+      <c r="N10" s="47"/>
+      <c r="O10" s="47"/>
+      <c r="P10" s="47"/>
+      <c r="Q10" s="47"/>
+      <c r="R10" s="47"/>
+      <c r="S10" s="47"/>
+      <c r="T10" s="47"/>
+      <c r="U10" s="47"/>
+      <c r="V10" s="47"/>
+      <c r="W10" s="47"/>
+      <c r="X10" s="47"/>
+      <c r="Y10" s="47"/>
+      <c r="Z10" s="48"/>
       <c r="AA10" s="11"/>
     </row>
     <row r="11" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1638,27 +1658,27 @@
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="52"/>
-      <c r="K12" s="52"/>
-      <c r="L12" s="52"/>
-      <c r="M12" s="52"/>
-      <c r="N12" s="52"/>
-      <c r="O12" s="52"/>
-      <c r="P12" s="52"/>
-      <c r="Q12" s="52"/>
-      <c r="R12" s="52"/>
-      <c r="S12" s="52"/>
-      <c r="T12" s="53"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="47"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="47"/>
+      <c r="N12" s="47"/>
+      <c r="O12" s="47"/>
+      <c r="P12" s="47"/>
+      <c r="Q12" s="47"/>
+      <c r="R12" s="47"/>
+      <c r="S12" s="47"/>
+      <c r="T12" s="48"/>
       <c r="U12" s="13"/>
       <c r="V12" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="W12" s="58"/>
-      <c r="X12" s="52"/>
-      <c r="Y12" s="52"/>
-      <c r="Z12" s="53"/>
+      <c r="W12" s="53"/>
+      <c r="X12" s="47"/>
+      <c r="Y12" s="47"/>
+      <c r="Z12" s="48"/>
       <c r="AA12" s="15"/>
     </row>
     <row r="13" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1692,63 +1712,63 @@
     </row>
     <row r="14" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
-      <c r="B14" s="64" t="s">
+      <c r="B14" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="62"/>
-      <c r="M14" s="62"/>
-      <c r="N14" s="62"/>
-      <c r="O14" s="62"/>
-      <c r="P14" s="62"/>
-      <c r="Q14" s="62"/>
-      <c r="R14" s="62"/>
-      <c r="S14" s="62"/>
-      <c r="T14" s="62"/>
-      <c r="U14" s="62"/>
-      <c r="V14" s="62"/>
-      <c r="W14" s="62"/>
-      <c r="X14" s="62"/>
-      <c r="Y14" s="62"/>
-      <c r="Z14" s="62"/>
-      <c r="AA14" s="63"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="57"/>
+      <c r="L14" s="57"/>
+      <c r="M14" s="57"/>
+      <c r="N14" s="57"/>
+      <c r="O14" s="57"/>
+      <c r="P14" s="57"/>
+      <c r="Q14" s="57"/>
+      <c r="R14" s="57"/>
+      <c r="S14" s="57"/>
+      <c r="T14" s="57"/>
+      <c r="U14" s="57"/>
+      <c r="V14" s="57"/>
+      <c r="W14" s="57"/>
+      <c r="X14" s="57"/>
+      <c r="Y14" s="57"/>
+      <c r="Z14" s="57"/>
+      <c r="AA14" s="58"/>
     </row>
     <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
-      <c r="B15" s="65"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="49"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="49"/>
-      <c r="L15" s="49"/>
-      <c r="M15" s="49"/>
-      <c r="N15" s="49"/>
-      <c r="O15" s="49"/>
-      <c r="P15" s="49"/>
-      <c r="Q15" s="49"/>
-      <c r="R15" s="49"/>
-      <c r="S15" s="49"/>
-      <c r="T15" s="49"/>
-      <c r="U15" s="49"/>
-      <c r="V15" s="49"/>
-      <c r="W15" s="49"/>
-      <c r="X15" s="49"/>
-      <c r="Y15" s="49"/>
-      <c r="Z15" s="49"/>
-      <c r="AA15" s="50"/>
+      <c r="B15" s="60"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="44"/>
+      <c r="L15" s="44"/>
+      <c r="M15" s="44"/>
+      <c r="N15" s="44"/>
+      <c r="O15" s="44"/>
+      <c r="P15" s="44"/>
+      <c r="Q15" s="44"/>
+      <c r="R15" s="44"/>
+      <c r="S15" s="44"/>
+      <c r="T15" s="44"/>
+      <c r="U15" s="44"/>
+      <c r="V15" s="44"/>
+      <c r="W15" s="44"/>
+      <c r="X15" s="44"/>
+      <c r="Y15" s="44"/>
+      <c r="Z15" s="44"/>
+      <c r="AA15" s="45"/>
     </row>
     <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
@@ -1781,7 +1801,7 @@
     </row>
     <row r="17" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
-      <c r="B17" s="56" t="s">
+      <c r="B17" s="51" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="41"/>
@@ -1789,25 +1809,25 @@
       <c r="E17" s="41"/>
       <c r="F17" s="41"/>
       <c r="G17" s="41"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
-      <c r="L17" s="52"/>
-      <c r="M17" s="52"/>
-      <c r="N17" s="52"/>
-      <c r="O17" s="52"/>
-      <c r="P17" s="52"/>
-      <c r="Q17" s="52"/>
-      <c r="R17" s="52"/>
-      <c r="S17" s="52"/>
-      <c r="T17" s="52"/>
-      <c r="U17" s="52"/>
-      <c r="V17" s="52"/>
-      <c r="W17" s="52"/>
-      <c r="X17" s="52"/>
-      <c r="Y17" s="52"/>
-      <c r="Z17" s="53"/>
+      <c r="H17" s="49"/>
+      <c r="I17" s="47"/>
+      <c r="J17" s="47"/>
+      <c r="K17" s="47"/>
+      <c r="L17" s="47"/>
+      <c r="M17" s="47"/>
+      <c r="N17" s="47"/>
+      <c r="O17" s="47"/>
+      <c r="P17" s="47"/>
+      <c r="Q17" s="47"/>
+      <c r="R17" s="47"/>
+      <c r="S17" s="47"/>
+      <c r="T17" s="47"/>
+      <c r="U17" s="47"/>
+      <c r="V17" s="47"/>
+      <c r="W17" s="47"/>
+      <c r="X17" s="47"/>
+      <c r="Y17" s="47"/>
+      <c r="Z17" s="48"/>
       <c r="AA17" s="24"/>
     </row>
     <row r="18" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1841,7 +1861,7 @@
     </row>
     <row r="19" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
-      <c r="B19" s="56" t="s">
+      <c r="B19" s="51" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="41"/>
@@ -1849,25 +1869,25 @@
       <c r="E19" s="41"/>
       <c r="F19" s="41"/>
       <c r="G19" s="41"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="52"/>
-      <c r="J19" s="52"/>
-      <c r="K19" s="52"/>
-      <c r="L19" s="52"/>
-      <c r="M19" s="52"/>
-      <c r="N19" s="52"/>
-      <c r="O19" s="52"/>
-      <c r="P19" s="52"/>
-      <c r="Q19" s="52"/>
-      <c r="R19" s="52"/>
-      <c r="S19" s="52"/>
-      <c r="T19" s="52"/>
-      <c r="U19" s="52"/>
-      <c r="V19" s="52"/>
-      <c r="W19" s="52"/>
-      <c r="X19" s="52"/>
-      <c r="Y19" s="52"/>
-      <c r="Z19" s="53"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="47"/>
+      <c r="K19" s="47"/>
+      <c r="L19" s="47"/>
+      <c r="M19" s="47"/>
+      <c r="N19" s="47"/>
+      <c r="O19" s="47"/>
+      <c r="P19" s="47"/>
+      <c r="Q19" s="47"/>
+      <c r="R19" s="47"/>
+      <c r="S19" s="47"/>
+      <c r="T19" s="47"/>
+      <c r="U19" s="47"/>
+      <c r="V19" s="47"/>
+      <c r="W19" s="47"/>
+      <c r="X19" s="47"/>
+      <c r="Y19" s="47"/>
+      <c r="Z19" s="48"/>
       <c r="AA19" s="24"/>
     </row>
     <row r="20" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1901,7 +1921,7 @@
     </row>
     <row r="21" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
-      <c r="B21" s="56" t="s">
+      <c r="B21" s="51" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="41"/>
@@ -1909,25 +1929,25 @@
       <c r="E21" s="41"/>
       <c r="F21" s="41"/>
       <c r="G21" s="41"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="52"/>
-      <c r="J21" s="52"/>
-      <c r="K21" s="52"/>
-      <c r="L21" s="52"/>
-      <c r="M21" s="52"/>
-      <c r="N21" s="52"/>
-      <c r="O21" s="52"/>
-      <c r="P21" s="52"/>
-      <c r="Q21" s="52"/>
-      <c r="R21" s="52"/>
-      <c r="S21" s="52"/>
-      <c r="T21" s="52"/>
-      <c r="U21" s="52"/>
-      <c r="V21" s="52"/>
-      <c r="W21" s="52"/>
-      <c r="X21" s="52"/>
-      <c r="Y21" s="52"/>
-      <c r="Z21" s="53"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="47"/>
+      <c r="J21" s="47"/>
+      <c r="K21" s="47"/>
+      <c r="L21" s="47"/>
+      <c r="M21" s="47"/>
+      <c r="N21" s="47"/>
+      <c r="O21" s="47"/>
+      <c r="P21" s="47"/>
+      <c r="Q21" s="47"/>
+      <c r="R21" s="47"/>
+      <c r="S21" s="47"/>
+      <c r="T21" s="47"/>
+      <c r="U21" s="47"/>
+      <c r="V21" s="47"/>
+      <c r="W21" s="47"/>
+      <c r="X21" s="47"/>
+      <c r="Y21" s="47"/>
+      <c r="Z21" s="48"/>
       <c r="AA21" s="24"/>
     </row>
     <row r="22" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1961,968 +1981,968 @@
     </row>
     <row r="23" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
-      <c r="B23" s="48" t="s">
+      <c r="B23" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="49"/>
-      <c r="K23" s="49"/>
-      <c r="L23" s="49"/>
-      <c r="M23" s="49"/>
-      <c r="N23" s="49"/>
-      <c r="O23" s="49"/>
-      <c r="P23" s="49"/>
-      <c r="Q23" s="49"/>
-      <c r="R23" s="49"/>
-      <c r="S23" s="49"/>
-      <c r="T23" s="49"/>
-      <c r="U23" s="49"/>
-      <c r="V23" s="49"/>
-      <c r="W23" s="49"/>
-      <c r="X23" s="49"/>
-      <c r="Y23" s="49"/>
-      <c r="Z23" s="49"/>
-      <c r="AA23" s="50"/>
+      <c r="C23" s="66"/>
+      <c r="D23" s="66"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="66"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="66"/>
+      <c r="J23" s="66"/>
+      <c r="K23" s="66"/>
+      <c r="L23" s="66"/>
+      <c r="M23" s="66"/>
+      <c r="N23" s="66"/>
+      <c r="O23" s="66"/>
+      <c r="P23" s="66"/>
+      <c r="Q23" s="66"/>
+      <c r="R23" s="66"/>
+      <c r="S23" s="66"/>
+      <c r="T23" s="66"/>
+      <c r="U23" s="66"/>
+      <c r="V23" s="66"/>
+      <c r="W23" s="66"/>
+      <c r="X23" s="66"/>
+      <c r="Y23" s="66"/>
+      <c r="Z23" s="66"/>
+      <c r="AA23" s="67"/>
     </row>
     <row r="24" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="46"/>
-      <c r="M24" s="46"/>
-      <c r="N24" s="46"/>
-      <c r="O24" s="46"/>
-      <c r="P24" s="46"/>
-      <c r="Q24" s="46"/>
-      <c r="R24" s="46"/>
-      <c r="S24" s="46"/>
-      <c r="T24" s="46"/>
-      <c r="U24" s="46"/>
-      <c r="V24" s="46"/>
-      <c r="W24" s="46"/>
-      <c r="X24" s="46"/>
-      <c r="Y24" s="46"/>
-      <c r="Z24" s="46"/>
-      <c r="AA24" s="47"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="69"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="69"/>
+      <c r="H24" s="69"/>
+      <c r="I24" s="69"/>
+      <c r="J24" s="69"/>
+      <c r="K24" s="69"/>
+      <c r="L24" s="69"/>
+      <c r="M24" s="69"/>
+      <c r="N24" s="69"/>
+      <c r="O24" s="69"/>
+      <c r="P24" s="69"/>
+      <c r="Q24" s="69"/>
+      <c r="R24" s="69"/>
+      <c r="S24" s="69"/>
+      <c r="T24" s="69"/>
+      <c r="U24" s="69"/>
+      <c r="V24" s="69"/>
+      <c r="W24" s="69"/>
+      <c r="X24" s="69"/>
+      <c r="Y24" s="69"/>
+      <c r="Z24" s="69"/>
+      <c r="AA24" s="70"/>
     </row>
     <row r="25" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="46"/>
-      <c r="K25" s="46"/>
-      <c r="L25" s="46"/>
-      <c r="M25" s="46"/>
-      <c r="N25" s="46"/>
-      <c r="O25" s="46"/>
-      <c r="P25" s="46"/>
-      <c r="Q25" s="46"/>
-      <c r="R25" s="46"/>
-      <c r="S25" s="46"/>
-      <c r="T25" s="46"/>
-      <c r="U25" s="46"/>
-      <c r="V25" s="46"/>
-      <c r="W25" s="46"/>
-      <c r="X25" s="46"/>
-      <c r="Y25" s="46"/>
-      <c r="Z25" s="46"/>
-      <c r="AA25" s="47"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="69"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="69"/>
+      <c r="F25" s="69"/>
+      <c r="G25" s="69"/>
+      <c r="H25" s="69"/>
+      <c r="I25" s="69"/>
+      <c r="J25" s="69"/>
+      <c r="K25" s="69"/>
+      <c r="L25" s="69"/>
+      <c r="M25" s="69"/>
+      <c r="N25" s="69"/>
+      <c r="O25" s="69"/>
+      <c r="P25" s="69"/>
+      <c r="Q25" s="69"/>
+      <c r="R25" s="69"/>
+      <c r="S25" s="69"/>
+      <c r="T25" s="69"/>
+      <c r="U25" s="69"/>
+      <c r="V25" s="69"/>
+      <c r="W25" s="69"/>
+      <c r="X25" s="69"/>
+      <c r="Y25" s="69"/>
+      <c r="Z25" s="69"/>
+      <c r="AA25" s="70"/>
     </row>
     <row r="26" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="46"/>
-      <c r="L26" s="46"/>
-      <c r="M26" s="46"/>
-      <c r="N26" s="46"/>
-      <c r="O26" s="46"/>
-      <c r="P26" s="46"/>
-      <c r="Q26" s="46"/>
-      <c r="R26" s="46"/>
-      <c r="S26" s="46"/>
-      <c r="T26" s="46"/>
-      <c r="U26" s="46"/>
-      <c r="V26" s="46"/>
-      <c r="W26" s="46"/>
-      <c r="X26" s="46"/>
-      <c r="Y26" s="46"/>
-      <c r="Z26" s="46"/>
-      <c r="AA26" s="47"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="69"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="69"/>
+      <c r="F26" s="69"/>
+      <c r="G26" s="69"/>
+      <c r="H26" s="69"/>
+      <c r="I26" s="69"/>
+      <c r="J26" s="69"/>
+      <c r="K26" s="69"/>
+      <c r="L26" s="69"/>
+      <c r="M26" s="69"/>
+      <c r="N26" s="69"/>
+      <c r="O26" s="69"/>
+      <c r="P26" s="69"/>
+      <c r="Q26" s="69"/>
+      <c r="R26" s="69"/>
+      <c r="S26" s="69"/>
+      <c r="T26" s="69"/>
+      <c r="U26" s="69"/>
+      <c r="V26" s="69"/>
+      <c r="W26" s="69"/>
+      <c r="X26" s="69"/>
+      <c r="Y26" s="69"/>
+      <c r="Z26" s="69"/>
+      <c r="AA26" s="70"/>
     </row>
     <row r="27" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="46"/>
-      <c r="K27" s="46"/>
-      <c r="L27" s="46"/>
-      <c r="M27" s="46"/>
-      <c r="N27" s="46"/>
-      <c r="O27" s="46"/>
-      <c r="P27" s="46"/>
-      <c r="Q27" s="46"/>
-      <c r="R27" s="46"/>
-      <c r="S27" s="46"/>
-      <c r="T27" s="46"/>
-      <c r="U27" s="46"/>
-      <c r="V27" s="46"/>
-      <c r="W27" s="46"/>
-      <c r="X27" s="46"/>
-      <c r="Y27" s="46"/>
-      <c r="Z27" s="46"/>
-      <c r="AA27" s="47"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="69"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="69"/>
+      <c r="F27" s="69"/>
+      <c r="G27" s="69"/>
+      <c r="H27" s="69"/>
+      <c r="I27" s="69"/>
+      <c r="J27" s="69"/>
+      <c r="K27" s="69"/>
+      <c r="L27" s="69"/>
+      <c r="M27" s="69"/>
+      <c r="N27" s="69"/>
+      <c r="O27" s="69"/>
+      <c r="P27" s="69"/>
+      <c r="Q27" s="69"/>
+      <c r="R27" s="69"/>
+      <c r="S27" s="69"/>
+      <c r="T27" s="69"/>
+      <c r="U27" s="69"/>
+      <c r="V27" s="69"/>
+      <c r="W27" s="69"/>
+      <c r="X27" s="69"/>
+      <c r="Y27" s="69"/>
+      <c r="Z27" s="69"/>
+      <c r="AA27" s="70"/>
     </row>
     <row r="28" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="46"/>
-      <c r="I28" s="46"/>
-      <c r="J28" s="46"/>
-      <c r="K28" s="46"/>
-      <c r="L28" s="46"/>
-      <c r="M28" s="46"/>
-      <c r="N28" s="46"/>
-      <c r="O28" s="46"/>
-      <c r="P28" s="46"/>
-      <c r="Q28" s="46"/>
-      <c r="R28" s="46"/>
-      <c r="S28" s="46"/>
-      <c r="T28" s="46"/>
-      <c r="U28" s="46"/>
-      <c r="V28" s="46"/>
-      <c r="W28" s="46"/>
-      <c r="X28" s="46"/>
-      <c r="Y28" s="46"/>
-      <c r="Z28" s="46"/>
-      <c r="AA28" s="47"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="69"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="69"/>
+      <c r="H28" s="69"/>
+      <c r="I28" s="69"/>
+      <c r="J28" s="69"/>
+      <c r="K28" s="69"/>
+      <c r="L28" s="69"/>
+      <c r="M28" s="69"/>
+      <c r="N28" s="69"/>
+      <c r="O28" s="69"/>
+      <c r="P28" s="69"/>
+      <c r="Q28" s="69"/>
+      <c r="R28" s="69"/>
+      <c r="S28" s="69"/>
+      <c r="T28" s="69"/>
+      <c r="U28" s="69"/>
+      <c r="V28" s="69"/>
+      <c r="W28" s="69"/>
+      <c r="X28" s="69"/>
+      <c r="Y28" s="69"/>
+      <c r="Z28" s="69"/>
+      <c r="AA28" s="70"/>
     </row>
     <row r="29" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="46"/>
-      <c r="D29" s="46"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="46"/>
-      <c r="H29" s="46"/>
-      <c r="I29" s="46"/>
-      <c r="J29" s="46"/>
-      <c r="K29" s="46"/>
-      <c r="L29" s="46"/>
-      <c r="M29" s="46"/>
-      <c r="N29" s="46"/>
-      <c r="O29" s="46"/>
-      <c r="P29" s="46"/>
-      <c r="Q29" s="46"/>
-      <c r="R29" s="46"/>
-      <c r="S29" s="46"/>
-      <c r="T29" s="46"/>
-      <c r="U29" s="46"/>
-      <c r="V29" s="46"/>
-      <c r="W29" s="46"/>
-      <c r="X29" s="46"/>
-      <c r="Y29" s="46"/>
-      <c r="Z29" s="46"/>
-      <c r="AA29" s="47"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="69"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="69"/>
+      <c r="G29" s="69"/>
+      <c r="H29" s="69"/>
+      <c r="I29" s="69"/>
+      <c r="J29" s="69"/>
+      <c r="K29" s="69"/>
+      <c r="L29" s="69"/>
+      <c r="M29" s="69"/>
+      <c r="N29" s="69"/>
+      <c r="O29" s="69"/>
+      <c r="P29" s="69"/>
+      <c r="Q29" s="69"/>
+      <c r="R29" s="69"/>
+      <c r="S29" s="69"/>
+      <c r="T29" s="69"/>
+      <c r="U29" s="69"/>
+      <c r="V29" s="69"/>
+      <c r="W29" s="69"/>
+      <c r="X29" s="69"/>
+      <c r="Y29" s="69"/>
+      <c r="Z29" s="69"/>
+      <c r="AA29" s="70"/>
     </row>
     <row r="30" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="46"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="46"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="46"/>
-      <c r="L30" s="46"/>
-      <c r="M30" s="46"/>
-      <c r="N30" s="46"/>
-      <c r="O30" s="46"/>
-      <c r="P30" s="46"/>
-      <c r="Q30" s="46"/>
-      <c r="R30" s="46"/>
-      <c r="S30" s="46"/>
-      <c r="T30" s="46"/>
-      <c r="U30" s="46"/>
-      <c r="V30" s="46"/>
-      <c r="W30" s="46"/>
-      <c r="X30" s="46"/>
-      <c r="Y30" s="46"/>
-      <c r="Z30" s="46"/>
-      <c r="AA30" s="47"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="69"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="69"/>
+      <c r="H30" s="69"/>
+      <c r="I30" s="69"/>
+      <c r="J30" s="69"/>
+      <c r="K30" s="69"/>
+      <c r="L30" s="69"/>
+      <c r="M30" s="69"/>
+      <c r="N30" s="69"/>
+      <c r="O30" s="69"/>
+      <c r="P30" s="69"/>
+      <c r="Q30" s="69"/>
+      <c r="R30" s="69"/>
+      <c r="S30" s="69"/>
+      <c r="T30" s="69"/>
+      <c r="U30" s="69"/>
+      <c r="V30" s="69"/>
+      <c r="W30" s="69"/>
+      <c r="X30" s="69"/>
+      <c r="Y30" s="69"/>
+      <c r="Z30" s="69"/>
+      <c r="AA30" s="70"/>
     </row>
     <row r="31" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
-      <c r="B31" s="45"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="46"/>
-      <c r="E31" s="46"/>
-      <c r="F31" s="46"/>
-      <c r="G31" s="46"/>
-      <c r="H31" s="46"/>
-      <c r="I31" s="46"/>
-      <c r="J31" s="46"/>
-      <c r="K31" s="46"/>
-      <c r="L31" s="46"/>
-      <c r="M31" s="46"/>
-      <c r="N31" s="46"/>
-      <c r="O31" s="46"/>
-      <c r="P31" s="46"/>
-      <c r="Q31" s="46"/>
-      <c r="R31" s="46"/>
-      <c r="S31" s="46"/>
-      <c r="T31" s="46"/>
-      <c r="U31" s="46"/>
-      <c r="V31" s="46"/>
-      <c r="W31" s="46"/>
-      <c r="X31" s="46"/>
-      <c r="Y31" s="46"/>
-      <c r="Z31" s="46"/>
-      <c r="AA31" s="47"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="69"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="69"/>
+      <c r="H31" s="69"/>
+      <c r="I31" s="69"/>
+      <c r="J31" s="69"/>
+      <c r="K31" s="69"/>
+      <c r="L31" s="69"/>
+      <c r="M31" s="69"/>
+      <c r="N31" s="69"/>
+      <c r="O31" s="69"/>
+      <c r="P31" s="69"/>
+      <c r="Q31" s="69"/>
+      <c r="R31" s="69"/>
+      <c r="S31" s="69"/>
+      <c r="T31" s="69"/>
+      <c r="U31" s="69"/>
+      <c r="V31" s="69"/>
+      <c r="W31" s="69"/>
+      <c r="X31" s="69"/>
+      <c r="Y31" s="69"/>
+      <c r="Z31" s="69"/>
+      <c r="AA31" s="70"/>
     </row>
     <row r="32" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
       <c r="B32" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="43"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="43"/>
-      <c r="G32" s="43"/>
-      <c r="H32" s="43"/>
-      <c r="I32" s="43"/>
-      <c r="J32" s="43"/>
-      <c r="K32" s="43"/>
-      <c r="L32" s="43"/>
-      <c r="M32" s="43"/>
-      <c r="N32" s="43"/>
-      <c r="O32" s="43"/>
-      <c r="P32" s="43"/>
-      <c r="Q32" s="43"/>
-      <c r="R32" s="43"/>
-      <c r="S32" s="43"/>
-      <c r="T32" s="43"/>
-      <c r="U32" s="43"/>
-      <c r="V32" s="43"/>
-      <c r="W32" s="43"/>
-      <c r="X32" s="43"/>
-      <c r="Y32" s="43"/>
-      <c r="Z32" s="43"/>
-      <c r="AA32" s="44"/>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="71"/>
+      <c r="L32" s="71"/>
+      <c r="M32" s="71"/>
+      <c r="N32" s="71"/>
+      <c r="O32" s="71"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="71"/>
+      <c r="S32" s="71"/>
+      <c r="T32" s="71"/>
+      <c r="U32" s="71"/>
+      <c r="V32" s="71"/>
+      <c r="W32" s="71"/>
+      <c r="X32" s="71"/>
+      <c r="Y32" s="71"/>
+      <c r="Z32" s="71"/>
+      <c r="AA32" s="72"/>
     </row>
     <row r="33" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
-      <c r="B33" s="45"/>
-      <c r="C33" s="46"/>
-      <c r="D33" s="46"/>
-      <c r="E33" s="46"/>
-      <c r="F33" s="46"/>
-      <c r="G33" s="46"/>
-      <c r="H33" s="46"/>
-      <c r="I33" s="46"/>
-      <c r="J33" s="46"/>
-      <c r="K33" s="46"/>
-      <c r="L33" s="46"/>
-      <c r="M33" s="46"/>
-      <c r="N33" s="46"/>
-      <c r="O33" s="46"/>
-      <c r="P33" s="46"/>
-      <c r="Q33" s="46"/>
-      <c r="R33" s="46"/>
-      <c r="S33" s="46"/>
-      <c r="T33" s="46"/>
-      <c r="U33" s="46"/>
-      <c r="V33" s="46"/>
-      <c r="W33" s="46"/>
-      <c r="X33" s="46"/>
-      <c r="Y33" s="46"/>
-      <c r="Z33" s="46"/>
-      <c r="AA33" s="47"/>
+      <c r="B33" s="68"/>
+      <c r="C33" s="69"/>
+      <c r="D33" s="69"/>
+      <c r="E33" s="69"/>
+      <c r="F33" s="69"/>
+      <c r="G33" s="69"/>
+      <c r="H33" s="69"/>
+      <c r="I33" s="69"/>
+      <c r="J33" s="69"/>
+      <c r="K33" s="69"/>
+      <c r="L33" s="69"/>
+      <c r="M33" s="69"/>
+      <c r="N33" s="69"/>
+      <c r="O33" s="69"/>
+      <c r="P33" s="69"/>
+      <c r="Q33" s="69"/>
+      <c r="R33" s="69"/>
+      <c r="S33" s="69"/>
+      <c r="T33" s="69"/>
+      <c r="U33" s="69"/>
+      <c r="V33" s="69"/>
+      <c r="W33" s="69"/>
+      <c r="X33" s="69"/>
+      <c r="Y33" s="69"/>
+      <c r="Z33" s="69"/>
+      <c r="AA33" s="70"/>
     </row>
     <row r="34" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
-      <c r="B34" s="45"/>
-      <c r="C34" s="46"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="46"/>
-      <c r="F34" s="46"/>
-      <c r="G34" s="46"/>
-      <c r="H34" s="46"/>
-      <c r="I34" s="46"/>
-      <c r="J34" s="46"/>
-      <c r="K34" s="46"/>
-      <c r="L34" s="46"/>
-      <c r="M34" s="46"/>
-      <c r="N34" s="46"/>
-      <c r="O34" s="46"/>
-      <c r="P34" s="46"/>
-      <c r="Q34" s="46"/>
-      <c r="R34" s="46"/>
-      <c r="S34" s="46"/>
-      <c r="T34" s="46"/>
-      <c r="U34" s="46"/>
-      <c r="V34" s="46"/>
-      <c r="W34" s="46"/>
-      <c r="X34" s="46"/>
-      <c r="Y34" s="46"/>
-      <c r="Z34" s="46"/>
-      <c r="AA34" s="47"/>
+      <c r="B34" s="68"/>
+      <c r="C34" s="69"/>
+      <c r="D34" s="69"/>
+      <c r="E34" s="69"/>
+      <c r="F34" s="69"/>
+      <c r="G34" s="69"/>
+      <c r="H34" s="69"/>
+      <c r="I34" s="69"/>
+      <c r="J34" s="69"/>
+      <c r="K34" s="69"/>
+      <c r="L34" s="69"/>
+      <c r="M34" s="69"/>
+      <c r="N34" s="69"/>
+      <c r="O34" s="69"/>
+      <c r="P34" s="69"/>
+      <c r="Q34" s="69"/>
+      <c r="R34" s="69"/>
+      <c r="S34" s="69"/>
+      <c r="T34" s="69"/>
+      <c r="U34" s="69"/>
+      <c r="V34" s="69"/>
+      <c r="W34" s="69"/>
+      <c r="X34" s="69"/>
+      <c r="Y34" s="69"/>
+      <c r="Z34" s="69"/>
+      <c r="AA34" s="70"/>
     </row>
     <row r="35" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
-      <c r="B35" s="45"/>
-      <c r="C35" s="46"/>
-      <c r="D35" s="46"/>
-      <c r="E35" s="46"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="46"/>
-      <c r="H35" s="46"/>
-      <c r="I35" s="46"/>
-      <c r="J35" s="46"/>
-      <c r="K35" s="46"/>
-      <c r="L35" s="46"/>
-      <c r="M35" s="46"/>
-      <c r="N35" s="46"/>
-      <c r="O35" s="46"/>
-      <c r="P35" s="46"/>
-      <c r="Q35" s="46"/>
-      <c r="R35" s="46"/>
-      <c r="S35" s="46"/>
-      <c r="T35" s="46"/>
-      <c r="U35" s="46"/>
-      <c r="V35" s="46"/>
-      <c r="W35" s="46"/>
-      <c r="X35" s="46"/>
-      <c r="Y35" s="46"/>
-      <c r="Z35" s="46"/>
-      <c r="AA35" s="47"/>
+      <c r="B35" s="68"/>
+      <c r="C35" s="69"/>
+      <c r="D35" s="69"/>
+      <c r="E35" s="69"/>
+      <c r="F35" s="69"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
+      <c r="I35" s="69"/>
+      <c r="J35" s="69"/>
+      <c r="K35" s="69"/>
+      <c r="L35" s="69"/>
+      <c r="M35" s="69"/>
+      <c r="N35" s="69"/>
+      <c r="O35" s="69"/>
+      <c r="P35" s="69"/>
+      <c r="Q35" s="69"/>
+      <c r="R35" s="69"/>
+      <c r="S35" s="69"/>
+      <c r="T35" s="69"/>
+      <c r="U35" s="69"/>
+      <c r="V35" s="69"/>
+      <c r="W35" s="69"/>
+      <c r="X35" s="69"/>
+      <c r="Y35" s="69"/>
+      <c r="Z35" s="69"/>
+      <c r="AA35" s="70"/>
     </row>
     <row r="36" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
-      <c r="B36" s="45"/>
-      <c r="C36" s="46"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="46"/>
-      <c r="J36" s="46"/>
-      <c r="K36" s="46"/>
-      <c r="L36" s="46"/>
-      <c r="M36" s="46"/>
-      <c r="N36" s="46"/>
-      <c r="O36" s="46"/>
-      <c r="P36" s="46"/>
-      <c r="Q36" s="46"/>
-      <c r="R36" s="46"/>
-      <c r="S36" s="46"/>
-      <c r="T36" s="46"/>
-      <c r="U36" s="46"/>
-      <c r="V36" s="46"/>
-      <c r="W36" s="46"/>
-      <c r="X36" s="46"/>
-      <c r="Y36" s="46"/>
-      <c r="Z36" s="46"/>
-      <c r="AA36" s="47"/>
+      <c r="B36" s="68"/>
+      <c r="C36" s="69"/>
+      <c r="D36" s="69"/>
+      <c r="E36" s="69"/>
+      <c r="F36" s="69"/>
+      <c r="G36" s="69"/>
+      <c r="H36" s="69"/>
+      <c r="I36" s="69"/>
+      <c r="J36" s="69"/>
+      <c r="K36" s="69"/>
+      <c r="L36" s="69"/>
+      <c r="M36" s="69"/>
+      <c r="N36" s="69"/>
+      <c r="O36" s="69"/>
+      <c r="P36" s="69"/>
+      <c r="Q36" s="69"/>
+      <c r="R36" s="69"/>
+      <c r="S36" s="69"/>
+      <c r="T36" s="69"/>
+      <c r="U36" s="69"/>
+      <c r="V36" s="69"/>
+      <c r="W36" s="69"/>
+      <c r="X36" s="69"/>
+      <c r="Y36" s="69"/>
+      <c r="Z36" s="69"/>
+      <c r="AA36" s="70"/>
     </row>
     <row r="37" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
-      <c r="B37" s="45"/>
-      <c r="C37" s="46"/>
-      <c r="D37" s="46"/>
-      <c r="E37" s="46"/>
-      <c r="F37" s="46"/>
-      <c r="G37" s="46"/>
-      <c r="H37" s="46"/>
-      <c r="I37" s="46"/>
-      <c r="J37" s="46"/>
-      <c r="K37" s="46"/>
-      <c r="L37" s="46"/>
-      <c r="M37" s="46"/>
-      <c r="N37" s="46"/>
-      <c r="O37" s="46"/>
-      <c r="P37" s="46"/>
-      <c r="Q37" s="46"/>
-      <c r="R37" s="46"/>
-      <c r="S37" s="46"/>
-      <c r="T37" s="46"/>
-      <c r="U37" s="46"/>
-      <c r="V37" s="46"/>
-      <c r="W37" s="46"/>
-      <c r="X37" s="46"/>
-      <c r="Y37" s="46"/>
-      <c r="Z37" s="46"/>
-      <c r="AA37" s="47"/>
+      <c r="B37" s="68"/>
+      <c r="C37" s="69"/>
+      <c r="D37" s="69"/>
+      <c r="E37" s="69"/>
+      <c r="F37" s="69"/>
+      <c r="G37" s="69"/>
+      <c r="H37" s="69"/>
+      <c r="I37" s="69"/>
+      <c r="J37" s="69"/>
+      <c r="K37" s="69"/>
+      <c r="L37" s="69"/>
+      <c r="M37" s="69"/>
+      <c r="N37" s="69"/>
+      <c r="O37" s="69"/>
+      <c r="P37" s="69"/>
+      <c r="Q37" s="69"/>
+      <c r="R37" s="69"/>
+      <c r="S37" s="69"/>
+      <c r="T37" s="69"/>
+      <c r="U37" s="69"/>
+      <c r="V37" s="69"/>
+      <c r="W37" s="69"/>
+      <c r="X37" s="69"/>
+      <c r="Y37" s="69"/>
+      <c r="Z37" s="69"/>
+      <c r="AA37" s="70"/>
     </row>
     <row r="38" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
-      <c r="B38" s="45"/>
-      <c r="C38" s="46"/>
-      <c r="D38" s="46"/>
-      <c r="E38" s="46"/>
-      <c r="F38" s="46"/>
-      <c r="G38" s="46"/>
-      <c r="H38" s="46"/>
-      <c r="I38" s="46"/>
-      <c r="J38" s="46"/>
-      <c r="K38" s="46"/>
-      <c r="L38" s="46"/>
-      <c r="M38" s="46"/>
-      <c r="N38" s="46"/>
-      <c r="O38" s="46"/>
-      <c r="P38" s="46"/>
-      <c r="Q38" s="46"/>
-      <c r="R38" s="46"/>
-      <c r="S38" s="46"/>
-      <c r="T38" s="46"/>
-      <c r="U38" s="46"/>
-      <c r="V38" s="46"/>
-      <c r="W38" s="46"/>
-      <c r="X38" s="46"/>
-      <c r="Y38" s="46"/>
-      <c r="Z38" s="46"/>
-      <c r="AA38" s="47"/>
+      <c r="B38" s="68"/>
+      <c r="C38" s="69"/>
+      <c r="D38" s="69"/>
+      <c r="E38" s="69"/>
+      <c r="F38" s="69"/>
+      <c r="G38" s="69"/>
+      <c r="H38" s="69"/>
+      <c r="I38" s="69"/>
+      <c r="J38" s="69"/>
+      <c r="K38" s="69"/>
+      <c r="L38" s="69"/>
+      <c r="M38" s="69"/>
+      <c r="N38" s="69"/>
+      <c r="O38" s="69"/>
+      <c r="P38" s="69"/>
+      <c r="Q38" s="69"/>
+      <c r="R38" s="69"/>
+      <c r="S38" s="69"/>
+      <c r="T38" s="69"/>
+      <c r="U38" s="69"/>
+      <c r="V38" s="69"/>
+      <c r="W38" s="69"/>
+      <c r="X38" s="69"/>
+      <c r="Y38" s="69"/>
+      <c r="Z38" s="69"/>
+      <c r="AA38" s="70"/>
     </row>
     <row r="39" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
-      <c r="B39" s="45"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="46"/>
-      <c r="E39" s="46"/>
-      <c r="F39" s="46"/>
-      <c r="G39" s="46"/>
-      <c r="H39" s="46"/>
-      <c r="I39" s="46"/>
-      <c r="J39" s="46"/>
-      <c r="K39" s="46"/>
-      <c r="L39" s="46"/>
-      <c r="M39" s="46"/>
-      <c r="N39" s="46"/>
-      <c r="O39" s="46"/>
-      <c r="P39" s="46"/>
-      <c r="Q39" s="46"/>
-      <c r="R39" s="46"/>
-      <c r="S39" s="46"/>
-      <c r="T39" s="46"/>
-      <c r="U39" s="46"/>
-      <c r="V39" s="46"/>
-      <c r="W39" s="46"/>
-      <c r="X39" s="46"/>
-      <c r="Y39" s="46"/>
-      <c r="Z39" s="46"/>
-      <c r="AA39" s="47"/>
+      <c r="B39" s="68"/>
+      <c r="C39" s="69"/>
+      <c r="D39" s="69"/>
+      <c r="E39" s="69"/>
+      <c r="F39" s="69"/>
+      <c r="G39" s="69"/>
+      <c r="H39" s="69"/>
+      <c r="I39" s="69"/>
+      <c r="J39" s="69"/>
+      <c r="K39" s="69"/>
+      <c r="L39" s="69"/>
+      <c r="M39" s="69"/>
+      <c r="N39" s="69"/>
+      <c r="O39" s="69"/>
+      <c r="P39" s="69"/>
+      <c r="Q39" s="69"/>
+      <c r="R39" s="69"/>
+      <c r="S39" s="69"/>
+      <c r="T39" s="69"/>
+      <c r="U39" s="69"/>
+      <c r="V39" s="69"/>
+      <c r="W39" s="69"/>
+      <c r="X39" s="69"/>
+      <c r="Y39" s="69"/>
+      <c r="Z39" s="69"/>
+      <c r="AA39" s="70"/>
     </row>
     <row r="40" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
       <c r="B40" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="43"/>
-      <c r="D40" s="43"/>
-      <c r="E40" s="43"/>
-      <c r="F40" s="43"/>
-      <c r="G40" s="43"/>
-      <c r="H40" s="43"/>
-      <c r="I40" s="43"/>
-      <c r="J40" s="43"/>
-      <c r="K40" s="43"/>
-      <c r="L40" s="43"/>
-      <c r="M40" s="43"/>
-      <c r="N40" s="43"/>
-      <c r="O40" s="43"/>
-      <c r="P40" s="43"/>
-      <c r="Q40" s="43"/>
-      <c r="R40" s="43"/>
-      <c r="S40" s="43"/>
-      <c r="T40" s="43"/>
-      <c r="U40" s="43"/>
-      <c r="V40" s="43"/>
-      <c r="W40" s="43"/>
-      <c r="X40" s="43"/>
-      <c r="Y40" s="43"/>
-      <c r="Z40" s="43"/>
-      <c r="AA40" s="44"/>
+      <c r="C40" s="71"/>
+      <c r="D40" s="71"/>
+      <c r="E40" s="71"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="71"/>
+      <c r="I40" s="71"/>
+      <c r="J40" s="71"/>
+      <c r="K40" s="71"/>
+      <c r="L40" s="71"/>
+      <c r="M40" s="71"/>
+      <c r="N40" s="71"/>
+      <c r="O40" s="71"/>
+      <c r="P40" s="71"/>
+      <c r="Q40" s="71"/>
+      <c r="R40" s="71"/>
+      <c r="S40" s="71"/>
+      <c r="T40" s="71"/>
+      <c r="U40" s="71"/>
+      <c r="V40" s="71"/>
+      <c r="W40" s="71"/>
+      <c r="X40" s="71"/>
+      <c r="Y40" s="71"/>
+      <c r="Z40" s="71"/>
+      <c r="AA40" s="72"/>
     </row>
     <row r="41" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
-      <c r="B41" s="45"/>
-      <c r="C41" s="46"/>
-      <c r="D41" s="46"/>
-      <c r="E41" s="46"/>
-      <c r="F41" s="46"/>
-      <c r="G41" s="46"/>
-      <c r="H41" s="46"/>
-      <c r="I41" s="46"/>
-      <c r="J41" s="46"/>
-      <c r="K41" s="46"/>
-      <c r="L41" s="46"/>
-      <c r="M41" s="46"/>
-      <c r="N41" s="46"/>
-      <c r="O41" s="46"/>
-      <c r="P41" s="46"/>
-      <c r="Q41" s="46"/>
-      <c r="R41" s="46"/>
-      <c r="S41" s="46"/>
-      <c r="T41" s="46"/>
-      <c r="U41" s="46"/>
-      <c r="V41" s="46"/>
-      <c r="W41" s="46"/>
-      <c r="X41" s="46"/>
-      <c r="Y41" s="46"/>
-      <c r="Z41" s="46"/>
-      <c r="AA41" s="47"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="69"/>
+      <c r="D41" s="69"/>
+      <c r="E41" s="69"/>
+      <c r="F41" s="69"/>
+      <c r="G41" s="69"/>
+      <c r="H41" s="69"/>
+      <c r="I41" s="69"/>
+      <c r="J41" s="69"/>
+      <c r="K41" s="69"/>
+      <c r="L41" s="69"/>
+      <c r="M41" s="69"/>
+      <c r="N41" s="69"/>
+      <c r="O41" s="69"/>
+      <c r="P41" s="69"/>
+      <c r="Q41" s="69"/>
+      <c r="R41" s="69"/>
+      <c r="S41" s="69"/>
+      <c r="T41" s="69"/>
+      <c r="U41" s="69"/>
+      <c r="V41" s="69"/>
+      <c r="W41" s="69"/>
+      <c r="X41" s="69"/>
+      <c r="Y41" s="69"/>
+      <c r="Z41" s="69"/>
+      <c r="AA41" s="70"/>
     </row>
     <row r="42" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
-      <c r="B42" s="45"/>
-      <c r="C42" s="46"/>
-      <c r="D42" s="46"/>
-      <c r="E42" s="46"/>
-      <c r="F42" s="46"/>
-      <c r="G42" s="46"/>
-      <c r="H42" s="46"/>
-      <c r="I42" s="46"/>
-      <c r="J42" s="46"/>
-      <c r="K42" s="46"/>
-      <c r="L42" s="46"/>
-      <c r="M42" s="46"/>
-      <c r="N42" s="46"/>
-      <c r="O42" s="46"/>
-      <c r="P42" s="46"/>
-      <c r="Q42" s="46"/>
-      <c r="R42" s="46"/>
-      <c r="S42" s="46"/>
-      <c r="T42" s="46"/>
-      <c r="U42" s="46"/>
-      <c r="V42" s="46"/>
-      <c r="W42" s="46"/>
-      <c r="X42" s="46"/>
-      <c r="Y42" s="46"/>
-      <c r="Z42" s="46"/>
-      <c r="AA42" s="47"/>
+      <c r="B42" s="68"/>
+      <c r="C42" s="69"/>
+      <c r="D42" s="69"/>
+      <c r="E42" s="69"/>
+      <c r="F42" s="69"/>
+      <c r="G42" s="69"/>
+      <c r="H42" s="69"/>
+      <c r="I42" s="69"/>
+      <c r="J42" s="69"/>
+      <c r="K42" s="69"/>
+      <c r="L42" s="69"/>
+      <c r="M42" s="69"/>
+      <c r="N42" s="69"/>
+      <c r="O42" s="69"/>
+      <c r="P42" s="69"/>
+      <c r="Q42" s="69"/>
+      <c r="R42" s="69"/>
+      <c r="S42" s="69"/>
+      <c r="T42" s="69"/>
+      <c r="U42" s="69"/>
+      <c r="V42" s="69"/>
+      <c r="W42" s="69"/>
+      <c r="X42" s="69"/>
+      <c r="Y42" s="69"/>
+      <c r="Z42" s="69"/>
+      <c r="AA42" s="70"/>
     </row>
     <row r="43" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
-      <c r="B43" s="45"/>
-      <c r="C43" s="46"/>
-      <c r="D43" s="46"/>
-      <c r="E43" s="46"/>
-      <c r="F43" s="46"/>
-      <c r="G43" s="46"/>
-      <c r="H43" s="46"/>
-      <c r="I43" s="46"/>
-      <c r="J43" s="46"/>
-      <c r="K43" s="46"/>
-      <c r="L43" s="46"/>
-      <c r="M43" s="46"/>
-      <c r="N43" s="46"/>
-      <c r="O43" s="46"/>
-      <c r="P43" s="46"/>
-      <c r="Q43" s="46"/>
-      <c r="R43" s="46"/>
-      <c r="S43" s="46"/>
-      <c r="T43" s="46"/>
-      <c r="U43" s="46"/>
-      <c r="V43" s="46"/>
-      <c r="W43" s="46"/>
-      <c r="X43" s="46"/>
-      <c r="Y43" s="46"/>
-      <c r="Z43" s="46"/>
-      <c r="AA43" s="47"/>
+      <c r="B43" s="68"/>
+      <c r="C43" s="69"/>
+      <c r="D43" s="69"/>
+      <c r="E43" s="69"/>
+      <c r="F43" s="69"/>
+      <c r="G43" s="69"/>
+      <c r="H43" s="69"/>
+      <c r="I43" s="69"/>
+      <c r="J43" s="69"/>
+      <c r="K43" s="69"/>
+      <c r="L43" s="69"/>
+      <c r="M43" s="69"/>
+      <c r="N43" s="69"/>
+      <c r="O43" s="69"/>
+      <c r="P43" s="69"/>
+      <c r="Q43" s="69"/>
+      <c r="R43" s="69"/>
+      <c r="S43" s="69"/>
+      <c r="T43" s="69"/>
+      <c r="U43" s="69"/>
+      <c r="V43" s="69"/>
+      <c r="W43" s="69"/>
+      <c r="X43" s="69"/>
+      <c r="Y43" s="69"/>
+      <c r="Z43" s="69"/>
+      <c r="AA43" s="70"/>
     </row>
     <row r="44" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
-      <c r="B44" s="45"/>
-      <c r="C44" s="46"/>
-      <c r="D44" s="46"/>
-      <c r="E44" s="46"/>
-      <c r="F44" s="46"/>
-      <c r="G44" s="46"/>
-      <c r="H44" s="46"/>
-      <c r="I44" s="46"/>
-      <c r="J44" s="46"/>
-      <c r="K44" s="46"/>
-      <c r="L44" s="46"/>
-      <c r="M44" s="46"/>
-      <c r="N44" s="46"/>
-      <c r="O44" s="46"/>
-      <c r="P44" s="46"/>
-      <c r="Q44" s="46"/>
-      <c r="R44" s="46"/>
-      <c r="S44" s="46"/>
-      <c r="T44" s="46"/>
-      <c r="U44" s="46"/>
-      <c r="V44" s="46"/>
-      <c r="W44" s="46"/>
-      <c r="X44" s="46"/>
-      <c r="Y44" s="46"/>
-      <c r="Z44" s="46"/>
-      <c r="AA44" s="47"/>
+      <c r="B44" s="68"/>
+      <c r="C44" s="69"/>
+      <c r="D44" s="69"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="69"/>
+      <c r="G44" s="69"/>
+      <c r="H44" s="69"/>
+      <c r="I44" s="69"/>
+      <c r="J44" s="69"/>
+      <c r="K44" s="69"/>
+      <c r="L44" s="69"/>
+      <c r="M44" s="69"/>
+      <c r="N44" s="69"/>
+      <c r="O44" s="69"/>
+      <c r="P44" s="69"/>
+      <c r="Q44" s="69"/>
+      <c r="R44" s="69"/>
+      <c r="S44" s="69"/>
+      <c r="T44" s="69"/>
+      <c r="U44" s="69"/>
+      <c r="V44" s="69"/>
+      <c r="W44" s="69"/>
+      <c r="X44" s="69"/>
+      <c r="Y44" s="69"/>
+      <c r="Z44" s="69"/>
+      <c r="AA44" s="70"/>
     </row>
     <row r="45" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
-      <c r="B45" s="45"/>
-      <c r="C45" s="46"/>
-      <c r="D45" s="46"/>
-      <c r="E45" s="46"/>
-      <c r="F45" s="46"/>
-      <c r="G45" s="46"/>
-      <c r="H45" s="46"/>
-      <c r="I45" s="46"/>
-      <c r="J45" s="46"/>
-      <c r="K45" s="46"/>
-      <c r="L45" s="46"/>
-      <c r="M45" s="46"/>
-      <c r="N45" s="46"/>
-      <c r="O45" s="46"/>
-      <c r="P45" s="46"/>
-      <c r="Q45" s="46"/>
-      <c r="R45" s="46"/>
-      <c r="S45" s="46"/>
-      <c r="T45" s="46"/>
-      <c r="U45" s="46"/>
-      <c r="V45" s="46"/>
-      <c r="W45" s="46"/>
-      <c r="X45" s="46"/>
-      <c r="Y45" s="46"/>
-      <c r="Z45" s="46"/>
-      <c r="AA45" s="47"/>
+      <c r="B45" s="68"/>
+      <c r="C45" s="69"/>
+      <c r="D45" s="69"/>
+      <c r="E45" s="69"/>
+      <c r="F45" s="69"/>
+      <c r="G45" s="69"/>
+      <c r="H45" s="69"/>
+      <c r="I45" s="69"/>
+      <c r="J45" s="69"/>
+      <c r="K45" s="69"/>
+      <c r="L45" s="69"/>
+      <c r="M45" s="69"/>
+      <c r="N45" s="69"/>
+      <c r="O45" s="69"/>
+      <c r="P45" s="69"/>
+      <c r="Q45" s="69"/>
+      <c r="R45" s="69"/>
+      <c r="S45" s="69"/>
+      <c r="T45" s="69"/>
+      <c r="U45" s="69"/>
+      <c r="V45" s="69"/>
+      <c r="W45" s="69"/>
+      <c r="X45" s="69"/>
+      <c r="Y45" s="69"/>
+      <c r="Z45" s="69"/>
+      <c r="AA45" s="70"/>
     </row>
     <row r="46" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
-      <c r="B46" s="45"/>
-      <c r="C46" s="46"/>
-      <c r="D46" s="46"/>
-      <c r="E46" s="46"/>
-      <c r="F46" s="46"/>
-      <c r="G46" s="46"/>
-      <c r="H46" s="46"/>
-      <c r="I46" s="46"/>
-      <c r="J46" s="46"/>
-      <c r="K46" s="46"/>
-      <c r="L46" s="46"/>
-      <c r="M46" s="46"/>
-      <c r="N46" s="46"/>
-      <c r="O46" s="46"/>
-      <c r="P46" s="46"/>
-      <c r="Q46" s="46"/>
-      <c r="R46" s="46"/>
-      <c r="S46" s="46"/>
-      <c r="T46" s="46"/>
-      <c r="U46" s="46"/>
-      <c r="V46" s="46"/>
-      <c r="W46" s="46"/>
-      <c r="X46" s="46"/>
-      <c r="Y46" s="46"/>
-      <c r="Z46" s="46"/>
-      <c r="AA46" s="47"/>
+      <c r="B46" s="68"/>
+      <c r="C46" s="69"/>
+      <c r="D46" s="69"/>
+      <c r="E46" s="69"/>
+      <c r="F46" s="69"/>
+      <c r="G46" s="69"/>
+      <c r="H46" s="69"/>
+      <c r="I46" s="69"/>
+      <c r="J46" s="69"/>
+      <c r="K46" s="69"/>
+      <c r="L46" s="69"/>
+      <c r="M46" s="69"/>
+      <c r="N46" s="69"/>
+      <c r="O46" s="69"/>
+      <c r="P46" s="69"/>
+      <c r="Q46" s="69"/>
+      <c r="R46" s="69"/>
+      <c r="S46" s="69"/>
+      <c r="T46" s="69"/>
+      <c r="U46" s="69"/>
+      <c r="V46" s="69"/>
+      <c r="W46" s="69"/>
+      <c r="X46" s="69"/>
+      <c r="Y46" s="69"/>
+      <c r="Z46" s="69"/>
+      <c r="AA46" s="70"/>
     </row>
     <row r="47" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
-      <c r="B47" s="45"/>
-      <c r="C47" s="46"/>
-      <c r="D47" s="46"/>
-      <c r="E47" s="46"/>
-      <c r="F47" s="46"/>
-      <c r="G47" s="46"/>
-      <c r="H47" s="46"/>
-      <c r="I47" s="46"/>
-      <c r="J47" s="46"/>
-      <c r="K47" s="46"/>
-      <c r="L47" s="46"/>
-      <c r="M47" s="46"/>
-      <c r="N47" s="46"/>
-      <c r="O47" s="46"/>
-      <c r="P47" s="46"/>
-      <c r="Q47" s="46"/>
-      <c r="R47" s="46"/>
-      <c r="S47" s="46"/>
-      <c r="T47" s="46"/>
-      <c r="U47" s="46"/>
-      <c r="V47" s="46"/>
-      <c r="W47" s="46"/>
-      <c r="X47" s="46"/>
-      <c r="Y47" s="46"/>
-      <c r="Z47" s="46"/>
-      <c r="AA47" s="47"/>
+      <c r="B47" s="68"/>
+      <c r="C47" s="69"/>
+      <c r="D47" s="69"/>
+      <c r="E47" s="69"/>
+      <c r="F47" s="69"/>
+      <c r="G47" s="69"/>
+      <c r="H47" s="69"/>
+      <c r="I47" s="69"/>
+      <c r="J47" s="69"/>
+      <c r="K47" s="69"/>
+      <c r="L47" s="69"/>
+      <c r="M47" s="69"/>
+      <c r="N47" s="69"/>
+      <c r="O47" s="69"/>
+      <c r="P47" s="69"/>
+      <c r="Q47" s="69"/>
+      <c r="R47" s="69"/>
+      <c r="S47" s="69"/>
+      <c r="T47" s="69"/>
+      <c r="U47" s="69"/>
+      <c r="V47" s="69"/>
+      <c r="W47" s="69"/>
+      <c r="X47" s="69"/>
+      <c r="Y47" s="69"/>
+      <c r="Z47" s="69"/>
+      <c r="AA47" s="70"/>
     </row>
     <row r="48" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
-      <c r="B48" s="61" t="s">
+      <c r="B48" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="62"/>
-      <c r="D48" s="62"/>
-      <c r="E48" s="62"/>
-      <c r="F48" s="62"/>
-      <c r="G48" s="62"/>
-      <c r="H48" s="62"/>
-      <c r="I48" s="62"/>
-      <c r="J48" s="62"/>
-      <c r="K48" s="62"/>
-      <c r="L48" s="62"/>
-      <c r="M48" s="62"/>
-      <c r="N48" s="62"/>
-      <c r="O48" s="62"/>
-      <c r="P48" s="62"/>
-      <c r="Q48" s="62"/>
-      <c r="R48" s="62"/>
-      <c r="S48" s="62"/>
-      <c r="T48" s="62"/>
-      <c r="U48" s="62"/>
-      <c r="V48" s="62"/>
-      <c r="W48" s="62"/>
-      <c r="X48" s="62"/>
-      <c r="Y48" s="62"/>
-      <c r="Z48" s="62"/>
-      <c r="AA48" s="63"/>
+      <c r="C48" s="73"/>
+      <c r="D48" s="73"/>
+      <c r="E48" s="73"/>
+      <c r="F48" s="73"/>
+      <c r="G48" s="73"/>
+      <c r="H48" s="73"/>
+      <c r="I48" s="73"/>
+      <c r="J48" s="73"/>
+      <c r="K48" s="73"/>
+      <c r="L48" s="73"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="73"/>
+      <c r="O48" s="73"/>
+      <c r="P48" s="73"/>
+      <c r="Q48" s="73"/>
+      <c r="R48" s="73"/>
+      <c r="S48" s="73"/>
+      <c r="T48" s="73"/>
+      <c r="U48" s="73"/>
+      <c r="V48" s="73"/>
+      <c r="W48" s="73"/>
+      <c r="X48" s="73"/>
+      <c r="Y48" s="73"/>
+      <c r="Z48" s="73"/>
+      <c r="AA48" s="74"/>
     </row>
     <row r="49" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="30"/>
-      <c r="B49" s="45"/>
-      <c r="C49" s="46"/>
-      <c r="D49" s="46"/>
-      <c r="E49" s="46"/>
-      <c r="F49" s="46"/>
-      <c r="G49" s="46"/>
-      <c r="H49" s="46"/>
-      <c r="I49" s="46"/>
-      <c r="J49" s="46"/>
-      <c r="K49" s="46"/>
-      <c r="L49" s="46"/>
-      <c r="M49" s="46"/>
-      <c r="N49" s="46"/>
-      <c r="O49" s="46"/>
-      <c r="P49" s="46"/>
-      <c r="Q49" s="46"/>
-      <c r="R49" s="46"/>
-      <c r="S49" s="46"/>
-      <c r="T49" s="46"/>
-      <c r="U49" s="46"/>
-      <c r="V49" s="46"/>
-      <c r="W49" s="46"/>
-      <c r="X49" s="46"/>
-      <c r="Y49" s="46"/>
-      <c r="Z49" s="46"/>
-      <c r="AA49" s="47"/>
+      <c r="B49" s="68"/>
+      <c r="C49" s="69"/>
+      <c r="D49" s="69"/>
+      <c r="E49" s="69"/>
+      <c r="F49" s="69"/>
+      <c r="G49" s="69"/>
+      <c r="H49" s="69"/>
+      <c r="I49" s="69"/>
+      <c r="J49" s="69"/>
+      <c r="K49" s="69"/>
+      <c r="L49" s="69"/>
+      <c r="M49" s="69"/>
+      <c r="N49" s="69"/>
+      <c r="O49" s="69"/>
+      <c r="P49" s="69"/>
+      <c r="Q49" s="69"/>
+      <c r="R49" s="69"/>
+      <c r="S49" s="69"/>
+      <c r="T49" s="69"/>
+      <c r="U49" s="69"/>
+      <c r="V49" s="69"/>
+      <c r="W49" s="69"/>
+      <c r="X49" s="69"/>
+      <c r="Y49" s="69"/>
+      <c r="Z49" s="69"/>
+      <c r="AA49" s="70"/>
     </row>
     <row r="50" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="30"/>
-      <c r="B50" s="45"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="46"/>
-      <c r="E50" s="46"/>
-      <c r="F50" s="46"/>
-      <c r="G50" s="46"/>
-      <c r="H50" s="46"/>
-      <c r="I50" s="46"/>
-      <c r="J50" s="46"/>
-      <c r="K50" s="46"/>
-      <c r="L50" s="46"/>
-      <c r="M50" s="46"/>
-      <c r="N50" s="46"/>
-      <c r="O50" s="46"/>
-      <c r="P50" s="46"/>
-      <c r="Q50" s="46"/>
-      <c r="R50" s="46"/>
-      <c r="S50" s="46"/>
-      <c r="T50" s="46"/>
-      <c r="U50" s="46"/>
-      <c r="V50" s="46"/>
-      <c r="W50" s="46"/>
-      <c r="X50" s="46"/>
-      <c r="Y50" s="46"/>
-      <c r="Z50" s="46"/>
-      <c r="AA50" s="47"/>
+      <c r="B50" s="68"/>
+      <c r="C50" s="69"/>
+      <c r="D50" s="69"/>
+      <c r="E50" s="69"/>
+      <c r="F50" s="69"/>
+      <c r="G50" s="69"/>
+      <c r="H50" s="69"/>
+      <c r="I50" s="69"/>
+      <c r="J50" s="69"/>
+      <c r="K50" s="69"/>
+      <c r="L50" s="69"/>
+      <c r="M50" s="69"/>
+      <c r="N50" s="69"/>
+      <c r="O50" s="69"/>
+      <c r="P50" s="69"/>
+      <c r="Q50" s="69"/>
+      <c r="R50" s="69"/>
+      <c r="S50" s="69"/>
+      <c r="T50" s="69"/>
+      <c r="U50" s="69"/>
+      <c r="V50" s="69"/>
+      <c r="W50" s="69"/>
+      <c r="X50" s="69"/>
+      <c r="Y50" s="69"/>
+      <c r="Z50" s="69"/>
+      <c r="AA50" s="70"/>
     </row>
     <row r="51" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="30"/>
-      <c r="B51" s="45"/>
-      <c r="C51" s="46"/>
-      <c r="D51" s="46"/>
-      <c r="E51" s="46"/>
-      <c r="F51" s="46"/>
-      <c r="G51" s="46"/>
-      <c r="H51" s="46"/>
-      <c r="I51" s="46"/>
-      <c r="J51" s="46"/>
-      <c r="K51" s="46"/>
-      <c r="L51" s="46"/>
-      <c r="M51" s="46"/>
-      <c r="N51" s="46"/>
-      <c r="O51" s="46"/>
-      <c r="P51" s="46"/>
-      <c r="Q51" s="46"/>
-      <c r="R51" s="46"/>
-      <c r="S51" s="46"/>
-      <c r="T51" s="46"/>
-      <c r="U51" s="46"/>
-      <c r="V51" s="46"/>
-      <c r="W51" s="46"/>
-      <c r="X51" s="46"/>
-      <c r="Y51" s="46"/>
-      <c r="Z51" s="46"/>
-      <c r="AA51" s="47"/>
+      <c r="B51" s="68"/>
+      <c r="C51" s="69"/>
+      <c r="D51" s="69"/>
+      <c r="E51" s="69"/>
+      <c r="F51" s="69"/>
+      <c r="G51" s="69"/>
+      <c r="H51" s="69"/>
+      <c r="I51" s="69"/>
+      <c r="J51" s="69"/>
+      <c r="K51" s="69"/>
+      <c r="L51" s="69"/>
+      <c r="M51" s="69"/>
+      <c r="N51" s="69"/>
+      <c r="O51" s="69"/>
+      <c r="P51" s="69"/>
+      <c r="Q51" s="69"/>
+      <c r="R51" s="69"/>
+      <c r="S51" s="69"/>
+      <c r="T51" s="69"/>
+      <c r="U51" s="69"/>
+      <c r="V51" s="69"/>
+      <c r="W51" s="69"/>
+      <c r="X51" s="69"/>
+      <c r="Y51" s="69"/>
+      <c r="Z51" s="69"/>
+      <c r="AA51" s="70"/>
     </row>
     <row r="52" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="30"/>
-      <c r="B52" s="45"/>
-      <c r="C52" s="46"/>
-      <c r="D52" s="46"/>
-      <c r="E52" s="46"/>
-      <c r="F52" s="46"/>
-      <c r="G52" s="46"/>
-      <c r="H52" s="46"/>
-      <c r="I52" s="46"/>
-      <c r="J52" s="46"/>
-      <c r="K52" s="46"/>
-      <c r="L52" s="46"/>
-      <c r="M52" s="46"/>
-      <c r="N52" s="46"/>
-      <c r="O52" s="46"/>
-      <c r="P52" s="46"/>
-      <c r="Q52" s="46"/>
-      <c r="R52" s="46"/>
-      <c r="S52" s="46"/>
-      <c r="T52" s="46"/>
-      <c r="U52" s="46"/>
-      <c r="V52" s="46"/>
-      <c r="W52" s="46"/>
-      <c r="X52" s="46"/>
-      <c r="Y52" s="46"/>
-      <c r="Z52" s="46"/>
-      <c r="AA52" s="47"/>
+      <c r="B52" s="68"/>
+      <c r="C52" s="69"/>
+      <c r="D52" s="69"/>
+      <c r="E52" s="69"/>
+      <c r="F52" s="69"/>
+      <c r="G52" s="69"/>
+      <c r="H52" s="69"/>
+      <c r="I52" s="69"/>
+      <c r="J52" s="69"/>
+      <c r="K52" s="69"/>
+      <c r="L52" s="69"/>
+      <c r="M52" s="69"/>
+      <c r="N52" s="69"/>
+      <c r="O52" s="69"/>
+      <c r="P52" s="69"/>
+      <c r="Q52" s="69"/>
+      <c r="R52" s="69"/>
+      <c r="S52" s="69"/>
+      <c r="T52" s="69"/>
+      <c r="U52" s="69"/>
+      <c r="V52" s="69"/>
+      <c r="W52" s="69"/>
+      <c r="X52" s="69"/>
+      <c r="Y52" s="69"/>
+      <c r="Z52" s="69"/>
+      <c r="AA52" s="70"/>
     </row>
     <row r="53" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="30"/>
-      <c r="B53" s="45"/>
-      <c r="C53" s="46"/>
-      <c r="D53" s="46"/>
-      <c r="E53" s="46"/>
-      <c r="F53" s="46"/>
-      <c r="G53" s="46"/>
-      <c r="H53" s="46"/>
-      <c r="I53" s="46"/>
-      <c r="J53" s="46"/>
-      <c r="K53" s="46"/>
-      <c r="L53" s="46"/>
-      <c r="M53" s="46"/>
-      <c r="N53" s="46"/>
-      <c r="O53" s="46"/>
-      <c r="P53" s="46"/>
-      <c r="Q53" s="46"/>
-      <c r="R53" s="46"/>
-      <c r="S53" s="46"/>
-      <c r="T53" s="46"/>
-      <c r="U53" s="46"/>
-      <c r="V53" s="46"/>
-      <c r="W53" s="46"/>
-      <c r="X53" s="46"/>
-      <c r="Y53" s="46"/>
-      <c r="Z53" s="46"/>
-      <c r="AA53" s="47"/>
+      <c r="B53" s="68"/>
+      <c r="C53" s="69"/>
+      <c r="D53" s="69"/>
+      <c r="E53" s="69"/>
+      <c r="F53" s="69"/>
+      <c r="G53" s="69"/>
+      <c r="H53" s="69"/>
+      <c r="I53" s="69"/>
+      <c r="J53" s="69"/>
+      <c r="K53" s="69"/>
+      <c r="L53" s="69"/>
+      <c r="M53" s="69"/>
+      <c r="N53" s="69"/>
+      <c r="O53" s="69"/>
+      <c r="P53" s="69"/>
+      <c r="Q53" s="69"/>
+      <c r="R53" s="69"/>
+      <c r="S53" s="69"/>
+      <c r="T53" s="69"/>
+      <c r="U53" s="69"/>
+      <c r="V53" s="69"/>
+      <c r="W53" s="69"/>
+      <c r="X53" s="69"/>
+      <c r="Y53" s="69"/>
+      <c r="Z53" s="69"/>
+      <c r="AA53" s="70"/>
     </row>
     <row r="54" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="30"/>
-      <c r="B54" s="45"/>
-      <c r="C54" s="46"/>
-      <c r="D54" s="46"/>
-      <c r="E54" s="46"/>
-      <c r="F54" s="46"/>
-      <c r="G54" s="46"/>
-      <c r="H54" s="46"/>
-      <c r="I54" s="46"/>
-      <c r="J54" s="46"/>
-      <c r="K54" s="46"/>
-      <c r="L54" s="46"/>
-      <c r="M54" s="46"/>
-      <c r="N54" s="46"/>
-      <c r="O54" s="46"/>
-      <c r="P54" s="46"/>
-      <c r="Q54" s="46"/>
-      <c r="R54" s="46"/>
-      <c r="S54" s="46"/>
-      <c r="T54" s="46"/>
-      <c r="U54" s="46"/>
-      <c r="V54" s="46"/>
-      <c r="W54" s="46"/>
-      <c r="X54" s="46"/>
-      <c r="Y54" s="46"/>
-      <c r="Z54" s="46"/>
-      <c r="AA54" s="47"/>
+      <c r="B54" s="68"/>
+      <c r="C54" s="69"/>
+      <c r="D54" s="69"/>
+      <c r="E54" s="69"/>
+      <c r="F54" s="69"/>
+      <c r="G54" s="69"/>
+      <c r="H54" s="69"/>
+      <c r="I54" s="69"/>
+      <c r="J54" s="69"/>
+      <c r="K54" s="69"/>
+      <c r="L54" s="69"/>
+      <c r="M54" s="69"/>
+      <c r="N54" s="69"/>
+      <c r="O54" s="69"/>
+      <c r="P54" s="69"/>
+      <c r="Q54" s="69"/>
+      <c r="R54" s="69"/>
+      <c r="S54" s="69"/>
+      <c r="T54" s="69"/>
+      <c r="U54" s="69"/>
+      <c r="V54" s="69"/>
+      <c r="W54" s="69"/>
+      <c r="X54" s="69"/>
+      <c r="Y54" s="69"/>
+      <c r="Z54" s="69"/>
+      <c r="AA54" s="70"/>
     </row>
     <row r="55" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="30"/>
-      <c r="B55" s="45"/>
-      <c r="C55" s="46"/>
-      <c r="D55" s="46"/>
-      <c r="E55" s="46"/>
-      <c r="F55" s="46"/>
-      <c r="G55" s="46"/>
-      <c r="H55" s="46"/>
-      <c r="I55" s="46"/>
-      <c r="J55" s="46"/>
-      <c r="K55" s="46"/>
-      <c r="L55" s="46"/>
-      <c r="M55" s="46"/>
-      <c r="N55" s="46"/>
-      <c r="O55" s="46"/>
-      <c r="P55" s="46"/>
-      <c r="Q55" s="46"/>
-      <c r="R55" s="46"/>
-      <c r="S55" s="46"/>
-      <c r="T55" s="46"/>
-      <c r="U55" s="46"/>
-      <c r="V55" s="46"/>
-      <c r="W55" s="46"/>
-      <c r="X55" s="46"/>
-      <c r="Y55" s="46"/>
-      <c r="Z55" s="46"/>
-      <c r="AA55" s="47"/>
+      <c r="B55" s="68"/>
+      <c r="C55" s="69"/>
+      <c r="D55" s="69"/>
+      <c r="E55" s="69"/>
+      <c r="F55" s="69"/>
+      <c r="G55" s="69"/>
+      <c r="H55" s="69"/>
+      <c r="I55" s="69"/>
+      <c r="J55" s="69"/>
+      <c r="K55" s="69"/>
+      <c r="L55" s="69"/>
+      <c r="M55" s="69"/>
+      <c r="N55" s="69"/>
+      <c r="O55" s="69"/>
+      <c r="P55" s="69"/>
+      <c r="Q55" s="69"/>
+      <c r="R55" s="69"/>
+      <c r="S55" s="69"/>
+      <c r="T55" s="69"/>
+      <c r="U55" s="69"/>
+      <c r="V55" s="69"/>
+      <c r="W55" s="69"/>
+      <c r="X55" s="69"/>
+      <c r="Y55" s="69"/>
+      <c r="Z55" s="69"/>
+      <c r="AA55" s="70"/>
     </row>
     <row r="56" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
@@ -3013,31 +3033,31 @@
     </row>
     <row r="59" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
-      <c r="B59" s="66"/>
-      <c r="C59" s="66"/>
-      <c r="D59" s="66"/>
-      <c r="E59" s="66"/>
-      <c r="F59" s="66"/>
-      <c r="G59" s="66"/>
-      <c r="H59" s="66"/>
-      <c r="I59" s="66"/>
-      <c r="J59" s="66"/>
-      <c r="K59" s="67"/>
-      <c r="L59" s="68"/>
-      <c r="M59" s="68"/>
-      <c r="N59" s="68"/>
-      <c r="O59" s="68"/>
-      <c r="P59" s="68"/>
-      <c r="Q59" s="68"/>
-      <c r="R59" s="69"/>
-      <c r="S59" s="69"/>
-      <c r="T59" s="69"/>
-      <c r="U59" s="69"/>
-      <c r="V59" s="69"/>
-      <c r="W59" s="69"/>
-      <c r="X59" s="69"/>
-      <c r="Y59" s="70"/>
-      <c r="Z59" s="70"/>
+      <c r="B59" s="61"/>
+      <c r="C59" s="61"/>
+      <c r="D59" s="61"/>
+      <c r="E59" s="61"/>
+      <c r="F59" s="61"/>
+      <c r="G59" s="61"/>
+      <c r="H59" s="61"/>
+      <c r="I59" s="61"/>
+      <c r="J59" s="61"/>
+      <c r="K59" s="62"/>
+      <c r="L59" s="63"/>
+      <c r="M59" s="63"/>
+      <c r="N59" s="63"/>
+      <c r="O59" s="63"/>
+      <c r="P59" s="63"/>
+      <c r="Q59" s="63"/>
+      <c r="R59" s="64"/>
+      <c r="S59" s="64"/>
+      <c r="T59" s="64"/>
+      <c r="U59" s="64"/>
+      <c r="V59" s="64"/>
+      <c r="W59" s="64"/>
+      <c r="X59" s="64"/>
+      <c r="Y59" s="65"/>
+      <c r="Z59" s="65"/>
       <c r="AA59" s="1"/>
     </row>
     <row r="60" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">

--- a/static/templates/tec02-A_template.xlsx
+++ b/static/templates/tec02-A_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\diseño-afk\static\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98859015-B9ED-41CE-91F3-10E462BC177F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F0F812-236E-4D30-BE40-97F7DB213F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -578,7 +578,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -693,31 +693,43 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -731,25 +743,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -757,25 +755,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -847,8 +843,8 @@
       <xdr:row>53</xdr:row>
       <xdr:rowOff>64957</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="5" name="Ink 4">
@@ -867,7 +863,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="5" name="Ink 4">
@@ -912,8 +908,8 @@
       <xdr:row>74</xdr:row>
       <xdr:rowOff>50520</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="6" name="Ink 5">
@@ -932,7 +928,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="6" name="Ink 5">
@@ -977,8 +973,8 @@
       <xdr:row>59</xdr:row>
       <xdr:rowOff>1280</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="8" name="Ink 7">
@@ -997,7 +993,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="8" name="Ink 7">
@@ -1381,125 +1377,125 @@
     </row>
     <row r="3" spans="1:27" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="41"/>
-      <c r="R3" s="41"/>
-      <c r="S3" s="41"/>
-      <c r="T3" s="41"/>
-      <c r="U3" s="41"/>
-      <c r="V3" s="41"/>
-      <c r="W3" s="41"/>
-      <c r="X3" s="41"/>
-      <c r="Y3" s="41"/>
-      <c r="Z3" s="41"/>
-      <c r="AA3" s="41"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="56"/>
+      <c r="N3" s="56"/>
+      <c r="O3" s="56"/>
+      <c r="P3" s="56"/>
+      <c r="Q3" s="56"/>
+      <c r="R3" s="56"/>
+      <c r="S3" s="56"/>
+      <c r="T3" s="56"/>
+      <c r="U3" s="56"/>
+      <c r="V3" s="56"/>
+      <c r="W3" s="56"/>
+      <c r="X3" s="56"/>
+      <c r="Y3" s="56"/>
+      <c r="Z3" s="56"/>
+      <c r="AA3" s="56"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="41"/>
-      <c r="R4" s="41"/>
-      <c r="S4" s="41"/>
-      <c r="T4" s="41"/>
-      <c r="U4" s="41"/>
-      <c r="V4" s="41"/>
-      <c r="W4" s="41"/>
-      <c r="X4" s="41"/>
-      <c r="Y4" s="41"/>
-      <c r="Z4" s="41"/>
-      <c r="AA4" s="41"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="56"/>
+      <c r="N4" s="56"/>
+      <c r="O4" s="56"/>
+      <c r="P4" s="56"/>
+      <c r="Q4" s="56"/>
+      <c r="R4" s="56"/>
+      <c r="S4" s="56"/>
+      <c r="T4" s="56"/>
+      <c r="U4" s="56"/>
+      <c r="V4" s="56"/>
+      <c r="W4" s="56"/>
+      <c r="X4" s="56"/>
+      <c r="Y4" s="56"/>
+      <c r="Z4" s="56"/>
+      <c r="AA4" s="56"/>
     </row>
     <row r="5" spans="1:27" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
-      <c r="L5" s="41"/>
-      <c r="M5" s="41"/>
-      <c r="N5" s="41"/>
-      <c r="O5" s="41"/>
-      <c r="P5" s="41"/>
-      <c r="Q5" s="41"/>
-      <c r="R5" s="41"/>
-      <c r="S5" s="41"/>
-      <c r="T5" s="41"/>
-      <c r="U5" s="41"/>
-      <c r="V5" s="41"/>
-      <c r="W5" s="41"/>
-      <c r="X5" s="41"/>
-      <c r="Y5" s="41"/>
-      <c r="Z5" s="41"/>
-      <c r="AA5" s="41"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="56"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="56"/>
+      <c r="P5" s="56"/>
+      <c r="Q5" s="56"/>
+      <c r="R5" s="56"/>
+      <c r="S5" s="56"/>
+      <c r="T5" s="56"/>
+      <c r="U5" s="56"/>
+      <c r="V5" s="56"/>
+      <c r="W5" s="56"/>
+      <c r="X5" s="56"/>
+      <c r="Y5" s="56"/>
+      <c r="Z5" s="56"/>
+      <c r="AA5" s="56"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
-      <c r="B6" s="52" t="s">
+      <c r="B6" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="41"/>
-      <c r="R6" s="41"/>
-      <c r="S6" s="41"/>
-      <c r="T6" s="41"/>
-      <c r="U6" s="41"/>
-      <c r="V6" s="41"/>
-      <c r="W6" s="41"/>
-      <c r="X6" s="41"/>
-      <c r="Y6" s="41"/>
-      <c r="Z6" s="41"/>
-      <c r="AA6" s="41"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="56"/>
+      <c r="N6" s="56"/>
+      <c r="O6" s="56"/>
+      <c r="P6" s="56"/>
+      <c r="Q6" s="56"/>
+      <c r="R6" s="56"/>
+      <c r="S6" s="56"/>
+      <c r="T6" s="56"/>
+      <c r="U6" s="56"/>
+      <c r="V6" s="56"/>
+      <c r="W6" s="56"/>
+      <c r="X6" s="56"/>
+      <c r="Y6" s="56"/>
+      <c r="Z6" s="56"/>
+      <c r="AA6" s="56"/>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2"/>
@@ -1598,25 +1594,25 @@
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="47"/>
-      <c r="K10" s="47"/>
-      <c r="L10" s="47"/>
-      <c r="M10" s="47"/>
-      <c r="N10" s="47"/>
-      <c r="O10" s="47"/>
-      <c r="P10" s="47"/>
-      <c r="Q10" s="47"/>
-      <c r="R10" s="47"/>
-      <c r="S10" s="47"/>
-      <c r="T10" s="47"/>
-      <c r="U10" s="47"/>
-      <c r="V10" s="47"/>
-      <c r="W10" s="47"/>
-      <c r="X10" s="47"/>
-      <c r="Y10" s="47"/>
-      <c r="Z10" s="48"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="53"/>
+      <c r="K10" s="53"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="53"/>
+      <c r="N10" s="53"/>
+      <c r="O10" s="53"/>
+      <c r="P10" s="53"/>
+      <c r="Q10" s="53"/>
+      <c r="R10" s="53"/>
+      <c r="S10" s="53"/>
+      <c r="T10" s="53"/>
+      <c r="U10" s="53"/>
+      <c r="V10" s="53"/>
+      <c r="W10" s="53"/>
+      <c r="X10" s="53"/>
+      <c r="Y10" s="53"/>
+      <c r="Z10" s="54"/>
       <c r="AA10" s="11"/>
     </row>
     <row r="11" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1658,27 +1654,27 @@
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="47"/>
-      <c r="K12" s="47"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="47"/>
-      <c r="N12" s="47"/>
-      <c r="O12" s="47"/>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="47"/>
-      <c r="R12" s="47"/>
-      <c r="S12" s="47"/>
-      <c r="T12" s="48"/>
+      <c r="H12" s="62"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="53"/>
+      <c r="M12" s="53"/>
+      <c r="N12" s="53"/>
+      <c r="O12" s="53"/>
+      <c r="P12" s="53"/>
+      <c r="Q12" s="53"/>
+      <c r="R12" s="53"/>
+      <c r="S12" s="53"/>
+      <c r="T12" s="54"/>
       <c r="U12" s="13"/>
       <c r="V12" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="W12" s="53"/>
-      <c r="X12" s="47"/>
-      <c r="Y12" s="47"/>
-      <c r="Z12" s="48"/>
+      <c r="W12" s="59"/>
+      <c r="X12" s="53"/>
+      <c r="Y12" s="53"/>
+      <c r="Z12" s="54"/>
       <c r="AA12" s="15"/>
     </row>
     <row r="13" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1712,63 +1708,63 @@
     </row>
     <row r="14" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
-      <c r="B14" s="59" t="s">
+      <c r="B14" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="57"/>
-      <c r="K14" s="57"/>
-      <c r="L14" s="57"/>
-      <c r="M14" s="57"/>
-      <c r="N14" s="57"/>
-      <c r="O14" s="57"/>
-      <c r="P14" s="57"/>
-      <c r="Q14" s="57"/>
-      <c r="R14" s="57"/>
-      <c r="S14" s="57"/>
-      <c r="T14" s="57"/>
-      <c r="U14" s="57"/>
-      <c r="V14" s="57"/>
-      <c r="W14" s="57"/>
-      <c r="X14" s="57"/>
-      <c r="Y14" s="57"/>
-      <c r="Z14" s="57"/>
-      <c r="AA14" s="58"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="47"/>
+      <c r="N14" s="47"/>
+      <c r="O14" s="47"/>
+      <c r="P14" s="47"/>
+      <c r="Q14" s="47"/>
+      <c r="R14" s="47"/>
+      <c r="S14" s="47"/>
+      <c r="T14" s="47"/>
+      <c r="U14" s="47"/>
+      <c r="V14" s="47"/>
+      <c r="W14" s="47"/>
+      <c r="X14" s="47"/>
+      <c r="Y14" s="47"/>
+      <c r="Z14" s="47"/>
+      <c r="AA14" s="48"/>
     </row>
     <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
-      <c r="B15" s="60"/>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="44"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="44"/>
-      <c r="L15" s="44"/>
-      <c r="M15" s="44"/>
-      <c r="N15" s="44"/>
-      <c r="O15" s="44"/>
-      <c r="P15" s="44"/>
-      <c r="Q15" s="44"/>
-      <c r="R15" s="44"/>
-      <c r="S15" s="44"/>
-      <c r="T15" s="44"/>
-      <c r="U15" s="44"/>
-      <c r="V15" s="44"/>
-      <c r="W15" s="44"/>
-      <c r="X15" s="44"/>
-      <c r="Y15" s="44"/>
-      <c r="Z15" s="44"/>
-      <c r="AA15" s="45"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="50"/>
+      <c r="J15" s="50"/>
+      <c r="K15" s="50"/>
+      <c r="L15" s="50"/>
+      <c r="M15" s="50"/>
+      <c r="N15" s="50"/>
+      <c r="O15" s="50"/>
+      <c r="P15" s="50"/>
+      <c r="Q15" s="50"/>
+      <c r="R15" s="50"/>
+      <c r="S15" s="50"/>
+      <c r="T15" s="50"/>
+      <c r="U15" s="50"/>
+      <c r="V15" s="50"/>
+      <c r="W15" s="50"/>
+      <c r="X15" s="50"/>
+      <c r="Y15" s="50"/>
+      <c r="Z15" s="50"/>
+      <c r="AA15" s="51"/>
     </row>
     <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
@@ -1801,33 +1797,33 @@
     </row>
     <row r="17" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
-      <c r="B17" s="51" t="s">
+      <c r="B17" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="47"/>
-      <c r="J17" s="47"/>
-      <c r="K17" s="47"/>
-      <c r="L17" s="47"/>
-      <c r="M17" s="47"/>
-      <c r="N17" s="47"/>
-      <c r="O17" s="47"/>
-      <c r="P17" s="47"/>
-      <c r="Q17" s="47"/>
-      <c r="R17" s="47"/>
-      <c r="S17" s="47"/>
-      <c r="T17" s="47"/>
-      <c r="U17" s="47"/>
-      <c r="V17" s="47"/>
-      <c r="W17" s="47"/>
-      <c r="X17" s="47"/>
-      <c r="Y17" s="47"/>
-      <c r="Z17" s="48"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="56"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="53"/>
+      <c r="K17" s="53"/>
+      <c r="L17" s="53"/>
+      <c r="M17" s="53"/>
+      <c r="N17" s="53"/>
+      <c r="O17" s="53"/>
+      <c r="P17" s="53"/>
+      <c r="Q17" s="53"/>
+      <c r="R17" s="53"/>
+      <c r="S17" s="53"/>
+      <c r="T17" s="53"/>
+      <c r="U17" s="53"/>
+      <c r="V17" s="53"/>
+      <c r="W17" s="53"/>
+      <c r="X17" s="53"/>
+      <c r="Y17" s="53"/>
+      <c r="Z17" s="54"/>
       <c r="AA17" s="24"/>
     </row>
     <row r="18" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1861,33 +1857,33 @@
     </row>
     <row r="19" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
-      <c r="B19" s="51" t="s">
+      <c r="B19" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="47"/>
-      <c r="J19" s="47"/>
-      <c r="K19" s="47"/>
-      <c r="L19" s="47"/>
-      <c r="M19" s="47"/>
-      <c r="N19" s="47"/>
-      <c r="O19" s="47"/>
-      <c r="P19" s="47"/>
-      <c r="Q19" s="47"/>
-      <c r="R19" s="47"/>
-      <c r="S19" s="47"/>
-      <c r="T19" s="47"/>
-      <c r="U19" s="47"/>
-      <c r="V19" s="47"/>
-      <c r="W19" s="47"/>
-      <c r="X19" s="47"/>
-      <c r="Y19" s="47"/>
-      <c r="Z19" s="48"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="56"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="53"/>
+      <c r="L19" s="53"/>
+      <c r="M19" s="53"/>
+      <c r="N19" s="53"/>
+      <c r="O19" s="53"/>
+      <c r="P19" s="53"/>
+      <c r="Q19" s="53"/>
+      <c r="R19" s="53"/>
+      <c r="S19" s="53"/>
+      <c r="T19" s="53"/>
+      <c r="U19" s="53"/>
+      <c r="V19" s="53"/>
+      <c r="W19" s="53"/>
+      <c r="X19" s="53"/>
+      <c r="Y19" s="53"/>
+      <c r="Z19" s="54"/>
       <c r="AA19" s="24"/>
     </row>
     <row r="20" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1921,33 +1917,33 @@
     </row>
     <row r="21" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
-      <c r="B21" s="51" t="s">
+      <c r="B21" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="47"/>
-      <c r="K21" s="47"/>
-      <c r="L21" s="47"/>
-      <c r="M21" s="47"/>
-      <c r="N21" s="47"/>
-      <c r="O21" s="47"/>
-      <c r="P21" s="47"/>
-      <c r="Q21" s="47"/>
-      <c r="R21" s="47"/>
-      <c r="S21" s="47"/>
-      <c r="T21" s="47"/>
-      <c r="U21" s="47"/>
-      <c r="V21" s="47"/>
-      <c r="W21" s="47"/>
-      <c r="X21" s="47"/>
-      <c r="Y21" s="47"/>
-      <c r="Z21" s="48"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="53"/>
+      <c r="O21" s="53"/>
+      <c r="P21" s="53"/>
+      <c r="Q21" s="53"/>
+      <c r="R21" s="53"/>
+      <c r="S21" s="53"/>
+      <c r="T21" s="53"/>
+      <c r="U21" s="53"/>
+      <c r="V21" s="53"/>
+      <c r="W21" s="53"/>
+      <c r="X21" s="53"/>
+      <c r="Y21" s="53"/>
+      <c r="Z21" s="54"/>
       <c r="AA21" s="24"/>
     </row>
     <row r="22" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1981,968 +1977,968 @@
     </row>
     <row r="23" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
-      <c r="B23" s="43" t="s">
+      <c r="B23" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="66"/>
-      <c r="D23" s="66"/>
-      <c r="E23" s="66"/>
-      <c r="F23" s="66"/>
-      <c r="G23" s="66"/>
-      <c r="H23" s="66"/>
-      <c r="I23" s="66"/>
-      <c r="J23" s="66"/>
-      <c r="K23" s="66"/>
-      <c r="L23" s="66"/>
-      <c r="M23" s="66"/>
-      <c r="N23" s="66"/>
-      <c r="O23" s="66"/>
-      <c r="P23" s="66"/>
-      <c r="Q23" s="66"/>
-      <c r="R23" s="66"/>
-      <c r="S23" s="66"/>
-      <c r="T23" s="66"/>
-      <c r="U23" s="66"/>
-      <c r="V23" s="66"/>
-      <c r="W23" s="66"/>
-      <c r="X23" s="66"/>
-      <c r="Y23" s="66"/>
-      <c r="Z23" s="66"/>
-      <c r="AA23" s="67"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="64"/>
+      <c r="F23" s="64"/>
+      <c r="G23" s="64"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="64"/>
+      <c r="J23" s="64"/>
+      <c r="K23" s="64"/>
+      <c r="L23" s="64"/>
+      <c r="M23" s="64"/>
+      <c r="N23" s="64"/>
+      <c r="O23" s="64"/>
+      <c r="P23" s="64"/>
+      <c r="Q23" s="64"/>
+      <c r="R23" s="64"/>
+      <c r="S23" s="64"/>
+      <c r="T23" s="64"/>
+      <c r="U23" s="64"/>
+      <c r="V23" s="64"/>
+      <c r="W23" s="64"/>
+      <c r="X23" s="64"/>
+      <c r="Y23" s="64"/>
+      <c r="Z23" s="64"/>
+      <c r="AA23" s="65"/>
     </row>
     <row r="24" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
-      <c r="B24" s="68"/>
-      <c r="C24" s="69"/>
-      <c r="D24" s="69"/>
-      <c r="E24" s="69"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="69"/>
-      <c r="I24" s="69"/>
-      <c r="J24" s="69"/>
-      <c r="K24" s="69"/>
-      <c r="L24" s="69"/>
-      <c r="M24" s="69"/>
-      <c r="N24" s="69"/>
-      <c r="O24" s="69"/>
-      <c r="P24" s="69"/>
-      <c r="Q24" s="69"/>
-      <c r="R24" s="69"/>
-      <c r="S24" s="69"/>
-      <c r="T24" s="69"/>
-      <c r="U24" s="69"/>
-      <c r="V24" s="69"/>
-      <c r="W24" s="69"/>
-      <c r="X24" s="69"/>
-      <c r="Y24" s="69"/>
-      <c r="Z24" s="69"/>
-      <c r="AA24" s="70"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="41"/>
+      <c r="K24" s="41"/>
+      <c r="L24" s="41"/>
+      <c r="M24" s="41"/>
+      <c r="N24" s="41"/>
+      <c r="O24" s="41"/>
+      <c r="P24" s="41"/>
+      <c r="Q24" s="41"/>
+      <c r="R24" s="41"/>
+      <c r="S24" s="41"/>
+      <c r="T24" s="41"/>
+      <c r="U24" s="41"/>
+      <c r="V24" s="41"/>
+      <c r="W24" s="41"/>
+      <c r="X24" s="41"/>
+      <c r="Y24" s="41"/>
+      <c r="Z24" s="41"/>
+      <c r="AA24" s="42"/>
     </row>
     <row r="25" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="69"/>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="69"/>
-      <c r="I25" s="69"/>
-      <c r="J25" s="69"/>
-      <c r="K25" s="69"/>
-      <c r="L25" s="69"/>
-      <c r="M25" s="69"/>
-      <c r="N25" s="69"/>
-      <c r="O25" s="69"/>
-      <c r="P25" s="69"/>
-      <c r="Q25" s="69"/>
-      <c r="R25" s="69"/>
-      <c r="S25" s="69"/>
-      <c r="T25" s="69"/>
-      <c r="U25" s="69"/>
-      <c r="V25" s="69"/>
-      <c r="W25" s="69"/>
-      <c r="X25" s="69"/>
-      <c r="Y25" s="69"/>
-      <c r="Z25" s="69"/>
-      <c r="AA25" s="70"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="41"/>
+      <c r="K25" s="41"/>
+      <c r="L25" s="41"/>
+      <c r="M25" s="41"/>
+      <c r="N25" s="41"/>
+      <c r="O25" s="41"/>
+      <c r="P25" s="41"/>
+      <c r="Q25" s="41"/>
+      <c r="R25" s="41"/>
+      <c r="S25" s="41"/>
+      <c r="T25" s="41"/>
+      <c r="U25" s="41"/>
+      <c r="V25" s="41"/>
+      <c r="W25" s="41"/>
+      <c r="X25" s="41"/>
+      <c r="Y25" s="41"/>
+      <c r="Z25" s="41"/>
+      <c r="AA25" s="42"/>
     </row>
     <row r="26" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="69"/>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="69"/>
-      <c r="H26" s="69"/>
-      <c r="I26" s="69"/>
-      <c r="J26" s="69"/>
-      <c r="K26" s="69"/>
-      <c r="L26" s="69"/>
-      <c r="M26" s="69"/>
-      <c r="N26" s="69"/>
-      <c r="O26" s="69"/>
-      <c r="P26" s="69"/>
-      <c r="Q26" s="69"/>
-      <c r="R26" s="69"/>
-      <c r="S26" s="69"/>
-      <c r="T26" s="69"/>
-      <c r="U26" s="69"/>
-      <c r="V26" s="69"/>
-      <c r="W26" s="69"/>
-      <c r="X26" s="69"/>
-      <c r="Y26" s="69"/>
-      <c r="Z26" s="69"/>
-      <c r="AA26" s="70"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="41"/>
+      <c r="K26" s="41"/>
+      <c r="L26" s="41"/>
+      <c r="M26" s="41"/>
+      <c r="N26" s="41"/>
+      <c r="O26" s="41"/>
+      <c r="P26" s="41"/>
+      <c r="Q26" s="41"/>
+      <c r="R26" s="41"/>
+      <c r="S26" s="41"/>
+      <c r="T26" s="41"/>
+      <c r="U26" s="41"/>
+      <c r="V26" s="41"/>
+      <c r="W26" s="41"/>
+      <c r="X26" s="41"/>
+      <c r="Y26" s="41"/>
+      <c r="Z26" s="41"/>
+      <c r="AA26" s="42"/>
     </row>
     <row r="27" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="69"/>
-      <c r="D27" s="69"/>
-      <c r="E27" s="69"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="69"/>
-      <c r="H27" s="69"/>
-      <c r="I27" s="69"/>
-      <c r="J27" s="69"/>
-      <c r="K27" s="69"/>
-      <c r="L27" s="69"/>
-      <c r="M27" s="69"/>
-      <c r="N27" s="69"/>
-      <c r="O27" s="69"/>
-      <c r="P27" s="69"/>
-      <c r="Q27" s="69"/>
-      <c r="R27" s="69"/>
-      <c r="S27" s="69"/>
-      <c r="T27" s="69"/>
-      <c r="U27" s="69"/>
-      <c r="V27" s="69"/>
-      <c r="W27" s="69"/>
-      <c r="X27" s="69"/>
-      <c r="Y27" s="69"/>
-      <c r="Z27" s="69"/>
-      <c r="AA27" s="70"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="41"/>
+      <c r="K27" s="41"/>
+      <c r="L27" s="41"/>
+      <c r="M27" s="41"/>
+      <c r="N27" s="41"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="41"/>
+      <c r="S27" s="41"/>
+      <c r="T27" s="41"/>
+      <c r="U27" s="41"/>
+      <c r="V27" s="41"/>
+      <c r="W27" s="41"/>
+      <c r="X27" s="41"/>
+      <c r="Y27" s="41"/>
+      <c r="Z27" s="41"/>
+      <c r="AA27" s="42"/>
     </row>
     <row r="28" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="69"/>
-      <c r="D28" s="69"/>
-      <c r="E28" s="69"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="69"/>
-      <c r="H28" s="69"/>
-      <c r="I28" s="69"/>
-      <c r="J28" s="69"/>
-      <c r="K28" s="69"/>
-      <c r="L28" s="69"/>
-      <c r="M28" s="69"/>
-      <c r="N28" s="69"/>
-      <c r="O28" s="69"/>
-      <c r="P28" s="69"/>
-      <c r="Q28" s="69"/>
-      <c r="R28" s="69"/>
-      <c r="S28" s="69"/>
-      <c r="T28" s="69"/>
-      <c r="U28" s="69"/>
-      <c r="V28" s="69"/>
-      <c r="W28" s="69"/>
-      <c r="X28" s="69"/>
-      <c r="Y28" s="69"/>
-      <c r="Z28" s="69"/>
-      <c r="AA28" s="70"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="41"/>
+      <c r="L28" s="41"/>
+      <c r="M28" s="41"/>
+      <c r="N28" s="41"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="41"/>
+      <c r="S28" s="41"/>
+      <c r="T28" s="41"/>
+      <c r="U28" s="41"/>
+      <c r="V28" s="41"/>
+      <c r="W28" s="41"/>
+      <c r="X28" s="41"/>
+      <c r="Y28" s="41"/>
+      <c r="Z28" s="41"/>
+      <c r="AA28" s="42"/>
     </row>
     <row r="29" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="69"/>
-      <c r="D29" s="69"/>
-      <c r="E29" s="69"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="69"/>
-      <c r="H29" s="69"/>
-      <c r="I29" s="69"/>
-      <c r="J29" s="69"/>
-      <c r="K29" s="69"/>
-      <c r="L29" s="69"/>
-      <c r="M29" s="69"/>
-      <c r="N29" s="69"/>
-      <c r="O29" s="69"/>
-      <c r="P29" s="69"/>
-      <c r="Q29" s="69"/>
-      <c r="R29" s="69"/>
-      <c r="S29" s="69"/>
-      <c r="T29" s="69"/>
-      <c r="U29" s="69"/>
-      <c r="V29" s="69"/>
-      <c r="W29" s="69"/>
-      <c r="X29" s="69"/>
-      <c r="Y29" s="69"/>
-      <c r="Z29" s="69"/>
-      <c r="AA29" s="70"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="41"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="41"/>
+      <c r="O29" s="41"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="41"/>
+      <c r="S29" s="41"/>
+      <c r="T29" s="41"/>
+      <c r="U29" s="41"/>
+      <c r="V29" s="41"/>
+      <c r="W29" s="41"/>
+      <c r="X29" s="41"/>
+      <c r="Y29" s="41"/>
+      <c r="Z29" s="41"/>
+      <c r="AA29" s="42"/>
     </row>
     <row r="30" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="69"/>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="69"/>
-      <c r="H30" s="69"/>
-      <c r="I30" s="69"/>
-      <c r="J30" s="69"/>
-      <c r="K30" s="69"/>
-      <c r="L30" s="69"/>
-      <c r="M30" s="69"/>
-      <c r="N30" s="69"/>
-      <c r="O30" s="69"/>
-      <c r="P30" s="69"/>
-      <c r="Q30" s="69"/>
-      <c r="R30" s="69"/>
-      <c r="S30" s="69"/>
-      <c r="T30" s="69"/>
-      <c r="U30" s="69"/>
-      <c r="V30" s="69"/>
-      <c r="W30" s="69"/>
-      <c r="X30" s="69"/>
-      <c r="Y30" s="69"/>
-      <c r="Z30" s="69"/>
-      <c r="AA30" s="70"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="41"/>
+      <c r="K30" s="41"/>
+      <c r="L30" s="41"/>
+      <c r="M30" s="41"/>
+      <c r="N30" s="41"/>
+      <c r="O30" s="41"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="41"/>
+      <c r="S30" s="41"/>
+      <c r="T30" s="41"/>
+      <c r="U30" s="41"/>
+      <c r="V30" s="41"/>
+      <c r="W30" s="41"/>
+      <c r="X30" s="41"/>
+      <c r="Y30" s="41"/>
+      <c r="Z30" s="41"/>
+      <c r="AA30" s="42"/>
     </row>
     <row r="31" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
-      <c r="B31" s="68"/>
-      <c r="C31" s="69"/>
-      <c r="D31" s="69"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="69"/>
-      <c r="H31" s="69"/>
-      <c r="I31" s="69"/>
-      <c r="J31" s="69"/>
-      <c r="K31" s="69"/>
-      <c r="L31" s="69"/>
-      <c r="M31" s="69"/>
-      <c r="N31" s="69"/>
-      <c r="O31" s="69"/>
-      <c r="P31" s="69"/>
-      <c r="Q31" s="69"/>
-      <c r="R31" s="69"/>
-      <c r="S31" s="69"/>
-      <c r="T31" s="69"/>
-      <c r="U31" s="69"/>
-      <c r="V31" s="69"/>
-      <c r="W31" s="69"/>
-      <c r="X31" s="69"/>
-      <c r="Y31" s="69"/>
-      <c r="Z31" s="69"/>
-      <c r="AA31" s="70"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="41"/>
+      <c r="K31" s="41"/>
+      <c r="L31" s="41"/>
+      <c r="M31" s="41"/>
+      <c r="N31" s="41"/>
+      <c r="O31" s="41"/>
+      <c r="P31" s="41"/>
+      <c r="Q31" s="41"/>
+      <c r="R31" s="41"/>
+      <c r="S31" s="41"/>
+      <c r="T31" s="41"/>
+      <c r="U31" s="41"/>
+      <c r="V31" s="41"/>
+      <c r="W31" s="41"/>
+      <c r="X31" s="41"/>
+      <c r="Y31" s="41"/>
+      <c r="Z31" s="41"/>
+      <c r="AA31" s="42"/>
     </row>
     <row r="32" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
-      <c r="B32" s="42" t="s">
+      <c r="B32" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="71"/>
-      <c r="D32" s="71"/>
-      <c r="E32" s="71"/>
-      <c r="F32" s="71"/>
-      <c r="G32" s="71"/>
-      <c r="H32" s="71"/>
-      <c r="I32" s="71"/>
-      <c r="J32" s="71"/>
-      <c r="K32" s="71"/>
-      <c r="L32" s="71"/>
-      <c r="M32" s="71"/>
-      <c r="N32" s="71"/>
-      <c r="O32" s="71"/>
-      <c r="P32" s="71"/>
-      <c r="Q32" s="71"/>
-      <c r="R32" s="71"/>
-      <c r="S32" s="71"/>
-      <c r="T32" s="71"/>
-      <c r="U32" s="71"/>
-      <c r="V32" s="71"/>
-      <c r="W32" s="71"/>
-      <c r="X32" s="71"/>
-      <c r="Y32" s="71"/>
-      <c r="Z32" s="71"/>
-      <c r="AA32" s="72"/>
+      <c r="C32" s="44"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="44"/>
+      <c r="J32" s="44"/>
+      <c r="K32" s="44"/>
+      <c r="L32" s="44"/>
+      <c r="M32" s="44"/>
+      <c r="N32" s="44"/>
+      <c r="O32" s="44"/>
+      <c r="P32" s="44"/>
+      <c r="Q32" s="44"/>
+      <c r="R32" s="44"/>
+      <c r="S32" s="44"/>
+      <c r="T32" s="44"/>
+      <c r="U32" s="44"/>
+      <c r="V32" s="44"/>
+      <c r="W32" s="44"/>
+      <c r="X32" s="44"/>
+      <c r="Y32" s="44"/>
+      <c r="Z32" s="44"/>
+      <c r="AA32" s="45"/>
     </row>
     <row r="33" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
-      <c r="B33" s="68"/>
-      <c r="C33" s="69"/>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="69"/>
-      <c r="H33" s="69"/>
-      <c r="I33" s="69"/>
-      <c r="J33" s="69"/>
-      <c r="K33" s="69"/>
-      <c r="L33" s="69"/>
-      <c r="M33" s="69"/>
-      <c r="N33" s="69"/>
-      <c r="O33" s="69"/>
-      <c r="P33" s="69"/>
-      <c r="Q33" s="69"/>
-      <c r="R33" s="69"/>
-      <c r="S33" s="69"/>
-      <c r="T33" s="69"/>
-      <c r="U33" s="69"/>
-      <c r="V33" s="69"/>
-      <c r="W33" s="69"/>
-      <c r="X33" s="69"/>
-      <c r="Y33" s="69"/>
-      <c r="Z33" s="69"/>
-      <c r="AA33" s="70"/>
+      <c r="B33" s="40"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="41"/>
+      <c r="K33" s="41"/>
+      <c r="L33" s="41"/>
+      <c r="M33" s="41"/>
+      <c r="N33" s="41"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="41"/>
+      <c r="S33" s="41"/>
+      <c r="T33" s="41"/>
+      <c r="U33" s="41"/>
+      <c r="V33" s="41"/>
+      <c r="W33" s="41"/>
+      <c r="X33" s="41"/>
+      <c r="Y33" s="41"/>
+      <c r="Z33" s="41"/>
+      <c r="AA33" s="42"/>
     </row>
     <row r="34" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
-      <c r="B34" s="68"/>
-      <c r="C34" s="69"/>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="69"/>
-      <c r="G34" s="69"/>
-      <c r="H34" s="69"/>
-      <c r="I34" s="69"/>
-      <c r="J34" s="69"/>
-      <c r="K34" s="69"/>
-      <c r="L34" s="69"/>
-      <c r="M34" s="69"/>
-      <c r="N34" s="69"/>
-      <c r="O34" s="69"/>
-      <c r="P34" s="69"/>
-      <c r="Q34" s="69"/>
-      <c r="R34" s="69"/>
-      <c r="S34" s="69"/>
-      <c r="T34" s="69"/>
-      <c r="U34" s="69"/>
-      <c r="V34" s="69"/>
-      <c r="W34" s="69"/>
-      <c r="X34" s="69"/>
-      <c r="Y34" s="69"/>
-      <c r="Z34" s="69"/>
-      <c r="AA34" s="70"/>
+      <c r="B34" s="40"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="41"/>
+      <c r="K34" s="41"/>
+      <c r="L34" s="41"/>
+      <c r="M34" s="41"/>
+      <c r="N34" s="41"/>
+      <c r="O34" s="41"/>
+      <c r="P34" s="41"/>
+      <c r="Q34" s="41"/>
+      <c r="R34" s="41"/>
+      <c r="S34" s="41"/>
+      <c r="T34" s="41"/>
+      <c r="U34" s="41"/>
+      <c r="V34" s="41"/>
+      <c r="W34" s="41"/>
+      <c r="X34" s="41"/>
+      <c r="Y34" s="41"/>
+      <c r="Z34" s="41"/>
+      <c r="AA34" s="42"/>
     </row>
     <row r="35" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
-      <c r="B35" s="68"/>
-      <c r="C35" s="69"/>
-      <c r="D35" s="69"/>
-      <c r="E35" s="69"/>
-      <c r="F35" s="69"/>
-      <c r="G35" s="69"/>
-      <c r="H35" s="69"/>
-      <c r="I35" s="69"/>
-      <c r="J35" s="69"/>
-      <c r="K35" s="69"/>
-      <c r="L35" s="69"/>
-      <c r="M35" s="69"/>
-      <c r="N35" s="69"/>
-      <c r="O35" s="69"/>
-      <c r="P35" s="69"/>
-      <c r="Q35" s="69"/>
-      <c r="R35" s="69"/>
-      <c r="S35" s="69"/>
-      <c r="T35" s="69"/>
-      <c r="U35" s="69"/>
-      <c r="V35" s="69"/>
-      <c r="W35" s="69"/>
-      <c r="X35" s="69"/>
-      <c r="Y35" s="69"/>
-      <c r="Z35" s="69"/>
-      <c r="AA35" s="70"/>
+      <c r="B35" s="40"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="41"/>
+      <c r="I35" s="41"/>
+      <c r="J35" s="41"/>
+      <c r="K35" s="41"/>
+      <c r="L35" s="41"/>
+      <c r="M35" s="41"/>
+      <c r="N35" s="41"/>
+      <c r="O35" s="41"/>
+      <c r="P35" s="41"/>
+      <c r="Q35" s="41"/>
+      <c r="R35" s="41"/>
+      <c r="S35" s="41"/>
+      <c r="T35" s="41"/>
+      <c r="U35" s="41"/>
+      <c r="V35" s="41"/>
+      <c r="W35" s="41"/>
+      <c r="X35" s="41"/>
+      <c r="Y35" s="41"/>
+      <c r="Z35" s="41"/>
+      <c r="AA35" s="42"/>
     </row>
     <row r="36" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
-      <c r="B36" s="68"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="69"/>
-      <c r="E36" s="69"/>
-      <c r="F36" s="69"/>
-      <c r="G36" s="69"/>
-      <c r="H36" s="69"/>
-      <c r="I36" s="69"/>
-      <c r="J36" s="69"/>
-      <c r="K36" s="69"/>
-      <c r="L36" s="69"/>
-      <c r="M36" s="69"/>
-      <c r="N36" s="69"/>
-      <c r="O36" s="69"/>
-      <c r="P36" s="69"/>
-      <c r="Q36" s="69"/>
-      <c r="R36" s="69"/>
-      <c r="S36" s="69"/>
-      <c r="T36" s="69"/>
-      <c r="U36" s="69"/>
-      <c r="V36" s="69"/>
-      <c r="W36" s="69"/>
-      <c r="X36" s="69"/>
-      <c r="Y36" s="69"/>
-      <c r="Z36" s="69"/>
-      <c r="AA36" s="70"/>
+      <c r="B36" s="40"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="41"/>
+      <c r="G36" s="41"/>
+      <c r="H36" s="41"/>
+      <c r="I36" s="41"/>
+      <c r="J36" s="41"/>
+      <c r="K36" s="41"/>
+      <c r="L36" s="41"/>
+      <c r="M36" s="41"/>
+      <c r="N36" s="41"/>
+      <c r="O36" s="41"/>
+      <c r="P36" s="41"/>
+      <c r="Q36" s="41"/>
+      <c r="R36" s="41"/>
+      <c r="S36" s="41"/>
+      <c r="T36" s="41"/>
+      <c r="U36" s="41"/>
+      <c r="V36" s="41"/>
+      <c r="W36" s="41"/>
+      <c r="X36" s="41"/>
+      <c r="Y36" s="41"/>
+      <c r="Z36" s="41"/>
+      <c r="AA36" s="42"/>
     </row>
     <row r="37" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
-      <c r="B37" s="68"/>
-      <c r="C37" s="69"/>
-      <c r="D37" s="69"/>
-      <c r="E37" s="69"/>
-      <c r="F37" s="69"/>
-      <c r="G37" s="69"/>
-      <c r="H37" s="69"/>
-      <c r="I37" s="69"/>
-      <c r="J37" s="69"/>
-      <c r="K37" s="69"/>
-      <c r="L37" s="69"/>
-      <c r="M37" s="69"/>
-      <c r="N37" s="69"/>
-      <c r="O37" s="69"/>
-      <c r="P37" s="69"/>
-      <c r="Q37" s="69"/>
-      <c r="R37" s="69"/>
-      <c r="S37" s="69"/>
-      <c r="T37" s="69"/>
-      <c r="U37" s="69"/>
-      <c r="V37" s="69"/>
-      <c r="W37" s="69"/>
-      <c r="X37" s="69"/>
-      <c r="Y37" s="69"/>
-      <c r="Z37" s="69"/>
-      <c r="AA37" s="70"/>
+      <c r="B37" s="40"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="41"/>
+      <c r="I37" s="41"/>
+      <c r="J37" s="41"/>
+      <c r="K37" s="41"/>
+      <c r="L37" s="41"/>
+      <c r="M37" s="41"/>
+      <c r="N37" s="41"/>
+      <c r="O37" s="41"/>
+      <c r="P37" s="41"/>
+      <c r="Q37" s="41"/>
+      <c r="R37" s="41"/>
+      <c r="S37" s="41"/>
+      <c r="T37" s="41"/>
+      <c r="U37" s="41"/>
+      <c r="V37" s="41"/>
+      <c r="W37" s="41"/>
+      <c r="X37" s="41"/>
+      <c r="Y37" s="41"/>
+      <c r="Z37" s="41"/>
+      <c r="AA37" s="42"/>
     </row>
     <row r="38" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
-      <c r="B38" s="68"/>
-      <c r="C38" s="69"/>
-      <c r="D38" s="69"/>
-      <c r="E38" s="69"/>
-      <c r="F38" s="69"/>
-      <c r="G38" s="69"/>
-      <c r="H38" s="69"/>
-      <c r="I38" s="69"/>
-      <c r="J38" s="69"/>
-      <c r="K38" s="69"/>
-      <c r="L38" s="69"/>
-      <c r="M38" s="69"/>
-      <c r="N38" s="69"/>
-      <c r="O38" s="69"/>
-      <c r="P38" s="69"/>
-      <c r="Q38" s="69"/>
-      <c r="R38" s="69"/>
-      <c r="S38" s="69"/>
-      <c r="T38" s="69"/>
-      <c r="U38" s="69"/>
-      <c r="V38" s="69"/>
-      <c r="W38" s="69"/>
-      <c r="X38" s="69"/>
-      <c r="Y38" s="69"/>
-      <c r="Z38" s="69"/>
-      <c r="AA38" s="70"/>
+      <c r="B38" s="40"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="41"/>
+      <c r="H38" s="41"/>
+      <c r="I38" s="41"/>
+      <c r="J38" s="41"/>
+      <c r="K38" s="41"/>
+      <c r="L38" s="41"/>
+      <c r="M38" s="41"/>
+      <c r="N38" s="41"/>
+      <c r="O38" s="41"/>
+      <c r="P38" s="41"/>
+      <c r="Q38" s="41"/>
+      <c r="R38" s="41"/>
+      <c r="S38" s="41"/>
+      <c r="T38" s="41"/>
+      <c r="U38" s="41"/>
+      <c r="V38" s="41"/>
+      <c r="W38" s="41"/>
+      <c r="X38" s="41"/>
+      <c r="Y38" s="41"/>
+      <c r="Z38" s="41"/>
+      <c r="AA38" s="42"/>
     </row>
     <row r="39" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
-      <c r="B39" s="68"/>
-      <c r="C39" s="69"/>
-      <c r="D39" s="69"/>
-      <c r="E39" s="69"/>
-      <c r="F39" s="69"/>
-      <c r="G39" s="69"/>
-      <c r="H39" s="69"/>
-      <c r="I39" s="69"/>
-      <c r="J39" s="69"/>
-      <c r="K39" s="69"/>
-      <c r="L39" s="69"/>
-      <c r="M39" s="69"/>
-      <c r="N39" s="69"/>
-      <c r="O39" s="69"/>
-      <c r="P39" s="69"/>
-      <c r="Q39" s="69"/>
-      <c r="R39" s="69"/>
-      <c r="S39" s="69"/>
-      <c r="T39" s="69"/>
-      <c r="U39" s="69"/>
-      <c r="V39" s="69"/>
-      <c r="W39" s="69"/>
-      <c r="X39" s="69"/>
-      <c r="Y39" s="69"/>
-      <c r="Z39" s="69"/>
-      <c r="AA39" s="70"/>
+      <c r="B39" s="40"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="41"/>
+      <c r="G39" s="41"/>
+      <c r="H39" s="41"/>
+      <c r="I39" s="41"/>
+      <c r="J39" s="41"/>
+      <c r="K39" s="41"/>
+      <c r="L39" s="41"/>
+      <c r="M39" s="41"/>
+      <c r="N39" s="41"/>
+      <c r="O39" s="41"/>
+      <c r="P39" s="41"/>
+      <c r="Q39" s="41"/>
+      <c r="R39" s="41"/>
+      <c r="S39" s="41"/>
+      <c r="T39" s="41"/>
+      <c r="U39" s="41"/>
+      <c r="V39" s="41"/>
+      <c r="W39" s="41"/>
+      <c r="X39" s="41"/>
+      <c r="Y39" s="41"/>
+      <c r="Z39" s="41"/>
+      <c r="AA39" s="42"/>
     </row>
     <row r="40" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
-      <c r="B40" s="42" t="s">
+      <c r="B40" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="71"/>
-      <c r="D40" s="71"/>
-      <c r="E40" s="71"/>
-      <c r="F40" s="71"/>
-      <c r="G40" s="71"/>
-      <c r="H40" s="71"/>
-      <c r="I40" s="71"/>
-      <c r="J40" s="71"/>
-      <c r="K40" s="71"/>
-      <c r="L40" s="71"/>
-      <c r="M40" s="71"/>
-      <c r="N40" s="71"/>
-      <c r="O40" s="71"/>
-      <c r="P40" s="71"/>
-      <c r="Q40" s="71"/>
-      <c r="R40" s="71"/>
-      <c r="S40" s="71"/>
-      <c r="T40" s="71"/>
-      <c r="U40" s="71"/>
-      <c r="V40" s="71"/>
-      <c r="W40" s="71"/>
-      <c r="X40" s="71"/>
-      <c r="Y40" s="71"/>
-      <c r="Z40" s="71"/>
-      <c r="AA40" s="72"/>
+      <c r="C40" s="44"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="44"/>
+      <c r="F40" s="44"/>
+      <c r="G40" s="44"/>
+      <c r="H40" s="44"/>
+      <c r="I40" s="44"/>
+      <c r="J40" s="44"/>
+      <c r="K40" s="44"/>
+      <c r="L40" s="44"/>
+      <c r="M40" s="44"/>
+      <c r="N40" s="44"/>
+      <c r="O40" s="44"/>
+      <c r="P40" s="44"/>
+      <c r="Q40" s="44"/>
+      <c r="R40" s="44"/>
+      <c r="S40" s="44"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="44"/>
+      <c r="V40" s="44"/>
+      <c r="W40" s="44"/>
+      <c r="X40" s="44"/>
+      <c r="Y40" s="44"/>
+      <c r="Z40" s="44"/>
+      <c r="AA40" s="45"/>
     </row>
     <row r="41" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
-      <c r="B41" s="68"/>
-      <c r="C41" s="69"/>
-      <c r="D41" s="69"/>
-      <c r="E41" s="69"/>
-      <c r="F41" s="69"/>
-      <c r="G41" s="69"/>
-      <c r="H41" s="69"/>
-      <c r="I41" s="69"/>
-      <c r="J41" s="69"/>
-      <c r="K41" s="69"/>
-      <c r="L41" s="69"/>
-      <c r="M41" s="69"/>
-      <c r="N41" s="69"/>
-      <c r="O41" s="69"/>
-      <c r="P41" s="69"/>
-      <c r="Q41" s="69"/>
-      <c r="R41" s="69"/>
-      <c r="S41" s="69"/>
-      <c r="T41" s="69"/>
-      <c r="U41" s="69"/>
-      <c r="V41" s="69"/>
-      <c r="W41" s="69"/>
-      <c r="X41" s="69"/>
-      <c r="Y41" s="69"/>
-      <c r="Z41" s="69"/>
-      <c r="AA41" s="70"/>
+      <c r="B41" s="40"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="41"/>
+      <c r="G41" s="41"/>
+      <c r="H41" s="41"/>
+      <c r="I41" s="41"/>
+      <c r="J41" s="41"/>
+      <c r="K41" s="41"/>
+      <c r="L41" s="41"/>
+      <c r="M41" s="41"/>
+      <c r="N41" s="41"/>
+      <c r="O41" s="41"/>
+      <c r="P41" s="41"/>
+      <c r="Q41" s="41"/>
+      <c r="R41" s="41"/>
+      <c r="S41" s="41"/>
+      <c r="T41" s="41"/>
+      <c r="U41" s="41"/>
+      <c r="V41" s="41"/>
+      <c r="W41" s="41"/>
+      <c r="X41" s="41"/>
+      <c r="Y41" s="41"/>
+      <c r="Z41" s="41"/>
+      <c r="AA41" s="42"/>
     </row>
     <row r="42" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
-      <c r="B42" s="68"/>
-      <c r="C42" s="69"/>
-      <c r="D42" s="69"/>
-      <c r="E42" s="69"/>
-      <c r="F42" s="69"/>
-      <c r="G42" s="69"/>
-      <c r="H42" s="69"/>
-      <c r="I42" s="69"/>
-      <c r="J42" s="69"/>
-      <c r="K42" s="69"/>
-      <c r="L42" s="69"/>
-      <c r="M42" s="69"/>
-      <c r="N42" s="69"/>
-      <c r="O42" s="69"/>
-      <c r="P42" s="69"/>
-      <c r="Q42" s="69"/>
-      <c r="R42" s="69"/>
-      <c r="S42" s="69"/>
-      <c r="T42" s="69"/>
-      <c r="U42" s="69"/>
-      <c r="V42" s="69"/>
-      <c r="W42" s="69"/>
-      <c r="X42" s="69"/>
-      <c r="Y42" s="69"/>
-      <c r="Z42" s="69"/>
-      <c r="AA42" s="70"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="41"/>
+      <c r="F42" s="41"/>
+      <c r="G42" s="41"/>
+      <c r="H42" s="41"/>
+      <c r="I42" s="41"/>
+      <c r="J42" s="41"/>
+      <c r="K42" s="41"/>
+      <c r="L42" s="41"/>
+      <c r="M42" s="41"/>
+      <c r="N42" s="41"/>
+      <c r="O42" s="41"/>
+      <c r="P42" s="41"/>
+      <c r="Q42" s="41"/>
+      <c r="R42" s="41"/>
+      <c r="S42" s="41"/>
+      <c r="T42" s="41"/>
+      <c r="U42" s="41"/>
+      <c r="V42" s="41"/>
+      <c r="W42" s="41"/>
+      <c r="X42" s="41"/>
+      <c r="Y42" s="41"/>
+      <c r="Z42" s="41"/>
+      <c r="AA42" s="42"/>
     </row>
     <row r="43" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
-      <c r="B43" s="68"/>
-      <c r="C43" s="69"/>
-      <c r="D43" s="69"/>
-      <c r="E43" s="69"/>
-      <c r="F43" s="69"/>
-      <c r="G43" s="69"/>
-      <c r="H43" s="69"/>
-      <c r="I43" s="69"/>
-      <c r="J43" s="69"/>
-      <c r="K43" s="69"/>
-      <c r="L43" s="69"/>
-      <c r="M43" s="69"/>
-      <c r="N43" s="69"/>
-      <c r="O43" s="69"/>
-      <c r="P43" s="69"/>
-      <c r="Q43" s="69"/>
-      <c r="R43" s="69"/>
-      <c r="S43" s="69"/>
-      <c r="T43" s="69"/>
-      <c r="U43" s="69"/>
-      <c r="V43" s="69"/>
-      <c r="W43" s="69"/>
-      <c r="X43" s="69"/>
-      <c r="Y43" s="69"/>
-      <c r="Z43" s="69"/>
-      <c r="AA43" s="70"/>
+      <c r="B43" s="40"/>
+      <c r="C43" s="41"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="41"/>
+      <c r="G43" s="41"/>
+      <c r="H43" s="41"/>
+      <c r="I43" s="41"/>
+      <c r="J43" s="41"/>
+      <c r="K43" s="41"/>
+      <c r="L43" s="41"/>
+      <c r="M43" s="41"/>
+      <c r="N43" s="41"/>
+      <c r="O43" s="41"/>
+      <c r="P43" s="41"/>
+      <c r="Q43" s="41"/>
+      <c r="R43" s="41"/>
+      <c r="S43" s="41"/>
+      <c r="T43" s="41"/>
+      <c r="U43" s="41"/>
+      <c r="V43" s="41"/>
+      <c r="W43" s="41"/>
+      <c r="X43" s="41"/>
+      <c r="Y43" s="41"/>
+      <c r="Z43" s="41"/>
+      <c r="AA43" s="42"/>
     </row>
     <row r="44" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
-      <c r="B44" s="68"/>
-      <c r="C44" s="69"/>
-      <c r="D44" s="69"/>
-      <c r="E44" s="69"/>
-      <c r="F44" s="69"/>
-      <c r="G44" s="69"/>
-      <c r="H44" s="69"/>
-      <c r="I44" s="69"/>
-      <c r="J44" s="69"/>
-      <c r="K44" s="69"/>
-      <c r="L44" s="69"/>
-      <c r="M44" s="69"/>
-      <c r="N44" s="69"/>
-      <c r="O44" s="69"/>
-      <c r="P44" s="69"/>
-      <c r="Q44" s="69"/>
-      <c r="R44" s="69"/>
-      <c r="S44" s="69"/>
-      <c r="T44" s="69"/>
-      <c r="U44" s="69"/>
-      <c r="V44" s="69"/>
-      <c r="W44" s="69"/>
-      <c r="X44" s="69"/>
-      <c r="Y44" s="69"/>
-      <c r="Z44" s="69"/>
-      <c r="AA44" s="70"/>
+      <c r="B44" s="40"/>
+      <c r="C44" s="41"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="41"/>
+      <c r="F44" s="41"/>
+      <c r="G44" s="41"/>
+      <c r="H44" s="41"/>
+      <c r="I44" s="41"/>
+      <c r="J44" s="41"/>
+      <c r="K44" s="41"/>
+      <c r="L44" s="41"/>
+      <c r="M44" s="41"/>
+      <c r="N44" s="41"/>
+      <c r="O44" s="41"/>
+      <c r="P44" s="41"/>
+      <c r="Q44" s="41"/>
+      <c r="R44" s="41"/>
+      <c r="S44" s="41"/>
+      <c r="T44" s="41"/>
+      <c r="U44" s="41"/>
+      <c r="V44" s="41"/>
+      <c r="W44" s="41"/>
+      <c r="X44" s="41"/>
+      <c r="Y44" s="41"/>
+      <c r="Z44" s="41"/>
+      <c r="AA44" s="42"/>
     </row>
     <row r="45" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
-      <c r="B45" s="68"/>
-      <c r="C45" s="69"/>
-      <c r="D45" s="69"/>
-      <c r="E45" s="69"/>
-      <c r="F45" s="69"/>
-      <c r="G45" s="69"/>
-      <c r="H45" s="69"/>
-      <c r="I45" s="69"/>
-      <c r="J45" s="69"/>
-      <c r="K45" s="69"/>
-      <c r="L45" s="69"/>
-      <c r="M45" s="69"/>
-      <c r="N45" s="69"/>
-      <c r="O45" s="69"/>
-      <c r="P45" s="69"/>
-      <c r="Q45" s="69"/>
-      <c r="R45" s="69"/>
-      <c r="S45" s="69"/>
-      <c r="T45" s="69"/>
-      <c r="U45" s="69"/>
-      <c r="V45" s="69"/>
-      <c r="W45" s="69"/>
-      <c r="X45" s="69"/>
-      <c r="Y45" s="69"/>
-      <c r="Z45" s="69"/>
-      <c r="AA45" s="70"/>
+      <c r="B45" s="40"/>
+      <c r="C45" s="41"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="41"/>
+      <c r="G45" s="41"/>
+      <c r="H45" s="41"/>
+      <c r="I45" s="41"/>
+      <c r="J45" s="41"/>
+      <c r="K45" s="41"/>
+      <c r="L45" s="41"/>
+      <c r="M45" s="41"/>
+      <c r="N45" s="41"/>
+      <c r="O45" s="41"/>
+      <c r="P45" s="41"/>
+      <c r="Q45" s="41"/>
+      <c r="R45" s="41"/>
+      <c r="S45" s="41"/>
+      <c r="T45" s="41"/>
+      <c r="U45" s="41"/>
+      <c r="V45" s="41"/>
+      <c r="W45" s="41"/>
+      <c r="X45" s="41"/>
+      <c r="Y45" s="41"/>
+      <c r="Z45" s="41"/>
+      <c r="AA45" s="42"/>
     </row>
     <row r="46" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
-      <c r="B46" s="68"/>
-      <c r="C46" s="69"/>
-      <c r="D46" s="69"/>
-      <c r="E46" s="69"/>
-      <c r="F46" s="69"/>
-      <c r="G46" s="69"/>
-      <c r="H46" s="69"/>
-      <c r="I46" s="69"/>
-      <c r="J46" s="69"/>
-      <c r="K46" s="69"/>
-      <c r="L46" s="69"/>
-      <c r="M46" s="69"/>
-      <c r="N46" s="69"/>
-      <c r="O46" s="69"/>
-      <c r="P46" s="69"/>
-      <c r="Q46" s="69"/>
-      <c r="R46" s="69"/>
-      <c r="S46" s="69"/>
-      <c r="T46" s="69"/>
-      <c r="U46" s="69"/>
-      <c r="V46" s="69"/>
-      <c r="W46" s="69"/>
-      <c r="X46" s="69"/>
-      <c r="Y46" s="69"/>
-      <c r="Z46" s="69"/>
-      <c r="AA46" s="70"/>
+      <c r="B46" s="40"/>
+      <c r="C46" s="41"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="41"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="41"/>
+      <c r="I46" s="41"/>
+      <c r="J46" s="41"/>
+      <c r="K46" s="41"/>
+      <c r="L46" s="41"/>
+      <c r="M46" s="41"/>
+      <c r="N46" s="41"/>
+      <c r="O46" s="41"/>
+      <c r="P46" s="41"/>
+      <c r="Q46" s="41"/>
+      <c r="R46" s="41"/>
+      <c r="S46" s="41"/>
+      <c r="T46" s="41"/>
+      <c r="U46" s="41"/>
+      <c r="V46" s="41"/>
+      <c r="W46" s="41"/>
+      <c r="X46" s="41"/>
+      <c r="Y46" s="41"/>
+      <c r="Z46" s="41"/>
+      <c r="AA46" s="42"/>
     </row>
     <row r="47" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
-      <c r="B47" s="68"/>
-      <c r="C47" s="69"/>
-      <c r="D47" s="69"/>
-      <c r="E47" s="69"/>
-      <c r="F47" s="69"/>
-      <c r="G47" s="69"/>
-      <c r="H47" s="69"/>
-      <c r="I47" s="69"/>
-      <c r="J47" s="69"/>
-      <c r="K47" s="69"/>
-      <c r="L47" s="69"/>
-      <c r="M47" s="69"/>
-      <c r="N47" s="69"/>
-      <c r="O47" s="69"/>
-      <c r="P47" s="69"/>
-      <c r="Q47" s="69"/>
-      <c r="R47" s="69"/>
-      <c r="S47" s="69"/>
-      <c r="T47" s="69"/>
-      <c r="U47" s="69"/>
-      <c r="V47" s="69"/>
-      <c r="W47" s="69"/>
-      <c r="X47" s="69"/>
-      <c r="Y47" s="69"/>
-      <c r="Z47" s="69"/>
-      <c r="AA47" s="70"/>
+      <c r="B47" s="40"/>
+      <c r="C47" s="41"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="41"/>
+      <c r="G47" s="41"/>
+      <c r="H47" s="41"/>
+      <c r="I47" s="41"/>
+      <c r="J47" s="41"/>
+      <c r="K47" s="41"/>
+      <c r="L47" s="41"/>
+      <c r="M47" s="41"/>
+      <c r="N47" s="41"/>
+      <c r="O47" s="41"/>
+      <c r="P47" s="41"/>
+      <c r="Q47" s="41"/>
+      <c r="R47" s="41"/>
+      <c r="S47" s="41"/>
+      <c r="T47" s="41"/>
+      <c r="U47" s="41"/>
+      <c r="V47" s="41"/>
+      <c r="W47" s="41"/>
+      <c r="X47" s="41"/>
+      <c r="Y47" s="41"/>
+      <c r="Z47" s="41"/>
+      <c r="AA47" s="42"/>
     </row>
     <row r="48" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
-      <c r="B48" s="56" t="s">
+      <c r="B48" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="73"/>
-      <c r="D48" s="73"/>
-      <c r="E48" s="73"/>
-      <c r="F48" s="73"/>
-      <c r="G48" s="73"/>
-      <c r="H48" s="73"/>
-      <c r="I48" s="73"/>
-      <c r="J48" s="73"/>
-      <c r="K48" s="73"/>
-      <c r="L48" s="73"/>
-      <c r="M48" s="73"/>
-      <c r="N48" s="73"/>
-      <c r="O48" s="73"/>
-      <c r="P48" s="73"/>
-      <c r="Q48" s="73"/>
-      <c r="R48" s="73"/>
-      <c r="S48" s="73"/>
-      <c r="T48" s="73"/>
-      <c r="U48" s="73"/>
-      <c r="V48" s="73"/>
-      <c r="W48" s="73"/>
-      <c r="X48" s="73"/>
-      <c r="Y48" s="73"/>
-      <c r="Z48" s="73"/>
-      <c r="AA48" s="74"/>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70"/>
+      <c r="I48" s="70"/>
+      <c r="J48" s="70"/>
+      <c r="K48" s="70"/>
+      <c r="L48" s="70"/>
+      <c r="M48" s="70"/>
+      <c r="N48" s="70"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="70"/>
+      <c r="Q48" s="70"/>
+      <c r="R48" s="70"/>
+      <c r="S48" s="70"/>
+      <c r="T48" s="70"/>
+      <c r="U48" s="70"/>
+      <c r="V48" s="70"/>
+      <c r="W48" s="70"/>
+      <c r="X48" s="70"/>
+      <c r="Y48" s="70"/>
+      <c r="Z48" s="70"/>
+      <c r="AA48" s="71"/>
     </row>
     <row r="49" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="30"/>
-      <c r="B49" s="68"/>
-      <c r="C49" s="69"/>
-      <c r="D49" s="69"/>
-      <c r="E49" s="69"/>
-      <c r="F49" s="69"/>
-      <c r="G49" s="69"/>
-      <c r="H49" s="69"/>
-      <c r="I49" s="69"/>
-      <c r="J49" s="69"/>
-      <c r="K49" s="69"/>
-      <c r="L49" s="69"/>
-      <c r="M49" s="69"/>
-      <c r="N49" s="69"/>
-      <c r="O49" s="69"/>
-      <c r="P49" s="69"/>
-      <c r="Q49" s="69"/>
-      <c r="R49" s="69"/>
-      <c r="S49" s="69"/>
-      <c r="T49" s="69"/>
-      <c r="U49" s="69"/>
-      <c r="V49" s="69"/>
-      <c r="W49" s="69"/>
-      <c r="X49" s="69"/>
-      <c r="Y49" s="69"/>
-      <c r="Z49" s="69"/>
-      <c r="AA49" s="70"/>
+      <c r="B49" s="40"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="41"/>
+      <c r="I49" s="41"/>
+      <c r="J49" s="41"/>
+      <c r="K49" s="41"/>
+      <c r="L49" s="41"/>
+      <c r="M49" s="41"/>
+      <c r="N49" s="41"/>
+      <c r="O49" s="41"/>
+      <c r="P49" s="41"/>
+      <c r="Q49" s="41"/>
+      <c r="R49" s="41"/>
+      <c r="S49" s="41"/>
+      <c r="T49" s="41"/>
+      <c r="U49" s="41"/>
+      <c r="V49" s="41"/>
+      <c r="W49" s="41"/>
+      <c r="X49" s="41"/>
+      <c r="Y49" s="41"/>
+      <c r="Z49" s="41"/>
+      <c r="AA49" s="42"/>
     </row>
     <row r="50" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="30"/>
-      <c r="B50" s="68"/>
-      <c r="C50" s="69"/>
-      <c r="D50" s="69"/>
-      <c r="E50" s="69"/>
-      <c r="F50" s="69"/>
-      <c r="G50" s="69"/>
-      <c r="H50" s="69"/>
-      <c r="I50" s="69"/>
-      <c r="J50" s="69"/>
-      <c r="K50" s="69"/>
-      <c r="L50" s="69"/>
-      <c r="M50" s="69"/>
-      <c r="N50" s="69"/>
-      <c r="O50" s="69"/>
-      <c r="P50" s="69"/>
-      <c r="Q50" s="69"/>
-      <c r="R50" s="69"/>
-      <c r="S50" s="69"/>
-      <c r="T50" s="69"/>
-      <c r="U50" s="69"/>
-      <c r="V50" s="69"/>
-      <c r="W50" s="69"/>
-      <c r="X50" s="69"/>
-      <c r="Y50" s="69"/>
-      <c r="Z50" s="69"/>
-      <c r="AA50" s="70"/>
+      <c r="B50" s="40"/>
+      <c r="C50" s="41"/>
+      <c r="D50" s="41"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="41"/>
+      <c r="G50" s="41"/>
+      <c r="H50" s="41"/>
+      <c r="I50" s="41"/>
+      <c r="J50" s="41"/>
+      <c r="K50" s="41"/>
+      <c r="L50" s="41"/>
+      <c r="M50" s="41"/>
+      <c r="N50" s="41"/>
+      <c r="O50" s="41"/>
+      <c r="P50" s="41"/>
+      <c r="Q50" s="41"/>
+      <c r="R50" s="41"/>
+      <c r="S50" s="41"/>
+      <c r="T50" s="41"/>
+      <c r="U50" s="41"/>
+      <c r="V50" s="41"/>
+      <c r="W50" s="41"/>
+      <c r="X50" s="41"/>
+      <c r="Y50" s="41"/>
+      <c r="Z50" s="41"/>
+      <c r="AA50" s="42"/>
     </row>
     <row r="51" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="30"/>
-      <c r="B51" s="68"/>
-      <c r="C51" s="69"/>
-      <c r="D51" s="69"/>
-      <c r="E51" s="69"/>
-      <c r="F51" s="69"/>
-      <c r="G51" s="69"/>
-      <c r="H51" s="69"/>
-      <c r="I51" s="69"/>
-      <c r="J51" s="69"/>
-      <c r="K51" s="69"/>
-      <c r="L51" s="69"/>
-      <c r="M51" s="69"/>
-      <c r="N51" s="69"/>
-      <c r="O51" s="69"/>
-      <c r="P51" s="69"/>
-      <c r="Q51" s="69"/>
-      <c r="R51" s="69"/>
-      <c r="S51" s="69"/>
-      <c r="T51" s="69"/>
-      <c r="U51" s="69"/>
-      <c r="V51" s="69"/>
-      <c r="W51" s="69"/>
-      <c r="X51" s="69"/>
-      <c r="Y51" s="69"/>
-      <c r="Z51" s="69"/>
-      <c r="AA51" s="70"/>
+      <c r="B51" s="40"/>
+      <c r="C51" s="41"/>
+      <c r="D51" s="41"/>
+      <c r="E51" s="41"/>
+      <c r="F51" s="41"/>
+      <c r="G51" s="41"/>
+      <c r="H51" s="41"/>
+      <c r="I51" s="41"/>
+      <c r="J51" s="41"/>
+      <c r="K51" s="41"/>
+      <c r="L51" s="41"/>
+      <c r="M51" s="41"/>
+      <c r="N51" s="41"/>
+      <c r="O51" s="41"/>
+      <c r="P51" s="41"/>
+      <c r="Q51" s="41"/>
+      <c r="R51" s="41"/>
+      <c r="S51" s="41"/>
+      <c r="T51" s="41"/>
+      <c r="U51" s="41"/>
+      <c r="V51" s="41"/>
+      <c r="W51" s="41"/>
+      <c r="X51" s="41"/>
+      <c r="Y51" s="41"/>
+      <c r="Z51" s="41"/>
+      <c r="AA51" s="42"/>
     </row>
     <row r="52" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="30"/>
-      <c r="B52" s="68"/>
-      <c r="C52" s="69"/>
-      <c r="D52" s="69"/>
-      <c r="E52" s="69"/>
-      <c r="F52" s="69"/>
-      <c r="G52" s="69"/>
-      <c r="H52" s="69"/>
-      <c r="I52" s="69"/>
-      <c r="J52" s="69"/>
-      <c r="K52" s="69"/>
-      <c r="L52" s="69"/>
-      <c r="M52" s="69"/>
-      <c r="N52" s="69"/>
-      <c r="O52" s="69"/>
-      <c r="P52" s="69"/>
-      <c r="Q52" s="69"/>
-      <c r="R52" s="69"/>
-      <c r="S52" s="69"/>
-      <c r="T52" s="69"/>
-      <c r="U52" s="69"/>
-      <c r="V52" s="69"/>
-      <c r="W52" s="69"/>
-      <c r="X52" s="69"/>
-      <c r="Y52" s="69"/>
-      <c r="Z52" s="69"/>
-      <c r="AA52" s="70"/>
+      <c r="B52" s="40"/>
+      <c r="C52" s="41"/>
+      <c r="D52" s="41"/>
+      <c r="E52" s="41"/>
+      <c r="F52" s="41"/>
+      <c r="G52" s="41"/>
+      <c r="H52" s="41"/>
+      <c r="I52" s="41"/>
+      <c r="J52" s="41"/>
+      <c r="K52" s="41"/>
+      <c r="L52" s="41"/>
+      <c r="M52" s="41"/>
+      <c r="N52" s="41"/>
+      <c r="O52" s="41"/>
+      <c r="P52" s="41"/>
+      <c r="Q52" s="41"/>
+      <c r="R52" s="41"/>
+      <c r="S52" s="41"/>
+      <c r="T52" s="41"/>
+      <c r="U52" s="41"/>
+      <c r="V52" s="41"/>
+      <c r="W52" s="41"/>
+      <c r="X52" s="41"/>
+      <c r="Y52" s="41"/>
+      <c r="Z52" s="41"/>
+      <c r="AA52" s="42"/>
     </row>
     <row r="53" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="30"/>
-      <c r="B53" s="68"/>
-      <c r="C53" s="69"/>
-      <c r="D53" s="69"/>
-      <c r="E53" s="69"/>
-      <c r="F53" s="69"/>
-      <c r="G53" s="69"/>
-      <c r="H53" s="69"/>
-      <c r="I53" s="69"/>
-      <c r="J53" s="69"/>
-      <c r="K53" s="69"/>
-      <c r="L53" s="69"/>
-      <c r="M53" s="69"/>
-      <c r="N53" s="69"/>
-      <c r="O53" s="69"/>
-      <c r="P53" s="69"/>
-      <c r="Q53" s="69"/>
-      <c r="R53" s="69"/>
-      <c r="S53" s="69"/>
-      <c r="T53" s="69"/>
-      <c r="U53" s="69"/>
-      <c r="V53" s="69"/>
-      <c r="W53" s="69"/>
-      <c r="X53" s="69"/>
-      <c r="Y53" s="69"/>
-      <c r="Z53" s="69"/>
-      <c r="AA53" s="70"/>
+      <c r="B53" s="40"/>
+      <c r="C53" s="41"/>
+      <c r="D53" s="41"/>
+      <c r="E53" s="41"/>
+      <c r="F53" s="41"/>
+      <c r="G53" s="41"/>
+      <c r="H53" s="41"/>
+      <c r="I53" s="41"/>
+      <c r="J53" s="41"/>
+      <c r="K53" s="41"/>
+      <c r="L53" s="41"/>
+      <c r="M53" s="41"/>
+      <c r="N53" s="41"/>
+      <c r="O53" s="41"/>
+      <c r="P53" s="41"/>
+      <c r="Q53" s="41"/>
+      <c r="R53" s="41"/>
+      <c r="S53" s="41"/>
+      <c r="T53" s="41"/>
+      <c r="U53" s="41"/>
+      <c r="V53" s="41"/>
+      <c r="W53" s="41"/>
+      <c r="X53" s="41"/>
+      <c r="Y53" s="41"/>
+      <c r="Z53" s="41"/>
+      <c r="AA53" s="42"/>
     </row>
     <row r="54" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="30"/>
-      <c r="B54" s="68"/>
-      <c r="C54" s="69"/>
-      <c r="D54" s="69"/>
-      <c r="E54" s="69"/>
-      <c r="F54" s="69"/>
-      <c r="G54" s="69"/>
-      <c r="H54" s="69"/>
-      <c r="I54" s="69"/>
-      <c r="J54" s="69"/>
-      <c r="K54" s="69"/>
-      <c r="L54" s="69"/>
-      <c r="M54" s="69"/>
-      <c r="N54" s="69"/>
-      <c r="O54" s="69"/>
-      <c r="P54" s="69"/>
-      <c r="Q54" s="69"/>
-      <c r="R54" s="69"/>
-      <c r="S54" s="69"/>
-      <c r="T54" s="69"/>
-      <c r="U54" s="69"/>
-      <c r="V54" s="69"/>
-      <c r="W54" s="69"/>
-      <c r="X54" s="69"/>
-      <c r="Y54" s="69"/>
-      <c r="Z54" s="69"/>
-      <c r="AA54" s="70"/>
+      <c r="B54" s="40"/>
+      <c r="C54" s="41"/>
+      <c r="D54" s="41"/>
+      <c r="E54" s="41"/>
+      <c r="F54" s="41"/>
+      <c r="G54" s="41"/>
+      <c r="H54" s="41"/>
+      <c r="I54" s="41"/>
+      <c r="J54" s="41"/>
+      <c r="K54" s="41"/>
+      <c r="L54" s="41"/>
+      <c r="M54" s="41"/>
+      <c r="N54" s="41"/>
+      <c r="O54" s="41"/>
+      <c r="P54" s="41"/>
+      <c r="Q54" s="41"/>
+      <c r="R54" s="41"/>
+      <c r="S54" s="41"/>
+      <c r="T54" s="41"/>
+      <c r="U54" s="41"/>
+      <c r="V54" s="41"/>
+      <c r="W54" s="41"/>
+      <c r="X54" s="41"/>
+      <c r="Y54" s="41"/>
+      <c r="Z54" s="41"/>
+      <c r="AA54" s="42"/>
     </row>
     <row r="55" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="30"/>
-      <c r="B55" s="68"/>
-      <c r="C55" s="69"/>
-      <c r="D55" s="69"/>
-      <c r="E55" s="69"/>
-      <c r="F55" s="69"/>
-      <c r="G55" s="69"/>
-      <c r="H55" s="69"/>
-      <c r="I55" s="69"/>
-      <c r="J55" s="69"/>
-      <c r="K55" s="69"/>
-      <c r="L55" s="69"/>
-      <c r="M55" s="69"/>
-      <c r="N55" s="69"/>
-      <c r="O55" s="69"/>
-      <c r="P55" s="69"/>
-      <c r="Q55" s="69"/>
-      <c r="R55" s="69"/>
-      <c r="S55" s="69"/>
-      <c r="T55" s="69"/>
-      <c r="U55" s="69"/>
-      <c r="V55" s="69"/>
-      <c r="W55" s="69"/>
-      <c r="X55" s="69"/>
-      <c r="Y55" s="69"/>
-      <c r="Z55" s="69"/>
-      <c r="AA55" s="70"/>
+      <c r="B55" s="40"/>
+      <c r="C55" s="41"/>
+      <c r="D55" s="41"/>
+      <c r="E55" s="41"/>
+      <c r="F55" s="41"/>
+      <c r="G55" s="41"/>
+      <c r="H55" s="41"/>
+      <c r="I55" s="41"/>
+      <c r="J55" s="41"/>
+      <c r="K55" s="41"/>
+      <c r="L55" s="41"/>
+      <c r="M55" s="41"/>
+      <c r="N55" s="41"/>
+      <c r="O55" s="41"/>
+      <c r="P55" s="41"/>
+      <c r="Q55" s="41"/>
+      <c r="R55" s="41"/>
+      <c r="S55" s="41"/>
+      <c r="T55" s="41"/>
+      <c r="U55" s="41"/>
+      <c r="V55" s="41"/>
+      <c r="W55" s="41"/>
+      <c r="X55" s="41"/>
+      <c r="Y55" s="41"/>
+      <c r="Z55" s="41"/>
+      <c r="AA55" s="42"/>
     </row>
     <row r="56" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
@@ -3004,15 +3000,15 @@
     </row>
     <row r="58" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
-      <c r="C58" s="1"/>
-      <c r="D58" s="36"/>
-      <c r="E58" s="36"/>
-      <c r="F58" s="36"/>
-      <c r="G58" s="36"/>
-      <c r="H58" s="36"/>
-      <c r="I58" s="36"/>
-      <c r="J58" s="36"/>
+      <c r="B58" s="72"/>
+      <c r="C58" s="72"/>
+      <c r="D58" s="72"/>
+      <c r="E58" s="72"/>
+      <c r="F58" s="72"/>
+      <c r="G58" s="72"/>
+      <c r="H58" s="72"/>
+      <c r="I58" s="72"/>
+      <c r="J58" s="72"/>
       <c r="K58" s="36"/>
       <c r="L58" s="36"/>
       <c r="M58" s="36"/>
@@ -3033,31 +3029,31 @@
     </row>
     <row r="59" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
-      <c r="B59" s="61"/>
-      <c r="C59" s="61"/>
-      <c r="D59" s="61"/>
-      <c r="E59" s="61"/>
-      <c r="F59" s="61"/>
-      <c r="G59" s="61"/>
-      <c r="H59" s="61"/>
-      <c r="I59" s="61"/>
-      <c r="J59" s="61"/>
-      <c r="K59" s="62"/>
-      <c r="L59" s="63"/>
-      <c r="M59" s="63"/>
-      <c r="N59" s="63"/>
-      <c r="O59" s="63"/>
-      <c r="P59" s="63"/>
-      <c r="Q59" s="63"/>
-      <c r="R59" s="64"/>
-      <c r="S59" s="64"/>
-      <c r="T59" s="64"/>
-      <c r="U59" s="64"/>
-      <c r="V59" s="64"/>
-      <c r="W59" s="64"/>
-      <c r="X59" s="64"/>
-      <c r="Y59" s="65"/>
-      <c r="Z59" s="65"/>
+      <c r="B59" s="72"/>
+      <c r="C59" s="72"/>
+      <c r="D59" s="72"/>
+      <c r="E59" s="72"/>
+      <c r="F59" s="72"/>
+      <c r="G59" s="72"/>
+      <c r="H59" s="72"/>
+      <c r="I59" s="72"/>
+      <c r="J59" s="72"/>
+      <c r="K59" s="67"/>
+      <c r="L59" s="68"/>
+      <c r="M59" s="68"/>
+      <c r="N59" s="68"/>
+      <c r="O59" s="68"/>
+      <c r="P59" s="68"/>
+      <c r="Q59" s="68"/>
+      <c r="R59" s="35"/>
+      <c r="S59" s="35"/>
+      <c r="T59" s="35"/>
+      <c r="U59" s="35"/>
+      <c r="V59" s="35"/>
+      <c r="W59" s="35"/>
+      <c r="X59" s="35"/>
+      <c r="Y59" s="36"/>
+      <c r="Z59" s="36"/>
       <c r="AA59" s="1"/>
     </row>
     <row r="60" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3209,61 +3205,61 @@
     <row r="65" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
       <c r="B65" s="34"/>
-      <c r="C65" s="40" t="s">
+      <c r="C65" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="D65" s="41"/>
-      <c r="E65" s="41"/>
-      <c r="F65" s="41"/>
-      <c r="G65" s="41"/>
-      <c r="H65" s="41"/>
-      <c r="I65" s="41"/>
-      <c r="J65" s="41"/>
-      <c r="K65" s="41"/>
-      <c r="L65" s="41"/>
-      <c r="M65" s="41"/>
-      <c r="N65" s="41"/>
-      <c r="O65" s="41"/>
-      <c r="P65" s="41"/>
-      <c r="Q65" s="41"/>
-      <c r="R65" s="41"/>
-      <c r="S65" s="41"/>
-      <c r="T65" s="41"/>
-      <c r="U65" s="41"/>
-      <c r="V65" s="41"/>
-      <c r="W65" s="41"/>
-      <c r="X65" s="41"/>
-      <c r="Y65" s="41"/>
-      <c r="Z65" s="41"/>
+      <c r="D65" s="56"/>
+      <c r="E65" s="56"/>
+      <c r="F65" s="56"/>
+      <c r="G65" s="56"/>
+      <c r="H65" s="56"/>
+      <c r="I65" s="56"/>
+      <c r="J65" s="56"/>
+      <c r="K65" s="56"/>
+      <c r="L65" s="56"/>
+      <c r="M65" s="56"/>
+      <c r="N65" s="56"/>
+      <c r="O65" s="56"/>
+      <c r="P65" s="56"/>
+      <c r="Q65" s="56"/>
+      <c r="R65" s="56"/>
+      <c r="S65" s="56"/>
+      <c r="T65" s="56"/>
+      <c r="U65" s="56"/>
+      <c r="V65" s="56"/>
+      <c r="W65" s="56"/>
+      <c r="X65" s="56"/>
+      <c r="Y65" s="56"/>
+      <c r="Z65" s="56"/>
       <c r="AA65" s="34"/>
     </row>
     <row r="66" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
       <c r="B66" s="34"/>
-      <c r="C66" s="41"/>
-      <c r="D66" s="41"/>
-      <c r="E66" s="41"/>
-      <c r="F66" s="41"/>
-      <c r="G66" s="41"/>
-      <c r="H66" s="41"/>
-      <c r="I66" s="41"/>
-      <c r="J66" s="41"/>
-      <c r="K66" s="41"/>
-      <c r="L66" s="41"/>
-      <c r="M66" s="41"/>
-      <c r="N66" s="41"/>
-      <c r="O66" s="41"/>
-      <c r="P66" s="41"/>
-      <c r="Q66" s="41"/>
-      <c r="R66" s="41"/>
-      <c r="S66" s="41"/>
-      <c r="T66" s="41"/>
-      <c r="U66" s="41"/>
-      <c r="V66" s="41"/>
-      <c r="W66" s="41"/>
-      <c r="X66" s="41"/>
-      <c r="Y66" s="41"/>
-      <c r="Z66" s="41"/>
+      <c r="C66" s="56"/>
+      <c r="D66" s="56"/>
+      <c r="E66" s="56"/>
+      <c r="F66" s="56"/>
+      <c r="G66" s="56"/>
+      <c r="H66" s="56"/>
+      <c r="I66" s="56"/>
+      <c r="J66" s="56"/>
+      <c r="K66" s="56"/>
+      <c r="L66" s="56"/>
+      <c r="M66" s="56"/>
+      <c r="N66" s="56"/>
+      <c r="O66" s="56"/>
+      <c r="P66" s="56"/>
+      <c r="Q66" s="56"/>
+      <c r="R66" s="56"/>
+      <c r="S66" s="56"/>
+      <c r="T66" s="56"/>
+      <c r="U66" s="56"/>
+      <c r="V66" s="56"/>
+      <c r="W66" s="56"/>
+      <c r="X66" s="56"/>
+      <c r="Y66" s="56"/>
+      <c r="Z66" s="56"/>
       <c r="AA66" s="34"/>
     </row>
     <row r="67" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30354,15 +30350,30 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="B36:AA36"/>
-    <mergeCell ref="B32:AA32"/>
-    <mergeCell ref="B50:AA50"/>
-    <mergeCell ref="B14:AA15"/>
-    <mergeCell ref="B26:AA26"/>
-    <mergeCell ref="B41:AA41"/>
-    <mergeCell ref="H19:Z19"/>
-    <mergeCell ref="B33:AA33"/>
-    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="C65:Z66"/>
+    <mergeCell ref="B40:AA40"/>
+    <mergeCell ref="B49:AA49"/>
+    <mergeCell ref="K59:Q59"/>
+    <mergeCell ref="B55:AA55"/>
+    <mergeCell ref="B42:AA42"/>
+    <mergeCell ref="B54:AA54"/>
+    <mergeCell ref="B48:AA48"/>
+    <mergeCell ref="B58:J59"/>
+    <mergeCell ref="H10:Z10"/>
+    <mergeCell ref="B51:AA51"/>
+    <mergeCell ref="B44:AA44"/>
+    <mergeCell ref="B53:AA53"/>
+    <mergeCell ref="B38:AA38"/>
+    <mergeCell ref="B29:AA29"/>
+    <mergeCell ref="H21:Z21"/>
+    <mergeCell ref="B34:AA34"/>
+    <mergeCell ref="B37:AA37"/>
+    <mergeCell ref="B28:AA28"/>
+    <mergeCell ref="B24:AA24"/>
+    <mergeCell ref="B30:AA30"/>
+    <mergeCell ref="H17:Z17"/>
+    <mergeCell ref="B47:AA47"/>
+    <mergeCell ref="B52:AA52"/>
     <mergeCell ref="B3:AA3"/>
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="B31:AA31"/>
@@ -30379,31 +30390,16 @@
     <mergeCell ref="H12:T12"/>
     <mergeCell ref="B25:AA25"/>
     <mergeCell ref="B45:AA45"/>
+    <mergeCell ref="B36:AA36"/>
+    <mergeCell ref="B32:AA32"/>
+    <mergeCell ref="B50:AA50"/>
+    <mergeCell ref="B14:AA15"/>
+    <mergeCell ref="B26:AA26"/>
+    <mergeCell ref="B41:AA41"/>
+    <mergeCell ref="H19:Z19"/>
+    <mergeCell ref="B33:AA33"/>
+    <mergeCell ref="B17:G17"/>
     <mergeCell ref="B23:AA23"/>
-    <mergeCell ref="H10:Z10"/>
-    <mergeCell ref="B51:AA51"/>
-    <mergeCell ref="B44:AA44"/>
-    <mergeCell ref="B53:AA53"/>
-    <mergeCell ref="B38:AA38"/>
-    <mergeCell ref="B29:AA29"/>
-    <mergeCell ref="H21:Z21"/>
-    <mergeCell ref="B34:AA34"/>
-    <mergeCell ref="B37:AA37"/>
-    <mergeCell ref="B28:AA28"/>
-    <mergeCell ref="B24:AA24"/>
-    <mergeCell ref="B30:AA30"/>
-    <mergeCell ref="H17:Z17"/>
-    <mergeCell ref="B47:AA47"/>
-    <mergeCell ref="B52:AA52"/>
-    <mergeCell ref="C65:Z66"/>
-    <mergeCell ref="B40:AA40"/>
-    <mergeCell ref="B49:AA49"/>
-    <mergeCell ref="K59:Q59"/>
-    <mergeCell ref="B55:AA55"/>
-    <mergeCell ref="B59:J59"/>
-    <mergeCell ref="B42:AA42"/>
-    <mergeCell ref="B54:AA54"/>
-    <mergeCell ref="B48:AA48"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.98425196850393704" header="0" footer="0"/>

--- a/static/templates/tec02-A_template.xlsx
+++ b/static/templates/tec02-A_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\diseño-afk\static\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F0F812-236E-4D30-BE40-97F7DB213F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953119E7-599E-4BDC-83C6-AE64A800C09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -578,7 +578,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -693,6 +693,19 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -702,34 +715,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -743,9 +753,14 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -755,24 +770,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1377,125 +1376,125 @@
     </row>
     <row r="3" spans="1:27" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="56"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="56"/>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="56"/>
-      <c r="S3" s="56"/>
-      <c r="T3" s="56"/>
-      <c r="U3" s="56"/>
-      <c r="V3" s="56"/>
-      <c r="W3" s="56"/>
-      <c r="X3" s="56"/>
-      <c r="Y3" s="56"/>
-      <c r="Z3" s="56"/>
-      <c r="AA3" s="56"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="41"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="41"/>
+      <c r="U3" s="41"/>
+      <c r="V3" s="41"/>
+      <c r="W3" s="41"/>
+      <c r="X3" s="41"/>
+      <c r="Y3" s="41"/>
+      <c r="Z3" s="41"/>
+      <c r="AA3" s="41"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
       <c r="B4" s="61"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="56"/>
-      <c r="Q4" s="56"/>
-      <c r="R4" s="56"/>
-      <c r="S4" s="56"/>
-      <c r="T4" s="56"/>
-      <c r="U4" s="56"/>
-      <c r="V4" s="56"/>
-      <c r="W4" s="56"/>
-      <c r="X4" s="56"/>
-      <c r="Y4" s="56"/>
-      <c r="Z4" s="56"/>
-      <c r="AA4" s="56"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="41"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="41"/>
+      <c r="U4" s="41"/>
+      <c r="V4" s="41"/>
+      <c r="W4" s="41"/>
+      <c r="X4" s="41"/>
+      <c r="Y4" s="41"/>
+      <c r="Z4" s="41"/>
+      <c r="AA4" s="41"/>
     </row>
     <row r="5" spans="1:27" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
       <c r="B5" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
-      <c r="K5" s="56"/>
-      <c r="L5" s="56"/>
-      <c r="M5" s="56"/>
-      <c r="N5" s="56"/>
-      <c r="O5" s="56"/>
-      <c r="P5" s="56"/>
-      <c r="Q5" s="56"/>
-      <c r="R5" s="56"/>
-      <c r="S5" s="56"/>
-      <c r="T5" s="56"/>
-      <c r="U5" s="56"/>
-      <c r="V5" s="56"/>
-      <c r="W5" s="56"/>
-      <c r="X5" s="56"/>
-      <c r="Y5" s="56"/>
-      <c r="Z5" s="56"/>
-      <c r="AA5" s="56"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="41"/>
+      <c r="R5" s="41"/>
+      <c r="S5" s="41"/>
+      <c r="T5" s="41"/>
+      <c r="U5" s="41"/>
+      <c r="V5" s="41"/>
+      <c r="W5" s="41"/>
+      <c r="X5" s="41"/>
+      <c r="Y5" s="41"/>
+      <c r="Z5" s="41"/>
+      <c r="AA5" s="41"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
       <c r="B6" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
-      <c r="M6" s="56"/>
-      <c r="N6" s="56"/>
-      <c r="O6" s="56"/>
-      <c r="P6" s="56"/>
-      <c r="Q6" s="56"/>
-      <c r="R6" s="56"/>
-      <c r="S6" s="56"/>
-      <c r="T6" s="56"/>
-      <c r="U6" s="56"/>
-      <c r="V6" s="56"/>
-      <c r="W6" s="56"/>
-      <c r="X6" s="56"/>
-      <c r="Y6" s="56"/>
-      <c r="Z6" s="56"/>
-      <c r="AA6" s="56"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="41"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="41"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="41"/>
+      <c r="V6" s="41"/>
+      <c r="W6" s="41"/>
+      <c r="X6" s="41"/>
+      <c r="Y6" s="41"/>
+      <c r="Z6" s="41"/>
+      <c r="AA6" s="41"/>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2"/>
@@ -1594,7 +1593,7 @@
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
-      <c r="H10" s="62"/>
+      <c r="H10" s="52"/>
       <c r="I10" s="53"/>
       <c r="J10" s="53"/>
       <c r="K10" s="53"/>
@@ -1654,7 +1653,7 @@
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
-      <c r="H12" s="62"/>
+      <c r="H12" s="52"/>
       <c r="I12" s="53"/>
       <c r="J12" s="53"/>
       <c r="K12" s="53"/>
@@ -1708,63 +1707,63 @@
     </row>
     <row r="14" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="47"/>
-      <c r="L14" s="47"/>
-      <c r="M14" s="47"/>
-      <c r="N14" s="47"/>
-      <c r="O14" s="47"/>
-      <c r="P14" s="47"/>
-      <c r="Q14" s="47"/>
-      <c r="R14" s="47"/>
-      <c r="S14" s="47"/>
-      <c r="T14" s="47"/>
-      <c r="U14" s="47"/>
-      <c r="V14" s="47"/>
-      <c r="W14" s="47"/>
-      <c r="X14" s="47"/>
-      <c r="Y14" s="47"/>
-      <c r="Z14" s="47"/>
-      <c r="AA14" s="48"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="63"/>
+      <c r="J14" s="63"/>
+      <c r="K14" s="63"/>
+      <c r="L14" s="63"/>
+      <c r="M14" s="63"/>
+      <c r="N14" s="63"/>
+      <c r="O14" s="63"/>
+      <c r="P14" s="63"/>
+      <c r="Q14" s="63"/>
+      <c r="R14" s="63"/>
+      <c r="S14" s="63"/>
+      <c r="T14" s="63"/>
+      <c r="U14" s="63"/>
+      <c r="V14" s="63"/>
+      <c r="W14" s="63"/>
+      <c r="X14" s="63"/>
+      <c r="Y14" s="63"/>
+      <c r="Z14" s="63"/>
+      <c r="AA14" s="64"/>
     </row>
     <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
-      <c r="B15" s="49"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="50"/>
-      <c r="K15" s="50"/>
-      <c r="L15" s="50"/>
-      <c r="M15" s="50"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="50"/>
-      <c r="P15" s="50"/>
-      <c r="Q15" s="50"/>
-      <c r="R15" s="50"/>
-      <c r="S15" s="50"/>
-      <c r="T15" s="50"/>
-      <c r="U15" s="50"/>
-      <c r="V15" s="50"/>
-      <c r="W15" s="50"/>
-      <c r="X15" s="50"/>
-      <c r="Y15" s="50"/>
-      <c r="Z15" s="50"/>
-      <c r="AA15" s="51"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="66"/>
+      <c r="J15" s="66"/>
+      <c r="K15" s="66"/>
+      <c r="L15" s="66"/>
+      <c r="M15" s="66"/>
+      <c r="N15" s="66"/>
+      <c r="O15" s="66"/>
+      <c r="P15" s="66"/>
+      <c r="Q15" s="66"/>
+      <c r="R15" s="66"/>
+      <c r="S15" s="66"/>
+      <c r="T15" s="66"/>
+      <c r="U15" s="66"/>
+      <c r="V15" s="66"/>
+      <c r="W15" s="66"/>
+      <c r="X15" s="66"/>
+      <c r="Y15" s="66"/>
+      <c r="Z15" s="66"/>
+      <c r="AA15" s="67"/>
     </row>
     <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
@@ -1797,15 +1796,15 @@
     </row>
     <row r="17" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
-      <c r="B17" s="55" t="s">
+      <c r="B17" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="56"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="56"/>
-      <c r="G17" s="56"/>
-      <c r="H17" s="52"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="55"/>
       <c r="I17" s="53"/>
       <c r="J17" s="53"/>
       <c r="K17" s="53"/>
@@ -1857,15 +1856,15 @@
     </row>
     <row r="19" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
-      <c r="B19" s="55" t="s">
+      <c r="B19" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
-      <c r="H19" s="52"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="55"/>
       <c r="I19" s="53"/>
       <c r="J19" s="53"/>
       <c r="K19" s="53"/>
@@ -1917,15 +1916,15 @@
     </row>
     <row r="21" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
-      <c r="B21" s="55" t="s">
+      <c r="B21" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="52"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="55"/>
       <c r="I21" s="53"/>
       <c r="J21" s="53"/>
       <c r="K21" s="53"/>
@@ -1977,968 +1976,968 @@
     </row>
     <row r="23" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
-      <c r="B23" s="63" t="s">
+      <c r="B23" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="64"/>
-      <c r="D23" s="64"/>
-      <c r="E23" s="64"/>
-      <c r="F23" s="64"/>
-      <c r="G23" s="64"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="64"/>
-      <c r="J23" s="64"/>
-      <c r="K23" s="64"/>
-      <c r="L23" s="64"/>
-      <c r="M23" s="64"/>
-      <c r="N23" s="64"/>
-      <c r="O23" s="64"/>
-      <c r="P23" s="64"/>
-      <c r="Q23" s="64"/>
-      <c r="R23" s="64"/>
-      <c r="S23" s="64"/>
-      <c r="T23" s="64"/>
-      <c r="U23" s="64"/>
-      <c r="V23" s="64"/>
-      <c r="W23" s="64"/>
-      <c r="X23" s="64"/>
-      <c r="Y23" s="64"/>
-      <c r="Z23" s="64"/>
-      <c r="AA23" s="65"/>
+      <c r="C23" s="69"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="69"/>
+      <c r="F23" s="69"/>
+      <c r="G23" s="69"/>
+      <c r="H23" s="69"/>
+      <c r="I23" s="69"/>
+      <c r="J23" s="69"/>
+      <c r="K23" s="69"/>
+      <c r="L23" s="69"/>
+      <c r="M23" s="69"/>
+      <c r="N23" s="69"/>
+      <c r="O23" s="69"/>
+      <c r="P23" s="69"/>
+      <c r="Q23" s="69"/>
+      <c r="R23" s="69"/>
+      <c r="S23" s="69"/>
+      <c r="T23" s="69"/>
+      <c r="U23" s="69"/>
+      <c r="V23" s="69"/>
+      <c r="W23" s="69"/>
+      <c r="X23" s="69"/>
+      <c r="Y23" s="69"/>
+      <c r="Z23" s="69"/>
+      <c r="AA23" s="70"/>
     </row>
     <row r="24" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="41"/>
-      <c r="J24" s="41"/>
-      <c r="K24" s="41"/>
-      <c r="L24" s="41"/>
-      <c r="M24" s="41"/>
-      <c r="N24" s="41"/>
-      <c r="O24" s="41"/>
-      <c r="P24" s="41"/>
-      <c r="Q24" s="41"/>
-      <c r="R24" s="41"/>
-      <c r="S24" s="41"/>
-      <c r="T24" s="41"/>
-      <c r="U24" s="41"/>
-      <c r="V24" s="41"/>
-      <c r="W24" s="41"/>
-      <c r="X24" s="41"/>
-      <c r="Y24" s="41"/>
-      <c r="Z24" s="41"/>
-      <c r="AA24" s="42"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
+      <c r="L24" s="46"/>
+      <c r="M24" s="46"/>
+      <c r="N24" s="46"/>
+      <c r="O24" s="46"/>
+      <c r="P24" s="46"/>
+      <c r="Q24" s="46"/>
+      <c r="R24" s="46"/>
+      <c r="S24" s="46"/>
+      <c r="T24" s="46"/>
+      <c r="U24" s="46"/>
+      <c r="V24" s="46"/>
+      <c r="W24" s="46"/>
+      <c r="X24" s="46"/>
+      <c r="Y24" s="46"/>
+      <c r="Z24" s="46"/>
+      <c r="AA24" s="47"/>
     </row>
     <row r="25" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="41"/>
-      <c r="J25" s="41"/>
-      <c r="K25" s="41"/>
-      <c r="L25" s="41"/>
-      <c r="M25" s="41"/>
-      <c r="N25" s="41"/>
-      <c r="O25" s="41"/>
-      <c r="P25" s="41"/>
-      <c r="Q25" s="41"/>
-      <c r="R25" s="41"/>
-      <c r="S25" s="41"/>
-      <c r="T25" s="41"/>
-      <c r="U25" s="41"/>
-      <c r="V25" s="41"/>
-      <c r="W25" s="41"/>
-      <c r="X25" s="41"/>
-      <c r="Y25" s="41"/>
-      <c r="Z25" s="41"/>
-      <c r="AA25" s="42"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="46"/>
+      <c r="K25" s="46"/>
+      <c r="L25" s="46"/>
+      <c r="M25" s="46"/>
+      <c r="N25" s="46"/>
+      <c r="O25" s="46"/>
+      <c r="P25" s="46"/>
+      <c r="Q25" s="46"/>
+      <c r="R25" s="46"/>
+      <c r="S25" s="46"/>
+      <c r="T25" s="46"/>
+      <c r="U25" s="46"/>
+      <c r="V25" s="46"/>
+      <c r="W25" s="46"/>
+      <c r="X25" s="46"/>
+      <c r="Y25" s="46"/>
+      <c r="Z25" s="46"/>
+      <c r="AA25" s="47"/>
     </row>
     <row r="26" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="41"/>
-      <c r="J26" s="41"/>
-      <c r="K26" s="41"/>
-      <c r="L26" s="41"/>
-      <c r="M26" s="41"/>
-      <c r="N26" s="41"/>
-      <c r="O26" s="41"/>
-      <c r="P26" s="41"/>
-      <c r="Q26" s="41"/>
-      <c r="R26" s="41"/>
-      <c r="S26" s="41"/>
-      <c r="T26" s="41"/>
-      <c r="U26" s="41"/>
-      <c r="V26" s="41"/>
-      <c r="W26" s="41"/>
-      <c r="X26" s="41"/>
-      <c r="Y26" s="41"/>
-      <c r="Z26" s="41"/>
-      <c r="AA26" s="42"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="46"/>
+      <c r="K26" s="46"/>
+      <c r="L26" s="46"/>
+      <c r="M26" s="46"/>
+      <c r="N26" s="46"/>
+      <c r="O26" s="46"/>
+      <c r="P26" s="46"/>
+      <c r="Q26" s="46"/>
+      <c r="R26" s="46"/>
+      <c r="S26" s="46"/>
+      <c r="T26" s="46"/>
+      <c r="U26" s="46"/>
+      <c r="V26" s="46"/>
+      <c r="W26" s="46"/>
+      <c r="X26" s="46"/>
+      <c r="Y26" s="46"/>
+      <c r="Z26" s="46"/>
+      <c r="AA26" s="47"/>
     </row>
     <row r="27" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="41"/>
-      <c r="J27" s="41"/>
-      <c r="K27" s="41"/>
-      <c r="L27" s="41"/>
-      <c r="M27" s="41"/>
-      <c r="N27" s="41"/>
-      <c r="O27" s="41"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="41"/>
-      <c r="S27" s="41"/>
-      <c r="T27" s="41"/>
-      <c r="U27" s="41"/>
-      <c r="V27" s="41"/>
-      <c r="W27" s="41"/>
-      <c r="X27" s="41"/>
-      <c r="Y27" s="41"/>
-      <c r="Z27" s="41"/>
-      <c r="AA27" s="42"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="46"/>
+      <c r="J27" s="46"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="46"/>
+      <c r="M27" s="46"/>
+      <c r="N27" s="46"/>
+      <c r="O27" s="46"/>
+      <c r="P27" s="46"/>
+      <c r="Q27" s="46"/>
+      <c r="R27" s="46"/>
+      <c r="S27" s="46"/>
+      <c r="T27" s="46"/>
+      <c r="U27" s="46"/>
+      <c r="V27" s="46"/>
+      <c r="W27" s="46"/>
+      <c r="X27" s="46"/>
+      <c r="Y27" s="46"/>
+      <c r="Z27" s="46"/>
+      <c r="AA27" s="47"/>
     </row>
     <row r="28" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
-      <c r="B28" s="40"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="41"/>
-      <c r="K28" s="41"/>
-      <c r="L28" s="41"/>
-      <c r="M28" s="41"/>
-      <c r="N28" s="41"/>
-      <c r="O28" s="41"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="41"/>
-      <c r="S28" s="41"/>
-      <c r="T28" s="41"/>
-      <c r="U28" s="41"/>
-      <c r="V28" s="41"/>
-      <c r="W28" s="41"/>
-      <c r="X28" s="41"/>
-      <c r="Y28" s="41"/>
-      <c r="Z28" s="41"/>
-      <c r="AA28" s="42"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="46"/>
+      <c r="J28" s="46"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="46"/>
+      <c r="M28" s="46"/>
+      <c r="N28" s="46"/>
+      <c r="O28" s="46"/>
+      <c r="P28" s="46"/>
+      <c r="Q28" s="46"/>
+      <c r="R28" s="46"/>
+      <c r="S28" s="46"/>
+      <c r="T28" s="46"/>
+      <c r="U28" s="46"/>
+      <c r="V28" s="46"/>
+      <c r="W28" s="46"/>
+      <c r="X28" s="46"/>
+      <c r="Y28" s="46"/>
+      <c r="Z28" s="46"/>
+      <c r="AA28" s="47"/>
     </row>
     <row r="29" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
-      <c r="B29" s="40"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="41"/>
-      <c r="J29" s="41"/>
-      <c r="K29" s="41"/>
-      <c r="L29" s="41"/>
-      <c r="M29" s="41"/>
-      <c r="N29" s="41"/>
-      <c r="O29" s="41"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="41"/>
-      <c r="S29" s="41"/>
-      <c r="T29" s="41"/>
-      <c r="U29" s="41"/>
-      <c r="V29" s="41"/>
-      <c r="W29" s="41"/>
-      <c r="X29" s="41"/>
-      <c r="Y29" s="41"/>
-      <c r="Z29" s="41"/>
-      <c r="AA29" s="42"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="46"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="46"/>
+      <c r="J29" s="46"/>
+      <c r="K29" s="46"/>
+      <c r="L29" s="46"/>
+      <c r="M29" s="46"/>
+      <c r="N29" s="46"/>
+      <c r="O29" s="46"/>
+      <c r="P29" s="46"/>
+      <c r="Q29" s="46"/>
+      <c r="R29" s="46"/>
+      <c r="S29" s="46"/>
+      <c r="T29" s="46"/>
+      <c r="U29" s="46"/>
+      <c r="V29" s="46"/>
+      <c r="W29" s="46"/>
+      <c r="X29" s="46"/>
+      <c r="Y29" s="46"/>
+      <c r="Z29" s="46"/>
+      <c r="AA29" s="47"/>
     </row>
     <row r="30" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
-      <c r="B30" s="40"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="41"/>
-      <c r="J30" s="41"/>
-      <c r="K30" s="41"/>
-      <c r="L30" s="41"/>
-      <c r="M30" s="41"/>
-      <c r="N30" s="41"/>
-      <c r="O30" s="41"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="41"/>
-      <c r="S30" s="41"/>
-      <c r="T30" s="41"/>
-      <c r="U30" s="41"/>
-      <c r="V30" s="41"/>
-      <c r="W30" s="41"/>
-      <c r="X30" s="41"/>
-      <c r="Y30" s="41"/>
-      <c r="Z30" s="41"/>
-      <c r="AA30" s="42"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="46"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="46"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="46"/>
+      <c r="K30" s="46"/>
+      <c r="L30" s="46"/>
+      <c r="M30" s="46"/>
+      <c r="N30" s="46"/>
+      <c r="O30" s="46"/>
+      <c r="P30" s="46"/>
+      <c r="Q30" s="46"/>
+      <c r="R30" s="46"/>
+      <c r="S30" s="46"/>
+      <c r="T30" s="46"/>
+      <c r="U30" s="46"/>
+      <c r="V30" s="46"/>
+      <c r="W30" s="46"/>
+      <c r="X30" s="46"/>
+      <c r="Y30" s="46"/>
+      <c r="Z30" s="46"/>
+      <c r="AA30" s="47"/>
     </row>
     <row r="31" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
-      <c r="B31" s="40"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="41"/>
-      <c r="J31" s="41"/>
-      <c r="K31" s="41"/>
-      <c r="L31" s="41"/>
-      <c r="M31" s="41"/>
-      <c r="N31" s="41"/>
-      <c r="O31" s="41"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="41"/>
-      <c r="S31" s="41"/>
-      <c r="T31" s="41"/>
-      <c r="U31" s="41"/>
-      <c r="V31" s="41"/>
-      <c r="W31" s="41"/>
-      <c r="X31" s="41"/>
-      <c r="Y31" s="41"/>
-      <c r="Z31" s="41"/>
-      <c r="AA31" s="42"/>
+      <c r="B31" s="45"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="46"/>
+      <c r="I31" s="46"/>
+      <c r="J31" s="46"/>
+      <c r="K31" s="46"/>
+      <c r="L31" s="46"/>
+      <c r="M31" s="46"/>
+      <c r="N31" s="46"/>
+      <c r="O31" s="46"/>
+      <c r="P31" s="46"/>
+      <c r="Q31" s="46"/>
+      <c r="R31" s="46"/>
+      <c r="S31" s="46"/>
+      <c r="T31" s="46"/>
+      <c r="U31" s="46"/>
+      <c r="V31" s="46"/>
+      <c r="W31" s="46"/>
+      <c r="X31" s="46"/>
+      <c r="Y31" s="46"/>
+      <c r="Z31" s="46"/>
+      <c r="AA31" s="47"/>
     </row>
     <row r="32" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
-      <c r="B32" s="43" t="s">
+      <c r="B32" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="44"/>
-      <c r="D32" s="44"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="44"/>
-      <c r="G32" s="44"/>
-      <c r="H32" s="44"/>
-      <c r="I32" s="44"/>
-      <c r="J32" s="44"/>
-      <c r="K32" s="44"/>
-      <c r="L32" s="44"/>
-      <c r="M32" s="44"/>
-      <c r="N32" s="44"/>
-      <c r="O32" s="44"/>
-      <c r="P32" s="44"/>
-      <c r="Q32" s="44"/>
-      <c r="R32" s="44"/>
-      <c r="S32" s="44"/>
-      <c r="T32" s="44"/>
-      <c r="U32" s="44"/>
-      <c r="V32" s="44"/>
-      <c r="W32" s="44"/>
-      <c r="X32" s="44"/>
-      <c r="Y32" s="44"/>
-      <c r="Z32" s="44"/>
-      <c r="AA32" s="45"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="43"/>
+      <c r="L32" s="43"/>
+      <c r="M32" s="43"/>
+      <c r="N32" s="43"/>
+      <c r="O32" s="43"/>
+      <c r="P32" s="43"/>
+      <c r="Q32" s="43"/>
+      <c r="R32" s="43"/>
+      <c r="S32" s="43"/>
+      <c r="T32" s="43"/>
+      <c r="U32" s="43"/>
+      <c r="V32" s="43"/>
+      <c r="W32" s="43"/>
+      <c r="X32" s="43"/>
+      <c r="Y32" s="43"/>
+      <c r="Z32" s="43"/>
+      <c r="AA32" s="44"/>
     </row>
     <row r="33" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
-      <c r="B33" s="40"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="41"/>
-      <c r="J33" s="41"/>
-      <c r="K33" s="41"/>
-      <c r="L33" s="41"/>
-      <c r="M33" s="41"/>
-      <c r="N33" s="41"/>
-      <c r="O33" s="41"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="41"/>
-      <c r="S33" s="41"/>
-      <c r="T33" s="41"/>
-      <c r="U33" s="41"/>
-      <c r="V33" s="41"/>
-      <c r="W33" s="41"/>
-      <c r="X33" s="41"/>
-      <c r="Y33" s="41"/>
-      <c r="Z33" s="41"/>
-      <c r="AA33" s="42"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="46"/>
+      <c r="I33" s="46"/>
+      <c r="J33" s="46"/>
+      <c r="K33" s="46"/>
+      <c r="L33" s="46"/>
+      <c r="M33" s="46"/>
+      <c r="N33" s="46"/>
+      <c r="O33" s="46"/>
+      <c r="P33" s="46"/>
+      <c r="Q33" s="46"/>
+      <c r="R33" s="46"/>
+      <c r="S33" s="46"/>
+      <c r="T33" s="46"/>
+      <c r="U33" s="46"/>
+      <c r="V33" s="46"/>
+      <c r="W33" s="46"/>
+      <c r="X33" s="46"/>
+      <c r="Y33" s="46"/>
+      <c r="Z33" s="46"/>
+      <c r="AA33" s="47"/>
     </row>
     <row r="34" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
-      <c r="B34" s="40"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="41"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="41"/>
-      <c r="I34" s="41"/>
-      <c r="J34" s="41"/>
-      <c r="K34" s="41"/>
-      <c r="L34" s="41"/>
-      <c r="M34" s="41"/>
-      <c r="N34" s="41"/>
-      <c r="O34" s="41"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="41"/>
-      <c r="S34" s="41"/>
-      <c r="T34" s="41"/>
-      <c r="U34" s="41"/>
-      <c r="V34" s="41"/>
-      <c r="W34" s="41"/>
-      <c r="X34" s="41"/>
-      <c r="Y34" s="41"/>
-      <c r="Z34" s="41"/>
-      <c r="AA34" s="42"/>
+      <c r="B34" s="45"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="46"/>
+      <c r="I34" s="46"/>
+      <c r="J34" s="46"/>
+      <c r="K34" s="46"/>
+      <c r="L34" s="46"/>
+      <c r="M34" s="46"/>
+      <c r="N34" s="46"/>
+      <c r="O34" s="46"/>
+      <c r="P34" s="46"/>
+      <c r="Q34" s="46"/>
+      <c r="R34" s="46"/>
+      <c r="S34" s="46"/>
+      <c r="T34" s="46"/>
+      <c r="U34" s="46"/>
+      <c r="V34" s="46"/>
+      <c r="W34" s="46"/>
+      <c r="X34" s="46"/>
+      <c r="Y34" s="46"/>
+      <c r="Z34" s="46"/>
+      <c r="AA34" s="47"/>
     </row>
     <row r="35" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
-      <c r="B35" s="40"/>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="41"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="41"/>
-      <c r="I35" s="41"/>
-      <c r="J35" s="41"/>
-      <c r="K35" s="41"/>
-      <c r="L35" s="41"/>
-      <c r="M35" s="41"/>
-      <c r="N35" s="41"/>
-      <c r="O35" s="41"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="41"/>
-      <c r="S35" s="41"/>
-      <c r="T35" s="41"/>
-      <c r="U35" s="41"/>
-      <c r="V35" s="41"/>
-      <c r="W35" s="41"/>
-      <c r="X35" s="41"/>
-      <c r="Y35" s="41"/>
-      <c r="Z35" s="41"/>
-      <c r="AA35" s="42"/>
+      <c r="B35" s="45"/>
+      <c r="C35" s="46"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="46"/>
+      <c r="F35" s="46"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="46"/>
+      <c r="I35" s="46"/>
+      <c r="J35" s="46"/>
+      <c r="K35" s="46"/>
+      <c r="L35" s="46"/>
+      <c r="M35" s="46"/>
+      <c r="N35" s="46"/>
+      <c r="O35" s="46"/>
+      <c r="P35" s="46"/>
+      <c r="Q35" s="46"/>
+      <c r="R35" s="46"/>
+      <c r="S35" s="46"/>
+      <c r="T35" s="46"/>
+      <c r="U35" s="46"/>
+      <c r="V35" s="46"/>
+      <c r="W35" s="46"/>
+      <c r="X35" s="46"/>
+      <c r="Y35" s="46"/>
+      <c r="Z35" s="46"/>
+      <c r="AA35" s="47"/>
     </row>
     <row r="36" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
-      <c r="B36" s="40"/>
-      <c r="C36" s="41"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="41"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="41"/>
-      <c r="I36" s="41"/>
-      <c r="J36" s="41"/>
-      <c r="K36" s="41"/>
-      <c r="L36" s="41"/>
-      <c r="M36" s="41"/>
-      <c r="N36" s="41"/>
-      <c r="O36" s="41"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="41"/>
-      <c r="S36" s="41"/>
-      <c r="T36" s="41"/>
-      <c r="U36" s="41"/>
-      <c r="V36" s="41"/>
-      <c r="W36" s="41"/>
-      <c r="X36" s="41"/>
-      <c r="Y36" s="41"/>
-      <c r="Z36" s="41"/>
-      <c r="AA36" s="42"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="46"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="46"/>
+      <c r="I36" s="46"/>
+      <c r="J36" s="46"/>
+      <c r="K36" s="46"/>
+      <c r="L36" s="46"/>
+      <c r="M36" s="46"/>
+      <c r="N36" s="46"/>
+      <c r="O36" s="46"/>
+      <c r="P36" s="46"/>
+      <c r="Q36" s="46"/>
+      <c r="R36" s="46"/>
+      <c r="S36" s="46"/>
+      <c r="T36" s="46"/>
+      <c r="U36" s="46"/>
+      <c r="V36" s="46"/>
+      <c r="W36" s="46"/>
+      <c r="X36" s="46"/>
+      <c r="Y36" s="46"/>
+      <c r="Z36" s="46"/>
+      <c r="AA36" s="47"/>
     </row>
     <row r="37" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
-      <c r="B37" s="40"/>
-      <c r="C37" s="41"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="41"/>
-      <c r="G37" s="41"/>
-      <c r="H37" s="41"/>
-      <c r="I37" s="41"/>
-      <c r="J37" s="41"/>
-      <c r="K37" s="41"/>
-      <c r="L37" s="41"/>
-      <c r="M37" s="41"/>
-      <c r="N37" s="41"/>
-      <c r="O37" s="41"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="41"/>
-      <c r="S37" s="41"/>
-      <c r="T37" s="41"/>
-      <c r="U37" s="41"/>
-      <c r="V37" s="41"/>
-      <c r="W37" s="41"/>
-      <c r="X37" s="41"/>
-      <c r="Y37" s="41"/>
-      <c r="Z37" s="41"/>
-      <c r="AA37" s="42"/>
+      <c r="B37" s="45"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="46"/>
+      <c r="H37" s="46"/>
+      <c r="I37" s="46"/>
+      <c r="J37" s="46"/>
+      <c r="K37" s="46"/>
+      <c r="L37" s="46"/>
+      <c r="M37" s="46"/>
+      <c r="N37" s="46"/>
+      <c r="O37" s="46"/>
+      <c r="P37" s="46"/>
+      <c r="Q37" s="46"/>
+      <c r="R37" s="46"/>
+      <c r="S37" s="46"/>
+      <c r="T37" s="46"/>
+      <c r="U37" s="46"/>
+      <c r="V37" s="46"/>
+      <c r="W37" s="46"/>
+      <c r="X37" s="46"/>
+      <c r="Y37" s="46"/>
+      <c r="Z37" s="46"/>
+      <c r="AA37" s="47"/>
     </row>
     <row r="38" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
-      <c r="B38" s="40"/>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="41"/>
-      <c r="I38" s="41"/>
-      <c r="J38" s="41"/>
-      <c r="K38" s="41"/>
-      <c r="L38" s="41"/>
-      <c r="M38" s="41"/>
-      <c r="N38" s="41"/>
-      <c r="O38" s="41"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="41"/>
-      <c r="S38" s="41"/>
-      <c r="T38" s="41"/>
-      <c r="U38" s="41"/>
-      <c r="V38" s="41"/>
-      <c r="W38" s="41"/>
-      <c r="X38" s="41"/>
-      <c r="Y38" s="41"/>
-      <c r="Z38" s="41"/>
-      <c r="AA38" s="42"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="46"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="46"/>
+      <c r="F38" s="46"/>
+      <c r="G38" s="46"/>
+      <c r="H38" s="46"/>
+      <c r="I38" s="46"/>
+      <c r="J38" s="46"/>
+      <c r="K38" s="46"/>
+      <c r="L38" s="46"/>
+      <c r="M38" s="46"/>
+      <c r="N38" s="46"/>
+      <c r="O38" s="46"/>
+      <c r="P38" s="46"/>
+      <c r="Q38" s="46"/>
+      <c r="R38" s="46"/>
+      <c r="S38" s="46"/>
+      <c r="T38" s="46"/>
+      <c r="U38" s="46"/>
+      <c r="V38" s="46"/>
+      <c r="W38" s="46"/>
+      <c r="X38" s="46"/>
+      <c r="Y38" s="46"/>
+      <c r="Z38" s="46"/>
+      <c r="AA38" s="47"/>
     </row>
     <row r="39" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
-      <c r="B39" s="40"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="41"/>
-      <c r="I39" s="41"/>
-      <c r="J39" s="41"/>
-      <c r="K39" s="41"/>
-      <c r="L39" s="41"/>
-      <c r="M39" s="41"/>
-      <c r="N39" s="41"/>
-      <c r="O39" s="41"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="41"/>
-      <c r="S39" s="41"/>
-      <c r="T39" s="41"/>
-      <c r="U39" s="41"/>
-      <c r="V39" s="41"/>
-      <c r="W39" s="41"/>
-      <c r="X39" s="41"/>
-      <c r="Y39" s="41"/>
-      <c r="Z39" s="41"/>
-      <c r="AA39" s="42"/>
+      <c r="B39" s="45"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="46"/>
+      <c r="F39" s="46"/>
+      <c r="G39" s="46"/>
+      <c r="H39" s="46"/>
+      <c r="I39" s="46"/>
+      <c r="J39" s="46"/>
+      <c r="K39" s="46"/>
+      <c r="L39" s="46"/>
+      <c r="M39" s="46"/>
+      <c r="N39" s="46"/>
+      <c r="O39" s="46"/>
+      <c r="P39" s="46"/>
+      <c r="Q39" s="46"/>
+      <c r="R39" s="46"/>
+      <c r="S39" s="46"/>
+      <c r="T39" s="46"/>
+      <c r="U39" s="46"/>
+      <c r="V39" s="46"/>
+      <c r="W39" s="46"/>
+      <c r="X39" s="46"/>
+      <c r="Y39" s="46"/>
+      <c r="Z39" s="46"/>
+      <c r="AA39" s="47"/>
     </row>
     <row r="40" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
-      <c r="B40" s="43" t="s">
+      <c r="B40" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="44"/>
-      <c r="D40" s="44"/>
-      <c r="E40" s="44"/>
-      <c r="F40" s="44"/>
-      <c r="G40" s="44"/>
-      <c r="H40" s="44"/>
-      <c r="I40" s="44"/>
-      <c r="J40" s="44"/>
-      <c r="K40" s="44"/>
-      <c r="L40" s="44"/>
-      <c r="M40" s="44"/>
-      <c r="N40" s="44"/>
-      <c r="O40" s="44"/>
-      <c r="P40" s="44"/>
-      <c r="Q40" s="44"/>
-      <c r="R40" s="44"/>
-      <c r="S40" s="44"/>
-      <c r="T40" s="44"/>
-      <c r="U40" s="44"/>
-      <c r="V40" s="44"/>
-      <c r="W40" s="44"/>
-      <c r="X40" s="44"/>
-      <c r="Y40" s="44"/>
-      <c r="Z40" s="44"/>
-      <c r="AA40" s="45"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="43"/>
+      <c r="L40" s="43"/>
+      <c r="M40" s="43"/>
+      <c r="N40" s="43"/>
+      <c r="O40" s="43"/>
+      <c r="P40" s="43"/>
+      <c r="Q40" s="43"/>
+      <c r="R40" s="43"/>
+      <c r="S40" s="43"/>
+      <c r="T40" s="43"/>
+      <c r="U40" s="43"/>
+      <c r="V40" s="43"/>
+      <c r="W40" s="43"/>
+      <c r="X40" s="43"/>
+      <c r="Y40" s="43"/>
+      <c r="Z40" s="43"/>
+      <c r="AA40" s="44"/>
     </row>
     <row r="41" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
-      <c r="B41" s="40"/>
-      <c r="C41" s="41"/>
-      <c r="D41" s="41"/>
-      <c r="E41" s="41"/>
-      <c r="F41" s="41"/>
-      <c r="G41" s="41"/>
-      <c r="H41" s="41"/>
-      <c r="I41" s="41"/>
-      <c r="J41" s="41"/>
-      <c r="K41" s="41"/>
-      <c r="L41" s="41"/>
-      <c r="M41" s="41"/>
-      <c r="N41" s="41"/>
-      <c r="O41" s="41"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="41"/>
-      <c r="S41" s="41"/>
-      <c r="T41" s="41"/>
-      <c r="U41" s="41"/>
-      <c r="V41" s="41"/>
-      <c r="W41" s="41"/>
-      <c r="X41" s="41"/>
-      <c r="Y41" s="41"/>
-      <c r="Z41" s="41"/>
-      <c r="AA41" s="42"/>
+      <c r="B41" s="45"/>
+      <c r="C41" s="46"/>
+      <c r="D41" s="46"/>
+      <c r="E41" s="46"/>
+      <c r="F41" s="46"/>
+      <c r="G41" s="46"/>
+      <c r="H41" s="46"/>
+      <c r="I41" s="46"/>
+      <c r="J41" s="46"/>
+      <c r="K41" s="46"/>
+      <c r="L41" s="46"/>
+      <c r="M41" s="46"/>
+      <c r="N41" s="46"/>
+      <c r="O41" s="46"/>
+      <c r="P41" s="46"/>
+      <c r="Q41" s="46"/>
+      <c r="R41" s="46"/>
+      <c r="S41" s="46"/>
+      <c r="T41" s="46"/>
+      <c r="U41" s="46"/>
+      <c r="V41" s="46"/>
+      <c r="W41" s="46"/>
+      <c r="X41" s="46"/>
+      <c r="Y41" s="46"/>
+      <c r="Z41" s="46"/>
+      <c r="AA41" s="47"/>
     </row>
     <row r="42" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
-      <c r="B42" s="40"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="41"/>
-      <c r="F42" s="41"/>
-      <c r="G42" s="41"/>
-      <c r="H42" s="41"/>
-      <c r="I42" s="41"/>
-      <c r="J42" s="41"/>
-      <c r="K42" s="41"/>
-      <c r="L42" s="41"/>
-      <c r="M42" s="41"/>
-      <c r="N42" s="41"/>
-      <c r="O42" s="41"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="41"/>
-      <c r="S42" s="41"/>
-      <c r="T42" s="41"/>
-      <c r="U42" s="41"/>
-      <c r="V42" s="41"/>
-      <c r="W42" s="41"/>
-      <c r="X42" s="41"/>
-      <c r="Y42" s="41"/>
-      <c r="Z42" s="41"/>
-      <c r="AA42" s="42"/>
+      <c r="B42" s="45"/>
+      <c r="C42" s="46"/>
+      <c r="D42" s="46"/>
+      <c r="E42" s="46"/>
+      <c r="F42" s="46"/>
+      <c r="G42" s="46"/>
+      <c r="H42" s="46"/>
+      <c r="I42" s="46"/>
+      <c r="J42" s="46"/>
+      <c r="K42" s="46"/>
+      <c r="L42" s="46"/>
+      <c r="M42" s="46"/>
+      <c r="N42" s="46"/>
+      <c r="O42" s="46"/>
+      <c r="P42" s="46"/>
+      <c r="Q42" s="46"/>
+      <c r="R42" s="46"/>
+      <c r="S42" s="46"/>
+      <c r="T42" s="46"/>
+      <c r="U42" s="46"/>
+      <c r="V42" s="46"/>
+      <c r="W42" s="46"/>
+      <c r="X42" s="46"/>
+      <c r="Y42" s="46"/>
+      <c r="Z42" s="46"/>
+      <c r="AA42" s="47"/>
     </row>
     <row r="43" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
-      <c r="B43" s="40"/>
-      <c r="C43" s="41"/>
-      <c r="D43" s="41"/>
-      <c r="E43" s="41"/>
-      <c r="F43" s="41"/>
-      <c r="G43" s="41"/>
-      <c r="H43" s="41"/>
-      <c r="I43" s="41"/>
-      <c r="J43" s="41"/>
-      <c r="K43" s="41"/>
-      <c r="L43" s="41"/>
-      <c r="M43" s="41"/>
-      <c r="N43" s="41"/>
-      <c r="O43" s="41"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="41"/>
-      <c r="S43" s="41"/>
-      <c r="T43" s="41"/>
-      <c r="U43" s="41"/>
-      <c r="V43" s="41"/>
-      <c r="W43" s="41"/>
-      <c r="X43" s="41"/>
-      <c r="Y43" s="41"/>
-      <c r="Z43" s="41"/>
-      <c r="AA43" s="42"/>
+      <c r="B43" s="45"/>
+      <c r="C43" s="46"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="46"/>
+      <c r="F43" s="46"/>
+      <c r="G43" s="46"/>
+      <c r="H43" s="46"/>
+      <c r="I43" s="46"/>
+      <c r="J43" s="46"/>
+      <c r="K43" s="46"/>
+      <c r="L43" s="46"/>
+      <c r="M43" s="46"/>
+      <c r="N43" s="46"/>
+      <c r="O43" s="46"/>
+      <c r="P43" s="46"/>
+      <c r="Q43" s="46"/>
+      <c r="R43" s="46"/>
+      <c r="S43" s="46"/>
+      <c r="T43" s="46"/>
+      <c r="U43" s="46"/>
+      <c r="V43" s="46"/>
+      <c r="W43" s="46"/>
+      <c r="X43" s="46"/>
+      <c r="Y43" s="46"/>
+      <c r="Z43" s="46"/>
+      <c r="AA43" s="47"/>
     </row>
     <row r="44" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
-      <c r="B44" s="40"/>
-      <c r="C44" s="41"/>
-      <c r="D44" s="41"/>
-      <c r="E44" s="41"/>
-      <c r="F44" s="41"/>
-      <c r="G44" s="41"/>
-      <c r="H44" s="41"/>
-      <c r="I44" s="41"/>
-      <c r="J44" s="41"/>
-      <c r="K44" s="41"/>
-      <c r="L44" s="41"/>
-      <c r="M44" s="41"/>
-      <c r="N44" s="41"/>
-      <c r="O44" s="41"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="41"/>
-      <c r="S44" s="41"/>
-      <c r="T44" s="41"/>
-      <c r="U44" s="41"/>
-      <c r="V44" s="41"/>
-      <c r="W44" s="41"/>
-      <c r="X44" s="41"/>
-      <c r="Y44" s="41"/>
-      <c r="Z44" s="41"/>
-      <c r="AA44" s="42"/>
+      <c r="B44" s="45"/>
+      <c r="C44" s="46"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="46"/>
+      <c r="F44" s="46"/>
+      <c r="G44" s="46"/>
+      <c r="H44" s="46"/>
+      <c r="I44" s="46"/>
+      <c r="J44" s="46"/>
+      <c r="K44" s="46"/>
+      <c r="L44" s="46"/>
+      <c r="M44" s="46"/>
+      <c r="N44" s="46"/>
+      <c r="O44" s="46"/>
+      <c r="P44" s="46"/>
+      <c r="Q44" s="46"/>
+      <c r="R44" s="46"/>
+      <c r="S44" s="46"/>
+      <c r="T44" s="46"/>
+      <c r="U44" s="46"/>
+      <c r="V44" s="46"/>
+      <c r="W44" s="46"/>
+      <c r="X44" s="46"/>
+      <c r="Y44" s="46"/>
+      <c r="Z44" s="46"/>
+      <c r="AA44" s="47"/>
     </row>
     <row r="45" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
-      <c r="B45" s="40"/>
-      <c r="C45" s="41"/>
-      <c r="D45" s="41"/>
-      <c r="E45" s="41"/>
-      <c r="F45" s="41"/>
-      <c r="G45" s="41"/>
-      <c r="H45" s="41"/>
-      <c r="I45" s="41"/>
-      <c r="J45" s="41"/>
-      <c r="K45" s="41"/>
-      <c r="L45" s="41"/>
-      <c r="M45" s="41"/>
-      <c r="N45" s="41"/>
-      <c r="O45" s="41"/>
-      <c r="P45" s="41"/>
-      <c r="Q45" s="41"/>
-      <c r="R45" s="41"/>
-      <c r="S45" s="41"/>
-      <c r="T45" s="41"/>
-      <c r="U45" s="41"/>
-      <c r="V45" s="41"/>
-      <c r="W45" s="41"/>
-      <c r="X45" s="41"/>
-      <c r="Y45" s="41"/>
-      <c r="Z45" s="41"/>
-      <c r="AA45" s="42"/>
+      <c r="B45" s="45"/>
+      <c r="C45" s="46"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="46"/>
+      <c r="F45" s="46"/>
+      <c r="G45" s="46"/>
+      <c r="H45" s="46"/>
+      <c r="I45" s="46"/>
+      <c r="J45" s="46"/>
+      <c r="K45" s="46"/>
+      <c r="L45" s="46"/>
+      <c r="M45" s="46"/>
+      <c r="N45" s="46"/>
+      <c r="O45" s="46"/>
+      <c r="P45" s="46"/>
+      <c r="Q45" s="46"/>
+      <c r="R45" s="46"/>
+      <c r="S45" s="46"/>
+      <c r="T45" s="46"/>
+      <c r="U45" s="46"/>
+      <c r="V45" s="46"/>
+      <c r="W45" s="46"/>
+      <c r="X45" s="46"/>
+      <c r="Y45" s="46"/>
+      <c r="Z45" s="46"/>
+      <c r="AA45" s="47"/>
     </row>
     <row r="46" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
-      <c r="B46" s="40"/>
-      <c r="C46" s="41"/>
-      <c r="D46" s="41"/>
-      <c r="E46" s="41"/>
-      <c r="F46" s="41"/>
-      <c r="G46" s="41"/>
-      <c r="H46" s="41"/>
-      <c r="I46" s="41"/>
-      <c r="J46" s="41"/>
-      <c r="K46" s="41"/>
-      <c r="L46" s="41"/>
-      <c r="M46" s="41"/>
-      <c r="N46" s="41"/>
-      <c r="O46" s="41"/>
-      <c r="P46" s="41"/>
-      <c r="Q46" s="41"/>
-      <c r="R46" s="41"/>
-      <c r="S46" s="41"/>
-      <c r="T46" s="41"/>
-      <c r="U46" s="41"/>
-      <c r="V46" s="41"/>
-      <c r="W46" s="41"/>
-      <c r="X46" s="41"/>
-      <c r="Y46" s="41"/>
-      <c r="Z46" s="41"/>
-      <c r="AA46" s="42"/>
+      <c r="B46" s="45"/>
+      <c r="C46" s="46"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="46"/>
+      <c r="G46" s="46"/>
+      <c r="H46" s="46"/>
+      <c r="I46" s="46"/>
+      <c r="J46" s="46"/>
+      <c r="K46" s="46"/>
+      <c r="L46" s="46"/>
+      <c r="M46" s="46"/>
+      <c r="N46" s="46"/>
+      <c r="O46" s="46"/>
+      <c r="P46" s="46"/>
+      <c r="Q46" s="46"/>
+      <c r="R46" s="46"/>
+      <c r="S46" s="46"/>
+      <c r="T46" s="46"/>
+      <c r="U46" s="46"/>
+      <c r="V46" s="46"/>
+      <c r="W46" s="46"/>
+      <c r="X46" s="46"/>
+      <c r="Y46" s="46"/>
+      <c r="Z46" s="46"/>
+      <c r="AA46" s="47"/>
     </row>
     <row r="47" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
-      <c r="B47" s="40"/>
-      <c r="C47" s="41"/>
-      <c r="D47" s="41"/>
-      <c r="E47" s="41"/>
-      <c r="F47" s="41"/>
-      <c r="G47" s="41"/>
-      <c r="H47" s="41"/>
-      <c r="I47" s="41"/>
-      <c r="J47" s="41"/>
-      <c r="K47" s="41"/>
-      <c r="L47" s="41"/>
-      <c r="M47" s="41"/>
-      <c r="N47" s="41"/>
-      <c r="O47" s="41"/>
-      <c r="P47" s="41"/>
-      <c r="Q47" s="41"/>
-      <c r="R47" s="41"/>
-      <c r="S47" s="41"/>
-      <c r="T47" s="41"/>
-      <c r="U47" s="41"/>
-      <c r="V47" s="41"/>
-      <c r="W47" s="41"/>
-      <c r="X47" s="41"/>
-      <c r="Y47" s="41"/>
-      <c r="Z47" s="41"/>
-      <c r="AA47" s="42"/>
+      <c r="B47" s="45"/>
+      <c r="C47" s="46"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="46"/>
+      <c r="G47" s="46"/>
+      <c r="H47" s="46"/>
+      <c r="I47" s="46"/>
+      <c r="J47" s="46"/>
+      <c r="K47" s="46"/>
+      <c r="L47" s="46"/>
+      <c r="M47" s="46"/>
+      <c r="N47" s="46"/>
+      <c r="O47" s="46"/>
+      <c r="P47" s="46"/>
+      <c r="Q47" s="46"/>
+      <c r="R47" s="46"/>
+      <c r="S47" s="46"/>
+      <c r="T47" s="46"/>
+      <c r="U47" s="46"/>
+      <c r="V47" s="46"/>
+      <c r="W47" s="46"/>
+      <c r="X47" s="46"/>
+      <c r="Y47" s="46"/>
+      <c r="Z47" s="46"/>
+      <c r="AA47" s="47"/>
     </row>
     <row r="48" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
-      <c r="B48" s="69" t="s">
+      <c r="B48" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="70"/>
-      <c r="D48" s="70"/>
-      <c r="E48" s="70"/>
-      <c r="F48" s="70"/>
-      <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
-      <c r="I48" s="70"/>
-      <c r="J48" s="70"/>
-      <c r="K48" s="70"/>
-      <c r="L48" s="70"/>
-      <c r="M48" s="70"/>
-      <c r="N48" s="70"/>
-      <c r="O48" s="70"/>
-      <c r="P48" s="70"/>
-      <c r="Q48" s="70"/>
-      <c r="R48" s="70"/>
-      <c r="S48" s="70"/>
-      <c r="T48" s="70"/>
-      <c r="U48" s="70"/>
-      <c r="V48" s="70"/>
-      <c r="W48" s="70"/>
-      <c r="X48" s="70"/>
-      <c r="Y48" s="70"/>
-      <c r="Z48" s="70"/>
-      <c r="AA48" s="71"/>
+      <c r="C48" s="49"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="49"/>
+      <c r="G48" s="49"/>
+      <c r="H48" s="49"/>
+      <c r="I48" s="49"/>
+      <c r="J48" s="49"/>
+      <c r="K48" s="49"/>
+      <c r="L48" s="49"/>
+      <c r="M48" s="49"/>
+      <c r="N48" s="49"/>
+      <c r="O48" s="49"/>
+      <c r="P48" s="49"/>
+      <c r="Q48" s="49"/>
+      <c r="R48" s="49"/>
+      <c r="S48" s="49"/>
+      <c r="T48" s="49"/>
+      <c r="U48" s="49"/>
+      <c r="V48" s="49"/>
+      <c r="W48" s="49"/>
+      <c r="X48" s="49"/>
+      <c r="Y48" s="49"/>
+      <c r="Z48" s="49"/>
+      <c r="AA48" s="50"/>
     </row>
     <row r="49" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="30"/>
-      <c r="B49" s="40"/>
-      <c r="C49" s="41"/>
-      <c r="D49" s="41"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="41"/>
-      <c r="I49" s="41"/>
-      <c r="J49" s="41"/>
-      <c r="K49" s="41"/>
-      <c r="L49" s="41"/>
-      <c r="M49" s="41"/>
-      <c r="N49" s="41"/>
-      <c r="O49" s="41"/>
-      <c r="P49" s="41"/>
-      <c r="Q49" s="41"/>
-      <c r="R49" s="41"/>
-      <c r="S49" s="41"/>
-      <c r="T49" s="41"/>
-      <c r="U49" s="41"/>
-      <c r="V49" s="41"/>
-      <c r="W49" s="41"/>
-      <c r="X49" s="41"/>
-      <c r="Y49" s="41"/>
-      <c r="Z49" s="41"/>
-      <c r="AA49" s="42"/>
+      <c r="B49" s="45"/>
+      <c r="C49" s="46"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="46"/>
+      <c r="G49" s="46"/>
+      <c r="H49" s="46"/>
+      <c r="I49" s="46"/>
+      <c r="J49" s="46"/>
+      <c r="K49" s="46"/>
+      <c r="L49" s="46"/>
+      <c r="M49" s="46"/>
+      <c r="N49" s="46"/>
+      <c r="O49" s="46"/>
+      <c r="P49" s="46"/>
+      <c r="Q49" s="46"/>
+      <c r="R49" s="46"/>
+      <c r="S49" s="46"/>
+      <c r="T49" s="46"/>
+      <c r="U49" s="46"/>
+      <c r="V49" s="46"/>
+      <c r="W49" s="46"/>
+      <c r="X49" s="46"/>
+      <c r="Y49" s="46"/>
+      <c r="Z49" s="46"/>
+      <c r="AA49" s="47"/>
     </row>
     <row r="50" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="30"/>
-      <c r="B50" s="40"/>
-      <c r="C50" s="41"/>
-      <c r="D50" s="41"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="41"/>
-      <c r="G50" s="41"/>
-      <c r="H50" s="41"/>
-      <c r="I50" s="41"/>
-      <c r="J50" s="41"/>
-      <c r="K50" s="41"/>
-      <c r="L50" s="41"/>
-      <c r="M50" s="41"/>
-      <c r="N50" s="41"/>
-      <c r="O50" s="41"/>
-      <c r="P50" s="41"/>
-      <c r="Q50" s="41"/>
-      <c r="R50" s="41"/>
-      <c r="S50" s="41"/>
-      <c r="T50" s="41"/>
-      <c r="U50" s="41"/>
-      <c r="V50" s="41"/>
-      <c r="W50" s="41"/>
-      <c r="X50" s="41"/>
-      <c r="Y50" s="41"/>
-      <c r="Z50" s="41"/>
-      <c r="AA50" s="42"/>
+      <c r="B50" s="45"/>
+      <c r="C50" s="46"/>
+      <c r="D50" s="46"/>
+      <c r="E50" s="46"/>
+      <c r="F50" s="46"/>
+      <c r="G50" s="46"/>
+      <c r="H50" s="46"/>
+      <c r="I50" s="46"/>
+      <c r="J50" s="46"/>
+      <c r="K50" s="46"/>
+      <c r="L50" s="46"/>
+      <c r="M50" s="46"/>
+      <c r="N50" s="46"/>
+      <c r="O50" s="46"/>
+      <c r="P50" s="46"/>
+      <c r="Q50" s="46"/>
+      <c r="R50" s="46"/>
+      <c r="S50" s="46"/>
+      <c r="T50" s="46"/>
+      <c r="U50" s="46"/>
+      <c r="V50" s="46"/>
+      <c r="W50" s="46"/>
+      <c r="X50" s="46"/>
+      <c r="Y50" s="46"/>
+      <c r="Z50" s="46"/>
+      <c r="AA50" s="47"/>
     </row>
     <row r="51" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="30"/>
-      <c r="B51" s="40"/>
-      <c r="C51" s="41"/>
-      <c r="D51" s="41"/>
-      <c r="E51" s="41"/>
-      <c r="F51" s="41"/>
-      <c r="G51" s="41"/>
-      <c r="H51" s="41"/>
-      <c r="I51" s="41"/>
-      <c r="J51" s="41"/>
-      <c r="K51" s="41"/>
-      <c r="L51" s="41"/>
-      <c r="M51" s="41"/>
-      <c r="N51" s="41"/>
-      <c r="O51" s="41"/>
-      <c r="P51" s="41"/>
-      <c r="Q51" s="41"/>
-      <c r="R51" s="41"/>
-      <c r="S51" s="41"/>
-      <c r="T51" s="41"/>
-      <c r="U51" s="41"/>
-      <c r="V51" s="41"/>
-      <c r="W51" s="41"/>
-      <c r="X51" s="41"/>
-      <c r="Y51" s="41"/>
-      <c r="Z51" s="41"/>
-      <c r="AA51" s="42"/>
+      <c r="B51" s="45"/>
+      <c r="C51" s="46"/>
+      <c r="D51" s="46"/>
+      <c r="E51" s="46"/>
+      <c r="F51" s="46"/>
+      <c r="G51" s="46"/>
+      <c r="H51" s="46"/>
+      <c r="I51" s="46"/>
+      <c r="J51" s="46"/>
+      <c r="K51" s="46"/>
+      <c r="L51" s="46"/>
+      <c r="M51" s="46"/>
+      <c r="N51" s="46"/>
+      <c r="O51" s="46"/>
+      <c r="P51" s="46"/>
+      <c r="Q51" s="46"/>
+      <c r="R51" s="46"/>
+      <c r="S51" s="46"/>
+      <c r="T51" s="46"/>
+      <c r="U51" s="46"/>
+      <c r="V51" s="46"/>
+      <c r="W51" s="46"/>
+      <c r="X51" s="46"/>
+      <c r="Y51" s="46"/>
+      <c r="Z51" s="46"/>
+      <c r="AA51" s="47"/>
     </row>
     <row r="52" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="30"/>
-      <c r="B52" s="40"/>
-      <c r="C52" s="41"/>
-      <c r="D52" s="41"/>
-      <c r="E52" s="41"/>
-      <c r="F52" s="41"/>
-      <c r="G52" s="41"/>
-      <c r="H52" s="41"/>
-      <c r="I52" s="41"/>
-      <c r="J52" s="41"/>
-      <c r="K52" s="41"/>
-      <c r="L52" s="41"/>
-      <c r="M52" s="41"/>
-      <c r="N52" s="41"/>
-      <c r="O52" s="41"/>
-      <c r="P52" s="41"/>
-      <c r="Q52" s="41"/>
-      <c r="R52" s="41"/>
-      <c r="S52" s="41"/>
-      <c r="T52" s="41"/>
-      <c r="U52" s="41"/>
-      <c r="V52" s="41"/>
-      <c r="W52" s="41"/>
-      <c r="X52" s="41"/>
-      <c r="Y52" s="41"/>
-      <c r="Z52" s="41"/>
-      <c r="AA52" s="42"/>
+      <c r="B52" s="45"/>
+      <c r="C52" s="46"/>
+      <c r="D52" s="46"/>
+      <c r="E52" s="46"/>
+      <c r="F52" s="46"/>
+      <c r="G52" s="46"/>
+      <c r="H52" s="46"/>
+      <c r="I52" s="46"/>
+      <c r="J52" s="46"/>
+      <c r="K52" s="46"/>
+      <c r="L52" s="46"/>
+      <c r="M52" s="46"/>
+      <c r="N52" s="46"/>
+      <c r="O52" s="46"/>
+      <c r="P52" s="46"/>
+      <c r="Q52" s="46"/>
+      <c r="R52" s="46"/>
+      <c r="S52" s="46"/>
+      <c r="T52" s="46"/>
+      <c r="U52" s="46"/>
+      <c r="V52" s="46"/>
+      <c r="W52" s="46"/>
+      <c r="X52" s="46"/>
+      <c r="Y52" s="46"/>
+      <c r="Z52" s="46"/>
+      <c r="AA52" s="47"/>
     </row>
     <row r="53" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="30"/>
-      <c r="B53" s="40"/>
-      <c r="C53" s="41"/>
-      <c r="D53" s="41"/>
-      <c r="E53" s="41"/>
-      <c r="F53" s="41"/>
-      <c r="G53" s="41"/>
-      <c r="H53" s="41"/>
-      <c r="I53" s="41"/>
-      <c r="J53" s="41"/>
-      <c r="K53" s="41"/>
-      <c r="L53" s="41"/>
-      <c r="M53" s="41"/>
-      <c r="N53" s="41"/>
-      <c r="O53" s="41"/>
-      <c r="P53" s="41"/>
-      <c r="Q53" s="41"/>
-      <c r="R53" s="41"/>
-      <c r="S53" s="41"/>
-      <c r="T53" s="41"/>
-      <c r="U53" s="41"/>
-      <c r="V53" s="41"/>
-      <c r="W53" s="41"/>
-      <c r="X53" s="41"/>
-      <c r="Y53" s="41"/>
-      <c r="Z53" s="41"/>
-      <c r="AA53" s="42"/>
+      <c r="B53" s="45"/>
+      <c r="C53" s="46"/>
+      <c r="D53" s="46"/>
+      <c r="E53" s="46"/>
+      <c r="F53" s="46"/>
+      <c r="G53" s="46"/>
+      <c r="H53" s="46"/>
+      <c r="I53" s="46"/>
+      <c r="J53" s="46"/>
+      <c r="K53" s="46"/>
+      <c r="L53" s="46"/>
+      <c r="M53" s="46"/>
+      <c r="N53" s="46"/>
+      <c r="O53" s="46"/>
+      <c r="P53" s="46"/>
+      <c r="Q53" s="46"/>
+      <c r="R53" s="46"/>
+      <c r="S53" s="46"/>
+      <c r="T53" s="46"/>
+      <c r="U53" s="46"/>
+      <c r="V53" s="46"/>
+      <c r="W53" s="46"/>
+      <c r="X53" s="46"/>
+      <c r="Y53" s="46"/>
+      <c r="Z53" s="46"/>
+      <c r="AA53" s="47"/>
     </row>
     <row r="54" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="30"/>
-      <c r="B54" s="40"/>
-      <c r="C54" s="41"/>
-      <c r="D54" s="41"/>
-      <c r="E54" s="41"/>
-      <c r="F54" s="41"/>
-      <c r="G54" s="41"/>
-      <c r="H54" s="41"/>
-      <c r="I54" s="41"/>
-      <c r="J54" s="41"/>
-      <c r="K54" s="41"/>
-      <c r="L54" s="41"/>
-      <c r="M54" s="41"/>
-      <c r="N54" s="41"/>
-      <c r="O54" s="41"/>
-      <c r="P54" s="41"/>
-      <c r="Q54" s="41"/>
-      <c r="R54" s="41"/>
-      <c r="S54" s="41"/>
-      <c r="T54" s="41"/>
-      <c r="U54" s="41"/>
-      <c r="V54" s="41"/>
-      <c r="W54" s="41"/>
-      <c r="X54" s="41"/>
-      <c r="Y54" s="41"/>
-      <c r="Z54" s="41"/>
-      <c r="AA54" s="42"/>
+      <c r="B54" s="45"/>
+      <c r="C54" s="46"/>
+      <c r="D54" s="46"/>
+      <c r="E54" s="46"/>
+      <c r="F54" s="46"/>
+      <c r="G54" s="46"/>
+      <c r="H54" s="46"/>
+      <c r="I54" s="46"/>
+      <c r="J54" s="46"/>
+      <c r="K54" s="46"/>
+      <c r="L54" s="46"/>
+      <c r="M54" s="46"/>
+      <c r="N54" s="46"/>
+      <c r="O54" s="46"/>
+      <c r="P54" s="46"/>
+      <c r="Q54" s="46"/>
+      <c r="R54" s="46"/>
+      <c r="S54" s="46"/>
+      <c r="T54" s="46"/>
+      <c r="U54" s="46"/>
+      <c r="V54" s="46"/>
+      <c r="W54" s="46"/>
+      <c r="X54" s="46"/>
+      <c r="Y54" s="46"/>
+      <c r="Z54" s="46"/>
+      <c r="AA54" s="47"/>
     </row>
     <row r="55" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="30"/>
-      <c r="B55" s="40"/>
-      <c r="C55" s="41"/>
-      <c r="D55" s="41"/>
-      <c r="E55" s="41"/>
-      <c r="F55" s="41"/>
-      <c r="G55" s="41"/>
-      <c r="H55" s="41"/>
-      <c r="I55" s="41"/>
-      <c r="J55" s="41"/>
-      <c r="K55" s="41"/>
-      <c r="L55" s="41"/>
-      <c r="M55" s="41"/>
-      <c r="N55" s="41"/>
-      <c r="O55" s="41"/>
-      <c r="P55" s="41"/>
-      <c r="Q55" s="41"/>
-      <c r="R55" s="41"/>
-      <c r="S55" s="41"/>
-      <c r="T55" s="41"/>
-      <c r="U55" s="41"/>
-      <c r="V55" s="41"/>
-      <c r="W55" s="41"/>
-      <c r="X55" s="41"/>
-      <c r="Y55" s="41"/>
-      <c r="Z55" s="41"/>
-      <c r="AA55" s="42"/>
+      <c r="B55" s="45"/>
+      <c r="C55" s="46"/>
+      <c r="D55" s="46"/>
+      <c r="E55" s="46"/>
+      <c r="F55" s="46"/>
+      <c r="G55" s="46"/>
+      <c r="H55" s="46"/>
+      <c r="I55" s="46"/>
+      <c r="J55" s="46"/>
+      <c r="K55" s="46"/>
+      <c r="L55" s="46"/>
+      <c r="M55" s="46"/>
+      <c r="N55" s="46"/>
+      <c r="O55" s="46"/>
+      <c r="P55" s="46"/>
+      <c r="Q55" s="46"/>
+      <c r="R55" s="46"/>
+      <c r="S55" s="46"/>
+      <c r="T55" s="46"/>
+      <c r="U55" s="46"/>
+      <c r="V55" s="46"/>
+      <c r="W55" s="46"/>
+      <c r="X55" s="46"/>
+      <c r="Y55" s="46"/>
+      <c r="Z55" s="46"/>
+      <c r="AA55" s="47"/>
     </row>
     <row r="56" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
@@ -3000,15 +2999,15 @@
     </row>
     <row r="58" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1"/>
-      <c r="B58" s="72"/>
-      <c r="C58" s="72"/>
-      <c r="D58" s="72"/>
-      <c r="E58" s="72"/>
-      <c r="F58" s="72"/>
-      <c r="G58" s="72"/>
-      <c r="H58" s="72"/>
-      <c r="I58" s="72"/>
-      <c r="J58" s="72"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
       <c r="K58" s="36"/>
       <c r="L58" s="36"/>
       <c r="M58" s="36"/>
@@ -3029,25 +3028,25 @@
     </row>
     <row r="59" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
-      <c r="B59" s="72"/>
-      <c r="C59" s="72"/>
-      <c r="D59" s="72"/>
-      <c r="E59" s="72"/>
-      <c r="F59" s="72"/>
-      <c r="G59" s="72"/>
-      <c r="H59" s="72"/>
-      <c r="I59" s="72"/>
-      <c r="J59" s="72"/>
-      <c r="K59" s="67"/>
-      <c r="L59" s="68"/>
-      <c r="M59" s="68"/>
-      <c r="N59" s="68"/>
-      <c r="O59" s="68"/>
-      <c r="P59" s="68"/>
-      <c r="Q59" s="68"/>
-      <c r="R59" s="35"/>
-      <c r="S59" s="35"/>
-      <c r="T59" s="35"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="51"/>
+      <c r="F59" s="51"/>
+      <c r="G59" s="51"/>
+      <c r="H59" s="51"/>
+      <c r="I59" s="51"/>
+      <c r="J59" s="51"/>
+      <c r="K59" s="51"/>
+      <c r="L59" s="51"/>
+      <c r="M59" s="51"/>
+      <c r="N59" s="51"/>
+      <c r="O59" s="51"/>
+      <c r="P59" s="51"/>
+      <c r="Q59" s="71"/>
+      <c r="R59" s="71"/>
+      <c r="S59" s="71"/>
+      <c r="T59" s="71"/>
       <c r="U59" s="35"/>
       <c r="V59" s="35"/>
       <c r="W59" s="35"/>
@@ -3205,61 +3204,61 @@
     <row r="65" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
       <c r="B65" s="34"/>
-      <c r="C65" s="66" t="s">
+      <c r="C65" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="D65" s="56"/>
-      <c r="E65" s="56"/>
-      <c r="F65" s="56"/>
-      <c r="G65" s="56"/>
-      <c r="H65" s="56"/>
-      <c r="I65" s="56"/>
-      <c r="J65" s="56"/>
-      <c r="K65" s="56"/>
-      <c r="L65" s="56"/>
-      <c r="M65" s="56"/>
-      <c r="N65" s="56"/>
-      <c r="O65" s="56"/>
-      <c r="P65" s="56"/>
-      <c r="Q65" s="56"/>
-      <c r="R65" s="56"/>
-      <c r="S65" s="56"/>
-      <c r="T65" s="56"/>
-      <c r="U65" s="56"/>
-      <c r="V65" s="56"/>
-      <c r="W65" s="56"/>
-      <c r="X65" s="56"/>
-      <c r="Y65" s="56"/>
-      <c r="Z65" s="56"/>
+      <c r="D65" s="41"/>
+      <c r="E65" s="41"/>
+      <c r="F65" s="41"/>
+      <c r="G65" s="41"/>
+      <c r="H65" s="41"/>
+      <c r="I65" s="41"/>
+      <c r="J65" s="41"/>
+      <c r="K65" s="41"/>
+      <c r="L65" s="41"/>
+      <c r="M65" s="41"/>
+      <c r="N65" s="41"/>
+      <c r="O65" s="41"/>
+      <c r="P65" s="41"/>
+      <c r="Q65" s="41"/>
+      <c r="R65" s="41"/>
+      <c r="S65" s="41"/>
+      <c r="T65" s="41"/>
+      <c r="U65" s="41"/>
+      <c r="V65" s="41"/>
+      <c r="W65" s="41"/>
+      <c r="X65" s="41"/>
+      <c r="Y65" s="41"/>
+      <c r="Z65" s="41"/>
       <c r="AA65" s="34"/>
     </row>
     <row r="66" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
       <c r="B66" s="34"/>
-      <c r="C66" s="56"/>
-      <c r="D66" s="56"/>
-      <c r="E66" s="56"/>
-      <c r="F66" s="56"/>
-      <c r="G66" s="56"/>
-      <c r="H66" s="56"/>
-      <c r="I66" s="56"/>
-      <c r="J66" s="56"/>
-      <c r="K66" s="56"/>
-      <c r="L66" s="56"/>
-      <c r="M66" s="56"/>
-      <c r="N66" s="56"/>
-      <c r="O66" s="56"/>
-      <c r="P66" s="56"/>
-      <c r="Q66" s="56"/>
-      <c r="R66" s="56"/>
-      <c r="S66" s="56"/>
-      <c r="T66" s="56"/>
-      <c r="U66" s="56"/>
-      <c r="V66" s="56"/>
-      <c r="W66" s="56"/>
-      <c r="X66" s="56"/>
-      <c r="Y66" s="56"/>
-      <c r="Z66" s="56"/>
+      <c r="C66" s="41"/>
+      <c r="D66" s="41"/>
+      <c r="E66" s="41"/>
+      <c r="F66" s="41"/>
+      <c r="G66" s="41"/>
+      <c r="H66" s="41"/>
+      <c r="I66" s="41"/>
+      <c r="J66" s="41"/>
+      <c r="K66" s="41"/>
+      <c r="L66" s="41"/>
+      <c r="M66" s="41"/>
+      <c r="N66" s="41"/>
+      <c r="O66" s="41"/>
+      <c r="P66" s="41"/>
+      <c r="Q66" s="41"/>
+      <c r="R66" s="41"/>
+      <c r="S66" s="41"/>
+      <c r="T66" s="41"/>
+      <c r="U66" s="41"/>
+      <c r="V66" s="41"/>
+      <c r="W66" s="41"/>
+      <c r="X66" s="41"/>
+      <c r="Y66" s="41"/>
+      <c r="Z66" s="41"/>
       <c r="AA66" s="34"/>
     </row>
     <row r="67" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30350,30 +30349,15 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="C65:Z66"/>
-    <mergeCell ref="B40:AA40"/>
-    <mergeCell ref="B49:AA49"/>
-    <mergeCell ref="K59:Q59"/>
-    <mergeCell ref="B55:AA55"/>
-    <mergeCell ref="B42:AA42"/>
-    <mergeCell ref="B54:AA54"/>
-    <mergeCell ref="B48:AA48"/>
-    <mergeCell ref="B58:J59"/>
-    <mergeCell ref="H10:Z10"/>
-    <mergeCell ref="B51:AA51"/>
-    <mergeCell ref="B44:AA44"/>
-    <mergeCell ref="B53:AA53"/>
-    <mergeCell ref="B38:AA38"/>
-    <mergeCell ref="B29:AA29"/>
-    <mergeCell ref="H21:Z21"/>
-    <mergeCell ref="B34:AA34"/>
-    <mergeCell ref="B37:AA37"/>
-    <mergeCell ref="B28:AA28"/>
-    <mergeCell ref="B24:AA24"/>
-    <mergeCell ref="B30:AA30"/>
-    <mergeCell ref="H17:Z17"/>
-    <mergeCell ref="B47:AA47"/>
-    <mergeCell ref="B52:AA52"/>
+    <mergeCell ref="B32:AA32"/>
+    <mergeCell ref="B50:AA50"/>
+    <mergeCell ref="B14:AA15"/>
+    <mergeCell ref="B26:AA26"/>
+    <mergeCell ref="B41:AA41"/>
+    <mergeCell ref="H19:Z19"/>
+    <mergeCell ref="B33:AA33"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B23:AA23"/>
     <mergeCell ref="B3:AA3"/>
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="B31:AA31"/>
@@ -30390,16 +30374,31 @@
     <mergeCell ref="H12:T12"/>
     <mergeCell ref="B25:AA25"/>
     <mergeCell ref="B45:AA45"/>
+    <mergeCell ref="H10:Z10"/>
+    <mergeCell ref="B51:AA51"/>
+    <mergeCell ref="B44:AA44"/>
+    <mergeCell ref="B53:AA53"/>
+    <mergeCell ref="B38:AA38"/>
+    <mergeCell ref="B29:AA29"/>
+    <mergeCell ref="H21:Z21"/>
+    <mergeCell ref="B34:AA34"/>
+    <mergeCell ref="B37:AA37"/>
+    <mergeCell ref="B28:AA28"/>
+    <mergeCell ref="B24:AA24"/>
+    <mergeCell ref="B30:AA30"/>
+    <mergeCell ref="H17:Z17"/>
+    <mergeCell ref="B47:AA47"/>
+    <mergeCell ref="B52:AA52"/>
     <mergeCell ref="B36:AA36"/>
-    <mergeCell ref="B32:AA32"/>
-    <mergeCell ref="B50:AA50"/>
-    <mergeCell ref="B14:AA15"/>
-    <mergeCell ref="B26:AA26"/>
-    <mergeCell ref="B41:AA41"/>
-    <mergeCell ref="H19:Z19"/>
-    <mergeCell ref="B33:AA33"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B23:AA23"/>
+    <mergeCell ref="C65:Z66"/>
+    <mergeCell ref="B40:AA40"/>
+    <mergeCell ref="B49:AA49"/>
+    <mergeCell ref="B55:AA55"/>
+    <mergeCell ref="B42:AA42"/>
+    <mergeCell ref="B54:AA54"/>
+    <mergeCell ref="B48:AA48"/>
+    <mergeCell ref="E59:P59"/>
+    <mergeCell ref="Q59:T59"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.98425196850393704" header="0" footer="0"/>
